--- a/artfynd/A 18989-2024 artfynd.xlsx
+++ b/artfynd/A 18989-2024 artfynd.xlsx
@@ -3354,10 +3354,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121471896</v>
+        <v>121471535</v>
       </c>
       <c r="B23" t="n">
-        <v>80575</v>
+        <v>76945</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3370,21 +3370,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1182</v>
+        <v>1342</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>428370</v>
+        <v>428160</v>
       </c>
       <c r="R23" t="n">
-        <v>6233102</v>
+        <v>6233209</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3424,12 +3424,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3456,10 +3456,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121471937</v>
+        <v>121471931</v>
       </c>
       <c r="B24" t="n">
-        <v>96721</v>
+        <v>80252</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3468,25 +3468,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>428062</v>
+        <v>428075</v>
       </c>
       <c r="R24" t="n">
         <v>6233301</v>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121471902</v>
+        <v>121471926</v>
       </c>
       <c r="B25" t="n">
-        <v>94584</v>
+        <v>94389</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3574,21 +3574,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>428387</v>
+        <v>428073</v>
       </c>
       <c r="R25" t="n">
-        <v>6233096</v>
+        <v>6233383</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3660,10 +3660,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121471912</v>
+        <v>121471803</v>
       </c>
       <c r="B26" t="n">
-        <v>78404</v>
+        <v>80252</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3672,25 +3672,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>924</v>
+        <v>1144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>428351</v>
+        <v>428334</v>
       </c>
       <c r="R26" t="n">
-        <v>6233082</v>
+        <v>6233284</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3730,12 +3730,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3762,10 +3762,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121471844</v>
+        <v>121471854</v>
       </c>
       <c r="B27" t="n">
-        <v>76945</v>
+        <v>96721</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3774,25 +3774,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>428248</v>
+        <v>428302</v>
       </c>
       <c r="R27" t="n">
-        <v>6233241</v>
+        <v>6233177</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3864,10 +3864,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121471691</v>
+        <v>121471913</v>
       </c>
       <c r="B28" t="n">
-        <v>96721</v>
+        <v>76945</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3876,25 +3876,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>428128</v>
+        <v>428342</v>
       </c>
       <c r="R28" t="n">
-        <v>6233385</v>
+        <v>6233082</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3934,12 +3934,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3966,10 +3966,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121471825</v>
+        <v>121471865</v>
       </c>
       <c r="B29" t="n">
-        <v>80239</v>
+        <v>74696</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3982,21 +3982,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>230185</v>
+        <v>306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>428233</v>
+        <v>428438</v>
       </c>
       <c r="R29" t="n">
-        <v>6233332</v>
+        <v>6233202</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4068,10 +4068,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121471846</v>
+        <v>121471905</v>
       </c>
       <c r="B30" t="n">
-        <v>80239</v>
+        <v>74606</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4080,25 +4080,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>230185</v>
+        <v>1118</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>428241</v>
+        <v>428377</v>
       </c>
       <c r="R30" t="n">
-        <v>6233222</v>
+        <v>6233095</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4138,12 +4138,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4170,10 +4170,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121471833</v>
+        <v>121471897</v>
       </c>
       <c r="B31" t="n">
-        <v>80239</v>
+        <v>78404</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4182,25 +4182,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>230185</v>
+        <v>924</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>428139</v>
+        <v>428369</v>
       </c>
       <c r="R31" t="n">
-        <v>6233315</v>
+        <v>6233104</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4240,12 +4240,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4272,10 +4272,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121471864</v>
+        <v>121471930</v>
       </c>
       <c r="B32" t="n">
-        <v>94584</v>
+        <v>74606</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4284,25 +4284,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2671</v>
+        <v>1118</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>428410</v>
+        <v>428078</v>
       </c>
       <c r="R32" t="n">
-        <v>6233214</v>
+        <v>6233294</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4342,12 +4342,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4374,10 +4374,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121471826</v>
+        <v>121471910</v>
       </c>
       <c r="B33" t="n">
-        <v>78860</v>
+        <v>76945</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4386,25 +4386,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6459</v>
+        <v>1342</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4414,10 +4414,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>428228</v>
+        <v>428377</v>
       </c>
       <c r="R33" t="n">
-        <v>6233340</v>
+        <v>6233090</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4444,12 +4444,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4476,7 +4476,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121471870</v>
+        <v>121471907</v>
       </c>
       <c r="B34" t="n">
         <v>76945</v>
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>428356</v>
+        <v>428375</v>
       </c>
       <c r="R34" t="n">
-        <v>6233243</v>
+        <v>6233092</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4546,12 +4546,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4578,10 +4578,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121471836</v>
+        <v>121471697</v>
       </c>
       <c r="B35" t="n">
-        <v>94584</v>
+        <v>74696</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4594,21 +4594,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2671</v>
+        <v>306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>428145</v>
+        <v>428043</v>
       </c>
       <c r="R35" t="n">
-        <v>6233244</v>
+        <v>6233298</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4648,12 +4648,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4680,10 +4680,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121471939</v>
+        <v>121471686</v>
       </c>
       <c r="B36" t="n">
-        <v>94595</v>
+        <v>80252</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4692,25 +4692,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4720,10 +4720,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>428046</v>
+        <v>428187</v>
       </c>
       <c r="R36" t="n">
-        <v>6233296</v>
+        <v>6233403</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4750,12 +4750,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4782,10 +4782,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121471858</v>
+        <v>121471539</v>
       </c>
       <c r="B37" t="n">
-        <v>80252</v>
+        <v>94584</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4794,25 +4794,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1144</v>
+        <v>2671</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>428372</v>
+        <v>428262</v>
       </c>
       <c r="R37" t="n">
-        <v>6233270</v>
+        <v>6233134</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4884,10 +4884,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121471944</v>
+        <v>121471896</v>
       </c>
       <c r="B38" t="n">
-        <v>94595</v>
+        <v>80575</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4896,25 +4896,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2667</v>
+        <v>1182</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>428034</v>
+        <v>428370</v>
       </c>
       <c r="R38" t="n">
-        <v>6233348</v>
+        <v>6233102</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4986,7 +4986,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121471940</v>
+        <v>121471916</v>
       </c>
       <c r="B39" t="n">
         <v>94605</v>
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>428037</v>
+        <v>428283</v>
       </c>
       <c r="R39" t="n">
-        <v>6233291</v>
+        <v>6233084</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5088,7 +5088,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121471923</v>
+        <v>121471928</v>
       </c>
       <c r="B40" t="n">
         <v>80252</v>
@@ -5128,10 +5128,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>428091</v>
+        <v>428075</v>
       </c>
       <c r="R40" t="n">
-        <v>6233386</v>
+        <v>6233294</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5190,7 +5190,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121471911</v>
+        <v>121471909</v>
       </c>
       <c r="B41" t="n">
         <v>76945</v>
@@ -5230,10 +5230,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>428352</v>
+        <v>428373</v>
       </c>
       <c r="R41" t="n">
-        <v>6233082</v>
+        <v>6233088</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5292,10 +5292,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121471868</v>
+        <v>121471860</v>
       </c>
       <c r="B42" t="n">
-        <v>94595</v>
+        <v>96721</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5308,21 +5308,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5332,10 +5332,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>428347</v>
+        <v>428404</v>
       </c>
       <c r="R42" t="n">
-        <v>6233241</v>
+        <v>6233275</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5394,10 +5394,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121471878</v>
+        <v>121471800</v>
       </c>
       <c r="B43" t="n">
-        <v>96769</v>
+        <v>80252</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5406,25 +5406,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2604</v>
+        <v>1144</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5434,10 +5434,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>428445</v>
+        <v>428387</v>
       </c>
       <c r="R43" t="n">
-        <v>6233151</v>
+        <v>6233322</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5496,10 +5496,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121471829</v>
+        <v>121471839</v>
       </c>
       <c r="B44" t="n">
-        <v>80252</v>
+        <v>94584</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5508,25 +5508,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1144</v>
+        <v>2671</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>428147</v>
+        <v>428184</v>
       </c>
       <c r="R44" t="n">
-        <v>6233304</v>
+        <v>6233240</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5598,10 +5598,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121471901</v>
+        <v>121471852</v>
       </c>
       <c r="B45" t="n">
-        <v>76945</v>
+        <v>80252</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5610,25 +5610,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>428390</v>
+        <v>428311</v>
       </c>
       <c r="R45" t="n">
-        <v>6233099</v>
+        <v>6233183</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5668,12 +5668,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5700,10 +5700,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121471853</v>
+        <v>121471845</v>
       </c>
       <c r="B46" t="n">
-        <v>76945</v>
+        <v>80252</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5712,25 +5712,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>428311</v>
+        <v>428248</v>
       </c>
       <c r="R46" t="n">
-        <v>6233183</v>
+        <v>6233242</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5802,10 +5802,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121471839</v>
+        <v>121471695</v>
       </c>
       <c r="B47" t="n">
-        <v>94584</v>
+        <v>80239</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5818,21 +5818,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2671</v>
+        <v>230185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5842,10 +5842,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>428184</v>
+        <v>428053</v>
       </c>
       <c r="R47" t="n">
-        <v>6233240</v>
+        <v>6233336</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5872,12 +5872,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5904,10 +5904,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121471804</v>
+        <v>121471544</v>
       </c>
       <c r="B48" t="n">
-        <v>76945</v>
+        <v>94595</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5916,25 +5916,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1342</v>
+        <v>2667</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5944,10 +5944,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>428335</v>
+        <v>428219</v>
       </c>
       <c r="R48" t="n">
-        <v>6233286</v>
+        <v>6233278</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5974,12 +5974,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6006,10 +6006,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121471871</v>
+        <v>121471806</v>
       </c>
       <c r="B49" t="n">
-        <v>80239</v>
+        <v>80252</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6018,25 +6018,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6046,10 +6046,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>428302</v>
+        <v>428325</v>
       </c>
       <c r="R49" t="n">
-        <v>6233176</v>
+        <v>6233291</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6108,10 +6108,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121471852</v>
+        <v>121471908</v>
       </c>
       <c r="B50" t="n">
-        <v>80252</v>
+        <v>74606</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6120,25 +6120,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1144</v>
+        <v>1118</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6148,10 +6148,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>428311</v>
+        <v>428377</v>
       </c>
       <c r="R50" t="n">
-        <v>6233183</v>
+        <v>6233090</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6178,12 +6178,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6210,10 +6210,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121471822</v>
+        <v>121471922</v>
       </c>
       <c r="B51" t="n">
-        <v>94595</v>
+        <v>76945</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6222,25 +6222,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>428288</v>
+        <v>428091</v>
       </c>
       <c r="R51" t="n">
-        <v>6233325</v>
+        <v>6233385</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6280,12 +6280,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6312,10 +6312,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121471867</v>
+        <v>121471866</v>
       </c>
       <c r="B52" t="n">
-        <v>76945</v>
+        <v>80239</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6324,25 +6324,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6414,10 +6414,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121471817</v>
+        <v>121471856</v>
       </c>
       <c r="B53" t="n">
-        <v>74694</v>
+        <v>76945</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6426,25 +6426,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6439</v>
+        <v>1342</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6454,10 +6454,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>428312</v>
+        <v>428360</v>
       </c>
       <c r="R53" t="n">
-        <v>6233323</v>
+        <v>6233266</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6516,10 +6516,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121471831</v>
+        <v>121471864</v>
       </c>
       <c r="B54" t="n">
-        <v>80252</v>
+        <v>94584</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6528,25 +6528,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1144</v>
+        <v>2671</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6556,10 +6556,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>428145</v>
+        <v>428410</v>
       </c>
       <c r="R54" t="n">
-        <v>6233315</v>
+        <v>6233214</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6618,10 +6618,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121471694</v>
+        <v>121471817</v>
       </c>
       <c r="B55" t="n">
-        <v>80252</v>
+        <v>74694</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6630,25 +6630,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1144</v>
+        <v>6439</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>428125</v>
+        <v>428312</v>
       </c>
       <c r="R55" t="n">
-        <v>6233379</v>
+        <v>6233323</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6720,10 +6720,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121471931</v>
+        <v>121471815</v>
       </c>
       <c r="B56" t="n">
-        <v>80252</v>
+        <v>80409</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6736,21 +6736,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1144</v>
+        <v>1557</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Röd pysslinglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelopsis rubella</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>Nyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6760,10 +6760,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>428075</v>
+        <v>428333</v>
       </c>
       <c r="R56" t="n">
-        <v>6233301</v>
+        <v>6233339</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6790,12 +6790,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6822,7 +6822,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121471834</v>
+        <v>121471801</v>
       </c>
       <c r="B57" t="n">
         <v>80252</v>
@@ -6862,10 +6862,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>428137</v>
+        <v>428370</v>
       </c>
       <c r="R57" t="n">
-        <v>6233320</v>
+        <v>6233336</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6924,10 +6924,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121471856</v>
+        <v>121471895</v>
       </c>
       <c r="B58" t="n">
-        <v>76945</v>
+        <v>80239</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6936,25 +6936,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6964,10 +6964,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>428360</v>
+        <v>428355</v>
       </c>
       <c r="R58" t="n">
-        <v>6233266</v>
+        <v>6233123</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6994,12 +6994,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7026,10 +7026,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121471869</v>
+        <v>121471831</v>
       </c>
       <c r="B59" t="n">
-        <v>96721</v>
+        <v>80252</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7038,25 +7038,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7066,10 +7066,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>428354</v>
+        <v>428145</v>
       </c>
       <c r="R59" t="n">
-        <v>6233242</v>
+        <v>6233315</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7128,10 +7128,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121471814</v>
+        <v>121471691</v>
       </c>
       <c r="B60" t="n">
-        <v>80252</v>
+        <v>96721</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7140,25 +7140,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7168,10 +7168,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>428331</v>
+        <v>428128</v>
       </c>
       <c r="R60" t="n">
-        <v>6233339</v>
+        <v>6233385</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7198,12 +7198,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7230,7 +7230,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121471935</v>
+        <v>121471941</v>
       </c>
       <c r="B61" t="n">
         <v>80239</v>
@@ -7270,10 +7270,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>428097</v>
+        <v>428046</v>
       </c>
       <c r="R61" t="n">
-        <v>6233286</v>
+        <v>6233350</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7332,10 +7332,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121471877</v>
+        <v>121471796</v>
       </c>
       <c r="B62" t="n">
-        <v>94595</v>
+        <v>80252</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7344,25 +7344,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7372,10 +7372,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>428445</v>
+        <v>428390</v>
       </c>
       <c r="R62" t="n">
-        <v>6233151</v>
+        <v>6233312</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7434,10 +7434,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121471859</v>
+        <v>121471819</v>
       </c>
       <c r="B63" t="n">
-        <v>80239</v>
+        <v>94595</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7450,21 +7450,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7474,10 +7474,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>428404</v>
+        <v>428304</v>
       </c>
       <c r="R63" t="n">
-        <v>6233275</v>
+        <v>6233306</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7536,10 +7536,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121471813</v>
+        <v>121471851</v>
       </c>
       <c r="B64" t="n">
-        <v>94584</v>
+        <v>78860</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7552,21 +7552,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2671</v>
+        <v>6459</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7576,10 +7576,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>428332</v>
+        <v>428293</v>
       </c>
       <c r="R64" t="n">
-        <v>6233341</v>
+        <v>6233170</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7638,10 +7638,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121471696</v>
+        <v>121471683</v>
       </c>
       <c r="B65" t="n">
-        <v>96721</v>
+        <v>94584</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7654,21 +7654,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2606</v>
+        <v>2671</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7678,10 +7678,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>428054</v>
+        <v>428278</v>
       </c>
       <c r="R65" t="n">
-        <v>6233337</v>
+        <v>6233417</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7740,14 +7740,14 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121471800</v>
+        <v>121471875</v>
       </c>
       <c r="B66" t="n">
         <v>80252</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -7774,16 +7774,19 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>428387</v>
+        <v>428340</v>
       </c>
       <c r="R66" t="n">
-        <v>6233322</v>
+        <v>6233229</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7818,11 +7821,21 @@
           <t>2024-11-21</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>kollekt</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG66" t="b">
         <v>0</v>
@@ -7842,10 +7855,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121471810</v>
+        <v>121471936</v>
       </c>
       <c r="B67" t="n">
-        <v>80252</v>
+        <v>94605</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7854,25 +7867,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1144</v>
+        <v>1080</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7882,10 +7895,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>428347</v>
+        <v>428079</v>
       </c>
       <c r="R67" t="n">
-        <v>6233326</v>
+        <v>6233262</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7912,12 +7925,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7944,10 +7957,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121471807</v>
+        <v>121471829</v>
       </c>
       <c r="B68" t="n">
-        <v>76945</v>
+        <v>80252</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7956,25 +7969,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7984,10 +7997,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>428327</v>
+        <v>428147</v>
       </c>
       <c r="R68" t="n">
-        <v>6233292</v>
+        <v>6233304</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8046,10 +8059,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121471908</v>
+        <v>121471814</v>
       </c>
       <c r="B69" t="n">
-        <v>74606</v>
+        <v>80252</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8058,25 +8071,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1118</v>
+        <v>1144</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8086,10 +8099,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>428377</v>
+        <v>428331</v>
       </c>
       <c r="R69" t="n">
-        <v>6233090</v>
+        <v>6233339</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8116,12 +8129,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8148,7 +8161,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121471862</v>
+        <v>121471825</v>
       </c>
       <c r="B70" t="n">
         <v>80239</v>
@@ -8188,10 +8201,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>428411</v>
+        <v>428233</v>
       </c>
       <c r="R70" t="n">
-        <v>6233213</v>
+        <v>6233332</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8250,10 +8263,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121471809</v>
+        <v>121471855</v>
       </c>
       <c r="B71" t="n">
-        <v>74560</v>
+        <v>94389</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8262,25 +8275,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1116</v>
+        <v>2779</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8290,10 +8303,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>428352</v>
+        <v>428365</v>
       </c>
       <c r="R71" t="n">
-        <v>6233315</v>
+        <v>6233269</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8352,7 +8365,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121471543</v>
+        <v>121471533</v>
       </c>
       <c r="B72" t="n">
         <v>80239</v>
@@ -8392,10 +8405,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>428209</v>
+        <v>428144</v>
       </c>
       <c r="R72" t="n">
-        <v>6233279</v>
+        <v>6233229</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8454,10 +8467,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121471841</v>
+        <v>121471874</v>
       </c>
       <c r="B73" t="n">
-        <v>96721</v>
+        <v>80252</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8466,25 +8479,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8494,10 +8507,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>428221</v>
+        <v>428375</v>
       </c>
       <c r="R73" t="n">
-        <v>6233212</v>
+        <v>6233151</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8556,10 +8569,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121471917</v>
+        <v>121471692</v>
       </c>
       <c r="B74" t="n">
-        <v>80239</v>
+        <v>94595</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8572,21 +8585,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8596,10 +8609,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>428284</v>
+        <v>428126</v>
       </c>
       <c r="R74" t="n">
-        <v>6233109</v>
+        <v>6233380</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8626,12 +8639,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8658,10 +8671,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121471881</v>
+        <v>121471696</v>
       </c>
       <c r="B75" t="n">
-        <v>78404</v>
+        <v>96721</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8670,25 +8683,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>924</v>
+        <v>2606</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8698,10 +8711,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>428445</v>
+        <v>428054</v>
       </c>
       <c r="R75" t="n">
-        <v>6233151</v>
+        <v>6233337</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8728,12 +8741,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8760,7 +8773,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121471943</v>
+        <v>121471688</v>
       </c>
       <c r="B76" t="n">
         <v>96721</v>
@@ -8800,10 +8813,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>428034</v>
+        <v>428159</v>
       </c>
       <c r="R76" t="n">
-        <v>6233348</v>
+        <v>6233394</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8830,12 +8843,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8862,10 +8875,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121471899</v>
+        <v>121471685</v>
       </c>
       <c r="B77" t="n">
-        <v>94389</v>
+        <v>80252</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8874,25 +8887,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2779</v>
+        <v>1144</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8902,10 +8915,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>428389</v>
+        <v>428228</v>
       </c>
       <c r="R77" t="n">
-        <v>6233099</v>
+        <v>6233391</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8932,12 +8945,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8964,10 +8977,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121471684</v>
+        <v>121471818</v>
       </c>
       <c r="B78" t="n">
-        <v>80409</v>
+        <v>96721</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8976,25 +8989,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1557</v>
+        <v>2606</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Röd pysslinglav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Thelopsis rubella</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Nyl.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9004,10 +9017,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>428227</v>
+        <v>428307</v>
       </c>
       <c r="R78" t="n">
-        <v>6233392</v>
+        <v>6233311</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9034,12 +9047,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9066,10 +9079,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121471920</v>
+        <v>121471827</v>
       </c>
       <c r="B79" t="n">
-        <v>91108</v>
+        <v>94595</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9078,25 +9091,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2023</v>
+        <v>2667</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sydlig sotticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ischnoderma resinosum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schrad.) P.Karst.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9106,10 +9119,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>428095</v>
+        <v>428185</v>
       </c>
       <c r="R79" t="n">
-        <v>6233349</v>
+        <v>6233287</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9136,12 +9149,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9168,10 +9181,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121471798</v>
+        <v>121471904</v>
       </c>
       <c r="B80" t="n">
-        <v>96721</v>
+        <v>78404</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9180,25 +9193,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2606</v>
+        <v>924</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9211,7 +9224,7 @@
         <v>428387</v>
       </c>
       <c r="R80" t="n">
-        <v>6233326</v>
+        <v>6233098</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9238,12 +9251,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9270,10 +9283,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121471863</v>
+        <v>121471541</v>
       </c>
       <c r="B81" t="n">
-        <v>96721</v>
+        <v>80239</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9286,21 +9299,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9310,10 +9323,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>428411</v>
+        <v>428209</v>
       </c>
       <c r="R81" t="n">
-        <v>6233213</v>
+        <v>6233184</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9340,12 +9353,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9372,10 +9385,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121471851</v>
+        <v>121471919</v>
       </c>
       <c r="B82" t="n">
-        <v>78860</v>
+        <v>80252</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9384,25 +9397,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6459</v>
+        <v>1144</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9412,10 +9425,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>428293</v>
+        <v>428106</v>
       </c>
       <c r="R82" t="n">
-        <v>6233170</v>
+        <v>6233304</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9442,12 +9455,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9474,10 +9487,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121471545</v>
+        <v>121471925</v>
       </c>
       <c r="B83" t="n">
-        <v>80252</v>
+        <v>94597</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9486,25 +9499,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1144</v>
+        <v>2666</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9514,10 +9527,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>428172</v>
+        <v>428076</v>
       </c>
       <c r="R83" t="n">
-        <v>6233315</v>
+        <v>6233382</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9544,12 +9557,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9576,10 +9589,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121471805</v>
+        <v>121471867</v>
       </c>
       <c r="B84" t="n">
-        <v>80252</v>
+        <v>76945</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9588,25 +9601,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9616,10 +9629,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>428333</v>
+        <v>428442</v>
       </c>
       <c r="R84" t="n">
-        <v>6233283</v>
+        <v>6233170</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9678,7 +9691,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121471837</v>
+        <v>121471859</v>
       </c>
       <c r="B85" t="n">
         <v>80239</v>
@@ -9718,10 +9731,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>428145</v>
+        <v>428404</v>
       </c>
       <c r="R85" t="n">
-        <v>6233244</v>
+        <v>6233275</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9780,10 +9793,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121471796</v>
+        <v>121471943</v>
       </c>
       <c r="B86" t="n">
-        <v>80252</v>
+        <v>96721</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9792,25 +9805,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9820,10 +9833,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>428390</v>
+        <v>428034</v>
       </c>
       <c r="R86" t="n">
-        <v>6233312</v>
+        <v>6233348</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9850,12 +9863,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9882,7 +9895,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121471910</v>
+        <v>121471824</v>
       </c>
       <c r="B87" t="n">
         <v>76945</v>
@@ -9922,10 +9935,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>428377</v>
+        <v>428288</v>
       </c>
       <c r="R87" t="n">
-        <v>6233090</v>
+        <v>6233325</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9952,12 +9965,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9984,10 +9997,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121471843</v>
+        <v>121471937</v>
       </c>
       <c r="B88" t="n">
-        <v>57367</v>
+        <v>96721</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9996,25 +10009,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10024,10 +10037,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>428252</v>
+        <v>428062</v>
       </c>
       <c r="R88" t="n">
-        <v>6233262</v>
+        <v>6233301</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10054,12 +10067,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10086,10 +10099,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121471876</v>
+        <v>121471532</v>
       </c>
       <c r="B89" t="n">
-        <v>80282</v>
+        <v>94595</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10102,21 +10115,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1223</v>
+        <v>2667</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rikfruktig blemlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phlyctis agelaea</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Flot.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10126,10 +10139,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>428446</v>
+        <v>428133</v>
       </c>
       <c r="R89" t="n">
-        <v>6233151</v>
+        <v>6233219</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10156,12 +10169,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10188,10 +10201,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121471909</v>
+        <v>121471540</v>
       </c>
       <c r="B90" t="n">
-        <v>76945</v>
+        <v>96721</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10200,25 +10213,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10228,10 +10241,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>428373</v>
+        <v>428227</v>
       </c>
       <c r="R90" t="n">
-        <v>6233088</v>
+        <v>6233132</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10258,12 +10271,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10290,10 +10303,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121471857</v>
+        <v>121471534</v>
       </c>
       <c r="B91" t="n">
-        <v>80252</v>
+        <v>96721</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10302,25 +10315,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10330,10 +10343,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>428362</v>
+        <v>428147</v>
       </c>
       <c r="R91" t="n">
-        <v>6233272</v>
+        <v>6233224</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10360,12 +10373,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10392,10 +10405,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121471686</v>
+        <v>121471802</v>
       </c>
       <c r="B92" t="n">
-        <v>80252</v>
+        <v>94584</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10404,25 +10417,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1144</v>
+        <v>2671</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10432,10 +10445,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>428187</v>
+        <v>428332</v>
       </c>
       <c r="R92" t="n">
-        <v>6233403</v>
+        <v>6233287</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10462,12 +10475,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10494,10 +10507,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121471693</v>
+        <v>121471863</v>
       </c>
       <c r="B93" t="n">
-        <v>94584</v>
+        <v>96721</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10510,21 +10523,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10534,10 +10547,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>428125</v>
+        <v>428411</v>
       </c>
       <c r="R93" t="n">
-        <v>6233379</v>
+        <v>6233213</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10564,12 +10577,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10596,10 +10609,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121471827</v>
+        <v>121471915</v>
       </c>
       <c r="B94" t="n">
-        <v>94595</v>
+        <v>96769</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10612,21 +10625,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2667</v>
+        <v>2604</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10636,10 +10649,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>428185</v>
+        <v>428281</v>
       </c>
       <c r="R94" t="n">
-        <v>6233287</v>
+        <v>6233082</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10666,12 +10679,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10698,10 +10711,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121471934</v>
+        <v>121471869</v>
       </c>
       <c r="B95" t="n">
-        <v>94389</v>
+        <v>96721</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10714,21 +10727,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2779</v>
+        <v>2606</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10738,10 +10751,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>428090</v>
+        <v>428354</v>
       </c>
       <c r="R95" t="n">
-        <v>6233309</v>
+        <v>6233242</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10768,12 +10781,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10800,10 +10813,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121471695</v>
+        <v>121471849</v>
       </c>
       <c r="B96" t="n">
-        <v>80239</v>
+        <v>80252</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10812,25 +10825,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10840,10 +10853,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>428053</v>
+        <v>428299</v>
       </c>
       <c r="R96" t="n">
-        <v>6233336</v>
+        <v>6233126</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10870,12 +10883,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10902,7 +10915,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121471541</v>
+        <v>121471924</v>
       </c>
       <c r="B97" t="n">
         <v>80239</v>
@@ -10942,10 +10955,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>428209</v>
+        <v>428097</v>
       </c>
       <c r="R97" t="n">
-        <v>6233184</v>
+        <v>6233382</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10972,12 +10985,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11004,10 +11017,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121471926</v>
+        <v>121471811</v>
       </c>
       <c r="B98" t="n">
-        <v>94389</v>
+        <v>76945</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11016,25 +11029,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2779</v>
+        <v>1342</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11044,10 +11057,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>428073</v>
+        <v>428349</v>
       </c>
       <c r="R98" t="n">
-        <v>6233383</v>
+        <v>6233325</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11074,12 +11087,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11106,10 +11119,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121471873</v>
+        <v>121471861</v>
       </c>
       <c r="B99" t="n">
-        <v>74560</v>
+        <v>94595</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11118,25 +11131,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1116</v>
+        <v>2667</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11146,10 +11159,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>428301</v>
+        <v>428404</v>
       </c>
       <c r="R99" t="n">
-        <v>6233171</v>
+        <v>6233275</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11208,10 +11221,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121471688</v>
+        <v>121471903</v>
       </c>
       <c r="B100" t="n">
-        <v>96721</v>
+        <v>76945</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11220,25 +11233,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11248,10 +11261,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>428159</v>
+        <v>428385</v>
       </c>
       <c r="R100" t="n">
-        <v>6233394</v>
+        <v>6233097</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11278,12 +11291,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11310,10 +11323,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121471801</v>
+        <v>121471933</v>
       </c>
       <c r="B101" t="n">
-        <v>80252</v>
+        <v>94584</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11322,25 +11335,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1144</v>
+        <v>2671</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11350,10 +11363,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>428370</v>
+        <v>428090</v>
       </c>
       <c r="R101" t="n">
-        <v>6233336</v>
+        <v>6233309</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11380,12 +11393,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11412,10 +11425,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121471811</v>
+        <v>121471836</v>
       </c>
       <c r="B102" t="n">
-        <v>76945</v>
+        <v>94584</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11424,25 +11437,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1342</v>
+        <v>2671</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11452,10 +11465,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>428349</v>
+        <v>428145</v>
       </c>
       <c r="R102" t="n">
-        <v>6233325</v>
+        <v>6233244</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11514,10 +11527,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121471913</v>
+        <v>121471912</v>
       </c>
       <c r="B103" t="n">
-        <v>76945</v>
+        <v>78404</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11530,21 +11543,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1342</v>
+        <v>924</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11554,7 +11567,7 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>428342</v>
+        <v>428351</v>
       </c>
       <c r="R103" t="n">
         <v>6233082</v>
@@ -11616,10 +11629,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121471534</v>
+        <v>121471833</v>
       </c>
       <c r="B104" t="n">
-        <v>96721</v>
+        <v>80239</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11632,21 +11645,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11656,10 +11669,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>428147</v>
+        <v>428139</v>
       </c>
       <c r="R104" t="n">
-        <v>6233224</v>
+        <v>6233315</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11686,12 +11699,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11718,10 +11731,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121471936</v>
+        <v>121471837</v>
       </c>
       <c r="B105" t="n">
-        <v>94605</v>
+        <v>80239</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11734,21 +11747,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1080</v>
+        <v>230185</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11758,10 +11771,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>428079</v>
+        <v>428145</v>
       </c>
       <c r="R105" t="n">
-        <v>6233262</v>
+        <v>6233244</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11788,12 +11801,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11820,10 +11833,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121471933</v>
+        <v>121471809</v>
       </c>
       <c r="B106" t="n">
-        <v>94584</v>
+        <v>74560</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11832,25 +11845,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2671</v>
+        <v>1116</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11860,10 +11873,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>428090</v>
+        <v>428352</v>
       </c>
       <c r="R106" t="n">
-        <v>6233309</v>
+        <v>6233315</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11890,12 +11903,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11922,10 +11935,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121471916</v>
+        <v>121471917</v>
       </c>
       <c r="B107" t="n">
-        <v>94605</v>
+        <v>80239</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11938,21 +11951,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1080</v>
+        <v>230185</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11962,10 +11975,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>428283</v>
+        <v>428284</v>
       </c>
       <c r="R107" t="n">
-        <v>6233084</v>
+        <v>6233109</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12024,10 +12037,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121471532</v>
+        <v>121471846</v>
       </c>
       <c r="B108" t="n">
-        <v>94595</v>
+        <v>80239</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12040,21 +12053,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12064,10 +12077,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>428133</v>
+        <v>428241</v>
       </c>
       <c r="R108" t="n">
-        <v>6233219</v>
+        <v>6233222</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12094,12 +12107,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12126,10 +12139,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121471874</v>
+        <v>121471693</v>
       </c>
       <c r="B109" t="n">
-        <v>80252</v>
+        <v>94584</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12138,25 +12151,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1144</v>
+        <v>2671</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12166,10 +12179,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>428375</v>
+        <v>428125</v>
       </c>
       <c r="R109" t="n">
-        <v>6233151</v>
+        <v>6233379</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12196,12 +12209,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12228,10 +12241,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121471689</v>
+        <v>121471920</v>
       </c>
       <c r="B110" t="n">
-        <v>94595</v>
+        <v>91108</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12240,25 +12253,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2667</v>
+        <v>2023</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Sydlig sotticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Ischnoderma resinosum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Schrad.) P.Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12268,10 +12281,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>428161</v>
+        <v>428095</v>
       </c>
       <c r="R110" t="n">
-        <v>6233396</v>
+        <v>6233349</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12298,12 +12311,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12330,10 +12343,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121471855</v>
+        <v>121471542</v>
       </c>
       <c r="B111" t="n">
-        <v>94389</v>
+        <v>80252</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12342,25 +12355,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2779</v>
+        <v>1144</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12370,10 +12383,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>428365</v>
+        <v>428198</v>
       </c>
       <c r="R111" t="n">
-        <v>6233269</v>
+        <v>6233249</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12400,12 +12413,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12432,10 +12445,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121471854</v>
+        <v>121471684</v>
       </c>
       <c r="B112" t="n">
-        <v>96721</v>
+        <v>80409</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12444,25 +12457,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2606</v>
+        <v>1557</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Röd pysslinglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelopsis rubella</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Nyl.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12472,10 +12485,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>428302</v>
+        <v>428227</v>
       </c>
       <c r="R112" t="n">
-        <v>6233177</v>
+        <v>6233392</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12502,12 +12515,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12534,10 +12547,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121471820</v>
+        <v>121471882</v>
       </c>
       <c r="B113" t="n">
-        <v>94389</v>
+        <v>74606</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12546,25 +12559,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2779</v>
+        <v>1118</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12574,10 +12587,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>428304</v>
+        <v>428445</v>
       </c>
       <c r="R113" t="n">
-        <v>6233306</v>
+        <v>6233151</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12636,10 +12649,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121471865</v>
+        <v>121471798</v>
       </c>
       <c r="B114" t="n">
-        <v>74696</v>
+        <v>96721</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12652,21 +12665,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>306</v>
+        <v>2606</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12676,10 +12689,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>428438</v>
+        <v>428387</v>
       </c>
       <c r="R114" t="n">
-        <v>6233202</v>
+        <v>6233326</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12738,7 +12751,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121471538</v>
+        <v>121471938</v>
       </c>
       <c r="B115" t="n">
         <v>80239</v>
@@ -12778,10 +12791,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>428166</v>
+        <v>428062</v>
       </c>
       <c r="R115" t="n">
-        <v>6233198</v>
+        <v>6233301</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12808,12 +12821,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12840,10 +12853,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121471919</v>
+        <v>121471844</v>
       </c>
       <c r="B116" t="n">
-        <v>80252</v>
+        <v>76945</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12852,25 +12865,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12880,10 +12893,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>428106</v>
+        <v>428248</v>
       </c>
       <c r="R116" t="n">
-        <v>6233304</v>
+        <v>6233241</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12910,12 +12923,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12942,7 +12955,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121471924</v>
+        <v>121471871</v>
       </c>
       <c r="B117" t="n">
         <v>80239</v>
@@ -12982,10 +12995,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>428097</v>
+        <v>428302</v>
       </c>
       <c r="R117" t="n">
-        <v>6233382</v>
+        <v>6233176</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13012,12 +13025,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13044,10 +13057,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121471879</v>
+        <v>121471538</v>
       </c>
       <c r="B118" t="n">
-        <v>76945</v>
+        <v>80239</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13056,25 +13069,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13084,10 +13097,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>428445</v>
+        <v>428166</v>
       </c>
       <c r="R118" t="n">
-        <v>6233151</v>
+        <v>6233198</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13114,12 +13127,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13146,10 +13159,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121471941</v>
+        <v>121471873</v>
       </c>
       <c r="B119" t="n">
-        <v>80239</v>
+        <v>74560</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13158,25 +13171,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>230185</v>
+        <v>1116</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13186,10 +13199,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>428046</v>
+        <v>428301</v>
       </c>
       <c r="R119" t="n">
-        <v>6233350</v>
+        <v>6233171</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13216,12 +13229,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13248,10 +13261,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121471925</v>
+        <v>121471868</v>
       </c>
       <c r="B120" t="n">
-        <v>94597</v>
+        <v>94595</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13264,16 +13277,16 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2666</v>
+        <v>2667</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -13288,10 +13301,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>428076</v>
+        <v>428347</v>
       </c>
       <c r="R120" t="n">
-        <v>6233382</v>
+        <v>6233241</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13318,12 +13331,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13350,10 +13363,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121471806</v>
+        <v>121471940</v>
       </c>
       <c r="B121" t="n">
-        <v>80252</v>
+        <v>94605</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13362,25 +13375,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1144</v>
+        <v>1080</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13390,7 +13403,7 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>428325</v>
+        <v>428037</v>
       </c>
       <c r="R121" t="n">
         <v>6233291</v>
@@ -13420,12 +13433,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13452,10 +13465,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121471914</v>
+        <v>121471934</v>
       </c>
       <c r="B122" t="n">
-        <v>94595</v>
+        <v>94389</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13468,21 +13481,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13492,10 +13505,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>428318</v>
+        <v>428090</v>
       </c>
       <c r="R122" t="n">
-        <v>6233075</v>
+        <v>6233309</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13554,10 +13567,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121471530</v>
+        <v>121471804</v>
       </c>
       <c r="B123" t="n">
-        <v>80239</v>
+        <v>76945</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13566,25 +13579,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13594,10 +13607,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>428111</v>
+        <v>428335</v>
       </c>
       <c r="R123" t="n">
-        <v>6233222</v>
+        <v>6233286</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13624,12 +13637,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13656,10 +13669,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121471927</v>
+        <v>121471842</v>
       </c>
       <c r="B124" t="n">
-        <v>76945</v>
+        <v>94595</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13668,25 +13681,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1342</v>
+        <v>2667</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13696,10 +13709,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>428074</v>
+        <v>428221</v>
       </c>
       <c r="R124" t="n">
-        <v>6233297</v>
+        <v>6233212</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13726,12 +13739,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13758,10 +13771,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121471536</v>
+        <v>121471858</v>
       </c>
       <c r="B125" t="n">
-        <v>80575</v>
+        <v>80252</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13770,25 +13783,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1182</v>
+        <v>1144</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13798,10 +13811,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>428166</v>
+        <v>428372</v>
       </c>
       <c r="R125" t="n">
-        <v>6233202</v>
+        <v>6233270</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13828,12 +13841,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13860,7 +13873,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121471544</v>
+        <v>121471944</v>
       </c>
       <c r="B126" t="n">
         <v>94595</v>
@@ -13900,10 +13913,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>428219</v>
+        <v>428034</v>
       </c>
       <c r="R126" t="n">
-        <v>6233278</v>
+        <v>6233348</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13930,12 +13943,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13962,7 +13975,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121471808</v>
+        <v>121471805</v>
       </c>
       <c r="B127" t="n">
         <v>80252</v>
@@ -14002,10 +14015,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>428350</v>
+        <v>428333</v>
       </c>
       <c r="R127" t="n">
-        <v>6233316</v>
+        <v>6233283</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14064,10 +14077,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121471928</v>
+        <v>121471862</v>
       </c>
       <c r="B128" t="n">
-        <v>80252</v>
+        <v>80239</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14076,25 +14089,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14104,10 +14117,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>428075</v>
+        <v>428411</v>
       </c>
       <c r="R128" t="n">
-        <v>6233294</v>
+        <v>6233213</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14134,12 +14147,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14166,10 +14179,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121471799</v>
+        <v>121471689</v>
       </c>
       <c r="B129" t="n">
-        <v>94584</v>
+        <v>94595</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14182,21 +14195,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14206,10 +14219,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>428389</v>
+        <v>428161</v>
       </c>
       <c r="R129" t="n">
-        <v>6233324</v>
+        <v>6233396</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14236,12 +14249,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14268,10 +14281,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121471818</v>
+        <v>121471812</v>
       </c>
       <c r="B130" t="n">
-        <v>96721</v>
+        <v>94389</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14284,21 +14297,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2606</v>
+        <v>2779</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14308,10 +14321,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>428307</v>
+        <v>428331</v>
       </c>
       <c r="R130" t="n">
-        <v>6233311</v>
+        <v>6233335</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14370,10 +14383,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121471802</v>
+        <v>121471826</v>
       </c>
       <c r="B131" t="n">
-        <v>94584</v>
+        <v>78860</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14386,21 +14399,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2671</v>
+        <v>6459</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14410,10 +14423,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>428332</v>
+        <v>428228</v>
       </c>
       <c r="R131" t="n">
-        <v>6233287</v>
+        <v>6233340</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14472,10 +14485,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121471922</v>
+        <v>121471816</v>
       </c>
       <c r="B132" t="n">
-        <v>76945</v>
+        <v>96769</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14484,25 +14497,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1342</v>
+        <v>2604</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14512,10 +14525,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>428091</v>
+        <v>428317</v>
       </c>
       <c r="R132" t="n">
-        <v>6233385</v>
+        <v>6233324</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14542,12 +14555,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14574,10 +14587,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121471816</v>
+        <v>121471853</v>
       </c>
       <c r="B133" t="n">
-        <v>96769</v>
+        <v>76945</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14586,25 +14599,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2604</v>
+        <v>1342</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14614,10 +14627,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>428317</v>
+        <v>428311</v>
       </c>
       <c r="R133" t="n">
-        <v>6233324</v>
+        <v>6233183</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14676,10 +14689,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121471683</v>
+        <v>121471808</v>
       </c>
       <c r="B134" t="n">
-        <v>94584</v>
+        <v>80252</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14688,25 +14701,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2671</v>
+        <v>1144</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14716,10 +14729,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>428278</v>
+        <v>428350</v>
       </c>
       <c r="R134" t="n">
-        <v>6233417</v>
+        <v>6233316</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14746,12 +14759,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14778,10 +14791,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121471539</v>
+        <v>121471840</v>
       </c>
       <c r="B135" t="n">
-        <v>94584</v>
+        <v>78984</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14794,21 +14807,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2671</v>
+        <v>6431</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14818,10 +14831,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>428262</v>
+        <v>428183</v>
       </c>
       <c r="R135" t="n">
-        <v>6233134</v>
+        <v>6233239</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14848,12 +14861,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14880,10 +14893,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121471897</v>
+        <v>121471820</v>
       </c>
       <c r="B136" t="n">
-        <v>78404</v>
+        <v>94389</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14892,25 +14905,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>924</v>
+        <v>2779</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14920,10 +14933,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>428369</v>
+        <v>428304</v>
       </c>
       <c r="R136" t="n">
-        <v>6233104</v>
+        <v>6233306</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14950,12 +14963,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14982,10 +14995,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121471819</v>
+        <v>121471881</v>
       </c>
       <c r="B137" t="n">
-        <v>94595</v>
+        <v>78404</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14994,25 +15007,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2667</v>
+        <v>924</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15022,10 +15035,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>428304</v>
+        <v>428445</v>
       </c>
       <c r="R137" t="n">
-        <v>6233306</v>
+        <v>6233151</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15084,10 +15097,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121471540</v>
+        <v>121471923</v>
       </c>
       <c r="B138" t="n">
-        <v>96721</v>
+        <v>80252</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15096,25 +15109,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15124,10 +15137,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>428227</v>
+        <v>428091</v>
       </c>
       <c r="R138" t="n">
-        <v>6233132</v>
+        <v>6233386</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15154,12 +15167,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15186,10 +15199,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121471860</v>
+        <v>121471694</v>
       </c>
       <c r="B139" t="n">
-        <v>96721</v>
+        <v>80252</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15198,25 +15211,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15226,10 +15239,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>428404</v>
+        <v>428125</v>
       </c>
       <c r="R139" t="n">
-        <v>6233275</v>
+        <v>6233379</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15256,12 +15269,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15288,10 +15301,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121471882</v>
+        <v>121471537</v>
       </c>
       <c r="B140" t="n">
-        <v>74606</v>
+        <v>96721</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15300,25 +15313,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1118</v>
+        <v>2606</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15328,10 +15341,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>428445</v>
+        <v>428163</v>
       </c>
       <c r="R140" t="n">
-        <v>6233151</v>
+        <v>6233193</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15358,12 +15371,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15390,10 +15403,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121471685</v>
+        <v>121471939</v>
       </c>
       <c r="B141" t="n">
-        <v>80252</v>
+        <v>94595</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15402,25 +15415,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15430,10 +15443,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>428228</v>
+        <v>428046</v>
       </c>
       <c r="R141" t="n">
-        <v>6233391</v>
+        <v>6233296</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15460,12 +15473,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15492,7 +15505,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121471938</v>
+        <v>121471828</v>
       </c>
       <c r="B142" t="n">
         <v>80239</v>
@@ -15532,10 +15545,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>428062</v>
+        <v>428185</v>
       </c>
       <c r="R142" t="n">
-        <v>6233301</v>
+        <v>6233289</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15562,12 +15575,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15576,6 +15589,7 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15594,10 +15608,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121471929</v>
+        <v>121471850</v>
       </c>
       <c r="B143" t="n">
-        <v>94389</v>
+        <v>80239</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15610,21 +15624,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2779</v>
+        <v>230185</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15634,10 +15648,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>428078</v>
+        <v>428293</v>
       </c>
       <c r="R143" t="n">
-        <v>6233294</v>
+        <v>6233170</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15664,12 +15678,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15696,10 +15710,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121471842</v>
+        <v>121471847</v>
       </c>
       <c r="B144" t="n">
-        <v>94595</v>
+        <v>76945</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15708,25 +15722,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15736,10 +15750,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>428221</v>
+        <v>428300</v>
       </c>
       <c r="R144" t="n">
-        <v>6233212</v>
+        <v>6233125</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15798,10 +15812,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121471692</v>
+        <v>121471841</v>
       </c>
       <c r="B145" t="n">
-        <v>94595</v>
+        <v>96721</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15814,21 +15828,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15838,10 +15852,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>428126</v>
+        <v>428221</v>
       </c>
       <c r="R145" t="n">
-        <v>6233380</v>
+        <v>6233212</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15868,12 +15882,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15900,7 +15914,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121471903</v>
+        <v>121471879</v>
       </c>
       <c r="B146" t="n">
         <v>76945</v>
@@ -15940,10 +15954,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>428385</v>
+        <v>428445</v>
       </c>
       <c r="R146" t="n">
-        <v>6233097</v>
+        <v>6233151</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15970,12 +15984,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16002,10 +16016,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121471866</v>
+        <v>121471927</v>
       </c>
       <c r="B147" t="n">
-        <v>80239</v>
+        <v>76945</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16014,25 +16028,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16042,10 +16056,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>428442</v>
+        <v>428074</v>
       </c>
       <c r="R147" t="n">
-        <v>6233170</v>
+        <v>6233297</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16072,12 +16086,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16104,10 +16118,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121471847</v>
+        <v>121471876</v>
       </c>
       <c r="B148" t="n">
-        <v>76945</v>
+        <v>80282</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16116,25 +16130,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1342</v>
+        <v>1223</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Rikfruktig blemlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Phlyctis agelaea</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Flot.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16144,10 +16158,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>428300</v>
+        <v>428446</v>
       </c>
       <c r="R148" t="n">
-        <v>6233125</v>
+        <v>6233151</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16206,10 +16220,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121471861</v>
+        <v>121471878</v>
       </c>
       <c r="B149" t="n">
-        <v>94595</v>
+        <v>96769</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16222,21 +16236,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>2667</v>
+        <v>2604</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16246,10 +16260,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>428404</v>
+        <v>428445</v>
       </c>
       <c r="R149" t="n">
-        <v>6233275</v>
+        <v>6233151</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16308,10 +16322,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121471531</v>
+        <v>121471877</v>
       </c>
       <c r="B150" t="n">
-        <v>94605</v>
+        <v>94595</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16324,21 +16338,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1080</v>
+        <v>2667</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16348,10 +16362,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>428110</v>
+        <v>428445</v>
       </c>
       <c r="R150" t="n">
-        <v>6233224</v>
+        <v>6233151</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16378,12 +16392,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16410,7 +16424,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121471942</v>
+        <v>121471911</v>
       </c>
       <c r="B151" t="n">
         <v>76945</v>
@@ -16450,10 +16464,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>428032</v>
+        <v>428352</v>
       </c>
       <c r="R151" t="n">
-        <v>6233345</v>
+        <v>6233082</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16512,10 +16526,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121471533</v>
+        <v>121471899</v>
       </c>
       <c r="B152" t="n">
-        <v>80239</v>
+        <v>94389</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16528,21 +16542,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>230185</v>
+        <v>2779</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16552,10 +16566,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>428144</v>
+        <v>428389</v>
       </c>
       <c r="R152" t="n">
-        <v>6233229</v>
+        <v>6233099</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16582,12 +16596,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16614,10 +16628,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121471904</v>
+        <v>121471945</v>
       </c>
       <c r="B153" t="n">
-        <v>78404</v>
+        <v>96769</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16626,25 +16640,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>924</v>
+        <v>2604</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16654,10 +16668,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>428387</v>
+        <v>428035</v>
       </c>
       <c r="R153" t="n">
-        <v>6233098</v>
+        <v>6233349</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16716,10 +16730,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121471824</v>
+        <v>121471822</v>
       </c>
       <c r="B154" t="n">
-        <v>76945</v>
+        <v>94595</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16728,25 +16742,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1342</v>
+        <v>2667</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16818,10 +16832,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121471915</v>
+        <v>121471929</v>
       </c>
       <c r="B155" t="n">
-        <v>96769</v>
+        <v>94389</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16834,21 +16848,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2604</v>
+        <v>2779</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16858,10 +16872,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>428281</v>
+        <v>428078</v>
       </c>
       <c r="R155" t="n">
-        <v>6233082</v>
+        <v>6233294</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16920,7 +16934,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121471849</v>
+        <v>121471857</v>
       </c>
       <c r="B156" t="n">
         <v>80252</v>
@@ -16960,10 +16974,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>428299</v>
+        <v>428362</v>
       </c>
       <c r="R156" t="n">
-        <v>6233126</v>
+        <v>6233272</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17022,10 +17036,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121471537</v>
+        <v>121471901</v>
       </c>
       <c r="B157" t="n">
-        <v>96721</v>
+        <v>76945</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17034,25 +17048,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17062,10 +17076,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>428163</v>
+        <v>428390</v>
       </c>
       <c r="R157" t="n">
-        <v>6233193</v>
+        <v>6233099</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17092,12 +17106,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17124,10 +17138,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121471905</v>
+        <v>121471843</v>
       </c>
       <c r="B158" t="n">
-        <v>74606</v>
+        <v>57367</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17140,21 +17154,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1118</v>
+        <v>100049</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17164,10 +17178,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>428377</v>
+        <v>428252</v>
       </c>
       <c r="R158" t="n">
-        <v>6233095</v>
+        <v>6233262</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17194,12 +17208,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17226,53 +17240,50 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121471875</v>
+        <v>121471935</v>
       </c>
       <c r="B159" t="n">
-        <v>80252</v>
+        <v>80239</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>428340</v>
+        <v>428097</v>
       </c>
       <c r="R159" t="n">
-        <v>6233229</v>
+        <v>6233286</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17299,17 +17310,12 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>kollekt</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17317,11 +17323,6 @@
       </c>
       <c r="AE159" t="b">
         <v>0</v>
-      </c>
-      <c r="AF159" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG159" t="b">
         <v>0</v>
@@ -17341,10 +17342,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121471697</v>
+        <v>121471810</v>
       </c>
       <c r="B160" t="n">
-        <v>74696</v>
+        <v>80252</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17353,25 +17354,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>306</v>
+        <v>1144</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17381,10 +17382,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>428043</v>
+        <v>428347</v>
       </c>
       <c r="R160" t="n">
-        <v>6233298</v>
+        <v>6233326</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17411,12 +17412,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17443,10 +17444,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121471895</v>
+        <v>121471914</v>
       </c>
       <c r="B161" t="n">
-        <v>80239</v>
+        <v>94595</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17459,21 +17460,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17483,10 +17484,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>428355</v>
+        <v>428318</v>
       </c>
       <c r="R161" t="n">
-        <v>6233123</v>
+        <v>6233075</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17545,10 +17546,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121471690</v>
+        <v>121471942</v>
       </c>
       <c r="B162" t="n">
-        <v>80239</v>
+        <v>76945</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17557,25 +17558,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17585,10 +17586,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>428161</v>
+        <v>428032</v>
       </c>
       <c r="R162" t="n">
-        <v>6233396</v>
+        <v>6233345</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17615,12 +17616,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17647,10 +17648,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121471542</v>
+        <v>121471536</v>
       </c>
       <c r="B163" t="n">
-        <v>80252</v>
+        <v>80575</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17659,25 +17660,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1144</v>
+        <v>1182</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17687,10 +17688,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>428198</v>
+        <v>428166</v>
       </c>
       <c r="R163" t="n">
-        <v>6233249</v>
+        <v>6233202</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17749,10 +17750,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121471815</v>
+        <v>121471545</v>
       </c>
       <c r="B164" t="n">
-        <v>80409</v>
+        <v>80252</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17765,21 +17766,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1557</v>
+        <v>1144</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Röd pysslinglav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Thelopsis rubella</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Nyl.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17789,10 +17790,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>428333</v>
+        <v>428172</v>
       </c>
       <c r="R164" t="n">
-        <v>6233339</v>
+        <v>6233315</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17819,12 +17820,12 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17851,10 +17852,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121471945</v>
+        <v>121471531</v>
       </c>
       <c r="B165" t="n">
-        <v>96769</v>
+        <v>94605</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17867,21 +17868,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>2604</v>
+        <v>1080</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17891,10 +17892,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>428035</v>
+        <v>428110</v>
       </c>
       <c r="R165" t="n">
-        <v>6233349</v>
+        <v>6233224</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17921,12 +17922,12 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17953,7 +17954,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121471828</v>
+        <v>121471690</v>
       </c>
       <c r="B166" t="n">
         <v>80239</v>
@@ -17993,10 +17994,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>428185</v>
+        <v>428161</v>
       </c>
       <c r="R166" t="n">
-        <v>6233289</v>
+        <v>6233396</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18023,12 +18024,12 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18037,7 +18038,6 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
-      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
@@ -18056,10 +18056,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121471535</v>
+        <v>121471530</v>
       </c>
       <c r="B167" t="n">
-        <v>76945</v>
+        <v>80239</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18068,25 +18068,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18096,10 +18096,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>428160</v>
+        <v>428111</v>
       </c>
       <c r="R167" t="n">
-        <v>6233209</v>
+        <v>6233222</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18158,10 +18158,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121471845</v>
+        <v>121471543</v>
       </c>
       <c r="B168" t="n">
-        <v>80252</v>
+        <v>80239</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18170,25 +18170,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18198,10 +18198,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>428248</v>
+        <v>428209</v>
       </c>
       <c r="R168" t="n">
-        <v>6233242</v>
+        <v>6233279</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18228,12 +18228,12 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18260,10 +18260,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121471907</v>
+        <v>121471799</v>
       </c>
       <c r="B169" t="n">
-        <v>76945</v>
+        <v>94584</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -18272,25 +18272,25 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>1342</v>
+        <v>2671</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18300,10 +18300,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>428375</v>
+        <v>428389</v>
       </c>
       <c r="R169" t="n">
-        <v>6233092</v>
+        <v>6233324</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18330,12 +18330,12 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18362,10 +18362,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121471930</v>
+        <v>121471813</v>
       </c>
       <c r="B170" t="n">
-        <v>74606</v>
+        <v>94584</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18374,25 +18374,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1118</v>
+        <v>2671</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18402,10 +18402,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>428078</v>
+        <v>428332</v>
       </c>
       <c r="R170" t="n">
-        <v>6233294</v>
+        <v>6233341</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18432,12 +18432,12 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18464,10 +18464,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121471803</v>
+        <v>121471807</v>
       </c>
       <c r="B171" t="n">
-        <v>80252</v>
+        <v>76945</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18476,25 +18476,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18504,10 +18504,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>428334</v>
+        <v>428327</v>
       </c>
       <c r="R171" t="n">
-        <v>6233284</v>
+        <v>6233292</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18566,10 +18566,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121471840</v>
+        <v>121471834</v>
       </c>
       <c r="B172" t="n">
-        <v>78984</v>
+        <v>80252</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18578,25 +18578,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6431</v>
+        <v>1144</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18606,10 +18606,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>428183</v>
+        <v>428137</v>
       </c>
       <c r="R172" t="n">
-        <v>6233239</v>
+        <v>6233320</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18668,10 +18668,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121471835</v>
+        <v>121471870</v>
       </c>
       <c r="B173" t="n">
-        <v>96721</v>
+        <v>76945</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18680,25 +18680,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18708,10 +18708,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>428145</v>
+        <v>428356</v>
       </c>
       <c r="R173" t="n">
-        <v>6233244</v>
+        <v>6233243</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18770,10 +18770,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121471850</v>
+        <v>121471835</v>
       </c>
       <c r="B174" t="n">
-        <v>80239</v>
+        <v>96721</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18786,21 +18786,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18810,10 +18810,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>428293</v>
+        <v>428145</v>
       </c>
       <c r="R174" t="n">
-        <v>6233170</v>
+        <v>6233244</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18872,10 +18872,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121471812</v>
+        <v>121471902</v>
       </c>
       <c r="B175" t="n">
-        <v>94389</v>
+        <v>94584</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18888,21 +18888,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18912,10 +18912,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>428331</v>
+        <v>428387</v>
       </c>
       <c r="R175" t="n">
-        <v>6233335</v>
+        <v>6233096</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18942,12 +18942,12 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD175" t="b">

--- a/artfynd/A 18989-2024 artfynd.xlsx
+++ b/artfynd/A 18989-2024 artfynd.xlsx
@@ -3354,10 +3354,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121471535</v>
+        <v>121471684</v>
       </c>
       <c r="B23" t="n">
-        <v>76945</v>
+        <v>80409</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3366,25 +3366,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1342</v>
+        <v>1557</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Röd pysslinglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelopsis rubella</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>428160</v>
+        <v>428227</v>
       </c>
       <c r="R23" t="n">
-        <v>6233209</v>
+        <v>6233392</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3456,10 +3456,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121471931</v>
+        <v>121471945</v>
       </c>
       <c r="B24" t="n">
-        <v>80252</v>
+        <v>96770</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3468,25 +3468,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1144</v>
+        <v>2604</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>428075</v>
+        <v>428035</v>
       </c>
       <c r="R24" t="n">
-        <v>6233301</v>
+        <v>6233349</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121471926</v>
+        <v>121471540</v>
       </c>
       <c r="B25" t="n">
-        <v>94389</v>
+        <v>96722</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3574,21 +3574,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2779</v>
+        <v>2606</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>428073</v>
+        <v>428227</v>
       </c>
       <c r="R25" t="n">
-        <v>6233383</v>
+        <v>6233132</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3628,12 +3628,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3660,10 +3660,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121471803</v>
+        <v>121471836</v>
       </c>
       <c r="B26" t="n">
-        <v>80252</v>
+        <v>94585</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3672,25 +3672,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1144</v>
+        <v>2671</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>428334</v>
+        <v>428145</v>
       </c>
       <c r="R26" t="n">
-        <v>6233284</v>
+        <v>6233244</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3762,10 +3762,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121471854</v>
+        <v>121471843</v>
       </c>
       <c r="B27" t="n">
-        <v>96721</v>
+        <v>57367</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3774,25 +3774,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>428302</v>
+        <v>428252</v>
       </c>
       <c r="R27" t="n">
-        <v>6233177</v>
+        <v>6233262</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3864,10 +3864,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121471913</v>
+        <v>121471936</v>
       </c>
       <c r="B28" t="n">
-        <v>76945</v>
+        <v>94606</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3876,25 +3876,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1342</v>
+        <v>1080</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>428342</v>
+        <v>428079</v>
       </c>
       <c r="R28" t="n">
-        <v>6233082</v>
+        <v>6233262</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121471865</v>
+        <v>121471912</v>
       </c>
       <c r="B29" t="n">
-        <v>74696</v>
+        <v>78404</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3978,25 +3978,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>306</v>
+        <v>924</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>428438</v>
+        <v>428351</v>
       </c>
       <c r="R29" t="n">
-        <v>6233202</v>
+        <v>6233082</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4068,10 +4068,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121471905</v>
+        <v>121471806</v>
       </c>
       <c r="B30" t="n">
-        <v>74606</v>
+        <v>80252</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4080,25 +4080,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1118</v>
+        <v>1144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>428377</v>
+        <v>428325</v>
       </c>
       <c r="R30" t="n">
-        <v>6233095</v>
+        <v>6233291</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4138,12 +4138,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4170,10 +4170,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121471897</v>
+        <v>121471685</v>
       </c>
       <c r="B31" t="n">
-        <v>78404</v>
+        <v>80252</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4182,25 +4182,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>924</v>
+        <v>1144</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>428369</v>
+        <v>428228</v>
       </c>
       <c r="R31" t="n">
-        <v>6233104</v>
+        <v>6233391</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4240,12 +4240,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4272,10 +4272,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121471930</v>
+        <v>121471831</v>
       </c>
       <c r="B32" t="n">
-        <v>74606</v>
+        <v>80252</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4284,25 +4284,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1118</v>
+        <v>1144</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>428078</v>
+        <v>428145</v>
       </c>
       <c r="R32" t="n">
-        <v>6233294</v>
+        <v>6233315</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4342,12 +4342,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4374,10 +4374,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121471910</v>
+        <v>121471896</v>
       </c>
       <c r="B33" t="n">
-        <v>76945</v>
+        <v>80575</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4390,21 +4390,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1342</v>
+        <v>1182</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4414,10 +4414,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>428377</v>
+        <v>428370</v>
       </c>
       <c r="R33" t="n">
-        <v>6233090</v>
+        <v>6233102</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4476,10 +4476,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121471907</v>
+        <v>121471538</v>
       </c>
       <c r="B34" t="n">
-        <v>76945</v>
+        <v>80239</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4488,25 +4488,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>428375</v>
+        <v>428166</v>
       </c>
       <c r="R34" t="n">
-        <v>6233092</v>
+        <v>6233198</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4546,12 +4546,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4578,10 +4578,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121471697</v>
+        <v>121471942</v>
       </c>
       <c r="B35" t="n">
-        <v>74696</v>
+        <v>76945</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4590,25 +4590,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>306</v>
+        <v>1342</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>428043</v>
+        <v>428032</v>
       </c>
       <c r="R35" t="n">
-        <v>6233298</v>
+        <v>6233345</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4648,12 +4648,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4680,10 +4680,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121471686</v>
+        <v>121471934</v>
       </c>
       <c r="B36" t="n">
-        <v>80252</v>
+        <v>94390</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4692,25 +4692,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1144</v>
+        <v>2779</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4720,10 +4720,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>428187</v>
+        <v>428090</v>
       </c>
       <c r="R36" t="n">
-        <v>6233403</v>
+        <v>6233309</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4750,12 +4750,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4782,10 +4782,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121471539</v>
+        <v>121471944</v>
       </c>
       <c r="B37" t="n">
-        <v>94584</v>
+        <v>94596</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4798,21 +4798,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>428262</v>
+        <v>428034</v>
       </c>
       <c r="R37" t="n">
-        <v>6233134</v>
+        <v>6233348</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4884,10 +4884,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121471896</v>
+        <v>121471908</v>
       </c>
       <c r="B38" t="n">
-        <v>80575</v>
+        <v>74606</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4900,21 +4900,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1182</v>
+        <v>1118</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>428370</v>
+        <v>428377</v>
       </c>
       <c r="R38" t="n">
-        <v>6233102</v>
+        <v>6233090</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4986,10 +4986,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121471916</v>
+        <v>121471905</v>
       </c>
       <c r="B39" t="n">
-        <v>94605</v>
+        <v>74606</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4998,25 +4998,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1080</v>
+        <v>1118</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>428283</v>
+        <v>428377</v>
       </c>
       <c r="R39" t="n">
-        <v>6233084</v>
+        <v>6233095</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5088,7 +5088,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121471928</v>
+        <v>121471829</v>
       </c>
       <c r="B40" t="n">
         <v>80252</v>
@@ -5128,10 +5128,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>428075</v>
+        <v>428147</v>
       </c>
       <c r="R40" t="n">
-        <v>6233294</v>
+        <v>6233304</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5190,10 +5190,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121471909</v>
+        <v>121471895</v>
       </c>
       <c r="B41" t="n">
-        <v>76945</v>
+        <v>80239</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5202,25 +5202,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5230,10 +5230,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>428373</v>
+        <v>428355</v>
       </c>
       <c r="R41" t="n">
-        <v>6233088</v>
+        <v>6233123</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5292,10 +5292,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121471860</v>
+        <v>121471828</v>
       </c>
       <c r="B42" t="n">
-        <v>96721</v>
+        <v>80239</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5308,21 +5308,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5332,10 +5332,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>428404</v>
+        <v>428185</v>
       </c>
       <c r="R42" t="n">
-        <v>6233275</v>
+        <v>6233289</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5376,6 +5376,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5394,10 +5395,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121471800</v>
+        <v>121471844</v>
       </c>
       <c r="B43" t="n">
-        <v>80252</v>
+        <v>76945</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5406,25 +5407,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5434,10 +5435,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>428387</v>
+        <v>428248</v>
       </c>
       <c r="R43" t="n">
-        <v>6233322</v>
+        <v>6233241</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5496,10 +5497,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121471839</v>
+        <v>121471824</v>
       </c>
       <c r="B44" t="n">
-        <v>94584</v>
+        <v>76945</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5508,25 +5509,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2671</v>
+        <v>1342</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5536,10 +5537,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>428184</v>
+        <v>428288</v>
       </c>
       <c r="R44" t="n">
-        <v>6233240</v>
+        <v>6233325</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5598,10 +5599,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121471852</v>
+        <v>121471907</v>
       </c>
       <c r="B45" t="n">
-        <v>80252</v>
+        <v>76945</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5610,25 +5611,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5638,10 +5639,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>428311</v>
+        <v>428375</v>
       </c>
       <c r="R45" t="n">
-        <v>6233183</v>
+        <v>6233092</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5668,12 +5669,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5700,7 +5701,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121471845</v>
+        <v>121471808</v>
       </c>
       <c r="B46" t="n">
         <v>80252</v>
@@ -5740,10 +5741,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>428248</v>
+        <v>428350</v>
       </c>
       <c r="R46" t="n">
-        <v>6233242</v>
+        <v>6233316</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5802,10 +5803,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121471695</v>
+        <v>121471842</v>
       </c>
       <c r="B47" t="n">
-        <v>80239</v>
+        <v>94596</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5818,21 +5819,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5842,10 +5843,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>428053</v>
+        <v>428221</v>
       </c>
       <c r="R47" t="n">
-        <v>6233336</v>
+        <v>6233212</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5872,12 +5873,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5904,10 +5905,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121471544</v>
+        <v>121471822</v>
       </c>
       <c r="B48" t="n">
-        <v>94595</v>
+        <v>94596</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5944,10 +5945,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>428219</v>
+        <v>428288</v>
       </c>
       <c r="R48" t="n">
-        <v>6233278</v>
+        <v>6233325</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5974,12 +5975,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6006,10 +6007,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121471806</v>
+        <v>121471925</v>
       </c>
       <c r="B49" t="n">
-        <v>80252</v>
+        <v>94598</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6018,25 +6019,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1144</v>
+        <v>2666</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6046,10 +6047,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>428325</v>
+        <v>428076</v>
       </c>
       <c r="R49" t="n">
-        <v>6233291</v>
+        <v>6233382</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6076,12 +6077,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6108,10 +6109,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121471908</v>
+        <v>121471926</v>
       </c>
       <c r="B50" t="n">
-        <v>74606</v>
+        <v>94390</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6120,25 +6121,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1118</v>
+        <v>2779</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6148,10 +6149,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>428377</v>
+        <v>428073</v>
       </c>
       <c r="R50" t="n">
-        <v>6233090</v>
+        <v>6233383</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6210,10 +6211,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121471922</v>
+        <v>121471683</v>
       </c>
       <c r="B51" t="n">
-        <v>76945</v>
+        <v>94585</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6222,25 +6223,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1342</v>
+        <v>2671</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6250,10 +6251,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>428091</v>
+        <v>428278</v>
       </c>
       <c r="R51" t="n">
-        <v>6233385</v>
+        <v>6233417</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6280,12 +6281,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6312,7 +6313,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121471866</v>
+        <v>121471941</v>
       </c>
       <c r="B52" t="n">
         <v>80239</v>
@@ -6352,10 +6353,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>428442</v>
+        <v>428046</v>
       </c>
       <c r="R52" t="n">
-        <v>6233170</v>
+        <v>6233350</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6382,12 +6383,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6414,10 +6415,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121471856</v>
+        <v>121471859</v>
       </c>
       <c r="B53" t="n">
-        <v>76945</v>
+        <v>80239</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6426,25 +6427,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6454,10 +6455,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>428360</v>
+        <v>428404</v>
       </c>
       <c r="R53" t="n">
-        <v>6233266</v>
+        <v>6233275</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6516,10 +6517,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121471864</v>
+        <v>121471856</v>
       </c>
       <c r="B54" t="n">
-        <v>94584</v>
+        <v>76945</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6528,25 +6529,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2671</v>
+        <v>1342</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6556,10 +6557,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>428410</v>
+        <v>428360</v>
       </c>
       <c r="R54" t="n">
-        <v>6233214</v>
+        <v>6233266</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6618,10 +6619,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121471817</v>
+        <v>121471915</v>
       </c>
       <c r="B55" t="n">
-        <v>74694</v>
+        <v>96770</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6634,21 +6635,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6439</v>
+        <v>2604</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6658,10 +6659,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>428312</v>
+        <v>428281</v>
       </c>
       <c r="R55" t="n">
-        <v>6233323</v>
+        <v>6233082</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6688,12 +6689,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6720,10 +6721,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121471815</v>
+        <v>121471937</v>
       </c>
       <c r="B56" t="n">
-        <v>80409</v>
+        <v>96722</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6732,25 +6733,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1557</v>
+        <v>2606</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Röd pysslinglav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Thelopsis rubella</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Nyl.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6760,10 +6761,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>428333</v>
+        <v>428062</v>
       </c>
       <c r="R56" t="n">
-        <v>6233339</v>
+        <v>6233301</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6790,12 +6791,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6822,10 +6823,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121471801</v>
+        <v>121471860</v>
       </c>
       <c r="B57" t="n">
-        <v>80252</v>
+        <v>96722</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6834,25 +6835,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6862,10 +6863,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>428370</v>
+        <v>428404</v>
       </c>
       <c r="R57" t="n">
-        <v>6233336</v>
+        <v>6233275</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6924,10 +6925,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121471895</v>
+        <v>121471810</v>
       </c>
       <c r="B58" t="n">
-        <v>80239</v>
+        <v>80252</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6936,25 +6937,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6964,10 +6965,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>428355</v>
+        <v>428347</v>
       </c>
       <c r="R58" t="n">
-        <v>6233123</v>
+        <v>6233326</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6994,12 +6995,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7026,10 +7027,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121471831</v>
+        <v>121471804</v>
       </c>
       <c r="B59" t="n">
-        <v>80252</v>
+        <v>76945</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7038,25 +7039,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7066,10 +7067,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>428145</v>
+        <v>428335</v>
       </c>
       <c r="R59" t="n">
-        <v>6233315</v>
+        <v>6233286</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7128,10 +7129,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121471691</v>
+        <v>121471854</v>
       </c>
       <c r="B60" t="n">
-        <v>96721</v>
+        <v>96722</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7168,10 +7169,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>428128</v>
+        <v>428302</v>
       </c>
       <c r="R60" t="n">
-        <v>6233385</v>
+        <v>6233177</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7198,12 +7199,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7230,10 +7231,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121471941</v>
+        <v>121471802</v>
       </c>
       <c r="B61" t="n">
-        <v>80239</v>
+        <v>94585</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7246,21 +7247,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>230185</v>
+        <v>2671</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7270,10 +7271,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>428046</v>
+        <v>428332</v>
       </c>
       <c r="R61" t="n">
-        <v>6233350</v>
+        <v>6233287</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7300,12 +7301,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7332,10 +7333,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121471796</v>
+        <v>121471851</v>
       </c>
       <c r="B62" t="n">
-        <v>80252</v>
+        <v>78860</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7344,25 +7345,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1144</v>
+        <v>6459</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7372,10 +7373,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>428390</v>
+        <v>428293</v>
       </c>
       <c r="R62" t="n">
-        <v>6233312</v>
+        <v>6233170</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7434,10 +7435,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121471819</v>
+        <v>121471543</v>
       </c>
       <c r="B63" t="n">
-        <v>94595</v>
+        <v>80239</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7450,21 +7451,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7474,10 +7475,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>428304</v>
+        <v>428209</v>
       </c>
       <c r="R63" t="n">
-        <v>6233306</v>
+        <v>6233279</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7504,12 +7505,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7536,10 +7537,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121471851</v>
+        <v>121471922</v>
       </c>
       <c r="B64" t="n">
-        <v>78860</v>
+        <v>76945</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7548,25 +7549,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6459</v>
+        <v>1342</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7576,10 +7577,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>428293</v>
+        <v>428091</v>
       </c>
       <c r="R64" t="n">
-        <v>6233170</v>
+        <v>6233385</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7606,12 +7607,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7638,10 +7639,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121471683</v>
+        <v>121471847</v>
       </c>
       <c r="B65" t="n">
-        <v>94584</v>
+        <v>76945</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7650,25 +7651,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2671</v>
+        <v>1342</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7678,10 +7679,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>428278</v>
+        <v>428300</v>
       </c>
       <c r="R65" t="n">
-        <v>6233417</v>
+        <v>6233125</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7708,12 +7709,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7740,53 +7741,50 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121471875</v>
+        <v>121471873</v>
       </c>
       <c r="B66" t="n">
-        <v>80252</v>
+        <v>74560</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1144</v>
+        <v>1116</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>428340</v>
+        <v>428301</v>
       </c>
       <c r="R66" t="n">
-        <v>6233229</v>
+        <v>6233171</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7821,21 +7819,11 @@
           <t>2024-11-21</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>kollekt</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
-      </c>
-      <c r="AF66" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG66" t="b">
         <v>0</v>
@@ -7855,10 +7843,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121471936</v>
+        <v>121471834</v>
       </c>
       <c r="B67" t="n">
-        <v>94605</v>
+        <v>80252</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7867,25 +7855,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1080</v>
+        <v>1144</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7895,10 +7883,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>428079</v>
+        <v>428137</v>
       </c>
       <c r="R67" t="n">
-        <v>6233262</v>
+        <v>6233320</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7925,12 +7913,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7957,10 +7945,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121471829</v>
+        <v>121471881</v>
       </c>
       <c r="B68" t="n">
-        <v>80252</v>
+        <v>78404</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7969,25 +7957,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1144</v>
+        <v>924</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7997,10 +7985,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>428147</v>
+        <v>428445</v>
       </c>
       <c r="R68" t="n">
-        <v>6233304</v>
+        <v>6233151</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8059,10 +8047,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121471814</v>
+        <v>121471696</v>
       </c>
       <c r="B69" t="n">
-        <v>80252</v>
+        <v>96722</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8071,25 +8059,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8099,10 +8087,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>428331</v>
+        <v>428054</v>
       </c>
       <c r="R69" t="n">
-        <v>6233339</v>
+        <v>6233337</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8129,12 +8117,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8161,10 +8149,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121471825</v>
+        <v>121471532</v>
       </c>
       <c r="B70" t="n">
-        <v>80239</v>
+        <v>94596</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8177,21 +8165,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8201,10 +8189,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>428233</v>
+        <v>428133</v>
       </c>
       <c r="R70" t="n">
-        <v>6233332</v>
+        <v>6233219</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8231,12 +8219,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8263,10 +8251,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121471855</v>
+        <v>121471846</v>
       </c>
       <c r="B71" t="n">
-        <v>94389</v>
+        <v>80239</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8279,21 +8267,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2779</v>
+        <v>230185</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8303,10 +8291,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>428365</v>
+        <v>428241</v>
       </c>
       <c r="R71" t="n">
-        <v>6233269</v>
+        <v>6233222</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8365,10 +8353,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121471533</v>
+        <v>121471853</v>
       </c>
       <c r="B72" t="n">
-        <v>80239</v>
+        <v>76945</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8377,25 +8365,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8405,10 +8393,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>428144</v>
+        <v>428311</v>
       </c>
       <c r="R72" t="n">
-        <v>6233229</v>
+        <v>6233183</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8435,12 +8423,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8467,7 +8455,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121471874</v>
+        <v>121471694</v>
       </c>
       <c r="B73" t="n">
         <v>80252</v>
@@ -8507,10 +8495,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>428375</v>
+        <v>428125</v>
       </c>
       <c r="R73" t="n">
-        <v>6233151</v>
+        <v>6233379</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8537,12 +8525,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8569,10 +8557,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121471692</v>
+        <v>121471882</v>
       </c>
       <c r="B74" t="n">
-        <v>94595</v>
+        <v>74606</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8581,25 +8569,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2667</v>
+        <v>1118</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8609,10 +8597,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>428126</v>
+        <v>428445</v>
       </c>
       <c r="R74" t="n">
-        <v>6233380</v>
+        <v>6233151</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8639,12 +8627,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8671,10 +8659,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121471696</v>
+        <v>121471697</v>
       </c>
       <c r="B75" t="n">
-        <v>96721</v>
+        <v>74696</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8687,21 +8675,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2606</v>
+        <v>306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8711,10 +8699,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>428054</v>
+        <v>428043</v>
       </c>
       <c r="R75" t="n">
-        <v>6233337</v>
+        <v>6233298</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8773,10 +8761,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121471688</v>
+        <v>121471693</v>
       </c>
       <c r="B76" t="n">
-        <v>96721</v>
+        <v>94585</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8789,21 +8777,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2606</v>
+        <v>2671</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8813,10 +8801,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>428159</v>
+        <v>428125</v>
       </c>
       <c r="R76" t="n">
-        <v>6233394</v>
+        <v>6233379</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8875,10 +8863,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121471685</v>
+        <v>121471689</v>
       </c>
       <c r="B77" t="n">
-        <v>80252</v>
+        <v>94596</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8887,25 +8875,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8915,10 +8903,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>428228</v>
+        <v>428161</v>
       </c>
       <c r="R77" t="n">
-        <v>6233391</v>
+        <v>6233396</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8977,10 +8965,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121471818</v>
+        <v>121471812</v>
       </c>
       <c r="B78" t="n">
-        <v>96721</v>
+        <v>94390</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8993,21 +8981,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2606</v>
+        <v>2779</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9017,10 +9005,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>428307</v>
+        <v>428331</v>
       </c>
       <c r="R78" t="n">
-        <v>6233311</v>
+        <v>6233335</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9079,10 +9067,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121471827</v>
+        <v>121471904</v>
       </c>
       <c r="B79" t="n">
-        <v>94595</v>
+        <v>78404</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9091,25 +9079,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2667</v>
+        <v>924</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9119,10 +9107,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>428185</v>
+        <v>428387</v>
       </c>
       <c r="R79" t="n">
-        <v>6233287</v>
+        <v>6233098</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9149,12 +9137,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9181,10 +9169,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121471904</v>
+        <v>121471801</v>
       </c>
       <c r="B80" t="n">
-        <v>78404</v>
+        <v>80252</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9193,25 +9181,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>924</v>
+        <v>1144</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9221,10 +9209,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>428387</v>
+        <v>428370</v>
       </c>
       <c r="R80" t="n">
-        <v>6233098</v>
+        <v>6233336</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9251,12 +9239,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9283,10 +9271,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121471541</v>
+        <v>121471535</v>
       </c>
       <c r="B81" t="n">
-        <v>80239</v>
+        <v>76945</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9295,25 +9283,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9323,10 +9311,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>428209</v>
+        <v>428160</v>
       </c>
       <c r="R81" t="n">
-        <v>6233184</v>
+        <v>6233209</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9385,10 +9373,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121471919</v>
+        <v>121471910</v>
       </c>
       <c r="B82" t="n">
-        <v>80252</v>
+        <v>76945</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9397,25 +9385,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9425,10 +9413,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>428106</v>
+        <v>428377</v>
       </c>
       <c r="R82" t="n">
-        <v>6233304</v>
+        <v>6233090</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9487,10 +9475,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121471925</v>
+        <v>121471927</v>
       </c>
       <c r="B83" t="n">
-        <v>94597</v>
+        <v>76945</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9499,25 +9487,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2666</v>
+        <v>1342</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9527,10 +9515,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>428076</v>
+        <v>428074</v>
       </c>
       <c r="R83" t="n">
-        <v>6233382</v>
+        <v>6233297</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9589,10 +9577,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121471867</v>
+        <v>121471530</v>
       </c>
       <c r="B84" t="n">
-        <v>76945</v>
+        <v>80239</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9601,25 +9589,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9629,10 +9617,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>428442</v>
+        <v>428111</v>
       </c>
       <c r="R84" t="n">
-        <v>6233170</v>
+        <v>6233222</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9659,12 +9647,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9691,10 +9679,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121471859</v>
+        <v>121471878</v>
       </c>
       <c r="B85" t="n">
-        <v>80239</v>
+        <v>96770</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9707,21 +9695,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>230185</v>
+        <v>2604</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9731,10 +9719,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>428404</v>
+        <v>428445</v>
       </c>
       <c r="R85" t="n">
-        <v>6233275</v>
+        <v>6233151</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9793,10 +9781,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121471943</v>
+        <v>121471688</v>
       </c>
       <c r="B86" t="n">
-        <v>96721</v>
+        <v>96722</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9833,10 +9821,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>428034</v>
+        <v>428159</v>
       </c>
       <c r="R86" t="n">
-        <v>6233348</v>
+        <v>6233394</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9863,12 +9851,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9895,10 +9883,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121471824</v>
+        <v>121471861</v>
       </c>
       <c r="B87" t="n">
-        <v>76945</v>
+        <v>94596</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9907,25 +9895,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1342</v>
+        <v>2667</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9935,10 +9923,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>428288</v>
+        <v>428404</v>
       </c>
       <c r="R87" t="n">
-        <v>6233325</v>
+        <v>6233275</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9997,10 +9985,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121471937</v>
+        <v>121471803</v>
       </c>
       <c r="B88" t="n">
-        <v>96721</v>
+        <v>80252</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10009,25 +9997,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10037,10 +10025,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>428062</v>
+        <v>428334</v>
       </c>
       <c r="R88" t="n">
-        <v>6233301</v>
+        <v>6233284</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10067,12 +10055,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10099,10 +10087,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121471532</v>
+        <v>121471814</v>
       </c>
       <c r="B89" t="n">
-        <v>94595</v>
+        <v>80252</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10111,25 +10099,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10139,10 +10127,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>428133</v>
+        <v>428331</v>
       </c>
       <c r="R89" t="n">
-        <v>6233219</v>
+        <v>6233339</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10169,12 +10157,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10201,10 +10189,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121471540</v>
+        <v>121471903</v>
       </c>
       <c r="B90" t="n">
-        <v>96721</v>
+        <v>76945</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10213,25 +10201,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10241,10 +10229,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>428227</v>
+        <v>428385</v>
       </c>
       <c r="R90" t="n">
-        <v>6233132</v>
+        <v>6233097</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10271,12 +10259,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10303,10 +10291,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121471534</v>
+        <v>121471544</v>
       </c>
       <c r="B91" t="n">
-        <v>96721</v>
+        <v>94596</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10319,21 +10307,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10343,10 +10331,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>428147</v>
+        <v>428219</v>
       </c>
       <c r="R91" t="n">
-        <v>6233224</v>
+        <v>6233278</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10405,10 +10393,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121471802</v>
+        <v>121471939</v>
       </c>
       <c r="B92" t="n">
-        <v>94584</v>
+        <v>94596</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10421,21 +10409,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10445,10 +10433,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>428332</v>
+        <v>428046</v>
       </c>
       <c r="R92" t="n">
-        <v>6233287</v>
+        <v>6233296</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10475,12 +10463,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10507,10 +10495,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121471863</v>
+        <v>121471796</v>
       </c>
       <c r="B93" t="n">
-        <v>96721</v>
+        <v>80252</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10519,25 +10507,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10547,10 +10535,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>428411</v>
+        <v>428390</v>
       </c>
       <c r="R93" t="n">
-        <v>6233213</v>
+        <v>6233312</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10609,10 +10597,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121471915</v>
+        <v>121471928</v>
       </c>
       <c r="B94" t="n">
-        <v>96769</v>
+        <v>80252</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10621,25 +10609,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2604</v>
+        <v>1144</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10649,10 +10637,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>428281</v>
+        <v>428075</v>
       </c>
       <c r="R94" t="n">
-        <v>6233082</v>
+        <v>6233294</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10711,10 +10699,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121471869</v>
+        <v>121471849</v>
       </c>
       <c r="B95" t="n">
-        <v>96721</v>
+        <v>80252</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10723,25 +10711,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10751,10 +10739,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>428354</v>
+        <v>428299</v>
       </c>
       <c r="R95" t="n">
-        <v>6233242</v>
+        <v>6233126</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10813,7 +10801,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121471849</v>
+        <v>121471874</v>
       </c>
       <c r="B96" t="n">
         <v>80252</v>
@@ -10853,10 +10841,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>428299</v>
+        <v>428375</v>
       </c>
       <c r="R96" t="n">
-        <v>6233126</v>
+        <v>6233151</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10915,10 +10903,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121471924</v>
+        <v>121471809</v>
       </c>
       <c r="B97" t="n">
-        <v>80239</v>
+        <v>74560</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10927,25 +10915,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>230185</v>
+        <v>1116</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10955,10 +10943,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>428097</v>
+        <v>428352</v>
       </c>
       <c r="R97" t="n">
-        <v>6233382</v>
+        <v>6233315</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10985,12 +10973,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11017,10 +11005,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121471811</v>
+        <v>121471923</v>
       </c>
       <c r="B98" t="n">
-        <v>76945</v>
+        <v>80252</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11029,25 +11017,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11057,10 +11045,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>428349</v>
+        <v>428091</v>
       </c>
       <c r="R98" t="n">
-        <v>6233325</v>
+        <v>6233386</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11087,12 +11075,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11119,10 +11107,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121471861</v>
+        <v>121471805</v>
       </c>
       <c r="B99" t="n">
-        <v>94595</v>
+        <v>80252</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11131,25 +11119,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11159,10 +11147,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>428404</v>
+        <v>428333</v>
       </c>
       <c r="R99" t="n">
-        <v>6233275</v>
+        <v>6233283</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11221,10 +11209,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121471903</v>
+        <v>121471924</v>
       </c>
       <c r="B100" t="n">
-        <v>76945</v>
+        <v>80239</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11233,25 +11221,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11261,10 +11249,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>428385</v>
+        <v>428097</v>
       </c>
       <c r="R100" t="n">
-        <v>6233097</v>
+        <v>6233382</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11323,10 +11311,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121471933</v>
+        <v>121471695</v>
       </c>
       <c r="B101" t="n">
-        <v>94584</v>
+        <v>80239</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11339,21 +11327,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2671</v>
+        <v>230185</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11363,10 +11351,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>428090</v>
+        <v>428053</v>
       </c>
       <c r="R101" t="n">
-        <v>6233309</v>
+        <v>6233336</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11393,12 +11381,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11425,10 +11413,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121471836</v>
+        <v>121471917</v>
       </c>
       <c r="B102" t="n">
-        <v>94584</v>
+        <v>80239</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11441,21 +11429,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2671</v>
+        <v>230185</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11465,10 +11453,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>428145</v>
+        <v>428284</v>
       </c>
       <c r="R102" t="n">
-        <v>6233244</v>
+        <v>6233109</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11495,12 +11483,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11527,10 +11515,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121471912</v>
+        <v>121471863</v>
       </c>
       <c r="B103" t="n">
-        <v>78404</v>
+        <v>96722</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11539,25 +11527,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>924</v>
+        <v>2606</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11567,10 +11555,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>428351</v>
+        <v>428411</v>
       </c>
       <c r="R103" t="n">
-        <v>6233082</v>
+        <v>6233213</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11597,12 +11585,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11629,10 +11617,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121471833</v>
+        <v>121471799</v>
       </c>
       <c r="B104" t="n">
-        <v>80239</v>
+        <v>94585</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11645,21 +11633,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>230185</v>
+        <v>2671</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11669,10 +11657,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>428139</v>
+        <v>428389</v>
       </c>
       <c r="R104" t="n">
-        <v>6233315</v>
+        <v>6233324</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11731,10 +11719,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121471837</v>
+        <v>121471914</v>
       </c>
       <c r="B105" t="n">
-        <v>80239</v>
+        <v>94596</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11747,21 +11735,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11771,10 +11759,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>428145</v>
+        <v>428318</v>
       </c>
       <c r="R105" t="n">
-        <v>6233244</v>
+        <v>6233075</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11801,12 +11789,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11833,10 +11821,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121471809</v>
+        <v>121471817</v>
       </c>
       <c r="B106" t="n">
-        <v>74560</v>
+        <v>74694</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11845,25 +11833,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1116</v>
+        <v>6439</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11873,10 +11861,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>428352</v>
+        <v>428312</v>
       </c>
       <c r="R106" t="n">
-        <v>6233315</v>
+        <v>6233323</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11935,7 +11923,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121471917</v>
+        <v>121471866</v>
       </c>
       <c r="B107" t="n">
         <v>80239</v>
@@ -11975,10 +11963,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>428284</v>
+        <v>428442</v>
       </c>
       <c r="R107" t="n">
-        <v>6233109</v>
+        <v>6233170</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12005,12 +11993,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12037,7 +12025,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121471846</v>
+        <v>121471850</v>
       </c>
       <c r="B108" t="n">
         <v>80239</v>
@@ -12077,10 +12065,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>428241</v>
+        <v>428293</v>
       </c>
       <c r="R108" t="n">
-        <v>6233222</v>
+        <v>6233170</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12139,10 +12127,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121471693</v>
+        <v>121471935</v>
       </c>
       <c r="B109" t="n">
-        <v>94584</v>
+        <v>80239</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12155,21 +12143,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2671</v>
+        <v>230185</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12179,10 +12167,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>428125</v>
+        <v>428097</v>
       </c>
       <c r="R109" t="n">
-        <v>6233379</v>
+        <v>6233286</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12209,12 +12197,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12241,10 +12229,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121471920</v>
+        <v>121471879</v>
       </c>
       <c r="B110" t="n">
-        <v>91108</v>
+        <v>76945</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12257,21 +12245,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2023</v>
+        <v>1342</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sydlig sotticka</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ischnoderma resinosum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Schrad.) P.Karst.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12281,10 +12269,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>428095</v>
+        <v>428445</v>
       </c>
       <c r="R110" t="n">
-        <v>6233349</v>
+        <v>6233151</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12311,12 +12299,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12343,10 +12331,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121471542</v>
+        <v>121471827</v>
       </c>
       <c r="B111" t="n">
-        <v>80252</v>
+        <v>94596</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12355,25 +12343,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12383,10 +12371,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>428198</v>
+        <v>428185</v>
       </c>
       <c r="R111" t="n">
-        <v>6233249</v>
+        <v>6233287</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12413,12 +12401,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12445,10 +12433,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121471684</v>
+        <v>121471816</v>
       </c>
       <c r="B112" t="n">
-        <v>80409</v>
+        <v>96770</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12457,25 +12445,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1557</v>
+        <v>2604</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Röd pysslinglav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Thelopsis rubella</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Nyl.</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12485,10 +12473,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>428227</v>
+        <v>428317</v>
       </c>
       <c r="R112" t="n">
-        <v>6233392</v>
+        <v>6233324</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12515,12 +12503,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12547,10 +12535,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121471882</v>
+        <v>121471839</v>
       </c>
       <c r="B113" t="n">
-        <v>74606</v>
+        <v>94585</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12559,25 +12547,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1118</v>
+        <v>2671</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12587,10 +12575,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>428445</v>
+        <v>428184</v>
       </c>
       <c r="R113" t="n">
-        <v>6233151</v>
+        <v>6233240</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12649,10 +12637,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121471798</v>
+        <v>121471919</v>
       </c>
       <c r="B114" t="n">
-        <v>96721</v>
+        <v>80252</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12661,25 +12649,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12689,10 +12677,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>428387</v>
+        <v>428106</v>
       </c>
       <c r="R114" t="n">
-        <v>6233326</v>
+        <v>6233304</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12719,12 +12707,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12751,10 +12739,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121471938</v>
+        <v>121471542</v>
       </c>
       <c r="B115" t="n">
-        <v>80239</v>
+        <v>80252</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12763,25 +12751,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12791,10 +12779,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>428062</v>
+        <v>428198</v>
       </c>
       <c r="R115" t="n">
-        <v>6233301</v>
+        <v>6233249</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12821,12 +12809,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12853,7 +12841,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121471844</v>
+        <v>121471911</v>
       </c>
       <c r="B116" t="n">
         <v>76945</v>
@@ -12893,10 +12881,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>428248</v>
+        <v>428352</v>
       </c>
       <c r="R116" t="n">
-        <v>6233241</v>
+        <v>6233082</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12923,12 +12911,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12955,10 +12943,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121471871</v>
+        <v>121471867</v>
       </c>
       <c r="B117" t="n">
-        <v>80239</v>
+        <v>76945</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12967,25 +12955,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12995,10 +12983,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>428302</v>
+        <v>428442</v>
       </c>
       <c r="R117" t="n">
-        <v>6233176</v>
+        <v>6233170</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13057,10 +13045,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121471538</v>
+        <v>121471807</v>
       </c>
       <c r="B118" t="n">
-        <v>80239</v>
+        <v>76945</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13069,25 +13057,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13097,10 +13085,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>428166</v>
+        <v>428327</v>
       </c>
       <c r="R118" t="n">
-        <v>6233198</v>
+        <v>6233292</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13127,12 +13115,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13159,10 +13147,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121471873</v>
+        <v>121471913</v>
       </c>
       <c r="B119" t="n">
-        <v>74560</v>
+        <v>76945</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13175,21 +13163,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1116</v>
+        <v>1342</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13199,10 +13187,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>428301</v>
+        <v>428342</v>
       </c>
       <c r="R119" t="n">
-        <v>6233171</v>
+        <v>6233082</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13229,12 +13217,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13261,10 +13249,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121471868</v>
+        <v>121471541</v>
       </c>
       <c r="B120" t="n">
-        <v>94595</v>
+        <v>80239</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13277,21 +13265,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13301,10 +13289,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>428347</v>
+        <v>428209</v>
       </c>
       <c r="R120" t="n">
-        <v>6233241</v>
+        <v>6233184</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13331,12 +13319,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13363,10 +13351,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121471940</v>
+        <v>121471690</v>
       </c>
       <c r="B121" t="n">
-        <v>94605</v>
+        <v>80239</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13379,21 +13367,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1080</v>
+        <v>230185</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13403,10 +13391,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>428037</v>
+        <v>428161</v>
       </c>
       <c r="R121" t="n">
-        <v>6233291</v>
+        <v>6233396</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13433,12 +13421,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13465,10 +13453,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121471934</v>
+        <v>121471871</v>
       </c>
       <c r="B122" t="n">
-        <v>94389</v>
+        <v>80239</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13481,21 +13469,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2779</v>
+        <v>230185</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13505,10 +13493,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>428090</v>
+        <v>428302</v>
       </c>
       <c r="R122" t="n">
-        <v>6233309</v>
+        <v>6233176</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13535,12 +13523,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13567,7 +13555,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121471804</v>
+        <v>121471909</v>
       </c>
       <c r="B123" t="n">
         <v>76945</v>
@@ -13607,10 +13595,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>428335</v>
+        <v>428373</v>
       </c>
       <c r="R123" t="n">
-        <v>6233286</v>
+        <v>6233088</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13637,12 +13625,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13669,10 +13657,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121471842</v>
+        <v>121471901</v>
       </c>
       <c r="B124" t="n">
-        <v>94595</v>
+        <v>76945</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13681,25 +13669,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13709,10 +13697,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>428221</v>
+        <v>428390</v>
       </c>
       <c r="R124" t="n">
-        <v>6233212</v>
+        <v>6233099</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13739,12 +13727,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13771,10 +13759,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121471858</v>
+        <v>121471868</v>
       </c>
       <c r="B125" t="n">
-        <v>80252</v>
+        <v>94596</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13783,25 +13771,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13811,10 +13799,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>428372</v>
+        <v>428347</v>
       </c>
       <c r="R125" t="n">
-        <v>6233270</v>
+        <v>6233241</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13873,10 +13861,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121471944</v>
+        <v>121471813</v>
       </c>
       <c r="B126" t="n">
-        <v>94595</v>
+        <v>94585</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13889,21 +13877,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13913,10 +13901,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>428034</v>
+        <v>428332</v>
       </c>
       <c r="R126" t="n">
-        <v>6233348</v>
+        <v>6233341</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13943,12 +13931,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13975,10 +13963,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121471805</v>
+        <v>121471940</v>
       </c>
       <c r="B127" t="n">
-        <v>80252</v>
+        <v>94606</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13987,25 +13975,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1144</v>
+        <v>1080</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14015,10 +14003,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>428333</v>
+        <v>428037</v>
       </c>
       <c r="R127" t="n">
-        <v>6233283</v>
+        <v>6233291</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14045,12 +14033,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14077,50 +14065,53 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121471862</v>
+        <v>121471875</v>
       </c>
       <c r="B128" t="n">
-        <v>80239</v>
+        <v>80252</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>428411</v>
+        <v>428340</v>
       </c>
       <c r="R128" t="n">
-        <v>6233213</v>
+        <v>6233229</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14155,11 +14146,21 @@
           <t>2024-11-21</t>
         </is>
       </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>kollekt</t>
+        </is>
+      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
       <c r="AE128" t="b">
         <v>0</v>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG128" t="b">
         <v>0</v>
@@ -14179,10 +14180,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121471689</v>
+        <v>121471845</v>
       </c>
       <c r="B129" t="n">
-        <v>94595</v>
+        <v>80252</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14191,25 +14192,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14219,10 +14220,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>428161</v>
+        <v>428248</v>
       </c>
       <c r="R129" t="n">
-        <v>6233396</v>
+        <v>6233242</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14249,12 +14250,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14281,10 +14282,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121471812</v>
+        <v>121471826</v>
       </c>
       <c r="B130" t="n">
-        <v>94389</v>
+        <v>78860</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14297,21 +14298,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2779</v>
+        <v>6459</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14321,10 +14322,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>428331</v>
+        <v>428228</v>
       </c>
       <c r="R130" t="n">
-        <v>6233335</v>
+        <v>6233340</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14383,10 +14384,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121471826</v>
+        <v>121471811</v>
       </c>
       <c r="B131" t="n">
-        <v>78860</v>
+        <v>76945</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14395,25 +14396,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6459</v>
+        <v>1342</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14423,10 +14424,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>428228</v>
+        <v>428349</v>
       </c>
       <c r="R131" t="n">
-        <v>6233340</v>
+        <v>6233325</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14485,10 +14486,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121471816</v>
+        <v>121471798</v>
       </c>
       <c r="B132" t="n">
-        <v>96769</v>
+        <v>96722</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14501,21 +14502,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2604</v>
+        <v>2606</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14525,10 +14526,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>428317</v>
+        <v>428387</v>
       </c>
       <c r="R132" t="n">
-        <v>6233324</v>
+        <v>6233326</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14587,10 +14588,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121471853</v>
+        <v>121471855</v>
       </c>
       <c r="B133" t="n">
-        <v>76945</v>
+        <v>94390</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14599,25 +14600,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1342</v>
+        <v>2779</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14627,10 +14628,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>428311</v>
+        <v>428365</v>
       </c>
       <c r="R133" t="n">
-        <v>6233183</v>
+        <v>6233269</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14689,10 +14690,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121471808</v>
+        <v>121471877</v>
       </c>
       <c r="B134" t="n">
-        <v>80252</v>
+        <v>94596</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14701,25 +14702,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14729,10 +14730,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>428350</v>
+        <v>428445</v>
       </c>
       <c r="R134" t="n">
-        <v>6233316</v>
+        <v>6233151</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14791,10 +14792,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121471840</v>
+        <v>121471858</v>
       </c>
       <c r="B135" t="n">
-        <v>78984</v>
+        <v>80252</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14803,25 +14804,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6431</v>
+        <v>1144</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14831,10 +14832,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>428183</v>
+        <v>428372</v>
       </c>
       <c r="R135" t="n">
-        <v>6233239</v>
+        <v>6233270</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14893,10 +14894,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121471820</v>
+        <v>121471545</v>
       </c>
       <c r="B136" t="n">
-        <v>94389</v>
+        <v>80252</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14905,25 +14906,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2779</v>
+        <v>1144</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14933,10 +14934,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>428304</v>
+        <v>428172</v>
       </c>
       <c r="R136" t="n">
-        <v>6233306</v>
+        <v>6233315</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14963,12 +14964,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14995,10 +14996,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121471881</v>
+        <v>121471800</v>
       </c>
       <c r="B137" t="n">
-        <v>78404</v>
+        <v>80252</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15007,25 +15008,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>924</v>
+        <v>1144</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15035,10 +15036,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>428445</v>
+        <v>428387</v>
       </c>
       <c r="R137" t="n">
-        <v>6233151</v>
+        <v>6233322</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15097,10 +15098,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121471923</v>
+        <v>121471862</v>
       </c>
       <c r="B138" t="n">
-        <v>80252</v>
+        <v>80239</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15109,25 +15110,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15137,10 +15138,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>428091</v>
+        <v>428411</v>
       </c>
       <c r="R138" t="n">
-        <v>6233386</v>
+        <v>6233213</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15167,12 +15168,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15199,10 +15200,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121471694</v>
+        <v>121471533</v>
       </c>
       <c r="B139" t="n">
-        <v>80252</v>
+        <v>80239</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15211,25 +15212,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15239,10 +15240,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>428125</v>
+        <v>428144</v>
       </c>
       <c r="R139" t="n">
-        <v>6233379</v>
+        <v>6233229</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15301,10 +15302,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121471537</v>
+        <v>121471943</v>
       </c>
       <c r="B140" t="n">
-        <v>96721</v>
+        <v>96722</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15341,10 +15342,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>428163</v>
+        <v>428034</v>
       </c>
       <c r="R140" t="n">
-        <v>6233193</v>
+        <v>6233348</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15371,12 +15372,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15403,10 +15404,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121471939</v>
+        <v>121471686</v>
       </c>
       <c r="B141" t="n">
-        <v>94595</v>
+        <v>80252</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15415,25 +15416,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15443,10 +15444,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>428046</v>
+        <v>428187</v>
       </c>
       <c r="R141" t="n">
-        <v>6233296</v>
+        <v>6233403</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15473,12 +15474,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15505,10 +15506,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121471828</v>
+        <v>121471876</v>
       </c>
       <c r="B142" t="n">
-        <v>80239</v>
+        <v>80282</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15521,21 +15522,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>230185</v>
+        <v>1223</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Rikfruktig blemlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Phlyctis agelaea</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Flot.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15545,10 +15546,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>428185</v>
+        <v>428446</v>
       </c>
       <c r="R142" t="n">
-        <v>6233289</v>
+        <v>6233151</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15589,7 +15590,6 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15608,10 +15608,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121471850</v>
+        <v>121471539</v>
       </c>
       <c r="B143" t="n">
-        <v>80239</v>
+        <v>94585</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15624,21 +15624,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>230185</v>
+        <v>2671</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15648,10 +15648,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>428293</v>
+        <v>428262</v>
       </c>
       <c r="R143" t="n">
-        <v>6233170</v>
+        <v>6233134</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15678,12 +15678,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15710,10 +15710,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121471847</v>
+        <v>121471692</v>
       </c>
       <c r="B144" t="n">
-        <v>76945</v>
+        <v>94596</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15722,25 +15722,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1342</v>
+        <v>2667</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15750,10 +15750,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>428300</v>
+        <v>428126</v>
       </c>
       <c r="R144" t="n">
-        <v>6233125</v>
+        <v>6233380</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15780,12 +15780,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15812,10 +15812,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121471841</v>
+        <v>121471818</v>
       </c>
       <c r="B145" t="n">
-        <v>96721</v>
+        <v>96722</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15852,10 +15852,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>428221</v>
+        <v>428307</v>
       </c>
       <c r="R145" t="n">
-        <v>6233212</v>
+        <v>6233311</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15914,10 +15914,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121471879</v>
+        <v>121471835</v>
       </c>
       <c r="B146" t="n">
-        <v>76945</v>
+        <v>96722</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15926,25 +15926,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15954,10 +15954,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>428445</v>
+        <v>428145</v>
       </c>
       <c r="R146" t="n">
-        <v>6233151</v>
+        <v>6233244</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16016,10 +16016,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121471927</v>
+        <v>121471930</v>
       </c>
       <c r="B147" t="n">
-        <v>76945</v>
+        <v>74606</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16032,21 +16032,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1342</v>
+        <v>1118</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16056,10 +16056,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>428074</v>
+        <v>428078</v>
       </c>
       <c r="R147" t="n">
-        <v>6233297</v>
+        <v>6233294</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16118,10 +16118,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121471876</v>
+        <v>121471837</v>
       </c>
       <c r="B148" t="n">
-        <v>80282</v>
+        <v>80239</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16134,21 +16134,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1223</v>
+        <v>230185</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Rikfruktig blemlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Phlyctis agelaea</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Flot.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16158,10 +16158,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>428446</v>
+        <v>428145</v>
       </c>
       <c r="R148" t="n">
-        <v>6233151</v>
+        <v>6233244</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16220,10 +16220,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121471878</v>
+        <v>121471938</v>
       </c>
       <c r="B149" t="n">
-        <v>96769</v>
+        <v>80239</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16236,21 +16236,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>2604</v>
+        <v>230185</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16260,10 +16260,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>428445</v>
+        <v>428062</v>
       </c>
       <c r="R149" t="n">
-        <v>6233151</v>
+        <v>6233301</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16290,12 +16290,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16322,10 +16322,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121471877</v>
+        <v>121471870</v>
       </c>
       <c r="B150" t="n">
-        <v>94595</v>
+        <v>76945</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16334,25 +16334,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16362,10 +16362,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>428445</v>
+        <v>428356</v>
       </c>
       <c r="R150" t="n">
-        <v>6233151</v>
+        <v>6233243</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16424,10 +16424,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121471911</v>
+        <v>121471933</v>
       </c>
       <c r="B151" t="n">
-        <v>76945</v>
+        <v>94585</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16436,25 +16436,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1342</v>
+        <v>2671</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16464,10 +16464,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>428352</v>
+        <v>428090</v>
       </c>
       <c r="R151" t="n">
-        <v>6233082</v>
+        <v>6233309</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16526,10 +16526,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121471899</v>
+        <v>121471869</v>
       </c>
       <c r="B152" t="n">
-        <v>94389</v>
+        <v>96722</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16542,21 +16542,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>2779</v>
+        <v>2606</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16566,10 +16566,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>428389</v>
+        <v>428354</v>
       </c>
       <c r="R152" t="n">
-        <v>6233099</v>
+        <v>6233242</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16596,12 +16596,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16628,10 +16628,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121471945</v>
+        <v>121471864</v>
       </c>
       <c r="B153" t="n">
-        <v>96769</v>
+        <v>94585</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16644,21 +16644,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>2604</v>
+        <v>2671</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16668,10 +16668,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>428035</v>
+        <v>428410</v>
       </c>
       <c r="R153" t="n">
-        <v>6233349</v>
+        <v>6233214</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16698,12 +16698,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16730,10 +16730,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121471822</v>
+        <v>121471929</v>
       </c>
       <c r="B154" t="n">
-        <v>94595</v>
+        <v>94390</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16746,21 +16746,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16770,10 +16770,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>428288</v>
+        <v>428078</v>
       </c>
       <c r="R154" t="n">
-        <v>6233325</v>
+        <v>6233294</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16800,12 +16800,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16832,10 +16832,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121471929</v>
+        <v>121471534</v>
       </c>
       <c r="B155" t="n">
-        <v>94389</v>
+        <v>96722</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16848,21 +16848,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2779</v>
+        <v>2606</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16872,10 +16872,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>428078</v>
+        <v>428147</v>
       </c>
       <c r="R155" t="n">
-        <v>6233294</v>
+        <v>6233224</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16902,12 +16902,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16934,10 +16934,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121471857</v>
+        <v>121471531</v>
       </c>
       <c r="B156" t="n">
-        <v>80252</v>
+        <v>94606</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16946,25 +16946,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1144</v>
+        <v>1080</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16974,10 +16974,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>428362</v>
+        <v>428110</v>
       </c>
       <c r="R156" t="n">
-        <v>6233272</v>
+        <v>6233224</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17004,12 +17004,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17036,10 +17036,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121471901</v>
+        <v>121471840</v>
       </c>
       <c r="B157" t="n">
-        <v>76945</v>
+        <v>78984</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17048,25 +17048,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1342</v>
+        <v>6431</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17076,10 +17076,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>428390</v>
+        <v>428183</v>
       </c>
       <c r="R157" t="n">
-        <v>6233099</v>
+        <v>6233239</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17106,12 +17106,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17138,10 +17138,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121471843</v>
+        <v>121471902</v>
       </c>
       <c r="B158" t="n">
-        <v>57367</v>
+        <v>94585</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17150,25 +17150,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100049</v>
+        <v>2671</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17178,10 +17178,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>428252</v>
+        <v>428387</v>
       </c>
       <c r="R158" t="n">
-        <v>6233262</v>
+        <v>6233096</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17208,12 +17208,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17240,10 +17240,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121471935</v>
+        <v>121471537</v>
       </c>
       <c r="B159" t="n">
-        <v>80239</v>
+        <v>96722</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17256,21 +17256,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17280,10 +17280,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>428097</v>
+        <v>428163</v>
       </c>
       <c r="R159" t="n">
-        <v>6233286</v>
+        <v>6233193</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17310,12 +17310,12 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17342,10 +17342,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121471810</v>
+        <v>121471899</v>
       </c>
       <c r="B160" t="n">
-        <v>80252</v>
+        <v>94390</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17354,25 +17354,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1144</v>
+        <v>2779</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17382,10 +17382,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>428347</v>
+        <v>428389</v>
       </c>
       <c r="R160" t="n">
-        <v>6233326</v>
+        <v>6233099</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17412,12 +17412,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17444,10 +17444,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121471914</v>
+        <v>121471931</v>
       </c>
       <c r="B161" t="n">
-        <v>94595</v>
+        <v>80252</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17456,25 +17456,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17484,10 +17484,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>428318</v>
+        <v>428075</v>
       </c>
       <c r="R161" t="n">
-        <v>6233075</v>
+        <v>6233301</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17546,10 +17546,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121471942</v>
+        <v>121471916</v>
       </c>
       <c r="B162" t="n">
-        <v>76945</v>
+        <v>94606</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17558,25 +17558,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1342</v>
+        <v>1080</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17586,10 +17586,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>428032</v>
+        <v>428283</v>
       </c>
       <c r="R162" t="n">
-        <v>6233345</v>
+        <v>6233084</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17648,10 +17648,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121471536</v>
+        <v>121471897</v>
       </c>
       <c r="B163" t="n">
-        <v>80575</v>
+        <v>78404</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17664,21 +17664,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1182</v>
+        <v>924</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17688,10 +17688,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>428166</v>
+        <v>428369</v>
       </c>
       <c r="R163" t="n">
-        <v>6233202</v>
+        <v>6233104</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17750,10 +17750,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121471545</v>
+        <v>121471865</v>
       </c>
       <c r="B164" t="n">
-        <v>80252</v>
+        <v>74696</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17762,25 +17762,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1144</v>
+        <v>306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17790,10 +17790,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>428172</v>
+        <v>428438</v>
       </c>
       <c r="R164" t="n">
-        <v>6233315</v>
+        <v>6233202</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17820,12 +17820,12 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17852,10 +17852,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121471531</v>
+        <v>121471833</v>
       </c>
       <c r="B165" t="n">
-        <v>94605</v>
+        <v>80239</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17868,21 +17868,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1080</v>
+        <v>230185</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17892,10 +17892,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>428110</v>
+        <v>428139</v>
       </c>
       <c r="R165" t="n">
-        <v>6233224</v>
+        <v>6233315</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17922,12 +17922,12 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17954,10 +17954,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121471690</v>
+        <v>121471920</v>
       </c>
       <c r="B166" t="n">
-        <v>80239</v>
+        <v>91109</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17966,25 +17966,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>230185</v>
+        <v>2023</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Sydlig sotticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Ischnoderma resinosum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schrad.) P.Karst.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17994,10 +17994,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>428161</v>
+        <v>428095</v>
       </c>
       <c r="R166" t="n">
-        <v>6233396</v>
+        <v>6233349</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18024,12 +18024,12 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18056,10 +18056,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121471530</v>
+        <v>121471857</v>
       </c>
       <c r="B167" t="n">
-        <v>80239</v>
+        <v>80252</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18068,25 +18068,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18096,10 +18096,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>428111</v>
+        <v>428362</v>
       </c>
       <c r="R167" t="n">
-        <v>6233222</v>
+        <v>6233272</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18126,12 +18126,12 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18158,10 +18158,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121471543</v>
+        <v>121471852</v>
       </c>
       <c r="B168" t="n">
-        <v>80239</v>
+        <v>80252</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18170,25 +18170,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18198,10 +18198,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>428209</v>
+        <v>428311</v>
       </c>
       <c r="R168" t="n">
-        <v>6233279</v>
+        <v>6233183</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18228,12 +18228,12 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18260,10 +18260,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121471799</v>
+        <v>121471825</v>
       </c>
       <c r="B169" t="n">
-        <v>94584</v>
+        <v>80239</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -18276,21 +18276,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>2671</v>
+        <v>230185</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18300,10 +18300,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>428389</v>
+        <v>428233</v>
       </c>
       <c r="R169" t="n">
-        <v>6233324</v>
+        <v>6233332</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18362,10 +18362,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121471813</v>
+        <v>121471819</v>
       </c>
       <c r="B170" t="n">
-        <v>94584</v>
+        <v>94596</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18378,21 +18378,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18402,10 +18402,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>428332</v>
+        <v>428304</v>
       </c>
       <c r="R170" t="n">
-        <v>6233341</v>
+        <v>6233306</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18464,10 +18464,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121471807</v>
+        <v>121471841</v>
       </c>
       <c r="B171" t="n">
-        <v>76945</v>
+        <v>96722</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18476,25 +18476,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18504,10 +18504,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>428327</v>
+        <v>428221</v>
       </c>
       <c r="R171" t="n">
-        <v>6233292</v>
+        <v>6233212</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18566,10 +18566,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121471834</v>
+        <v>121471691</v>
       </c>
       <c r="B172" t="n">
-        <v>80252</v>
+        <v>96722</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18578,25 +18578,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18606,10 +18606,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>428137</v>
+        <v>428128</v>
       </c>
       <c r="R172" t="n">
-        <v>6233320</v>
+        <v>6233385</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18636,12 +18636,12 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18668,10 +18668,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121471870</v>
+        <v>121471820</v>
       </c>
       <c r="B173" t="n">
-        <v>76945</v>
+        <v>94390</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18680,25 +18680,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1342</v>
+        <v>2779</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18708,10 +18708,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>428356</v>
+        <v>428304</v>
       </c>
       <c r="R173" t="n">
-        <v>6233243</v>
+        <v>6233306</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18770,10 +18770,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121471835</v>
+        <v>121471815</v>
       </c>
       <c r="B174" t="n">
-        <v>96721</v>
+        <v>80409</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18782,25 +18782,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>2606</v>
+        <v>1557</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Röd pysslinglav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelopsis rubella</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Nyl.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18810,10 +18810,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>428145</v>
+        <v>428333</v>
       </c>
       <c r="R174" t="n">
-        <v>6233244</v>
+        <v>6233339</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18872,10 +18872,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121471902</v>
+        <v>121471536</v>
       </c>
       <c r="B175" t="n">
-        <v>94584</v>
+        <v>80575</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18884,25 +18884,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>2671</v>
+        <v>1182</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18912,10 +18912,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>428387</v>
+        <v>428166</v>
       </c>
       <c r="R175" t="n">
-        <v>6233096</v>
+        <v>6233202</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18942,12 +18942,12 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD175" t="b">

--- a/artfynd/A 18989-2024 artfynd.xlsx
+++ b/artfynd/A 18989-2024 artfynd.xlsx
@@ -3354,10 +3354,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121471684</v>
+        <v>121471533</v>
       </c>
       <c r="B23" t="n">
-        <v>80409</v>
+        <v>80242</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3366,25 +3366,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1557</v>
+        <v>230185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Röd pysslinglav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Thelopsis rubella</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>428227</v>
+        <v>428144</v>
       </c>
       <c r="R23" t="n">
-        <v>6233392</v>
+        <v>6233229</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3456,10 +3456,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121471945</v>
+        <v>121471806</v>
       </c>
       <c r="B24" t="n">
-        <v>96770</v>
+        <v>80255</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3468,25 +3468,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2604</v>
+        <v>1144</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>428035</v>
+        <v>428325</v>
       </c>
       <c r="R24" t="n">
-        <v>6233349</v>
+        <v>6233291</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3526,12 +3526,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3558,10 +3558,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121471540</v>
+        <v>121471531</v>
       </c>
       <c r="B25" t="n">
-        <v>96722</v>
+        <v>94609</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3574,21 +3574,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2606</v>
+        <v>1080</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>428227</v>
+        <v>428110</v>
       </c>
       <c r="R25" t="n">
-        <v>6233132</v>
+        <v>6233224</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3660,10 +3660,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121471836</v>
+        <v>121471814</v>
       </c>
       <c r="B26" t="n">
-        <v>94585</v>
+        <v>80255</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3672,25 +3672,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2671</v>
+        <v>1144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>428145</v>
+        <v>428331</v>
       </c>
       <c r="R26" t="n">
-        <v>6233244</v>
+        <v>6233339</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3762,10 +3762,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121471843</v>
+        <v>121471939</v>
       </c>
       <c r="B27" t="n">
-        <v>57367</v>
+        <v>94599</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3774,25 +3774,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>2667</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>428252</v>
+        <v>428046</v>
       </c>
       <c r="R27" t="n">
-        <v>6233262</v>
+        <v>6233296</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3832,12 +3832,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3864,10 +3864,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121471936</v>
+        <v>121471812</v>
       </c>
       <c r="B28" t="n">
-        <v>94606</v>
+        <v>94393</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3880,21 +3880,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1080</v>
+        <v>2779</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>428079</v>
+        <v>428331</v>
       </c>
       <c r="R28" t="n">
-        <v>6233262</v>
+        <v>6233335</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3934,12 +3934,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3966,10 +3966,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121471912</v>
+        <v>121471929</v>
       </c>
       <c r="B29" t="n">
-        <v>78404</v>
+        <v>94393</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3978,25 +3978,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>924</v>
+        <v>2779</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>428351</v>
+        <v>428078</v>
       </c>
       <c r="R29" t="n">
-        <v>6233082</v>
+        <v>6233294</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4068,10 +4068,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121471806</v>
+        <v>121471688</v>
       </c>
       <c r="B30" t="n">
-        <v>80252</v>
+        <v>96725</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4080,25 +4080,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>428325</v>
+        <v>428159</v>
       </c>
       <c r="R30" t="n">
-        <v>6233291</v>
+        <v>6233394</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4138,12 +4138,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4170,10 +4170,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121471685</v>
+        <v>121471798</v>
       </c>
       <c r="B31" t="n">
-        <v>80252</v>
+        <v>96725</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4182,25 +4182,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>428228</v>
+        <v>428387</v>
       </c>
       <c r="R31" t="n">
-        <v>6233391</v>
+        <v>6233326</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4240,12 +4240,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4272,10 +4272,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121471831</v>
+        <v>121471684</v>
       </c>
       <c r="B32" t="n">
-        <v>80252</v>
+        <v>80412</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4288,21 +4288,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1144</v>
+        <v>1557</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Röd pysslinglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelopsis rubella</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>Nyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>428145</v>
+        <v>428227</v>
       </c>
       <c r="R32" t="n">
-        <v>6233315</v>
+        <v>6233392</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4342,12 +4342,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4374,10 +4374,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121471896</v>
+        <v>121471804</v>
       </c>
       <c r="B33" t="n">
-        <v>80575</v>
+        <v>76948</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4390,21 +4390,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1182</v>
+        <v>1342</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4414,10 +4414,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>428370</v>
+        <v>428335</v>
       </c>
       <c r="R33" t="n">
-        <v>6233102</v>
+        <v>6233286</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4444,12 +4444,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4476,10 +4476,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121471538</v>
+        <v>121471855</v>
       </c>
       <c r="B34" t="n">
-        <v>80239</v>
+        <v>94393</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4492,21 +4492,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>230185</v>
+        <v>2779</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>428166</v>
+        <v>428365</v>
       </c>
       <c r="R34" t="n">
-        <v>6233198</v>
+        <v>6233269</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4546,12 +4546,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4578,10 +4578,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121471942</v>
+        <v>121471817</v>
       </c>
       <c r="B35" t="n">
-        <v>76945</v>
+        <v>74697</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4590,25 +4590,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1342</v>
+        <v>6439</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>428032</v>
+        <v>428312</v>
       </c>
       <c r="R35" t="n">
-        <v>6233345</v>
+        <v>6233323</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4648,12 +4648,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4680,10 +4680,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121471934</v>
+        <v>121471833</v>
       </c>
       <c r="B36" t="n">
-        <v>94390</v>
+        <v>80242</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4696,21 +4696,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2779</v>
+        <v>230185</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4720,10 +4720,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>428090</v>
+        <v>428139</v>
       </c>
       <c r="R36" t="n">
-        <v>6233309</v>
+        <v>6233315</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4750,12 +4750,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4782,10 +4782,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121471944</v>
+        <v>121471876</v>
       </c>
       <c r="B37" t="n">
-        <v>94596</v>
+        <v>80285</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4798,21 +4798,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2667</v>
+        <v>1223</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Rikfruktig blemlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Phlyctis agelaea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Flot.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>428034</v>
+        <v>428446</v>
       </c>
       <c r="R37" t="n">
-        <v>6233348</v>
+        <v>6233151</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4884,10 +4884,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121471908</v>
+        <v>121471685</v>
       </c>
       <c r="B38" t="n">
-        <v>74606</v>
+        <v>80255</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4896,25 +4896,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1118</v>
+        <v>1144</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>428377</v>
+        <v>428228</v>
       </c>
       <c r="R38" t="n">
-        <v>6233090</v>
+        <v>6233391</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4954,12 +4954,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4986,10 +4986,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121471905</v>
+        <v>121471878</v>
       </c>
       <c r="B39" t="n">
-        <v>74606</v>
+        <v>96773</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4998,25 +4998,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1118</v>
+        <v>2604</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>428377</v>
+        <v>428445</v>
       </c>
       <c r="R39" t="n">
-        <v>6233095</v>
+        <v>6233151</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5088,10 +5088,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121471829</v>
+        <v>121471868</v>
       </c>
       <c r="B40" t="n">
-        <v>80252</v>
+        <v>94599</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5100,25 +5100,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5128,10 +5128,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>428147</v>
+        <v>428347</v>
       </c>
       <c r="R40" t="n">
-        <v>6233304</v>
+        <v>6233241</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5190,10 +5190,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121471895</v>
+        <v>121471835</v>
       </c>
       <c r="B41" t="n">
-        <v>80239</v>
+        <v>96725</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5206,21 +5206,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5230,10 +5230,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>428355</v>
+        <v>428145</v>
       </c>
       <c r="R41" t="n">
-        <v>6233123</v>
+        <v>6233244</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5260,12 +5260,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5292,10 +5292,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121471828</v>
+        <v>121471697</v>
       </c>
       <c r="B42" t="n">
-        <v>80239</v>
+        <v>74699</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5308,21 +5308,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>230185</v>
+        <v>306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5332,10 +5332,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>428185</v>
+        <v>428043</v>
       </c>
       <c r="R42" t="n">
-        <v>6233289</v>
+        <v>6233298</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5362,12 +5362,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5376,7 +5376,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5395,10 +5394,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121471844</v>
+        <v>121471865</v>
       </c>
       <c r="B43" t="n">
-        <v>76945</v>
+        <v>74699</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5407,25 +5406,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1342</v>
+        <v>306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5435,10 +5434,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>428248</v>
+        <v>428438</v>
       </c>
       <c r="R43" t="n">
-        <v>6233241</v>
+        <v>6233202</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5497,10 +5496,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121471824</v>
+        <v>121471896</v>
       </c>
       <c r="B44" t="n">
-        <v>76945</v>
+        <v>80578</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5513,21 +5512,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1342</v>
+        <v>1182</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5537,10 +5536,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>428288</v>
+        <v>428370</v>
       </c>
       <c r="R44" t="n">
-        <v>6233325</v>
+        <v>6233102</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5567,12 +5566,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5599,10 +5598,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121471907</v>
+        <v>121471542</v>
       </c>
       <c r="B45" t="n">
-        <v>76945</v>
+        <v>80255</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5611,25 +5610,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5639,10 +5638,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>428375</v>
+        <v>428198</v>
       </c>
       <c r="R45" t="n">
-        <v>6233092</v>
+        <v>6233249</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5669,12 +5668,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5701,10 +5700,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121471808</v>
+        <v>121471879</v>
       </c>
       <c r="B46" t="n">
-        <v>80252</v>
+        <v>76948</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5713,25 +5712,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5741,10 +5740,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>428350</v>
+        <v>428445</v>
       </c>
       <c r="R46" t="n">
-        <v>6233316</v>
+        <v>6233151</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5803,10 +5802,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121471842</v>
+        <v>121471694</v>
       </c>
       <c r="B47" t="n">
-        <v>94596</v>
+        <v>80255</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5815,25 +5814,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5843,10 +5842,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>428221</v>
+        <v>428125</v>
       </c>
       <c r="R47" t="n">
-        <v>6233212</v>
+        <v>6233379</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5873,12 +5872,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5905,10 +5904,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121471822</v>
+        <v>121471809</v>
       </c>
       <c r="B48" t="n">
-        <v>94596</v>
+        <v>74563</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5917,25 +5916,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2667</v>
+        <v>1116</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5945,10 +5944,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>428288</v>
+        <v>428352</v>
       </c>
       <c r="R48" t="n">
-        <v>6233325</v>
+        <v>6233315</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6007,10 +6006,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121471925</v>
+        <v>121471828</v>
       </c>
       <c r="B49" t="n">
-        <v>94598</v>
+        <v>80242</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6023,21 +6022,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2666</v>
+        <v>230185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6047,10 +6046,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>428076</v>
+        <v>428185</v>
       </c>
       <c r="R49" t="n">
-        <v>6233382</v>
+        <v>6233289</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6077,12 +6076,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6091,6 +6090,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6109,10 +6109,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121471926</v>
+        <v>121471924</v>
       </c>
       <c r="B50" t="n">
-        <v>94390</v>
+        <v>80242</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6125,21 +6125,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2779</v>
+        <v>230185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6149,10 +6149,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>428073</v>
+        <v>428097</v>
       </c>
       <c r="R50" t="n">
-        <v>6233383</v>
+        <v>6233382</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6211,10 +6211,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121471683</v>
+        <v>121471905</v>
       </c>
       <c r="B51" t="n">
-        <v>94585</v>
+        <v>74609</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6223,25 +6223,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2671</v>
+        <v>1118</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6251,10 +6251,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>428278</v>
+        <v>428377</v>
       </c>
       <c r="R51" t="n">
-        <v>6233417</v>
+        <v>6233095</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6281,12 +6281,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6313,10 +6313,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121471941</v>
+        <v>121471904</v>
       </c>
       <c r="B52" t="n">
-        <v>80239</v>
+        <v>78407</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6325,25 +6325,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>230185</v>
+        <v>924</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6353,10 +6353,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>428046</v>
+        <v>428387</v>
       </c>
       <c r="R52" t="n">
-        <v>6233350</v>
+        <v>6233098</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6415,10 +6415,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121471859</v>
+        <v>121471849</v>
       </c>
       <c r="B53" t="n">
-        <v>80239</v>
+        <v>80255</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6427,25 +6427,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6455,10 +6455,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>428404</v>
+        <v>428299</v>
       </c>
       <c r="R53" t="n">
-        <v>6233275</v>
+        <v>6233126</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6517,10 +6517,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121471856</v>
+        <v>121471911</v>
       </c>
       <c r="B54" t="n">
-        <v>76945</v>
+        <v>76948</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6557,10 +6557,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>428360</v>
+        <v>428352</v>
       </c>
       <c r="R54" t="n">
-        <v>6233266</v>
+        <v>6233082</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6587,12 +6587,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6619,10 +6619,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121471915</v>
+        <v>121471853</v>
       </c>
       <c r="B55" t="n">
-        <v>96770</v>
+        <v>76948</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6631,25 +6631,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2604</v>
+        <v>1342</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6659,10 +6659,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>428281</v>
+        <v>428311</v>
       </c>
       <c r="R55" t="n">
-        <v>6233082</v>
+        <v>6233183</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6721,10 +6721,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121471937</v>
+        <v>121471844</v>
       </c>
       <c r="B56" t="n">
-        <v>96722</v>
+        <v>76948</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6733,25 +6733,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6761,10 +6761,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>428062</v>
+        <v>428248</v>
       </c>
       <c r="R56" t="n">
-        <v>6233301</v>
+        <v>6233241</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6791,12 +6791,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6823,10 +6823,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121471860</v>
+        <v>121471937</v>
       </c>
       <c r="B57" t="n">
-        <v>96722</v>
+        <v>96725</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6863,10 +6863,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>428404</v>
+        <v>428062</v>
       </c>
       <c r="R57" t="n">
-        <v>6233275</v>
+        <v>6233301</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6893,12 +6893,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6925,10 +6925,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121471810</v>
+        <v>121471808</v>
       </c>
       <c r="B58" t="n">
-        <v>80252</v>
+        <v>80255</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>428347</v>
+        <v>428350</v>
       </c>
       <c r="R58" t="n">
-        <v>6233326</v>
+        <v>6233316</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7027,10 +7027,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121471804</v>
+        <v>121471834</v>
       </c>
       <c r="B59" t="n">
-        <v>76945</v>
+        <v>80255</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7039,25 +7039,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7067,10 +7067,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>428335</v>
+        <v>428137</v>
       </c>
       <c r="R59" t="n">
-        <v>6233286</v>
+        <v>6233320</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7129,10 +7129,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121471854</v>
+        <v>121471532</v>
       </c>
       <c r="B60" t="n">
-        <v>96722</v>
+        <v>94599</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7145,21 +7145,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7169,10 +7169,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>428302</v>
+        <v>428133</v>
       </c>
       <c r="R60" t="n">
-        <v>6233177</v>
+        <v>6233219</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7199,12 +7199,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7231,10 +7231,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121471802</v>
+        <v>121471841</v>
       </c>
       <c r="B61" t="n">
-        <v>94585</v>
+        <v>96725</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7247,21 +7247,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7271,10 +7271,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>428332</v>
+        <v>428221</v>
       </c>
       <c r="R61" t="n">
-        <v>6233287</v>
+        <v>6233212</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7333,10 +7333,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121471851</v>
+        <v>121471944</v>
       </c>
       <c r="B62" t="n">
-        <v>78860</v>
+        <v>94599</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7349,21 +7349,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6459</v>
+        <v>2667</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7373,10 +7373,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>428293</v>
+        <v>428034</v>
       </c>
       <c r="R62" t="n">
-        <v>6233170</v>
+        <v>6233348</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7403,12 +7403,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7435,10 +7435,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121471543</v>
+        <v>121471534</v>
       </c>
       <c r="B63" t="n">
-        <v>80239</v>
+        <v>96725</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7451,21 +7451,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>428209</v>
+        <v>428147</v>
       </c>
       <c r="R63" t="n">
-        <v>6233279</v>
+        <v>6233224</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7537,10 +7537,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121471922</v>
+        <v>121471908</v>
       </c>
       <c r="B64" t="n">
-        <v>76945</v>
+        <v>74609</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7553,21 +7553,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1342</v>
+        <v>1118</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7577,10 +7577,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>428091</v>
+        <v>428377</v>
       </c>
       <c r="R64" t="n">
-        <v>6233385</v>
+        <v>6233090</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7639,10 +7639,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121471847</v>
+        <v>121471859</v>
       </c>
       <c r="B65" t="n">
-        <v>76945</v>
+        <v>80242</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7651,25 +7651,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7679,10 +7679,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>428300</v>
+        <v>428404</v>
       </c>
       <c r="R65" t="n">
-        <v>6233125</v>
+        <v>6233275</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7741,10 +7741,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121471873</v>
+        <v>121471827</v>
       </c>
       <c r="B66" t="n">
-        <v>74560</v>
+        <v>94599</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7753,25 +7753,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1116</v>
+        <v>2667</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7781,10 +7781,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>428301</v>
+        <v>428185</v>
       </c>
       <c r="R66" t="n">
-        <v>6233171</v>
+        <v>6233287</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7843,10 +7843,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121471834</v>
+        <v>121471683</v>
       </c>
       <c r="B67" t="n">
-        <v>80252</v>
+        <v>94588</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7855,25 +7855,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1144</v>
+        <v>2671</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7883,10 +7883,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>428137</v>
+        <v>428278</v>
       </c>
       <c r="R67" t="n">
-        <v>6233320</v>
+        <v>6233417</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7913,12 +7913,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7945,10 +7945,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121471881</v>
+        <v>121471856</v>
       </c>
       <c r="B68" t="n">
-        <v>78404</v>
+        <v>76948</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7961,21 +7961,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>924</v>
+        <v>1342</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>428445</v>
+        <v>428360</v>
       </c>
       <c r="R68" t="n">
-        <v>6233151</v>
+        <v>6233266</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8047,10 +8047,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121471696</v>
+        <v>121471934</v>
       </c>
       <c r="B69" t="n">
-        <v>96722</v>
+        <v>94393</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8063,21 +8063,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2606</v>
+        <v>2779</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8087,10 +8087,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>428054</v>
+        <v>428090</v>
       </c>
       <c r="R69" t="n">
-        <v>6233337</v>
+        <v>6233309</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8117,12 +8117,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8149,10 +8149,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121471532</v>
+        <v>121471933</v>
       </c>
       <c r="B70" t="n">
-        <v>94596</v>
+        <v>94588</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8165,21 +8165,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8189,10 +8189,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>428133</v>
+        <v>428090</v>
       </c>
       <c r="R70" t="n">
-        <v>6233219</v>
+        <v>6233309</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8219,12 +8219,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8251,10 +8251,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121471846</v>
+        <v>121471942</v>
       </c>
       <c r="B71" t="n">
-        <v>80239</v>
+        <v>76948</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8263,25 +8263,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8291,10 +8291,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>428241</v>
+        <v>428032</v>
       </c>
       <c r="R71" t="n">
-        <v>6233222</v>
+        <v>6233345</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8321,12 +8321,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8353,10 +8353,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121471853</v>
+        <v>121471866</v>
       </c>
       <c r="B72" t="n">
-        <v>76945</v>
+        <v>80242</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8365,25 +8365,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8393,10 +8393,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>428311</v>
+        <v>428442</v>
       </c>
       <c r="R72" t="n">
-        <v>6233183</v>
+        <v>6233170</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8455,10 +8455,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121471694</v>
+        <v>121471938</v>
       </c>
       <c r="B73" t="n">
-        <v>80252</v>
+        <v>80242</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8467,25 +8467,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8495,10 +8495,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>428125</v>
+        <v>428062</v>
       </c>
       <c r="R73" t="n">
-        <v>6233379</v>
+        <v>6233301</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8525,12 +8525,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8557,10 +8557,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121471882</v>
+        <v>121471816</v>
       </c>
       <c r="B74" t="n">
-        <v>74606</v>
+        <v>96773</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8569,25 +8569,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1118</v>
+        <v>2604</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8597,10 +8597,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>428445</v>
+        <v>428317</v>
       </c>
       <c r="R74" t="n">
-        <v>6233151</v>
+        <v>6233324</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8659,10 +8659,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121471697</v>
+        <v>121471877</v>
       </c>
       <c r="B75" t="n">
-        <v>74696</v>
+        <v>94599</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8675,21 +8675,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>306</v>
+        <v>2667</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8699,10 +8699,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>428043</v>
+        <v>428445</v>
       </c>
       <c r="R75" t="n">
-        <v>6233298</v>
+        <v>6233151</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8729,12 +8729,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8761,10 +8761,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121471693</v>
+        <v>121471813</v>
       </c>
       <c r="B76" t="n">
-        <v>94585</v>
+        <v>94588</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8801,10 +8801,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>428125</v>
+        <v>428332</v>
       </c>
       <c r="R76" t="n">
-        <v>6233379</v>
+        <v>6233341</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8831,12 +8831,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8863,10 +8863,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121471689</v>
+        <v>121471864</v>
       </c>
       <c r="B77" t="n">
-        <v>94596</v>
+        <v>94588</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8879,21 +8879,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8903,10 +8903,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>428161</v>
+        <v>428410</v>
       </c>
       <c r="R77" t="n">
-        <v>6233396</v>
+        <v>6233214</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8965,10 +8965,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121471812</v>
+        <v>121471811</v>
       </c>
       <c r="B78" t="n">
-        <v>94390</v>
+        <v>76948</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8977,25 +8977,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2779</v>
+        <v>1342</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9005,10 +9005,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>428331</v>
+        <v>428349</v>
       </c>
       <c r="R78" t="n">
-        <v>6233335</v>
+        <v>6233325</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9067,10 +9067,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121471904</v>
+        <v>121471861</v>
       </c>
       <c r="B79" t="n">
-        <v>78404</v>
+        <v>94599</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9079,25 +9079,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>924</v>
+        <v>2667</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9107,10 +9107,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>428387</v>
+        <v>428404</v>
       </c>
       <c r="R79" t="n">
-        <v>6233098</v>
+        <v>6233275</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9137,12 +9137,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9169,10 +9169,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121471801</v>
+        <v>121471907</v>
       </c>
       <c r="B80" t="n">
-        <v>80252</v>
+        <v>76948</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9181,25 +9181,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9209,10 +9209,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>428370</v>
+        <v>428375</v>
       </c>
       <c r="R80" t="n">
-        <v>6233336</v>
+        <v>6233092</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9239,12 +9239,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9271,10 +9271,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121471535</v>
+        <v>121471686</v>
       </c>
       <c r="B81" t="n">
-        <v>76945</v>
+        <v>80255</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9283,25 +9283,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9311,10 +9311,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>428160</v>
+        <v>428187</v>
       </c>
       <c r="R81" t="n">
-        <v>6233209</v>
+        <v>6233403</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9373,10 +9373,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121471910</v>
+        <v>121471915</v>
       </c>
       <c r="B82" t="n">
-        <v>76945</v>
+        <v>96773</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9385,25 +9385,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1342</v>
+        <v>2604</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9413,10 +9413,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>428377</v>
+        <v>428281</v>
       </c>
       <c r="R82" t="n">
-        <v>6233090</v>
+        <v>6233082</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9475,10 +9475,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121471927</v>
+        <v>121471539</v>
       </c>
       <c r="B83" t="n">
-        <v>76945</v>
+        <v>94588</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9487,25 +9487,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1342</v>
+        <v>2671</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>428074</v>
+        <v>428262</v>
       </c>
       <c r="R83" t="n">
-        <v>6233297</v>
+        <v>6233134</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9545,12 +9545,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9577,10 +9577,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121471530</v>
+        <v>121471914</v>
       </c>
       <c r="B84" t="n">
-        <v>80239</v>
+        <v>94599</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9593,21 +9593,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9617,10 +9617,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>428111</v>
+        <v>428318</v>
       </c>
       <c r="R84" t="n">
-        <v>6233222</v>
+        <v>6233075</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9647,12 +9647,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9679,10 +9679,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121471878</v>
+        <v>121471543</v>
       </c>
       <c r="B85" t="n">
-        <v>96770</v>
+        <v>80242</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9695,21 +9695,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2604</v>
+        <v>230185</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9719,10 +9719,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>428445</v>
+        <v>428209</v>
       </c>
       <c r="R85" t="n">
-        <v>6233151</v>
+        <v>6233279</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9749,12 +9749,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9781,10 +9781,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121471688</v>
+        <v>121471926</v>
       </c>
       <c r="B86" t="n">
-        <v>96722</v>
+        <v>94393</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9797,21 +9797,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2606</v>
+        <v>2779</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9821,10 +9821,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>428159</v>
+        <v>428073</v>
       </c>
       <c r="R86" t="n">
-        <v>6233394</v>
+        <v>6233383</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9851,12 +9851,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9883,10 +9883,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121471861</v>
+        <v>121471931</v>
       </c>
       <c r="B87" t="n">
-        <v>94596</v>
+        <v>80255</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9895,25 +9895,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9923,10 +9923,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>428404</v>
+        <v>428075</v>
       </c>
       <c r="R87" t="n">
-        <v>6233275</v>
+        <v>6233301</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9953,12 +9953,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9985,10 +9985,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121471803</v>
+        <v>121471857</v>
       </c>
       <c r="B88" t="n">
-        <v>80252</v>
+        <v>80255</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10025,10 +10025,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>428334</v>
+        <v>428362</v>
       </c>
       <c r="R88" t="n">
-        <v>6233284</v>
+        <v>6233272</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10087,10 +10087,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121471814</v>
+        <v>121471881</v>
       </c>
       <c r="B89" t="n">
-        <v>80252</v>
+        <v>78407</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10099,25 +10099,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1144</v>
+        <v>924</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10127,10 +10127,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>428331</v>
+        <v>428445</v>
       </c>
       <c r="R89" t="n">
-        <v>6233339</v>
+        <v>6233151</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10189,10 +10189,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121471903</v>
+        <v>121471696</v>
       </c>
       <c r="B90" t="n">
-        <v>76945</v>
+        <v>96725</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10201,25 +10201,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10229,10 +10229,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>428385</v>
+        <v>428054</v>
       </c>
       <c r="R90" t="n">
-        <v>6233097</v>
+        <v>6233337</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10259,12 +10259,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10291,10 +10291,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121471544</v>
+        <v>121471867</v>
       </c>
       <c r="B91" t="n">
-        <v>94596</v>
+        <v>76948</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10303,25 +10303,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10331,10 +10331,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>428219</v>
+        <v>428442</v>
       </c>
       <c r="R91" t="n">
-        <v>6233278</v>
+        <v>6233170</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10361,12 +10361,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10393,10 +10393,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121471939</v>
+        <v>121471824</v>
       </c>
       <c r="B92" t="n">
-        <v>94596</v>
+        <v>76948</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10405,25 +10405,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10433,10 +10433,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>428046</v>
+        <v>428288</v>
       </c>
       <c r="R92" t="n">
-        <v>6233296</v>
+        <v>6233325</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10463,12 +10463,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10495,10 +10495,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121471796</v>
+        <v>121471917</v>
       </c>
       <c r="B93" t="n">
-        <v>80252</v>
+        <v>80242</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10507,25 +10507,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10535,10 +10535,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>428390</v>
+        <v>428284</v>
       </c>
       <c r="R93" t="n">
-        <v>6233312</v>
+        <v>6233109</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10565,12 +10565,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10600,7 +10600,7 @@
         <v>121471928</v>
       </c>
       <c r="B94" t="n">
-        <v>80252</v>
+        <v>80255</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10699,10 +10699,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121471849</v>
+        <v>121471897</v>
       </c>
       <c r="B95" t="n">
-        <v>80252</v>
+        <v>78407</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10711,25 +10711,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1144</v>
+        <v>924</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10739,10 +10739,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>428299</v>
+        <v>428369</v>
       </c>
       <c r="R95" t="n">
-        <v>6233126</v>
+        <v>6233104</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10769,12 +10769,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10801,10 +10801,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121471874</v>
+        <v>121471805</v>
       </c>
       <c r="B96" t="n">
-        <v>80252</v>
+        <v>80255</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10841,10 +10841,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>428375</v>
+        <v>428333</v>
       </c>
       <c r="R96" t="n">
-        <v>6233151</v>
+        <v>6233283</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10903,10 +10903,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121471809</v>
+        <v>121471852</v>
       </c>
       <c r="B97" t="n">
-        <v>74560</v>
+        <v>80255</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10915,25 +10915,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1116</v>
+        <v>1144</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10943,10 +10943,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>428352</v>
+        <v>428311</v>
       </c>
       <c r="R97" t="n">
-        <v>6233315</v>
+        <v>6233183</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11005,10 +11005,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121471923</v>
+        <v>121471922</v>
       </c>
       <c r="B98" t="n">
-        <v>80252</v>
+        <v>76948</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11017,25 +11017,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11048,7 +11048,7 @@
         <v>428091</v>
       </c>
       <c r="R98" t="n">
-        <v>6233386</v>
+        <v>6233385</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11107,10 +11107,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121471805</v>
+        <v>121471689</v>
       </c>
       <c r="B99" t="n">
-        <v>80252</v>
+        <v>94599</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11119,25 +11119,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11147,10 +11147,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>428333</v>
+        <v>428161</v>
       </c>
       <c r="R99" t="n">
-        <v>6233283</v>
+        <v>6233396</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11177,12 +11177,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11209,10 +11209,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121471924</v>
+        <v>121471854</v>
       </c>
       <c r="B100" t="n">
-        <v>80239</v>
+        <v>96725</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11225,21 +11225,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11249,10 +11249,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>428097</v>
+        <v>428302</v>
       </c>
       <c r="R100" t="n">
-        <v>6233382</v>
+        <v>6233177</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11279,12 +11279,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11311,10 +11311,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121471695</v>
+        <v>121471923</v>
       </c>
       <c r="B101" t="n">
-        <v>80239</v>
+        <v>80255</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11323,25 +11323,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11351,10 +11351,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>428053</v>
+        <v>428091</v>
       </c>
       <c r="R101" t="n">
-        <v>6233336</v>
+        <v>6233386</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11381,12 +11381,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11413,10 +11413,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121471917</v>
+        <v>121471845</v>
       </c>
       <c r="B102" t="n">
-        <v>80239</v>
+        <v>80255</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11425,25 +11425,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11453,10 +11453,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>428284</v>
+        <v>428248</v>
       </c>
       <c r="R102" t="n">
-        <v>6233109</v>
+        <v>6233242</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11483,12 +11483,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11515,10 +11515,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121471863</v>
+        <v>121471836</v>
       </c>
       <c r="B103" t="n">
-        <v>96722</v>
+        <v>94588</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11531,21 +11531,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2606</v>
+        <v>2671</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11555,10 +11555,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>428411</v>
+        <v>428145</v>
       </c>
       <c r="R103" t="n">
-        <v>6233213</v>
+        <v>6233244</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11617,10 +11617,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121471799</v>
+        <v>121471802</v>
       </c>
       <c r="B104" t="n">
-        <v>94585</v>
+        <v>94588</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11657,10 +11657,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>428389</v>
+        <v>428332</v>
       </c>
       <c r="R104" t="n">
-        <v>6233324</v>
+        <v>6233287</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11719,10 +11719,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121471914</v>
+        <v>121471863</v>
       </c>
       <c r="B105" t="n">
-        <v>94596</v>
+        <v>96725</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11735,21 +11735,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11759,10 +11759,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>428318</v>
+        <v>428411</v>
       </c>
       <c r="R105" t="n">
-        <v>6233075</v>
+        <v>6233213</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11789,12 +11789,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11821,10 +11821,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121471817</v>
+        <v>121471839</v>
       </c>
       <c r="B106" t="n">
-        <v>74694</v>
+        <v>94588</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11837,21 +11837,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6439</v>
+        <v>2671</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11861,10 +11861,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>428312</v>
+        <v>428184</v>
       </c>
       <c r="R106" t="n">
-        <v>6233323</v>
+        <v>6233240</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11923,10 +11923,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121471866</v>
+        <v>121471840</v>
       </c>
       <c r="B107" t="n">
-        <v>80239</v>
+        <v>78987</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11939,21 +11939,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>230185</v>
+        <v>6431</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11963,10 +11963,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>428442</v>
+        <v>428183</v>
       </c>
       <c r="R107" t="n">
-        <v>6233170</v>
+        <v>6233239</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12025,10 +12025,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121471850</v>
+        <v>121471895</v>
       </c>
       <c r="B108" t="n">
-        <v>80239</v>
+        <v>80242</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12065,10 +12065,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>428293</v>
+        <v>428355</v>
       </c>
       <c r="R108" t="n">
-        <v>6233170</v>
+        <v>6233123</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12095,12 +12095,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12127,10 +12127,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121471935</v>
+        <v>121471936</v>
       </c>
       <c r="B109" t="n">
-        <v>80239</v>
+        <v>94609</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12143,21 +12143,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>230185</v>
+        <v>1080</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12167,10 +12167,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>428097</v>
+        <v>428079</v>
       </c>
       <c r="R109" t="n">
-        <v>6233286</v>
+        <v>6233262</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12229,10 +12229,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121471879</v>
+        <v>121471536</v>
       </c>
       <c r="B110" t="n">
-        <v>76945</v>
+        <v>80578</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12245,21 +12245,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1342</v>
+        <v>1182</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12269,10 +12269,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>428445</v>
+        <v>428166</v>
       </c>
       <c r="R110" t="n">
-        <v>6233151</v>
+        <v>6233202</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12299,12 +12299,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12331,10 +12331,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121471827</v>
+        <v>121471930</v>
       </c>
       <c r="B111" t="n">
-        <v>94596</v>
+        <v>74609</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12343,25 +12343,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2667</v>
+        <v>1118</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12371,10 +12371,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>428185</v>
+        <v>428078</v>
       </c>
       <c r="R111" t="n">
-        <v>6233287</v>
+        <v>6233294</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12401,12 +12401,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12433,10 +12433,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121471816</v>
+        <v>121471860</v>
       </c>
       <c r="B112" t="n">
-        <v>96770</v>
+        <v>96725</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12449,21 +12449,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2604</v>
+        <v>2606</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12473,10 +12473,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>428317</v>
+        <v>428404</v>
       </c>
       <c r="R112" t="n">
-        <v>6233324</v>
+        <v>6233275</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12535,10 +12535,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121471839</v>
+        <v>121471927</v>
       </c>
       <c r="B113" t="n">
-        <v>94585</v>
+        <v>76948</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12547,25 +12547,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2671</v>
+        <v>1342</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12575,10 +12575,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>428184</v>
+        <v>428074</v>
       </c>
       <c r="R113" t="n">
-        <v>6233240</v>
+        <v>6233297</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12637,10 +12637,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121471919</v>
+        <v>121471537</v>
       </c>
       <c r="B114" t="n">
-        <v>80252</v>
+        <v>96725</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12649,25 +12649,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12677,10 +12677,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>428106</v>
+        <v>428163</v>
       </c>
       <c r="R114" t="n">
-        <v>6233304</v>
+        <v>6233193</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12707,12 +12707,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12739,10 +12739,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121471542</v>
+        <v>121471818</v>
       </c>
       <c r="B115" t="n">
-        <v>80252</v>
+        <v>96725</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12751,25 +12751,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12779,10 +12779,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>428198</v>
+        <v>428307</v>
       </c>
       <c r="R115" t="n">
-        <v>6233249</v>
+        <v>6233311</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12809,12 +12809,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12841,10 +12841,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121471911</v>
+        <v>121471925</v>
       </c>
       <c r="B116" t="n">
-        <v>76945</v>
+        <v>94601</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12853,25 +12853,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1342</v>
+        <v>2666</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12881,10 +12881,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>428352</v>
+        <v>428076</v>
       </c>
       <c r="R116" t="n">
-        <v>6233082</v>
+        <v>6233382</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12943,10 +12943,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121471867</v>
+        <v>121471909</v>
       </c>
       <c r="B117" t="n">
-        <v>76945</v>
+        <v>76948</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12983,10 +12983,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>428442</v>
+        <v>428373</v>
       </c>
       <c r="R117" t="n">
-        <v>6233170</v>
+        <v>6233088</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13013,12 +13013,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13045,10 +13045,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121471807</v>
+        <v>121471901</v>
       </c>
       <c r="B118" t="n">
-        <v>76945</v>
+        <v>76948</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13085,10 +13085,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>428327</v>
+        <v>428390</v>
       </c>
       <c r="R118" t="n">
-        <v>6233292</v>
+        <v>6233099</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13115,12 +13115,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13147,10 +13147,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121471913</v>
+        <v>121471945</v>
       </c>
       <c r="B119" t="n">
-        <v>76945</v>
+        <v>96773</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13159,25 +13159,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1342</v>
+        <v>2604</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13187,10 +13187,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>428342</v>
+        <v>428035</v>
       </c>
       <c r="R119" t="n">
-        <v>6233082</v>
+        <v>6233349</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13249,10 +13249,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121471541</v>
+        <v>121471820</v>
       </c>
       <c r="B120" t="n">
-        <v>80239</v>
+        <v>94393</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13265,21 +13265,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>230185</v>
+        <v>2779</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13289,10 +13289,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>428209</v>
+        <v>428304</v>
       </c>
       <c r="R120" t="n">
-        <v>6233184</v>
+        <v>6233306</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13319,12 +13319,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13351,10 +13351,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121471690</v>
+        <v>121471910</v>
       </c>
       <c r="B121" t="n">
-        <v>80239</v>
+        <v>76948</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13363,25 +13363,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13391,10 +13391,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>428161</v>
+        <v>428377</v>
       </c>
       <c r="R121" t="n">
-        <v>6233396</v>
+        <v>6233090</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13421,12 +13421,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13453,10 +13453,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121471871</v>
+        <v>121471541</v>
       </c>
       <c r="B122" t="n">
-        <v>80239</v>
+        <v>80242</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13493,10 +13493,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>428302</v>
+        <v>428209</v>
       </c>
       <c r="R122" t="n">
-        <v>6233176</v>
+        <v>6233184</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13523,12 +13523,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13555,10 +13555,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121471909</v>
+        <v>121471538</v>
       </c>
       <c r="B123" t="n">
-        <v>76945</v>
+        <v>80242</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13567,25 +13567,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13595,10 +13595,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>428373</v>
+        <v>428166</v>
       </c>
       <c r="R123" t="n">
-        <v>6233088</v>
+        <v>6233198</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13625,12 +13625,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13657,10 +13657,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121471901</v>
+        <v>121471919</v>
       </c>
       <c r="B124" t="n">
-        <v>76945</v>
+        <v>80255</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13669,25 +13669,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13697,10 +13697,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>428390</v>
+        <v>428106</v>
       </c>
       <c r="R124" t="n">
-        <v>6233099</v>
+        <v>6233304</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13759,10 +13759,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121471868</v>
+        <v>121471858</v>
       </c>
       <c r="B125" t="n">
-        <v>94596</v>
+        <v>80255</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13771,25 +13771,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13799,10 +13799,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>428347</v>
+        <v>428372</v>
       </c>
       <c r="R125" t="n">
-        <v>6233241</v>
+        <v>6233270</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13861,10 +13861,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121471813</v>
+        <v>121471851</v>
       </c>
       <c r="B126" t="n">
-        <v>94585</v>
+        <v>78863</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13877,21 +13877,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2671</v>
+        <v>6459</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13901,10 +13901,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>428332</v>
+        <v>428293</v>
       </c>
       <c r="R126" t="n">
-        <v>6233341</v>
+        <v>6233170</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13963,10 +13963,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121471940</v>
+        <v>121471899</v>
       </c>
       <c r="B127" t="n">
-        <v>94606</v>
+        <v>94393</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13979,21 +13979,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1080</v>
+        <v>2779</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14003,10 +14003,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>428037</v>
+        <v>428389</v>
       </c>
       <c r="R127" t="n">
-        <v>6233291</v>
+        <v>6233099</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14065,53 +14065,50 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121471875</v>
+        <v>121471850</v>
       </c>
       <c r="B128" t="n">
-        <v>80252</v>
+        <v>80242</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>428340</v>
+        <v>428293</v>
       </c>
       <c r="R128" t="n">
-        <v>6233229</v>
+        <v>6233170</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14146,21 +14143,11 @@
           <t>2024-11-21</t>
         </is>
       </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>kollekt</t>
-        </is>
-      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
       <c r="AE128" t="b">
         <v>0</v>
-      </c>
-      <c r="AF128" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG128" t="b">
         <v>0</v>
@@ -14180,10 +14167,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121471845</v>
+        <v>121471846</v>
       </c>
       <c r="B129" t="n">
-        <v>80252</v>
+        <v>80242</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14192,25 +14179,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14220,10 +14207,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>428248</v>
+        <v>428241</v>
       </c>
       <c r="R129" t="n">
-        <v>6233242</v>
+        <v>6233222</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14282,10 +14269,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121471826</v>
+        <v>121471916</v>
       </c>
       <c r="B130" t="n">
-        <v>78860</v>
+        <v>94609</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14298,21 +14285,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6459</v>
+        <v>1080</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14322,10 +14309,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>428228</v>
+        <v>428283</v>
       </c>
       <c r="R130" t="n">
-        <v>6233340</v>
+        <v>6233084</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14352,12 +14339,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14384,10 +14371,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121471811</v>
+        <v>121471810</v>
       </c>
       <c r="B131" t="n">
-        <v>76945</v>
+        <v>80255</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14396,25 +14383,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14424,10 +14411,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>428349</v>
+        <v>428347</v>
       </c>
       <c r="R131" t="n">
-        <v>6233325</v>
+        <v>6233326</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14486,10 +14473,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121471798</v>
+        <v>121471831</v>
       </c>
       <c r="B132" t="n">
-        <v>96722</v>
+        <v>80255</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14498,25 +14485,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14526,10 +14513,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>428387</v>
+        <v>428145</v>
       </c>
       <c r="R132" t="n">
-        <v>6233326</v>
+        <v>6233315</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14588,10 +14575,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121471855</v>
+        <v>121471695</v>
       </c>
       <c r="B133" t="n">
-        <v>94390</v>
+        <v>80242</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14604,21 +14591,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2779</v>
+        <v>230185</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14628,10 +14615,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>428365</v>
+        <v>428053</v>
       </c>
       <c r="R133" t="n">
-        <v>6233269</v>
+        <v>6233336</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14658,12 +14645,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14690,10 +14677,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121471877</v>
+        <v>121471940</v>
       </c>
       <c r="B134" t="n">
-        <v>94596</v>
+        <v>94609</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14706,21 +14693,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2667</v>
+        <v>1080</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14730,10 +14717,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>428445</v>
+        <v>428037</v>
       </c>
       <c r="R134" t="n">
-        <v>6233151</v>
+        <v>6233291</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14760,12 +14747,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14792,10 +14779,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121471858</v>
+        <v>121471862</v>
       </c>
       <c r="B135" t="n">
-        <v>80252</v>
+        <v>80242</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14804,25 +14791,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14832,10 +14819,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>428372</v>
+        <v>428411</v>
       </c>
       <c r="R135" t="n">
-        <v>6233270</v>
+        <v>6233213</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14894,10 +14881,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121471545</v>
+        <v>121471807</v>
       </c>
       <c r="B136" t="n">
-        <v>80252</v>
+        <v>76948</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14906,25 +14893,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14934,10 +14921,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>428172</v>
+        <v>428327</v>
       </c>
       <c r="R136" t="n">
-        <v>6233315</v>
+        <v>6233292</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14964,12 +14951,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14996,10 +14983,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121471800</v>
+        <v>121471819</v>
       </c>
       <c r="B137" t="n">
-        <v>80252</v>
+        <v>94599</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15008,25 +14995,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15036,10 +15023,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>428387</v>
+        <v>428304</v>
       </c>
       <c r="R137" t="n">
-        <v>6233322</v>
+        <v>6233306</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15098,10 +15085,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121471862</v>
+        <v>121471943</v>
       </c>
       <c r="B138" t="n">
-        <v>80239</v>
+        <v>96725</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15114,21 +15101,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15138,10 +15125,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>428411</v>
+        <v>428034</v>
       </c>
       <c r="R138" t="n">
-        <v>6233213</v>
+        <v>6233348</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15168,12 +15155,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15200,10 +15187,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121471533</v>
+        <v>121471920</v>
       </c>
       <c r="B139" t="n">
-        <v>80239</v>
+        <v>91112</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15212,25 +15199,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>230185</v>
+        <v>2023</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Sydlig sotticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Ischnoderma resinosum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schrad.) P.Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15240,10 +15227,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>428144</v>
+        <v>428095</v>
       </c>
       <c r="R139" t="n">
-        <v>6233229</v>
+        <v>6233349</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15270,12 +15257,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15302,10 +15289,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121471943</v>
+        <v>121471815</v>
       </c>
       <c r="B140" t="n">
-        <v>96722</v>
+        <v>80412</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15314,25 +15301,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2606</v>
+        <v>1557</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Röd pysslinglav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelopsis rubella</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Nyl.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15342,10 +15329,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>428034</v>
+        <v>428333</v>
       </c>
       <c r="R140" t="n">
-        <v>6233348</v>
+        <v>6233339</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15372,12 +15359,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15404,10 +15391,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121471686</v>
+        <v>121471540</v>
       </c>
       <c r="B141" t="n">
-        <v>80252</v>
+        <v>96725</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15416,25 +15403,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15444,10 +15431,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>428187</v>
+        <v>428227</v>
       </c>
       <c r="R141" t="n">
-        <v>6233403</v>
+        <v>6233132</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15506,10 +15493,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121471876</v>
+        <v>121471903</v>
       </c>
       <c r="B142" t="n">
-        <v>80282</v>
+        <v>76948</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15518,25 +15505,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1223</v>
+        <v>1342</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Rikfruktig blemlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Phlyctis agelaea</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Flot.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15546,10 +15533,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>428446</v>
+        <v>428385</v>
       </c>
       <c r="R142" t="n">
-        <v>6233151</v>
+        <v>6233097</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15576,12 +15563,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15608,10 +15595,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121471539</v>
+        <v>121471545</v>
       </c>
       <c r="B143" t="n">
-        <v>94585</v>
+        <v>80255</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15620,25 +15607,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2671</v>
+        <v>1144</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15648,10 +15635,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>428262</v>
+        <v>428172</v>
       </c>
       <c r="R143" t="n">
-        <v>6233134</v>
+        <v>6233315</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15710,10 +15697,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121471692</v>
+        <v>121471941</v>
       </c>
       <c r="B144" t="n">
-        <v>94596</v>
+        <v>80242</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15726,21 +15713,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15750,10 +15737,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>428126</v>
+        <v>428046</v>
       </c>
       <c r="R144" t="n">
-        <v>6233380</v>
+        <v>6233350</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15780,12 +15767,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15812,10 +15799,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121471818</v>
+        <v>121471822</v>
       </c>
       <c r="B145" t="n">
-        <v>96722</v>
+        <v>94599</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15828,21 +15815,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15852,10 +15839,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>428307</v>
+        <v>428288</v>
       </c>
       <c r="R145" t="n">
-        <v>6233311</v>
+        <v>6233325</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15914,10 +15901,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121471835</v>
+        <v>121471902</v>
       </c>
       <c r="B146" t="n">
-        <v>96722</v>
+        <v>94588</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15930,21 +15917,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2606</v>
+        <v>2671</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15954,10 +15941,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>428145</v>
+        <v>428387</v>
       </c>
       <c r="R146" t="n">
-        <v>6233244</v>
+        <v>6233096</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15984,12 +15971,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16016,10 +16003,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121471930</v>
+        <v>121471870</v>
       </c>
       <c r="B147" t="n">
-        <v>74606</v>
+        <v>76948</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16032,21 +16019,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1118</v>
+        <v>1342</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16056,10 +16043,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>428078</v>
+        <v>428356</v>
       </c>
       <c r="R147" t="n">
-        <v>6233294</v>
+        <v>6233243</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16086,12 +16073,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16118,10 +16105,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121471837</v>
+        <v>121471826</v>
       </c>
       <c r="B148" t="n">
-        <v>80239</v>
+        <v>78863</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16134,21 +16121,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>230185</v>
+        <v>6459</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16158,10 +16145,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>428145</v>
+        <v>428228</v>
       </c>
       <c r="R148" t="n">
-        <v>6233244</v>
+        <v>6233340</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16220,10 +16207,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121471938</v>
+        <v>121471837</v>
       </c>
       <c r="B149" t="n">
-        <v>80239</v>
+        <v>80242</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16260,10 +16247,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>428062</v>
+        <v>428145</v>
       </c>
       <c r="R149" t="n">
-        <v>6233301</v>
+        <v>6233244</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16290,12 +16277,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16322,10 +16309,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121471870</v>
+        <v>121471912</v>
       </c>
       <c r="B150" t="n">
-        <v>76945</v>
+        <v>78407</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16338,21 +16325,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1342</v>
+        <v>924</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16362,10 +16349,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>428356</v>
+        <v>428351</v>
       </c>
       <c r="R150" t="n">
-        <v>6233243</v>
+        <v>6233082</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16392,12 +16379,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16424,10 +16411,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121471933</v>
+        <v>121471692</v>
       </c>
       <c r="B151" t="n">
-        <v>94585</v>
+        <v>94599</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16440,21 +16427,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16464,10 +16451,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>428090</v>
+        <v>428126</v>
       </c>
       <c r="R151" t="n">
-        <v>6233309</v>
+        <v>6233380</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16494,12 +16481,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16526,10 +16513,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121471869</v>
+        <v>121471882</v>
       </c>
       <c r="B152" t="n">
-        <v>96722</v>
+        <v>74609</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16538,25 +16525,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>2606</v>
+        <v>1118</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16566,10 +16553,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>428354</v>
+        <v>428445</v>
       </c>
       <c r="R152" t="n">
-        <v>6233242</v>
+        <v>6233151</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16628,10 +16615,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121471864</v>
+        <v>121471913</v>
       </c>
       <c r="B153" t="n">
-        <v>94585</v>
+        <v>76948</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16640,25 +16627,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>2671</v>
+        <v>1342</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16668,10 +16655,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>428410</v>
+        <v>428342</v>
       </c>
       <c r="R153" t="n">
-        <v>6233214</v>
+        <v>6233082</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16698,12 +16685,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16730,10 +16717,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121471929</v>
+        <v>121471842</v>
       </c>
       <c r="B154" t="n">
-        <v>94390</v>
+        <v>94599</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16746,21 +16733,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16770,10 +16757,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>428078</v>
+        <v>428221</v>
       </c>
       <c r="R154" t="n">
-        <v>6233294</v>
+        <v>6233212</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16800,12 +16787,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16832,10 +16819,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121471534</v>
+        <v>121471796</v>
       </c>
       <c r="B155" t="n">
-        <v>96722</v>
+        <v>80255</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16844,25 +16831,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16872,10 +16859,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>428147</v>
+        <v>428390</v>
       </c>
       <c r="R155" t="n">
-        <v>6233224</v>
+        <v>6233312</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16902,12 +16889,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16934,10 +16921,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121471531</v>
+        <v>121471803</v>
       </c>
       <c r="B156" t="n">
-        <v>94606</v>
+        <v>80255</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16946,25 +16933,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1080</v>
+        <v>1144</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16974,10 +16961,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>428110</v>
+        <v>428334</v>
       </c>
       <c r="R156" t="n">
-        <v>6233224</v>
+        <v>6233284</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17004,12 +16991,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17036,10 +17023,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121471840</v>
+        <v>121471800</v>
       </c>
       <c r="B157" t="n">
-        <v>78984</v>
+        <v>80255</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17048,25 +17035,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6431</v>
+        <v>1144</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17076,10 +17063,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>428183</v>
+        <v>428387</v>
       </c>
       <c r="R157" t="n">
-        <v>6233239</v>
+        <v>6233322</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17138,10 +17125,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121471902</v>
+        <v>121471869</v>
       </c>
       <c r="B158" t="n">
-        <v>94585</v>
+        <v>96725</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17154,21 +17141,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17178,10 +17165,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>428387</v>
+        <v>428354</v>
       </c>
       <c r="R158" t="n">
-        <v>6233096</v>
+        <v>6233242</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17208,12 +17195,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17240,50 +17227,53 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121471537</v>
+        <v>121471875</v>
       </c>
       <c r="B159" t="n">
-        <v>96722</v>
+        <v>80255</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>428163</v>
+        <v>428340</v>
       </c>
       <c r="R159" t="n">
-        <v>6233193</v>
+        <v>6233229</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17310,12 +17300,17 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>kollekt</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17323,6 +17318,11 @@
       </c>
       <c r="AE159" t="b">
         <v>0</v>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG159" t="b">
         <v>0</v>
@@ -17342,10 +17342,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121471899</v>
+        <v>121471871</v>
       </c>
       <c r="B160" t="n">
-        <v>94390</v>
+        <v>80242</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17358,21 +17358,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>2779</v>
+        <v>230185</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17382,10 +17382,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>428389</v>
+        <v>428302</v>
       </c>
       <c r="R160" t="n">
-        <v>6233099</v>
+        <v>6233176</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17412,12 +17412,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17444,10 +17444,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121471931</v>
+        <v>121471825</v>
       </c>
       <c r="B161" t="n">
-        <v>80252</v>
+        <v>80242</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17456,25 +17456,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17484,10 +17484,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>428075</v>
+        <v>428233</v>
       </c>
       <c r="R161" t="n">
-        <v>6233301</v>
+        <v>6233332</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17546,10 +17546,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121471916</v>
+        <v>121471693</v>
       </c>
       <c r="B162" t="n">
-        <v>94606</v>
+        <v>94588</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17562,21 +17562,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1080</v>
+        <v>2671</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17586,10 +17586,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>428283</v>
+        <v>428125</v>
       </c>
       <c r="R162" t="n">
-        <v>6233084</v>
+        <v>6233379</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17616,12 +17616,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17648,10 +17648,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121471897</v>
+        <v>121471535</v>
       </c>
       <c r="B163" t="n">
-        <v>78404</v>
+        <v>76948</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17664,21 +17664,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>924</v>
+        <v>1342</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17688,10 +17688,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>428369</v>
+        <v>428160</v>
       </c>
       <c r="R163" t="n">
-        <v>6233104</v>
+        <v>6233209</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17750,10 +17750,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121471865</v>
+        <v>121471873</v>
       </c>
       <c r="B164" t="n">
-        <v>74696</v>
+        <v>74563</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17762,25 +17762,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>306</v>
+        <v>1116</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17790,10 +17790,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>428438</v>
+        <v>428301</v>
       </c>
       <c r="R164" t="n">
-        <v>6233202</v>
+        <v>6233171</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17852,10 +17852,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121471833</v>
+        <v>121471829</v>
       </c>
       <c r="B165" t="n">
-        <v>80239</v>
+        <v>80255</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17864,25 +17864,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17892,10 +17892,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>428139</v>
+        <v>428147</v>
       </c>
       <c r="R165" t="n">
-        <v>6233315</v>
+        <v>6233304</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17954,10 +17954,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121471920</v>
+        <v>121471801</v>
       </c>
       <c r="B166" t="n">
-        <v>91109</v>
+        <v>80255</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17966,25 +17966,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>2023</v>
+        <v>1144</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Sydlig sotticka</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Ischnoderma resinosum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Schrad.) P.Karst.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17994,10 +17994,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>428095</v>
+        <v>428370</v>
       </c>
       <c r="R166" t="n">
-        <v>6233349</v>
+        <v>6233336</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18024,12 +18024,12 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18056,10 +18056,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121471857</v>
+        <v>121471935</v>
       </c>
       <c r="B167" t="n">
-        <v>80252</v>
+        <v>80242</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18068,25 +18068,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18096,10 +18096,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>428362</v>
+        <v>428097</v>
       </c>
       <c r="R167" t="n">
-        <v>6233272</v>
+        <v>6233286</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18126,12 +18126,12 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18158,10 +18158,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121471852</v>
+        <v>121471690</v>
       </c>
       <c r="B168" t="n">
-        <v>80252</v>
+        <v>80242</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18170,25 +18170,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18198,10 +18198,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>428311</v>
+        <v>428161</v>
       </c>
       <c r="R168" t="n">
-        <v>6233183</v>
+        <v>6233396</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18228,12 +18228,12 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18260,10 +18260,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121471825</v>
+        <v>121471843</v>
       </c>
       <c r="B169" t="n">
-        <v>80239</v>
+        <v>57370</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -18272,25 +18272,25 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>230185</v>
+        <v>100049</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18300,10 +18300,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>428233</v>
+        <v>428252</v>
       </c>
       <c r="R169" t="n">
-        <v>6233332</v>
+        <v>6233262</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18362,10 +18362,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121471819</v>
+        <v>121471530</v>
       </c>
       <c r="B170" t="n">
-        <v>94596</v>
+        <v>80242</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18378,21 +18378,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18402,10 +18402,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>428304</v>
+        <v>428111</v>
       </c>
       <c r="R170" t="n">
-        <v>6233306</v>
+        <v>6233222</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18432,12 +18432,12 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18464,10 +18464,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121471841</v>
+        <v>121471874</v>
       </c>
       <c r="B171" t="n">
-        <v>96722</v>
+        <v>80255</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18476,25 +18476,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18504,10 +18504,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>428221</v>
+        <v>428375</v>
       </c>
       <c r="R171" t="n">
-        <v>6233212</v>
+        <v>6233151</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18566,10 +18566,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121471691</v>
+        <v>121471799</v>
       </c>
       <c r="B172" t="n">
-        <v>96722</v>
+        <v>94588</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18582,21 +18582,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>2606</v>
+        <v>2671</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18606,10 +18606,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>428128</v>
+        <v>428389</v>
       </c>
       <c r="R172" t="n">
-        <v>6233385</v>
+        <v>6233324</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18636,12 +18636,12 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18668,10 +18668,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121471820</v>
+        <v>121471847</v>
       </c>
       <c r="B173" t="n">
-        <v>94390</v>
+        <v>76948</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18680,25 +18680,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2779</v>
+        <v>1342</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18708,10 +18708,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>428304</v>
+        <v>428300</v>
       </c>
       <c r="R173" t="n">
-        <v>6233306</v>
+        <v>6233125</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18770,10 +18770,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121471815</v>
+        <v>121471691</v>
       </c>
       <c r="B174" t="n">
-        <v>80409</v>
+        <v>96725</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18782,25 +18782,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1557</v>
+        <v>2606</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Röd pysslinglav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Thelopsis rubella</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Nyl.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18810,10 +18810,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>428333</v>
+        <v>428128</v>
       </c>
       <c r="R174" t="n">
-        <v>6233339</v>
+        <v>6233385</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18840,12 +18840,12 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18872,10 +18872,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121471536</v>
+        <v>121471544</v>
       </c>
       <c r="B175" t="n">
-        <v>80575</v>
+        <v>94599</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18884,25 +18884,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1182</v>
+        <v>2667</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18912,10 +18912,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>428166</v>
+        <v>428219</v>
       </c>
       <c r="R175" t="n">
-        <v>6233202</v>
+        <v>6233278</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>

--- a/artfynd/A 18989-2024 artfynd.xlsx
+++ b/artfynd/A 18989-2024 artfynd.xlsx
@@ -3354,10 +3354,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121471533</v>
+        <v>121471805</v>
       </c>
       <c r="B23" t="n">
-        <v>80242</v>
+        <v>80255</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3366,25 +3366,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>428144</v>
+        <v>428333</v>
       </c>
       <c r="R23" t="n">
-        <v>6233229</v>
+        <v>6233283</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3424,12 +3424,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3456,10 +3456,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121471806</v>
+        <v>121471684</v>
       </c>
       <c r="B24" t="n">
-        <v>80255</v>
+        <v>80412</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3472,21 +3472,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1144</v>
+        <v>1557</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Röd pysslinglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelopsis rubella</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>Nyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>428325</v>
+        <v>428227</v>
       </c>
       <c r="R24" t="n">
-        <v>6233291</v>
+        <v>6233392</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3526,12 +3526,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3558,10 +3558,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121471531</v>
+        <v>121471532</v>
       </c>
       <c r="B25" t="n">
-        <v>94609</v>
+        <v>94599</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3574,21 +3574,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1080</v>
+        <v>2667</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>428110</v>
+        <v>428133</v>
       </c>
       <c r="R25" t="n">
-        <v>6233224</v>
+        <v>6233219</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3660,10 +3660,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121471814</v>
+        <v>121471826</v>
       </c>
       <c r="B26" t="n">
-        <v>80255</v>
+        <v>78863</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3672,25 +3672,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1144</v>
+        <v>6459</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>428331</v>
+        <v>428228</v>
       </c>
       <c r="R26" t="n">
-        <v>6233339</v>
+        <v>6233340</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3762,10 +3762,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121471939</v>
+        <v>121471530</v>
       </c>
       <c r="B27" t="n">
-        <v>94599</v>
+        <v>80242</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3778,21 +3778,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>428046</v>
+        <v>428111</v>
       </c>
       <c r="R27" t="n">
-        <v>6233296</v>
+        <v>6233222</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3832,12 +3832,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3864,10 +3864,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121471812</v>
+        <v>121471901</v>
       </c>
       <c r="B28" t="n">
-        <v>94393</v>
+        <v>76948</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3876,25 +3876,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2779</v>
+        <v>1342</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>428331</v>
+        <v>428390</v>
       </c>
       <c r="R28" t="n">
-        <v>6233335</v>
+        <v>6233099</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3934,12 +3934,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3966,10 +3966,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121471929</v>
+        <v>121471539</v>
       </c>
       <c r="B29" t="n">
-        <v>94393</v>
+        <v>94588</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3982,21 +3982,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>428078</v>
+        <v>428262</v>
       </c>
       <c r="R29" t="n">
-        <v>6233294</v>
+        <v>6233134</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4068,10 +4068,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121471688</v>
+        <v>121471864</v>
       </c>
       <c r="B30" t="n">
-        <v>96725</v>
+        <v>94588</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4084,21 +4084,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2606</v>
+        <v>2671</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>428159</v>
+        <v>428410</v>
       </c>
       <c r="R30" t="n">
-        <v>6233394</v>
+        <v>6233214</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4138,12 +4138,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4170,10 +4170,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121471798</v>
+        <v>121471899</v>
       </c>
       <c r="B31" t="n">
-        <v>96725</v>
+        <v>94393</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4186,21 +4186,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2606</v>
+        <v>2779</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>428387</v>
+        <v>428389</v>
       </c>
       <c r="R31" t="n">
-        <v>6233326</v>
+        <v>6233099</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4240,12 +4240,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4272,10 +4272,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121471684</v>
+        <v>121471939</v>
       </c>
       <c r="B32" t="n">
-        <v>80412</v>
+        <v>94599</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4284,25 +4284,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1557</v>
+        <v>2667</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Röd pysslinglav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Thelopsis rubella</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Nyl.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>428227</v>
+        <v>428046</v>
       </c>
       <c r="R32" t="n">
-        <v>6233392</v>
+        <v>6233296</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4342,12 +4342,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4374,10 +4374,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121471804</v>
+        <v>121471934</v>
       </c>
       <c r="B33" t="n">
-        <v>76948</v>
+        <v>94393</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4386,25 +4386,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1342</v>
+        <v>2779</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4414,10 +4414,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>428335</v>
+        <v>428090</v>
       </c>
       <c r="R33" t="n">
-        <v>6233286</v>
+        <v>6233309</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4444,12 +4444,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4476,10 +4476,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121471855</v>
+        <v>121471689</v>
       </c>
       <c r="B34" t="n">
-        <v>94393</v>
+        <v>94599</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4492,21 +4492,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>428365</v>
+        <v>428161</v>
       </c>
       <c r="R34" t="n">
-        <v>6233269</v>
+        <v>6233396</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4546,12 +4546,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4578,10 +4578,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121471817</v>
+        <v>121471914</v>
       </c>
       <c r="B35" t="n">
-        <v>74697</v>
+        <v>94599</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4594,21 +4594,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6439</v>
+        <v>2667</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>428312</v>
+        <v>428318</v>
       </c>
       <c r="R35" t="n">
-        <v>6233323</v>
+        <v>6233075</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4648,12 +4648,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4680,10 +4680,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121471833</v>
+        <v>121471873</v>
       </c>
       <c r="B36" t="n">
-        <v>80242</v>
+        <v>74563</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4692,25 +4692,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>230185</v>
+        <v>1116</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4720,10 +4720,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>428139</v>
+        <v>428301</v>
       </c>
       <c r="R36" t="n">
-        <v>6233315</v>
+        <v>6233171</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4782,10 +4782,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121471876</v>
+        <v>121471814</v>
       </c>
       <c r="B37" t="n">
-        <v>80285</v>
+        <v>80255</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4794,25 +4794,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1223</v>
+        <v>1144</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rikfruktig blemlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phlyctis agelaea</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Flot.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>428446</v>
+        <v>428331</v>
       </c>
       <c r="R37" t="n">
-        <v>6233151</v>
+        <v>6233339</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4884,7 +4884,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121471685</v>
+        <v>121471831</v>
       </c>
       <c r="B38" t="n">
         <v>80255</v>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>428228</v>
+        <v>428145</v>
       </c>
       <c r="R38" t="n">
-        <v>6233391</v>
+        <v>6233315</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4954,12 +4954,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4986,10 +4986,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121471878</v>
+        <v>121471922</v>
       </c>
       <c r="B39" t="n">
-        <v>96773</v>
+        <v>76948</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4998,25 +4998,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2604</v>
+        <v>1342</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>428445</v>
+        <v>428091</v>
       </c>
       <c r="R39" t="n">
-        <v>6233151</v>
+        <v>6233385</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5088,10 +5088,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121471868</v>
+        <v>121471825</v>
       </c>
       <c r="B40" t="n">
-        <v>94599</v>
+        <v>80242</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5104,21 +5104,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5128,10 +5128,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>428347</v>
+        <v>428233</v>
       </c>
       <c r="R40" t="n">
-        <v>6233241</v>
+        <v>6233332</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5190,10 +5190,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121471835</v>
+        <v>121471533</v>
       </c>
       <c r="B41" t="n">
-        <v>96725</v>
+        <v>80242</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5206,21 +5206,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5230,10 +5230,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>428145</v>
+        <v>428144</v>
       </c>
       <c r="R41" t="n">
-        <v>6233244</v>
+        <v>6233229</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5260,12 +5260,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5292,10 +5292,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121471697</v>
+        <v>121471535</v>
       </c>
       <c r="B42" t="n">
-        <v>74699</v>
+        <v>76948</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5304,25 +5304,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>306</v>
+        <v>1342</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5332,10 +5332,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>428043</v>
+        <v>428160</v>
       </c>
       <c r="R42" t="n">
-        <v>6233298</v>
+        <v>6233209</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5394,10 +5394,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121471865</v>
+        <v>121471811</v>
       </c>
       <c r="B43" t="n">
-        <v>74699</v>
+        <v>76948</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5406,25 +5406,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>306</v>
+        <v>1342</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5434,10 +5434,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>428438</v>
+        <v>428349</v>
       </c>
       <c r="R43" t="n">
-        <v>6233202</v>
+        <v>6233325</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5496,10 +5496,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121471896</v>
+        <v>121471801</v>
       </c>
       <c r="B44" t="n">
-        <v>80578</v>
+        <v>80255</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5508,25 +5508,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1182</v>
+        <v>1144</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5539,7 +5539,7 @@
         <v>428370</v>
       </c>
       <c r="R44" t="n">
-        <v>6233102</v>
+        <v>6233336</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5566,12 +5566,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5598,10 +5598,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121471542</v>
+        <v>121471540</v>
       </c>
       <c r="B45" t="n">
-        <v>80255</v>
+        <v>96725</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5610,25 +5610,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>428198</v>
+        <v>428227</v>
       </c>
       <c r="R45" t="n">
-        <v>6233249</v>
+        <v>6233132</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5700,10 +5700,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121471879</v>
+        <v>121471926</v>
       </c>
       <c r="B46" t="n">
-        <v>76948</v>
+        <v>94393</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5712,25 +5712,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1342</v>
+        <v>2779</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>428445</v>
+        <v>428073</v>
       </c>
       <c r="R46" t="n">
-        <v>6233151</v>
+        <v>6233383</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5802,10 +5802,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121471694</v>
+        <v>121471802</v>
       </c>
       <c r="B47" t="n">
-        <v>80255</v>
+        <v>94588</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5814,25 +5814,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1144</v>
+        <v>2671</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5842,10 +5842,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>428125</v>
+        <v>428332</v>
       </c>
       <c r="R47" t="n">
-        <v>6233379</v>
+        <v>6233287</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5872,12 +5872,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5904,10 +5904,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121471809</v>
+        <v>121471683</v>
       </c>
       <c r="B48" t="n">
-        <v>74563</v>
+        <v>94588</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5916,25 +5916,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1116</v>
+        <v>2671</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5944,10 +5944,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>428352</v>
+        <v>428278</v>
       </c>
       <c r="R48" t="n">
-        <v>6233315</v>
+        <v>6233417</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5974,12 +5974,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6006,10 +6006,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121471828</v>
+        <v>121471537</v>
       </c>
       <c r="B49" t="n">
-        <v>80242</v>
+        <v>96725</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6022,21 +6022,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6046,10 +6046,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>428185</v>
+        <v>428163</v>
       </c>
       <c r="R49" t="n">
-        <v>6233289</v>
+        <v>6233193</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6090,7 +6090,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6109,7 +6108,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121471924</v>
+        <v>121471859</v>
       </c>
       <c r="B50" t="n">
         <v>80242</v>
@@ -6149,10 +6148,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>428097</v>
+        <v>428404</v>
       </c>
       <c r="R50" t="n">
-        <v>6233382</v>
+        <v>6233275</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6179,12 +6178,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6211,10 +6210,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121471905</v>
+        <v>121471936</v>
       </c>
       <c r="B51" t="n">
-        <v>74609</v>
+        <v>94609</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6223,25 +6222,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1118</v>
+        <v>1080</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6251,10 +6250,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>428377</v>
+        <v>428079</v>
       </c>
       <c r="R51" t="n">
-        <v>6233095</v>
+        <v>6233262</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6313,10 +6312,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121471904</v>
+        <v>121471806</v>
       </c>
       <c r="B52" t="n">
-        <v>78407</v>
+        <v>80255</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6325,25 +6324,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>924</v>
+        <v>1144</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6353,10 +6352,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>428387</v>
+        <v>428325</v>
       </c>
       <c r="R52" t="n">
-        <v>6233098</v>
+        <v>6233291</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6383,12 +6382,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6415,7 +6414,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121471849</v>
+        <v>121471542</v>
       </c>
       <c r="B53" t="n">
         <v>80255</v>
@@ -6455,10 +6454,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>428299</v>
+        <v>428198</v>
       </c>
       <c r="R53" t="n">
-        <v>6233126</v>
+        <v>6233249</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6485,12 +6484,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6517,10 +6516,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121471911</v>
+        <v>121471940</v>
       </c>
       <c r="B54" t="n">
-        <v>76948</v>
+        <v>94609</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6529,25 +6528,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1342</v>
+        <v>1080</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6557,10 +6556,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>428352</v>
+        <v>428037</v>
       </c>
       <c r="R54" t="n">
-        <v>6233082</v>
+        <v>6233291</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6619,7 +6618,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121471853</v>
+        <v>121471867</v>
       </c>
       <c r="B55" t="n">
         <v>76948</v>
@@ -6659,10 +6658,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>428311</v>
+        <v>428442</v>
       </c>
       <c r="R55" t="n">
-        <v>6233183</v>
+        <v>6233170</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6721,7 +6720,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121471844</v>
+        <v>121471870</v>
       </c>
       <c r="B56" t="n">
         <v>76948</v>
@@ -6761,10 +6760,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>428248</v>
+        <v>428356</v>
       </c>
       <c r="R56" t="n">
-        <v>6233241</v>
+        <v>6233243</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6823,10 +6822,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121471937</v>
+        <v>121471815</v>
       </c>
       <c r="B57" t="n">
-        <v>96725</v>
+        <v>80412</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6835,25 +6834,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2606</v>
+        <v>1557</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Röd pysslinglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelopsis rubella</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Nyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6863,10 +6862,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>428062</v>
+        <v>428333</v>
       </c>
       <c r="R57" t="n">
-        <v>6233301</v>
+        <v>6233339</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6893,12 +6892,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6925,10 +6924,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121471808</v>
+        <v>121471697</v>
       </c>
       <c r="B58" t="n">
-        <v>80255</v>
+        <v>74699</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6937,25 +6936,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1144</v>
+        <v>306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6965,10 +6964,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>428350</v>
+        <v>428043</v>
       </c>
       <c r="R58" t="n">
-        <v>6233316</v>
+        <v>6233298</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6995,12 +6994,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7027,10 +7026,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121471834</v>
+        <v>121471876</v>
       </c>
       <c r="B59" t="n">
-        <v>80255</v>
+        <v>80285</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7039,25 +7038,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1144</v>
+        <v>1223</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Rikfruktig blemlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Phlyctis agelaea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Flot.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7067,10 +7066,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>428137</v>
+        <v>428446</v>
       </c>
       <c r="R59" t="n">
-        <v>6233320</v>
+        <v>6233151</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7129,10 +7128,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121471532</v>
+        <v>121471685</v>
       </c>
       <c r="B60" t="n">
-        <v>94599</v>
+        <v>80255</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7141,25 +7140,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7169,10 +7168,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>428133</v>
+        <v>428228</v>
       </c>
       <c r="R60" t="n">
-        <v>6233219</v>
+        <v>6233391</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7231,10 +7230,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121471841</v>
+        <v>121471929</v>
       </c>
       <c r="B61" t="n">
-        <v>96725</v>
+        <v>94393</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7247,21 +7246,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2606</v>
+        <v>2779</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7271,10 +7270,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>428221</v>
+        <v>428078</v>
       </c>
       <c r="R61" t="n">
-        <v>6233212</v>
+        <v>6233294</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7301,12 +7300,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7333,7 +7332,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121471944</v>
+        <v>121471868</v>
       </c>
       <c r="B62" t="n">
         <v>94599</v>
@@ -7373,10 +7372,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>428034</v>
+        <v>428347</v>
       </c>
       <c r="R62" t="n">
-        <v>6233348</v>
+        <v>6233241</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7403,12 +7402,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7435,10 +7434,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121471534</v>
+        <v>121471944</v>
       </c>
       <c r="B63" t="n">
-        <v>96725</v>
+        <v>94599</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7451,21 +7450,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7475,10 +7474,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>428147</v>
+        <v>428034</v>
       </c>
       <c r="R63" t="n">
-        <v>6233224</v>
+        <v>6233348</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7505,12 +7504,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7537,10 +7536,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121471908</v>
+        <v>121471544</v>
       </c>
       <c r="B64" t="n">
-        <v>74609</v>
+        <v>94599</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7549,25 +7548,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1118</v>
+        <v>2667</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7577,10 +7576,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>428377</v>
+        <v>428219</v>
       </c>
       <c r="R64" t="n">
-        <v>6233090</v>
+        <v>6233278</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7607,12 +7606,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7639,10 +7638,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121471859</v>
+        <v>121471855</v>
       </c>
       <c r="B65" t="n">
-        <v>80242</v>
+        <v>94393</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7655,21 +7654,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>230185</v>
+        <v>2779</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7679,10 +7678,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>428404</v>
+        <v>428365</v>
       </c>
       <c r="R65" t="n">
-        <v>6233275</v>
+        <v>6233269</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7741,10 +7740,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121471827</v>
+        <v>121471841</v>
       </c>
       <c r="B66" t="n">
-        <v>94599</v>
+        <v>96725</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7757,21 +7756,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7781,10 +7780,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>428185</v>
+        <v>428221</v>
       </c>
       <c r="R66" t="n">
-        <v>6233287</v>
+        <v>6233212</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7843,10 +7842,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121471683</v>
+        <v>121471835</v>
       </c>
       <c r="B67" t="n">
-        <v>94588</v>
+        <v>96725</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7859,21 +7858,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7883,10 +7882,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>428278</v>
+        <v>428145</v>
       </c>
       <c r="R67" t="n">
-        <v>6233417</v>
+        <v>6233244</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7913,12 +7912,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7945,10 +7944,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121471856</v>
+        <v>121471862</v>
       </c>
       <c r="B68" t="n">
-        <v>76948</v>
+        <v>80242</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7957,25 +7956,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7985,10 +7984,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>428360</v>
+        <v>428411</v>
       </c>
       <c r="R68" t="n">
-        <v>6233266</v>
+        <v>6233213</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8047,10 +8046,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121471934</v>
+        <v>121471846</v>
       </c>
       <c r="B69" t="n">
-        <v>94393</v>
+        <v>80242</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8063,21 +8062,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2779</v>
+        <v>230185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8087,10 +8086,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>428090</v>
+        <v>428241</v>
       </c>
       <c r="R69" t="n">
-        <v>6233309</v>
+        <v>6233222</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8117,12 +8116,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8149,10 +8148,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121471933</v>
+        <v>121471851</v>
       </c>
       <c r="B70" t="n">
-        <v>94588</v>
+        <v>78863</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8165,21 +8164,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2671</v>
+        <v>6459</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8189,10 +8188,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>428090</v>
+        <v>428293</v>
       </c>
       <c r="R70" t="n">
-        <v>6233309</v>
+        <v>6233170</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8219,12 +8218,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8251,10 +8250,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121471942</v>
+        <v>121471912</v>
       </c>
       <c r="B71" t="n">
-        <v>76948</v>
+        <v>78407</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8267,21 +8266,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1342</v>
+        <v>924</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8291,10 +8290,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>428032</v>
+        <v>428351</v>
       </c>
       <c r="R71" t="n">
-        <v>6233345</v>
+        <v>6233082</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8353,10 +8352,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121471866</v>
+        <v>121471908</v>
       </c>
       <c r="B72" t="n">
-        <v>80242</v>
+        <v>74609</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8365,25 +8364,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>230185</v>
+        <v>1118</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8393,10 +8392,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>428442</v>
+        <v>428377</v>
       </c>
       <c r="R72" t="n">
-        <v>6233170</v>
+        <v>6233090</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8423,12 +8422,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8455,10 +8454,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121471938</v>
+        <v>121471930</v>
       </c>
       <c r="B73" t="n">
-        <v>80242</v>
+        <v>74609</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8467,25 +8466,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>230185</v>
+        <v>1118</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8495,10 +8494,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>428062</v>
+        <v>428078</v>
       </c>
       <c r="R73" t="n">
-        <v>6233301</v>
+        <v>6233294</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8557,10 +8556,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121471816</v>
+        <v>121471829</v>
       </c>
       <c r="B74" t="n">
-        <v>96773</v>
+        <v>80255</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8569,25 +8568,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2604</v>
+        <v>1144</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8597,10 +8596,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>428317</v>
+        <v>428147</v>
       </c>
       <c r="R74" t="n">
-        <v>6233324</v>
+        <v>6233304</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8659,10 +8658,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121471877</v>
+        <v>121471923</v>
       </c>
       <c r="B75" t="n">
-        <v>94599</v>
+        <v>80255</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8671,25 +8670,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8699,10 +8698,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>428445</v>
+        <v>428091</v>
       </c>
       <c r="R75" t="n">
-        <v>6233151</v>
+        <v>6233386</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8729,12 +8728,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8761,10 +8760,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121471813</v>
+        <v>121471927</v>
       </c>
       <c r="B76" t="n">
-        <v>94588</v>
+        <v>76948</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8773,25 +8772,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2671</v>
+        <v>1342</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8801,10 +8800,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>428332</v>
+        <v>428074</v>
       </c>
       <c r="R76" t="n">
-        <v>6233341</v>
+        <v>6233297</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8831,12 +8830,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8863,10 +8862,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121471864</v>
+        <v>121471866</v>
       </c>
       <c r="B77" t="n">
-        <v>94588</v>
+        <v>80242</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8879,21 +8878,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2671</v>
+        <v>230185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8903,10 +8902,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>428410</v>
+        <v>428442</v>
       </c>
       <c r="R77" t="n">
-        <v>6233214</v>
+        <v>6233170</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8965,10 +8964,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121471811</v>
+        <v>121471931</v>
       </c>
       <c r="B78" t="n">
-        <v>76948</v>
+        <v>80255</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8977,25 +8976,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9005,10 +9004,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>428349</v>
+        <v>428075</v>
       </c>
       <c r="R78" t="n">
-        <v>6233325</v>
+        <v>6233301</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9035,12 +9034,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9067,10 +9066,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121471861</v>
+        <v>121471919</v>
       </c>
       <c r="B79" t="n">
-        <v>94599</v>
+        <v>80255</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9079,25 +9078,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9107,10 +9106,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>428404</v>
+        <v>428106</v>
       </c>
       <c r="R79" t="n">
-        <v>6233275</v>
+        <v>6233304</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9137,12 +9136,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9169,10 +9168,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121471907</v>
+        <v>121471800</v>
       </c>
       <c r="B80" t="n">
-        <v>76948</v>
+        <v>80255</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9181,25 +9180,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9209,10 +9208,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>428375</v>
+        <v>428387</v>
       </c>
       <c r="R80" t="n">
-        <v>6233092</v>
+        <v>6233322</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9239,12 +9238,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9271,7 +9270,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121471686</v>
+        <v>121471845</v>
       </c>
       <c r="B81" t="n">
         <v>80255</v>
@@ -9311,10 +9310,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>428187</v>
+        <v>428248</v>
       </c>
       <c r="R81" t="n">
-        <v>6233403</v>
+        <v>6233242</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9341,12 +9340,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9373,10 +9372,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121471915</v>
+        <v>121471693</v>
       </c>
       <c r="B82" t="n">
-        <v>96773</v>
+        <v>94588</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9389,21 +9388,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2604</v>
+        <v>2671</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9413,10 +9412,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>428281</v>
+        <v>428125</v>
       </c>
       <c r="R82" t="n">
-        <v>6233082</v>
+        <v>6233379</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9443,12 +9442,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9475,7 +9474,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121471539</v>
+        <v>121471813</v>
       </c>
       <c r="B83" t="n">
         <v>94588</v>
@@ -9515,10 +9514,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>428262</v>
+        <v>428332</v>
       </c>
       <c r="R83" t="n">
-        <v>6233134</v>
+        <v>6233341</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9545,12 +9544,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9577,10 +9576,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121471914</v>
+        <v>121471863</v>
       </c>
       <c r="B84" t="n">
-        <v>94599</v>
+        <v>96725</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9593,21 +9592,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9617,10 +9616,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>428318</v>
+        <v>428411</v>
       </c>
       <c r="R84" t="n">
-        <v>6233075</v>
+        <v>6233213</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9647,12 +9646,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9679,10 +9678,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121471543</v>
+        <v>121471688</v>
       </c>
       <c r="B85" t="n">
-        <v>80242</v>
+        <v>96725</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9695,21 +9694,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9719,10 +9718,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>428209</v>
+        <v>428159</v>
       </c>
       <c r="R85" t="n">
-        <v>6233279</v>
+        <v>6233394</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9781,10 +9780,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121471926</v>
+        <v>121471534</v>
       </c>
       <c r="B86" t="n">
-        <v>94393</v>
+        <v>96725</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9797,21 +9796,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2779</v>
+        <v>2606</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9821,10 +9820,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>428073</v>
+        <v>428147</v>
       </c>
       <c r="R86" t="n">
-        <v>6233383</v>
+        <v>6233224</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9851,12 +9850,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9883,10 +9882,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121471931</v>
+        <v>121471816</v>
       </c>
       <c r="B87" t="n">
-        <v>80255</v>
+        <v>96773</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9895,25 +9894,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1144</v>
+        <v>2604</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9923,10 +9922,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>428075</v>
+        <v>428317</v>
       </c>
       <c r="R87" t="n">
-        <v>6233301</v>
+        <v>6233324</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9953,12 +9952,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9985,10 +9984,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121471857</v>
+        <v>121471799</v>
       </c>
       <c r="B88" t="n">
-        <v>80255</v>
+        <v>94588</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9997,25 +9996,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1144</v>
+        <v>2671</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10025,10 +10024,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>428362</v>
+        <v>428389</v>
       </c>
       <c r="R88" t="n">
-        <v>6233272</v>
+        <v>6233324</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10087,10 +10086,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121471881</v>
+        <v>121471852</v>
       </c>
       <c r="B89" t="n">
-        <v>78407</v>
+        <v>80255</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10099,25 +10098,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>924</v>
+        <v>1144</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10127,10 +10126,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>428445</v>
+        <v>428311</v>
       </c>
       <c r="R89" t="n">
-        <v>6233151</v>
+        <v>6233183</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10189,10 +10188,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121471696</v>
+        <v>121471840</v>
       </c>
       <c r="B90" t="n">
-        <v>96725</v>
+        <v>78987</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10205,21 +10204,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2606</v>
+        <v>6431</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10229,10 +10228,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>428054</v>
+        <v>428183</v>
       </c>
       <c r="R90" t="n">
-        <v>6233337</v>
+        <v>6233239</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10259,12 +10258,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10291,10 +10290,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121471867</v>
+        <v>121471916</v>
       </c>
       <c r="B91" t="n">
-        <v>76948</v>
+        <v>94609</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10303,25 +10302,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1342</v>
+        <v>1080</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10331,10 +10330,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>428442</v>
+        <v>428283</v>
       </c>
       <c r="R91" t="n">
-        <v>6233170</v>
+        <v>6233084</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10361,12 +10360,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10393,7 +10392,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121471824</v>
+        <v>121471909</v>
       </c>
       <c r="B92" t="n">
         <v>76948</v>
@@ -10433,10 +10432,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>428288</v>
+        <v>428373</v>
       </c>
       <c r="R92" t="n">
-        <v>6233325</v>
+        <v>6233088</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10463,12 +10462,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10495,10 +10494,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121471917</v>
+        <v>121471920</v>
       </c>
       <c r="B93" t="n">
-        <v>80242</v>
+        <v>91112</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10507,25 +10506,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>230185</v>
+        <v>2023</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Sydlig sotticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Ischnoderma resinosum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schrad.) P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10535,10 +10534,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>428284</v>
+        <v>428095</v>
       </c>
       <c r="R93" t="n">
-        <v>6233109</v>
+        <v>6233349</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10597,10 +10596,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121471928</v>
+        <v>121471903</v>
       </c>
       <c r="B94" t="n">
-        <v>80255</v>
+        <v>76948</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10609,25 +10608,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10637,10 +10636,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>428075</v>
+        <v>428385</v>
       </c>
       <c r="R94" t="n">
-        <v>6233294</v>
+        <v>6233097</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10699,10 +10698,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121471897</v>
+        <v>121471812</v>
       </c>
       <c r="B95" t="n">
-        <v>78407</v>
+        <v>94393</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10711,25 +10710,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>924</v>
+        <v>2779</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10739,10 +10738,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>428369</v>
+        <v>428331</v>
       </c>
       <c r="R95" t="n">
-        <v>6233104</v>
+        <v>6233335</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10769,12 +10768,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10801,10 +10800,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121471805</v>
+        <v>121471925</v>
       </c>
       <c r="B96" t="n">
-        <v>80255</v>
+        <v>94601</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10813,25 +10812,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1144</v>
+        <v>2666</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10841,10 +10840,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>428333</v>
+        <v>428076</v>
       </c>
       <c r="R96" t="n">
-        <v>6233283</v>
+        <v>6233382</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10871,12 +10870,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10903,10 +10902,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121471852</v>
+        <v>121471820</v>
       </c>
       <c r="B97" t="n">
-        <v>80255</v>
+        <v>94393</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10915,25 +10914,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1144</v>
+        <v>2779</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10943,10 +10942,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>428311</v>
+        <v>428304</v>
       </c>
       <c r="R97" t="n">
-        <v>6233183</v>
+        <v>6233306</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11005,10 +11004,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121471922</v>
+        <v>121471819</v>
       </c>
       <c r="B98" t="n">
-        <v>76948</v>
+        <v>94599</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11017,25 +11016,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1342</v>
+        <v>2667</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11045,10 +11044,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>428091</v>
+        <v>428304</v>
       </c>
       <c r="R98" t="n">
-        <v>6233385</v>
+        <v>6233306</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11075,12 +11074,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11107,10 +11106,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121471689</v>
+        <v>121471943</v>
       </c>
       <c r="B99" t="n">
-        <v>94599</v>
+        <v>96725</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11123,21 +11122,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11147,10 +11146,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>428161</v>
+        <v>428034</v>
       </c>
       <c r="R99" t="n">
-        <v>6233396</v>
+        <v>6233348</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11177,12 +11176,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11209,10 +11208,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121471854</v>
+        <v>121471911</v>
       </c>
       <c r="B100" t="n">
-        <v>96725</v>
+        <v>76948</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11221,25 +11220,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11249,10 +11248,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>428302</v>
+        <v>428352</v>
       </c>
       <c r="R100" t="n">
-        <v>6233177</v>
+        <v>6233082</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11279,12 +11278,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11311,10 +11310,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121471923</v>
+        <v>121471853</v>
       </c>
       <c r="B101" t="n">
-        <v>80255</v>
+        <v>76948</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11323,25 +11322,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11351,10 +11350,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>428091</v>
+        <v>428311</v>
       </c>
       <c r="R101" t="n">
-        <v>6233386</v>
+        <v>6233183</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11381,12 +11380,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11413,10 +11412,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121471845</v>
+        <v>121471807</v>
       </c>
       <c r="B102" t="n">
-        <v>80255</v>
+        <v>76948</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11425,25 +11424,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11453,10 +11452,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>428248</v>
+        <v>428327</v>
       </c>
       <c r="R102" t="n">
-        <v>6233242</v>
+        <v>6233292</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11515,10 +11514,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121471836</v>
+        <v>121471913</v>
       </c>
       <c r="B103" t="n">
-        <v>94588</v>
+        <v>76948</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11527,25 +11526,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2671</v>
+        <v>1342</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11555,10 +11554,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>428145</v>
+        <v>428342</v>
       </c>
       <c r="R103" t="n">
-        <v>6233244</v>
+        <v>6233082</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11585,12 +11584,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11617,10 +11616,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121471802</v>
+        <v>121471897</v>
       </c>
       <c r="B104" t="n">
-        <v>94588</v>
+        <v>78407</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11629,25 +11628,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2671</v>
+        <v>924</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11657,10 +11656,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>428332</v>
+        <v>428369</v>
       </c>
       <c r="R104" t="n">
-        <v>6233287</v>
+        <v>6233104</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11687,12 +11686,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11719,10 +11718,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121471863</v>
+        <v>121471882</v>
       </c>
       <c r="B105" t="n">
-        <v>96725</v>
+        <v>74609</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11731,25 +11730,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2606</v>
+        <v>1118</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11759,10 +11758,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>428411</v>
+        <v>428445</v>
       </c>
       <c r="R105" t="n">
-        <v>6233213</v>
+        <v>6233151</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11821,10 +11820,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121471839</v>
+        <v>121471928</v>
       </c>
       <c r="B106" t="n">
-        <v>94588</v>
+        <v>80255</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11833,25 +11832,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2671</v>
+        <v>1144</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11861,10 +11860,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>428184</v>
+        <v>428075</v>
       </c>
       <c r="R106" t="n">
-        <v>6233240</v>
+        <v>6233294</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11891,12 +11890,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11923,10 +11922,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121471840</v>
+        <v>121471536</v>
       </c>
       <c r="B107" t="n">
-        <v>78987</v>
+        <v>80578</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11935,25 +11934,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6431</v>
+        <v>1182</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11963,10 +11962,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>428183</v>
+        <v>428166</v>
       </c>
       <c r="R107" t="n">
-        <v>6233239</v>
+        <v>6233202</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11993,12 +11992,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12025,50 +12024,53 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121471895</v>
+        <v>121471875</v>
       </c>
       <c r="B108" t="n">
-        <v>80242</v>
+        <v>80255</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>428355</v>
+        <v>428340</v>
       </c>
       <c r="R108" t="n">
-        <v>6233123</v>
+        <v>6233229</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12095,12 +12097,17 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>kollekt</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12108,6 +12115,11 @@
       </c>
       <c r="AE108" t="b">
         <v>0</v>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG108" t="b">
         <v>0</v>
@@ -12127,10 +12139,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121471936</v>
+        <v>121471854</v>
       </c>
       <c r="B109" t="n">
-        <v>94609</v>
+        <v>96725</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12143,21 +12155,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1080</v>
+        <v>2606</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12167,10 +12179,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>428079</v>
+        <v>428302</v>
       </c>
       <c r="R109" t="n">
-        <v>6233262</v>
+        <v>6233177</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12197,12 +12209,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12229,10 +12241,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121471536</v>
+        <v>121471935</v>
       </c>
       <c r="B110" t="n">
-        <v>80578</v>
+        <v>80242</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12241,25 +12253,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1182</v>
+        <v>230185</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12269,10 +12281,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>428166</v>
+        <v>428097</v>
       </c>
       <c r="R110" t="n">
-        <v>6233202</v>
+        <v>6233286</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12299,12 +12311,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12331,10 +12343,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121471930</v>
+        <v>121471917</v>
       </c>
       <c r="B111" t="n">
-        <v>74609</v>
+        <v>80242</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12343,25 +12355,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1118</v>
+        <v>230185</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12371,10 +12383,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>428078</v>
+        <v>428284</v>
       </c>
       <c r="R111" t="n">
-        <v>6233294</v>
+        <v>6233109</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12433,10 +12445,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121471860</v>
+        <v>121471915</v>
       </c>
       <c r="B112" t="n">
-        <v>96725</v>
+        <v>96773</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12449,21 +12461,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2606</v>
+        <v>2604</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12473,10 +12485,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>428404</v>
+        <v>428281</v>
       </c>
       <c r="R112" t="n">
-        <v>6233275</v>
+        <v>6233082</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12503,12 +12515,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12535,10 +12547,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121471927</v>
+        <v>121471837</v>
       </c>
       <c r="B113" t="n">
-        <v>76948</v>
+        <v>80242</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12547,25 +12559,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12575,10 +12587,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>428074</v>
+        <v>428145</v>
       </c>
       <c r="R113" t="n">
-        <v>6233297</v>
+        <v>6233244</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12605,12 +12617,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12637,10 +12649,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121471537</v>
+        <v>121471808</v>
       </c>
       <c r="B114" t="n">
-        <v>96725</v>
+        <v>80255</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12649,25 +12661,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12677,10 +12689,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>428163</v>
+        <v>428350</v>
       </c>
       <c r="R114" t="n">
-        <v>6233193</v>
+        <v>6233316</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12707,12 +12719,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12739,10 +12751,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121471818</v>
+        <v>121471531</v>
       </c>
       <c r="B115" t="n">
-        <v>96725</v>
+        <v>94609</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12755,21 +12767,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2606</v>
+        <v>1080</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12779,10 +12791,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>428307</v>
+        <v>428110</v>
       </c>
       <c r="R115" t="n">
-        <v>6233311</v>
+        <v>6233224</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12809,12 +12821,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12841,10 +12853,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121471925</v>
+        <v>121471844</v>
       </c>
       <c r="B116" t="n">
-        <v>94601</v>
+        <v>76948</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12853,25 +12865,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2666</v>
+        <v>1342</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12881,10 +12893,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>428076</v>
+        <v>428248</v>
       </c>
       <c r="R116" t="n">
-        <v>6233382</v>
+        <v>6233241</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12911,12 +12923,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12943,7 +12955,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121471909</v>
+        <v>121471879</v>
       </c>
       <c r="B117" t="n">
         <v>76948</v>
@@ -12983,10 +12995,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>428373</v>
+        <v>428445</v>
       </c>
       <c r="R117" t="n">
-        <v>6233088</v>
+        <v>6233151</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13013,12 +13025,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13045,10 +13057,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121471901</v>
+        <v>121471905</v>
       </c>
       <c r="B118" t="n">
-        <v>76948</v>
+        <v>74609</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13061,21 +13073,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1342</v>
+        <v>1118</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13085,10 +13097,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>428390</v>
+        <v>428377</v>
       </c>
       <c r="R118" t="n">
-        <v>6233099</v>
+        <v>6233095</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13147,10 +13159,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121471945</v>
+        <v>121471810</v>
       </c>
       <c r="B119" t="n">
-        <v>96773</v>
+        <v>80255</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13159,25 +13171,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2604</v>
+        <v>1144</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13187,10 +13199,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>428035</v>
+        <v>428347</v>
       </c>
       <c r="R119" t="n">
-        <v>6233349</v>
+        <v>6233326</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13217,12 +13229,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13249,10 +13261,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121471820</v>
+        <v>121471822</v>
       </c>
       <c r="B120" t="n">
-        <v>94393</v>
+        <v>94599</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13265,21 +13277,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13289,10 +13301,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>428304</v>
+        <v>428288</v>
       </c>
       <c r="R120" t="n">
-        <v>6233306</v>
+        <v>6233325</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13351,10 +13363,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121471910</v>
+        <v>121471933</v>
       </c>
       <c r="B121" t="n">
-        <v>76948</v>
+        <v>94588</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13363,25 +13375,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1342</v>
+        <v>2671</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13391,10 +13403,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>428377</v>
+        <v>428090</v>
       </c>
       <c r="R121" t="n">
-        <v>6233090</v>
+        <v>6233309</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13453,7 +13465,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121471541</v>
+        <v>121471850</v>
       </c>
       <c r="B122" t="n">
         <v>80242</v>
@@ -13493,10 +13505,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>428209</v>
+        <v>428293</v>
       </c>
       <c r="R122" t="n">
-        <v>6233184</v>
+        <v>6233170</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13523,12 +13535,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13657,10 +13669,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121471919</v>
+        <v>121471871</v>
       </c>
       <c r="B124" t="n">
-        <v>80255</v>
+        <v>80242</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13669,25 +13681,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13697,10 +13709,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>428106</v>
+        <v>428302</v>
       </c>
       <c r="R124" t="n">
-        <v>6233304</v>
+        <v>6233176</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13727,12 +13739,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13759,10 +13771,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121471858</v>
+        <v>121471945</v>
       </c>
       <c r="B125" t="n">
-        <v>80255</v>
+        <v>96773</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13771,25 +13783,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1144</v>
+        <v>2604</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13799,10 +13811,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>428372</v>
+        <v>428035</v>
       </c>
       <c r="R125" t="n">
-        <v>6233270</v>
+        <v>6233349</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13829,12 +13841,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13861,10 +13873,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121471851</v>
+        <v>121471818</v>
       </c>
       <c r="B126" t="n">
-        <v>78863</v>
+        <v>96725</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13877,21 +13889,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6459</v>
+        <v>2606</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13901,10 +13913,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>428293</v>
+        <v>428307</v>
       </c>
       <c r="R126" t="n">
-        <v>6233170</v>
+        <v>6233311</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13963,10 +13975,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121471899</v>
+        <v>121471691</v>
       </c>
       <c r="B127" t="n">
-        <v>94393</v>
+        <v>96725</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13979,21 +13991,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2779</v>
+        <v>2606</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14003,10 +14015,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>428389</v>
+        <v>428128</v>
       </c>
       <c r="R127" t="n">
-        <v>6233099</v>
+        <v>6233385</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14033,12 +14045,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14065,10 +14077,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121471850</v>
+        <v>121471686</v>
       </c>
       <c r="B128" t="n">
-        <v>80242</v>
+        <v>80255</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14077,25 +14089,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14105,10 +14117,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>428293</v>
+        <v>428187</v>
       </c>
       <c r="R128" t="n">
-        <v>6233170</v>
+        <v>6233403</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14135,12 +14147,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14167,10 +14179,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121471846</v>
+        <v>121471809</v>
       </c>
       <c r="B129" t="n">
-        <v>80242</v>
+        <v>74563</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14179,25 +14191,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>230185</v>
+        <v>1116</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14207,10 +14219,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>428241</v>
+        <v>428352</v>
       </c>
       <c r="R129" t="n">
-        <v>6233222</v>
+        <v>6233315</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14269,10 +14281,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121471916</v>
+        <v>121471856</v>
       </c>
       <c r="B130" t="n">
-        <v>94609</v>
+        <v>76948</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14281,25 +14293,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1080</v>
+        <v>1342</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14309,10 +14321,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>428283</v>
+        <v>428360</v>
       </c>
       <c r="R130" t="n">
-        <v>6233084</v>
+        <v>6233266</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14339,12 +14351,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14371,10 +14383,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121471810</v>
+        <v>121471847</v>
       </c>
       <c r="B131" t="n">
-        <v>80255</v>
+        <v>76948</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14383,25 +14395,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14411,10 +14423,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>428347</v>
+        <v>428300</v>
       </c>
       <c r="R131" t="n">
-        <v>6233326</v>
+        <v>6233125</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14473,10 +14485,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121471831</v>
+        <v>121471824</v>
       </c>
       <c r="B132" t="n">
-        <v>80255</v>
+        <v>76948</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14485,25 +14497,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14513,10 +14525,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>428145</v>
+        <v>428288</v>
       </c>
       <c r="R132" t="n">
-        <v>6233315</v>
+        <v>6233325</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14575,10 +14587,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121471695</v>
+        <v>121471907</v>
       </c>
       <c r="B133" t="n">
-        <v>80242</v>
+        <v>76948</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14587,25 +14599,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14615,10 +14627,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>428053</v>
+        <v>428375</v>
       </c>
       <c r="R133" t="n">
-        <v>6233336</v>
+        <v>6233092</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14645,12 +14657,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14677,10 +14689,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121471940</v>
+        <v>121471692</v>
       </c>
       <c r="B134" t="n">
-        <v>94609</v>
+        <v>94599</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14693,21 +14705,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1080</v>
+        <v>2667</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14717,10 +14729,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>428037</v>
+        <v>428126</v>
       </c>
       <c r="R134" t="n">
-        <v>6233291</v>
+        <v>6233380</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14747,12 +14759,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14779,10 +14791,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121471862</v>
+        <v>121471827</v>
       </c>
       <c r="B135" t="n">
-        <v>80242</v>
+        <v>94599</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14795,21 +14807,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14819,10 +14831,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>428411</v>
+        <v>428185</v>
       </c>
       <c r="R135" t="n">
-        <v>6233213</v>
+        <v>6233287</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14881,10 +14893,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121471807</v>
+        <v>121471937</v>
       </c>
       <c r="B136" t="n">
-        <v>76948</v>
+        <v>96725</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14893,25 +14905,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14921,10 +14933,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>428327</v>
+        <v>428062</v>
       </c>
       <c r="R136" t="n">
-        <v>6233292</v>
+        <v>6233301</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14951,12 +14963,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14983,10 +14995,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121471819</v>
+        <v>121471833</v>
       </c>
       <c r="B137" t="n">
-        <v>94599</v>
+        <v>80242</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14999,21 +15011,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15023,10 +15035,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>428304</v>
+        <v>428139</v>
       </c>
       <c r="R137" t="n">
-        <v>6233306</v>
+        <v>6233315</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15085,10 +15097,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121471943</v>
+        <v>121471904</v>
       </c>
       <c r="B138" t="n">
-        <v>96725</v>
+        <v>78407</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15097,25 +15109,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2606</v>
+        <v>924</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15125,10 +15137,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>428034</v>
+        <v>428387</v>
       </c>
       <c r="R138" t="n">
-        <v>6233348</v>
+        <v>6233098</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15187,10 +15199,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121471920</v>
+        <v>121471796</v>
       </c>
       <c r="B139" t="n">
-        <v>91112</v>
+        <v>80255</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15199,25 +15211,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2023</v>
+        <v>1144</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Sydlig sotticka</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Ischnoderma resinosum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Schrad.) P.Karst.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15227,10 +15239,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>428095</v>
+        <v>428390</v>
       </c>
       <c r="R139" t="n">
-        <v>6233349</v>
+        <v>6233312</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15257,12 +15269,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15289,10 +15301,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121471815</v>
+        <v>121471857</v>
       </c>
       <c r="B140" t="n">
-        <v>80412</v>
+        <v>80255</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15305,21 +15317,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1557</v>
+        <v>1144</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Röd pysslinglav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Thelopsis rubella</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Nyl.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15329,10 +15341,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>428333</v>
+        <v>428362</v>
       </c>
       <c r="R140" t="n">
-        <v>6233339</v>
+        <v>6233272</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15391,10 +15403,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121471540</v>
+        <v>121471834</v>
       </c>
       <c r="B141" t="n">
-        <v>96725</v>
+        <v>80255</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15403,25 +15415,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15431,10 +15443,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>428227</v>
+        <v>428137</v>
       </c>
       <c r="R141" t="n">
-        <v>6233132</v>
+        <v>6233320</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15461,12 +15473,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15493,10 +15505,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121471903</v>
+        <v>121471896</v>
       </c>
       <c r="B142" t="n">
-        <v>76948</v>
+        <v>80578</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15509,21 +15521,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1342</v>
+        <v>1182</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15533,10 +15545,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>428385</v>
+        <v>428370</v>
       </c>
       <c r="R142" t="n">
-        <v>6233097</v>
+        <v>6233102</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15595,10 +15607,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121471545</v>
+        <v>121471836</v>
       </c>
       <c r="B143" t="n">
-        <v>80255</v>
+        <v>94588</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15607,25 +15619,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1144</v>
+        <v>2671</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15635,10 +15647,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>428172</v>
+        <v>428145</v>
       </c>
       <c r="R143" t="n">
-        <v>6233315</v>
+        <v>6233244</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15665,12 +15677,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15697,10 +15709,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121471941</v>
+        <v>121471877</v>
       </c>
       <c r="B144" t="n">
-        <v>80242</v>
+        <v>94599</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15713,21 +15725,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15737,10 +15749,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>428046</v>
+        <v>428445</v>
       </c>
       <c r="R144" t="n">
-        <v>6233350</v>
+        <v>6233151</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15767,12 +15779,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15799,10 +15811,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121471822</v>
+        <v>121471696</v>
       </c>
       <c r="B145" t="n">
-        <v>94599</v>
+        <v>96725</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15815,21 +15827,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15839,10 +15851,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>428288</v>
+        <v>428054</v>
       </c>
       <c r="R145" t="n">
-        <v>6233325</v>
+        <v>6233337</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15869,12 +15881,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15901,10 +15913,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121471902</v>
+        <v>121471860</v>
       </c>
       <c r="B146" t="n">
-        <v>94588</v>
+        <v>96725</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15917,21 +15929,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15941,10 +15953,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>428387</v>
+        <v>428404</v>
       </c>
       <c r="R146" t="n">
-        <v>6233096</v>
+        <v>6233275</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15971,12 +15983,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16003,10 +16015,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121471870</v>
+        <v>121471843</v>
       </c>
       <c r="B147" t="n">
-        <v>76948</v>
+        <v>57370</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16019,21 +16031,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1342</v>
+        <v>100049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16043,10 +16055,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>428356</v>
+        <v>428252</v>
       </c>
       <c r="R147" t="n">
-        <v>6233243</v>
+        <v>6233262</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16105,10 +16117,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121471826</v>
+        <v>121471924</v>
       </c>
       <c r="B148" t="n">
-        <v>78863</v>
+        <v>80242</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16121,21 +16133,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6459</v>
+        <v>230185</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16145,10 +16157,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>428228</v>
+        <v>428097</v>
       </c>
       <c r="R148" t="n">
-        <v>6233340</v>
+        <v>6233382</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16175,12 +16187,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16207,10 +16219,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121471837</v>
+        <v>121471910</v>
       </c>
       <c r="B149" t="n">
-        <v>80242</v>
+        <v>76948</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16219,25 +16231,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16247,10 +16259,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>428145</v>
+        <v>428377</v>
       </c>
       <c r="R149" t="n">
-        <v>6233244</v>
+        <v>6233090</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16277,12 +16289,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16309,10 +16321,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121471912</v>
+        <v>121471861</v>
       </c>
       <c r="B150" t="n">
-        <v>78407</v>
+        <v>94599</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16321,25 +16333,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>924</v>
+        <v>2667</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16349,10 +16361,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>428351</v>
+        <v>428404</v>
       </c>
       <c r="R150" t="n">
-        <v>6233082</v>
+        <v>6233275</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16379,12 +16391,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16411,10 +16423,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121471692</v>
+        <v>121471817</v>
       </c>
       <c r="B151" t="n">
-        <v>94599</v>
+        <v>74697</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16427,21 +16439,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2667</v>
+        <v>6439</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16451,10 +16463,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>428126</v>
+        <v>428312</v>
       </c>
       <c r="R151" t="n">
-        <v>6233380</v>
+        <v>6233323</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16481,12 +16493,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16513,10 +16525,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121471882</v>
+        <v>121471828</v>
       </c>
       <c r="B152" t="n">
-        <v>74609</v>
+        <v>80242</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16525,25 +16537,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1118</v>
+        <v>230185</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16553,10 +16565,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>428445</v>
+        <v>428185</v>
       </c>
       <c r="R152" t="n">
-        <v>6233151</v>
+        <v>6233289</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16597,6 +16609,7 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -16615,10 +16628,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121471913</v>
+        <v>121471541</v>
       </c>
       <c r="B153" t="n">
-        <v>76948</v>
+        <v>80242</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16627,25 +16640,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16655,10 +16668,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>428342</v>
+        <v>428209</v>
       </c>
       <c r="R153" t="n">
-        <v>6233082</v>
+        <v>6233184</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16685,12 +16698,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16717,10 +16730,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121471842</v>
+        <v>121471690</v>
       </c>
       <c r="B154" t="n">
-        <v>94599</v>
+        <v>80242</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16733,21 +16746,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16757,10 +16770,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>428221</v>
+        <v>428161</v>
       </c>
       <c r="R154" t="n">
-        <v>6233212</v>
+        <v>6233396</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16787,12 +16800,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16819,7 +16832,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121471796</v>
+        <v>121471803</v>
       </c>
       <c r="B155" t="n">
         <v>80255</v>
@@ -16859,10 +16872,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>428390</v>
+        <v>428334</v>
       </c>
       <c r="R155" t="n">
-        <v>6233312</v>
+        <v>6233284</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16921,7 +16934,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121471803</v>
+        <v>121471849</v>
       </c>
       <c r="B156" t="n">
         <v>80255</v>
@@ -16961,10 +16974,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>428334</v>
+        <v>428299</v>
       </c>
       <c r="R156" t="n">
-        <v>6233284</v>
+        <v>6233126</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17023,10 +17036,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121471800</v>
+        <v>121471865</v>
       </c>
       <c r="B157" t="n">
-        <v>80255</v>
+        <v>74699</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17035,25 +17048,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1144</v>
+        <v>306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17063,10 +17076,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>428387</v>
+        <v>428438</v>
       </c>
       <c r="R157" t="n">
-        <v>6233322</v>
+        <v>6233202</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17227,14 +17240,14 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121471875</v>
+        <v>121471545</v>
       </c>
       <c r="B159" t="n">
         <v>80255</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -17261,19 +17274,16 @@
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>428340</v>
+        <v>428172</v>
       </c>
       <c r="R159" t="n">
-        <v>6233229</v>
+        <v>6233315</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17300,17 +17310,12 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>kollekt</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17318,11 +17323,6 @@
       </c>
       <c r="AE159" t="b">
         <v>0</v>
-      </c>
-      <c r="AF159" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG159" t="b">
         <v>0</v>
@@ -17342,10 +17342,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121471871</v>
+        <v>121471804</v>
       </c>
       <c r="B160" t="n">
-        <v>80242</v>
+        <v>76948</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17354,25 +17354,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17382,10 +17382,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>428302</v>
+        <v>428335</v>
       </c>
       <c r="R160" t="n">
-        <v>6233176</v>
+        <v>6233286</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17444,7 +17444,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121471825</v>
+        <v>121471543</v>
       </c>
       <c r="B161" t="n">
         <v>80242</v>
@@ -17484,10 +17484,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>428233</v>
+        <v>428209</v>
       </c>
       <c r="R161" t="n">
-        <v>6233332</v>
+        <v>6233279</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17546,10 +17546,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121471693</v>
+        <v>121471895</v>
       </c>
       <c r="B162" t="n">
-        <v>94588</v>
+        <v>80242</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17562,21 +17562,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>2671</v>
+        <v>230185</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17586,10 +17586,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>428125</v>
+        <v>428355</v>
       </c>
       <c r="R162" t="n">
-        <v>6233379</v>
+        <v>6233123</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17616,12 +17616,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17648,10 +17648,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121471535</v>
+        <v>121471881</v>
       </c>
       <c r="B163" t="n">
-        <v>76948</v>
+        <v>78407</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17664,21 +17664,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1342</v>
+        <v>924</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17688,10 +17688,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>428160</v>
+        <v>428445</v>
       </c>
       <c r="R163" t="n">
-        <v>6233209</v>
+        <v>6233151</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17750,10 +17750,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121471873</v>
+        <v>121471842</v>
       </c>
       <c r="B164" t="n">
-        <v>74563</v>
+        <v>94599</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17762,25 +17762,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1116</v>
+        <v>2667</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17790,10 +17790,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>428301</v>
+        <v>428221</v>
       </c>
       <c r="R164" t="n">
-        <v>6233171</v>
+        <v>6233212</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17852,10 +17852,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121471829</v>
+        <v>121471942</v>
       </c>
       <c r="B165" t="n">
-        <v>80255</v>
+        <v>76948</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17864,25 +17864,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17892,10 +17892,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>428147</v>
+        <v>428032</v>
       </c>
       <c r="R165" t="n">
-        <v>6233304</v>
+        <v>6233345</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17922,12 +17922,12 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17954,10 +17954,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121471801</v>
+        <v>121471941</v>
       </c>
       <c r="B166" t="n">
-        <v>80255</v>
+        <v>80242</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17966,25 +17966,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17994,10 +17994,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>428370</v>
+        <v>428046</v>
       </c>
       <c r="R166" t="n">
-        <v>6233336</v>
+        <v>6233350</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18024,12 +18024,12 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18056,7 +18056,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121471935</v>
+        <v>121471938</v>
       </c>
       <c r="B167" t="n">
         <v>80242</v>
@@ -18096,10 +18096,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>428097</v>
+        <v>428062</v>
       </c>
       <c r="R167" t="n">
-        <v>6233286</v>
+        <v>6233301</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18158,7 +18158,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121471690</v>
+        <v>121471695</v>
       </c>
       <c r="B168" t="n">
         <v>80242</v>
@@ -18198,10 +18198,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>428161</v>
+        <v>428053</v>
       </c>
       <c r="R168" t="n">
-        <v>6233396</v>
+        <v>6233336</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18260,10 +18260,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121471843</v>
+        <v>121471858</v>
       </c>
       <c r="B169" t="n">
-        <v>57370</v>
+        <v>80255</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -18272,25 +18272,25 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100049</v>
+        <v>1144</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18300,10 +18300,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>428252</v>
+        <v>428372</v>
       </c>
       <c r="R169" t="n">
-        <v>6233262</v>
+        <v>6233270</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18362,10 +18362,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121471530</v>
+        <v>121471874</v>
       </c>
       <c r="B170" t="n">
-        <v>80242</v>
+        <v>80255</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18374,25 +18374,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18402,10 +18402,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>428111</v>
+        <v>428375</v>
       </c>
       <c r="R170" t="n">
-        <v>6233222</v>
+        <v>6233151</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18432,12 +18432,12 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18464,7 +18464,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121471874</v>
+        <v>121471694</v>
       </c>
       <c r="B171" t="n">
         <v>80255</v>
@@ -18504,10 +18504,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>428375</v>
+        <v>428125</v>
       </c>
       <c r="R171" t="n">
-        <v>6233151</v>
+        <v>6233379</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18534,12 +18534,12 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18566,7 +18566,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121471799</v>
+        <v>121471902</v>
       </c>
       <c r="B172" t="n">
         <v>94588</v>
@@ -18606,10 +18606,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>428389</v>
+        <v>428387</v>
       </c>
       <c r="R172" t="n">
-        <v>6233324</v>
+        <v>6233096</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18636,12 +18636,12 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18668,10 +18668,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121471847</v>
+        <v>121471798</v>
       </c>
       <c r="B173" t="n">
-        <v>76948</v>
+        <v>96725</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18680,25 +18680,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18708,10 +18708,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>428300</v>
+        <v>428387</v>
       </c>
       <c r="R173" t="n">
-        <v>6233125</v>
+        <v>6233326</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18770,10 +18770,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121471691</v>
+        <v>121471839</v>
       </c>
       <c r="B174" t="n">
-        <v>96725</v>
+        <v>94588</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18786,21 +18786,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>2606</v>
+        <v>2671</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18810,10 +18810,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>428128</v>
+        <v>428184</v>
       </c>
       <c r="R174" t="n">
-        <v>6233385</v>
+        <v>6233240</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18840,12 +18840,12 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18872,10 +18872,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121471544</v>
+        <v>121471878</v>
       </c>
       <c r="B175" t="n">
-        <v>94599</v>
+        <v>96773</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18888,21 +18888,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>2667</v>
+        <v>2604</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18912,10 +18912,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>428219</v>
+        <v>428445</v>
       </c>
       <c r="R175" t="n">
-        <v>6233278</v>
+        <v>6233151</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18942,12 +18942,12 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD175" t="b">

--- a/artfynd/A 18989-2024 artfynd.xlsx
+++ b/artfynd/A 18989-2024 artfynd.xlsx
@@ -3660,10 +3660,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121471826</v>
+        <v>121471901</v>
       </c>
       <c r="B26" t="n">
-        <v>78863</v>
+        <v>76948</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3672,25 +3672,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6459</v>
+        <v>1342</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>428228</v>
+        <v>428390</v>
       </c>
       <c r="R26" t="n">
-        <v>6233340</v>
+        <v>6233099</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3730,12 +3730,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3762,10 +3762,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121471530</v>
+        <v>121471539</v>
       </c>
       <c r="B27" t="n">
-        <v>80242</v>
+        <v>94588</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3778,21 +3778,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>230185</v>
+        <v>2671</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>428111</v>
+        <v>428262</v>
       </c>
       <c r="R27" t="n">
-        <v>6233222</v>
+        <v>6233134</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3864,10 +3864,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121471901</v>
+        <v>121471864</v>
       </c>
       <c r="B28" t="n">
-        <v>76948</v>
+        <v>94588</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3876,25 +3876,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1342</v>
+        <v>2671</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>428390</v>
+        <v>428410</v>
       </c>
       <c r="R28" t="n">
-        <v>6233099</v>
+        <v>6233214</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3934,12 +3934,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3966,10 +3966,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121471539</v>
+        <v>121471899</v>
       </c>
       <c r="B29" t="n">
-        <v>94588</v>
+        <v>94393</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3982,21 +3982,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>428262</v>
+        <v>428389</v>
       </c>
       <c r="R29" t="n">
-        <v>6233134</v>
+        <v>6233099</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4068,10 +4068,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121471864</v>
+        <v>121471826</v>
       </c>
       <c r="B30" t="n">
-        <v>94588</v>
+        <v>78863</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4084,21 +4084,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2671</v>
+        <v>6459</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>428410</v>
+        <v>428228</v>
       </c>
       <c r="R30" t="n">
-        <v>6233214</v>
+        <v>6233340</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4170,10 +4170,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121471899</v>
+        <v>121471530</v>
       </c>
       <c r="B31" t="n">
-        <v>94393</v>
+        <v>80242</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4186,21 +4186,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2779</v>
+        <v>230185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>428389</v>
+        <v>428111</v>
       </c>
       <c r="R31" t="n">
-        <v>6233099</v>
+        <v>6233222</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4240,12 +4240,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4272,10 +4272,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121471939</v>
+        <v>121471873</v>
       </c>
       <c r="B32" t="n">
-        <v>94599</v>
+        <v>74563</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4284,25 +4284,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2667</v>
+        <v>1116</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>428046</v>
+        <v>428301</v>
       </c>
       <c r="R32" t="n">
-        <v>6233296</v>
+        <v>6233171</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4342,12 +4342,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4374,10 +4374,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121471934</v>
+        <v>121471814</v>
       </c>
       <c r="B33" t="n">
-        <v>94393</v>
+        <v>80255</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4386,25 +4386,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2779</v>
+        <v>1144</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4414,10 +4414,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>428090</v>
+        <v>428331</v>
       </c>
       <c r="R33" t="n">
-        <v>6233309</v>
+        <v>6233339</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4444,12 +4444,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4476,10 +4476,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121471689</v>
+        <v>121471831</v>
       </c>
       <c r="B34" t="n">
-        <v>94599</v>
+        <v>80255</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4488,25 +4488,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>428161</v>
+        <v>428145</v>
       </c>
       <c r="R34" t="n">
-        <v>6233396</v>
+        <v>6233315</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4546,12 +4546,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4578,10 +4578,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121471914</v>
+        <v>121471922</v>
       </c>
       <c r="B35" t="n">
-        <v>94599</v>
+        <v>76948</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4590,25 +4590,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>428318</v>
+        <v>428091</v>
       </c>
       <c r="R35" t="n">
-        <v>6233075</v>
+        <v>6233385</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4680,10 +4680,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121471873</v>
+        <v>121471939</v>
       </c>
       <c r="B36" t="n">
-        <v>74563</v>
+        <v>94599</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4692,25 +4692,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1116</v>
+        <v>2667</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4720,10 +4720,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>428301</v>
+        <v>428046</v>
       </c>
       <c r="R36" t="n">
-        <v>6233171</v>
+        <v>6233296</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4750,12 +4750,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4782,10 +4782,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121471814</v>
+        <v>121471934</v>
       </c>
       <c r="B37" t="n">
-        <v>80255</v>
+        <v>94393</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4794,25 +4794,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1144</v>
+        <v>2779</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>428331</v>
+        <v>428090</v>
       </c>
       <c r="R37" t="n">
-        <v>6233339</v>
+        <v>6233309</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4884,10 +4884,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121471831</v>
+        <v>121471689</v>
       </c>
       <c r="B38" t="n">
-        <v>80255</v>
+        <v>94599</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4896,25 +4896,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>428145</v>
+        <v>428161</v>
       </c>
       <c r="R38" t="n">
-        <v>6233315</v>
+        <v>6233396</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4954,12 +4954,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4986,10 +4986,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121471922</v>
+        <v>121471914</v>
       </c>
       <c r="B39" t="n">
-        <v>76948</v>
+        <v>94599</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4998,25 +4998,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1342</v>
+        <v>2667</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>428091</v>
+        <v>428318</v>
       </c>
       <c r="R39" t="n">
-        <v>6233385</v>
+        <v>6233075</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5598,10 +5598,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121471540</v>
+        <v>121471926</v>
       </c>
       <c r="B45" t="n">
-        <v>96725</v>
+        <v>94393</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5614,21 +5614,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2606</v>
+        <v>2779</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>428227</v>
+        <v>428073</v>
       </c>
       <c r="R45" t="n">
-        <v>6233132</v>
+        <v>6233383</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5668,12 +5668,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5700,10 +5700,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121471926</v>
+        <v>121471540</v>
       </c>
       <c r="B46" t="n">
-        <v>94393</v>
+        <v>96725</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5716,21 +5716,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2779</v>
+        <v>2606</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>428073</v>
+        <v>428227</v>
       </c>
       <c r="R46" t="n">
-        <v>6233383</v>
+        <v>6233132</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5802,10 +5802,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121471802</v>
+        <v>121471936</v>
       </c>
       <c r="B47" t="n">
-        <v>94588</v>
+        <v>94609</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5818,21 +5818,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2671</v>
+        <v>1080</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5842,10 +5842,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>428332</v>
+        <v>428079</v>
       </c>
       <c r="R47" t="n">
-        <v>6233287</v>
+        <v>6233262</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5872,12 +5872,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5904,10 +5904,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121471683</v>
+        <v>121471806</v>
       </c>
       <c r="B48" t="n">
-        <v>94588</v>
+        <v>80255</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5916,25 +5916,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2671</v>
+        <v>1144</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5944,10 +5944,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>428278</v>
+        <v>428325</v>
       </c>
       <c r="R48" t="n">
-        <v>6233417</v>
+        <v>6233291</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5974,12 +5974,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6006,10 +6006,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121471537</v>
+        <v>121471542</v>
       </c>
       <c r="B49" t="n">
-        <v>96725</v>
+        <v>80255</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6018,25 +6018,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6046,10 +6046,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>428163</v>
+        <v>428198</v>
       </c>
       <c r="R49" t="n">
-        <v>6233193</v>
+        <v>6233249</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6108,10 +6108,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121471859</v>
+        <v>121471940</v>
       </c>
       <c r="B50" t="n">
-        <v>80242</v>
+        <v>94609</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6124,21 +6124,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>230185</v>
+        <v>1080</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6148,10 +6148,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>428404</v>
+        <v>428037</v>
       </c>
       <c r="R50" t="n">
-        <v>6233275</v>
+        <v>6233291</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6178,12 +6178,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6210,10 +6210,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121471936</v>
+        <v>121471867</v>
       </c>
       <c r="B51" t="n">
-        <v>94609</v>
+        <v>76948</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6222,25 +6222,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1080</v>
+        <v>1342</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>428079</v>
+        <v>428442</v>
       </c>
       <c r="R51" t="n">
-        <v>6233262</v>
+        <v>6233170</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6280,12 +6280,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6312,10 +6312,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121471806</v>
+        <v>121471870</v>
       </c>
       <c r="B52" t="n">
-        <v>80255</v>
+        <v>76948</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6324,25 +6324,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6352,10 +6352,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>428325</v>
+        <v>428356</v>
       </c>
       <c r="R52" t="n">
-        <v>6233291</v>
+        <v>6233243</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6414,10 +6414,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121471542</v>
+        <v>121471815</v>
       </c>
       <c r="B53" t="n">
-        <v>80255</v>
+        <v>80412</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6430,21 +6430,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1144</v>
+        <v>1557</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Röd pysslinglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelopsis rubella</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>Nyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6454,10 +6454,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>428198</v>
+        <v>428333</v>
       </c>
       <c r="R53" t="n">
-        <v>6233249</v>
+        <v>6233339</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6484,12 +6484,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6516,10 +6516,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121471940</v>
+        <v>121471802</v>
       </c>
       <c r="B54" t="n">
-        <v>94609</v>
+        <v>94588</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6532,21 +6532,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1080</v>
+        <v>2671</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6556,10 +6556,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>428037</v>
+        <v>428332</v>
       </c>
       <c r="R54" t="n">
-        <v>6233291</v>
+        <v>6233287</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6586,12 +6586,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6618,10 +6618,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121471867</v>
+        <v>121471683</v>
       </c>
       <c r="B55" t="n">
-        <v>76948</v>
+        <v>94588</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6630,25 +6630,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1342</v>
+        <v>2671</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>428442</v>
+        <v>428278</v>
       </c>
       <c r="R55" t="n">
-        <v>6233170</v>
+        <v>6233417</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6720,10 +6720,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121471870</v>
+        <v>121471697</v>
       </c>
       <c r="B56" t="n">
-        <v>76948</v>
+        <v>74699</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6732,25 +6732,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1342</v>
+        <v>306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6760,10 +6760,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>428356</v>
+        <v>428043</v>
       </c>
       <c r="R56" t="n">
-        <v>6233243</v>
+        <v>6233298</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6790,12 +6790,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6822,10 +6822,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121471815</v>
+        <v>121471537</v>
       </c>
       <c r="B57" t="n">
-        <v>80412</v>
+        <v>96725</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6834,25 +6834,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1557</v>
+        <v>2606</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Röd pysslinglav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Thelopsis rubella</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Nyl.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6862,10 +6862,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>428333</v>
+        <v>428163</v>
       </c>
       <c r="R57" t="n">
-        <v>6233339</v>
+        <v>6233193</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6892,12 +6892,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6924,10 +6924,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121471697</v>
+        <v>121471859</v>
       </c>
       <c r="B58" t="n">
-        <v>74699</v>
+        <v>80242</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>306</v>
+        <v>230185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6964,10 +6964,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>428043</v>
+        <v>428404</v>
       </c>
       <c r="R58" t="n">
-        <v>6233298</v>
+        <v>6233275</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6994,12 +6994,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7740,10 +7740,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121471841</v>
+        <v>121471862</v>
       </c>
       <c r="B66" t="n">
-        <v>96725</v>
+        <v>80242</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7756,21 +7756,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>428221</v>
+        <v>428411</v>
       </c>
       <c r="R66" t="n">
-        <v>6233212</v>
+        <v>6233213</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7842,10 +7842,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121471835</v>
+        <v>121471846</v>
       </c>
       <c r="B67" t="n">
-        <v>96725</v>
+        <v>80242</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7858,21 +7858,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7882,10 +7882,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>428145</v>
+        <v>428241</v>
       </c>
       <c r="R67" t="n">
-        <v>6233244</v>
+        <v>6233222</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7944,10 +7944,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121471862</v>
+        <v>121471841</v>
       </c>
       <c r="B68" t="n">
-        <v>80242</v>
+        <v>96725</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7960,21 +7960,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7984,10 +7984,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>428411</v>
+        <v>428221</v>
       </c>
       <c r="R68" t="n">
-        <v>6233213</v>
+        <v>6233212</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8046,10 +8046,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121471846</v>
+        <v>121471835</v>
       </c>
       <c r="B69" t="n">
-        <v>80242</v>
+        <v>96725</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8062,21 +8062,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8086,10 +8086,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>428241</v>
+        <v>428145</v>
       </c>
       <c r="R69" t="n">
-        <v>6233222</v>
+        <v>6233244</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -11208,10 +11208,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121471911</v>
+        <v>121471897</v>
       </c>
       <c r="B100" t="n">
-        <v>76948</v>
+        <v>78407</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11224,21 +11224,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1342</v>
+        <v>924</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11248,10 +11248,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>428352</v>
+        <v>428369</v>
       </c>
       <c r="R100" t="n">
-        <v>6233082</v>
+        <v>6233104</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11310,10 +11310,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121471853</v>
+        <v>121471882</v>
       </c>
       <c r="B101" t="n">
-        <v>76948</v>
+        <v>74609</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11326,21 +11326,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1342</v>
+        <v>1118</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11350,10 +11350,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>428311</v>
+        <v>428445</v>
       </c>
       <c r="R101" t="n">
-        <v>6233183</v>
+        <v>6233151</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11412,10 +11412,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121471807</v>
+        <v>121471928</v>
       </c>
       <c r="B102" t="n">
-        <v>76948</v>
+        <v>80255</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11424,25 +11424,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11452,10 +11452,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>428327</v>
+        <v>428075</v>
       </c>
       <c r="R102" t="n">
-        <v>6233292</v>
+        <v>6233294</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11482,12 +11482,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11514,10 +11514,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121471913</v>
+        <v>121471536</v>
       </c>
       <c r="B103" t="n">
-        <v>76948</v>
+        <v>80578</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11530,21 +11530,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1342</v>
+        <v>1182</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11554,10 +11554,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>428342</v>
+        <v>428166</v>
       </c>
       <c r="R103" t="n">
-        <v>6233082</v>
+        <v>6233202</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11584,12 +11584,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11616,50 +11616,53 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121471897</v>
+        <v>121471875</v>
       </c>
       <c r="B104" t="n">
-        <v>78407</v>
+        <v>80255</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>924</v>
+        <v>1144</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>428369</v>
+        <v>428340</v>
       </c>
       <c r="R104" t="n">
-        <v>6233104</v>
+        <v>6233229</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11686,12 +11689,17 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>kollekt</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11699,6 +11707,11 @@
       </c>
       <c r="AE104" t="b">
         <v>0</v>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG104" t="b">
         <v>0</v>
@@ -11718,10 +11731,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121471882</v>
+        <v>121471911</v>
       </c>
       <c r="B105" t="n">
-        <v>74609</v>
+        <v>76948</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11734,21 +11747,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1118</v>
+        <v>1342</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11758,10 +11771,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>428445</v>
+        <v>428352</v>
       </c>
       <c r="R105" t="n">
-        <v>6233151</v>
+        <v>6233082</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11788,12 +11801,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11820,10 +11833,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121471928</v>
+        <v>121471853</v>
       </c>
       <c r="B106" t="n">
-        <v>80255</v>
+        <v>76948</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11832,25 +11845,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11860,10 +11873,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>428075</v>
+        <v>428311</v>
       </c>
       <c r="R106" t="n">
-        <v>6233294</v>
+        <v>6233183</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11890,12 +11903,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11922,10 +11935,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121471536</v>
+        <v>121471807</v>
       </c>
       <c r="B107" t="n">
-        <v>80578</v>
+        <v>76948</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11938,21 +11951,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1182</v>
+        <v>1342</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11962,10 +11975,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>428166</v>
+        <v>428327</v>
       </c>
       <c r="R107" t="n">
-        <v>6233202</v>
+        <v>6233292</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11992,12 +12005,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12024,53 +12037,50 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121471875</v>
+        <v>121471913</v>
       </c>
       <c r="B108" t="n">
-        <v>80255</v>
+        <v>76948</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>428340</v>
+        <v>428342</v>
       </c>
       <c r="R108" t="n">
-        <v>6233229</v>
+        <v>6233082</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12097,17 +12107,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>kollekt</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12115,11 +12120,6 @@
       </c>
       <c r="AE108" t="b">
         <v>0</v>
-      </c>
-      <c r="AF108" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG108" t="b">
         <v>0</v>
@@ -12445,10 +12445,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121471915</v>
+        <v>121471808</v>
       </c>
       <c r="B112" t="n">
-        <v>96773</v>
+        <v>80255</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12457,25 +12457,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2604</v>
+        <v>1144</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12485,10 +12485,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>428281</v>
+        <v>428350</v>
       </c>
       <c r="R112" t="n">
-        <v>6233082</v>
+        <v>6233316</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12515,12 +12515,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12547,10 +12547,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121471837</v>
+        <v>121471531</v>
       </c>
       <c r="B113" t="n">
-        <v>80242</v>
+        <v>94609</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12563,21 +12563,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>230185</v>
+        <v>1080</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12587,10 +12587,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>428145</v>
+        <v>428110</v>
       </c>
       <c r="R113" t="n">
-        <v>6233244</v>
+        <v>6233224</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12617,12 +12617,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12649,10 +12649,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121471808</v>
+        <v>121471915</v>
       </c>
       <c r="B114" t="n">
-        <v>80255</v>
+        <v>96773</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12661,25 +12661,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1144</v>
+        <v>2604</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12689,10 +12689,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>428350</v>
+        <v>428281</v>
       </c>
       <c r="R114" t="n">
-        <v>6233316</v>
+        <v>6233082</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12719,12 +12719,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12751,10 +12751,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121471531</v>
+        <v>121471844</v>
       </c>
       <c r="B115" t="n">
-        <v>94609</v>
+        <v>76948</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12763,25 +12763,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1080</v>
+        <v>1342</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12791,10 +12791,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>428110</v>
+        <v>428248</v>
       </c>
       <c r="R115" t="n">
-        <v>6233224</v>
+        <v>6233241</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12821,12 +12821,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12853,7 +12853,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121471844</v>
+        <v>121471879</v>
       </c>
       <c r="B116" t="n">
         <v>76948</v>
@@ -12893,10 +12893,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>428248</v>
+        <v>428445</v>
       </c>
       <c r="R116" t="n">
-        <v>6233241</v>
+        <v>6233151</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12955,10 +12955,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121471879</v>
+        <v>121471837</v>
       </c>
       <c r="B117" t="n">
-        <v>76948</v>
+        <v>80242</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12967,25 +12967,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12995,10 +12995,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>428445</v>
+        <v>428145</v>
       </c>
       <c r="R117" t="n">
-        <v>6233151</v>
+        <v>6233244</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13057,10 +13057,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121471905</v>
+        <v>121471822</v>
       </c>
       <c r="B118" t="n">
-        <v>74609</v>
+        <v>94599</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13069,25 +13069,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1118</v>
+        <v>2667</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13097,10 +13097,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>428377</v>
+        <v>428288</v>
       </c>
       <c r="R118" t="n">
-        <v>6233095</v>
+        <v>6233325</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13127,12 +13127,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13159,10 +13159,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121471810</v>
+        <v>121471933</v>
       </c>
       <c r="B119" t="n">
-        <v>80255</v>
+        <v>94588</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13171,25 +13171,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1144</v>
+        <v>2671</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13199,10 +13199,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>428347</v>
+        <v>428090</v>
       </c>
       <c r="R119" t="n">
-        <v>6233326</v>
+        <v>6233309</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13229,12 +13229,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13261,10 +13261,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121471822</v>
+        <v>121471850</v>
       </c>
       <c r="B120" t="n">
-        <v>94599</v>
+        <v>80242</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13277,21 +13277,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13301,10 +13301,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>428288</v>
+        <v>428293</v>
       </c>
       <c r="R120" t="n">
-        <v>6233325</v>
+        <v>6233170</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13363,10 +13363,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121471933</v>
+        <v>121471538</v>
       </c>
       <c r="B121" t="n">
-        <v>94588</v>
+        <v>80242</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13379,21 +13379,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2671</v>
+        <v>230185</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13403,10 +13403,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>428090</v>
+        <v>428166</v>
       </c>
       <c r="R121" t="n">
-        <v>6233309</v>
+        <v>6233198</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13433,12 +13433,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13465,7 +13465,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121471850</v>
+        <v>121471871</v>
       </c>
       <c r="B122" t="n">
         <v>80242</v>
@@ -13505,10 +13505,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>428293</v>
+        <v>428302</v>
       </c>
       <c r="R122" t="n">
-        <v>6233170</v>
+        <v>6233176</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13567,10 +13567,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121471538</v>
+        <v>121471905</v>
       </c>
       <c r="B123" t="n">
-        <v>80242</v>
+        <v>74609</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13579,25 +13579,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>230185</v>
+        <v>1118</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13607,10 +13607,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>428166</v>
+        <v>428377</v>
       </c>
       <c r="R123" t="n">
-        <v>6233198</v>
+        <v>6233095</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13637,12 +13637,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13669,10 +13669,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121471871</v>
+        <v>121471810</v>
       </c>
       <c r="B124" t="n">
-        <v>80242</v>
+        <v>80255</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13681,25 +13681,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13709,10 +13709,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>428302</v>
+        <v>428347</v>
       </c>
       <c r="R124" t="n">
-        <v>6233176</v>
+        <v>6233326</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14383,7 +14383,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121471847</v>
+        <v>121471824</v>
       </c>
       <c r="B131" t="n">
         <v>76948</v>
@@ -14423,10 +14423,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>428300</v>
+        <v>428288</v>
       </c>
       <c r="R131" t="n">
-        <v>6233125</v>
+        <v>6233325</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14485,7 +14485,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121471824</v>
+        <v>121471907</v>
       </c>
       <c r="B132" t="n">
         <v>76948</v>
@@ -14525,10 +14525,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>428288</v>
+        <v>428375</v>
       </c>
       <c r="R132" t="n">
-        <v>6233325</v>
+        <v>6233092</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14555,12 +14555,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14587,10 +14587,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121471907</v>
+        <v>121471833</v>
       </c>
       <c r="B133" t="n">
-        <v>76948</v>
+        <v>80242</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14599,25 +14599,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14627,10 +14627,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>428375</v>
+        <v>428139</v>
       </c>
       <c r="R133" t="n">
-        <v>6233092</v>
+        <v>6233315</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14657,12 +14657,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14689,10 +14689,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121471692</v>
+        <v>121471847</v>
       </c>
       <c r="B134" t="n">
-        <v>94599</v>
+        <v>76948</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14701,25 +14701,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14729,10 +14729,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>428126</v>
+        <v>428300</v>
       </c>
       <c r="R134" t="n">
-        <v>6233380</v>
+        <v>6233125</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14759,12 +14759,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14791,7 +14791,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121471827</v>
+        <v>121471692</v>
       </c>
       <c r="B135" t="n">
         <v>94599</v>
@@ -14831,10 +14831,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>428185</v>
+        <v>428126</v>
       </c>
       <c r="R135" t="n">
-        <v>6233287</v>
+        <v>6233380</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14861,12 +14861,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14893,10 +14893,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121471937</v>
+        <v>121471827</v>
       </c>
       <c r="B136" t="n">
-        <v>96725</v>
+        <v>94599</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14909,21 +14909,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14933,10 +14933,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>428062</v>
+        <v>428185</v>
       </c>
       <c r="R136" t="n">
-        <v>6233301</v>
+        <v>6233287</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14963,12 +14963,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14995,10 +14995,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121471833</v>
+        <v>121471937</v>
       </c>
       <c r="B137" t="n">
-        <v>80242</v>
+        <v>96725</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15011,21 +15011,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15035,10 +15035,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>428139</v>
+        <v>428062</v>
       </c>
       <c r="R137" t="n">
-        <v>6233315</v>
+        <v>6233301</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15065,12 +15065,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -17240,10 +17240,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121471545</v>
+        <v>121471881</v>
       </c>
       <c r="B159" t="n">
-        <v>80255</v>
+        <v>78407</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17252,25 +17252,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1144</v>
+        <v>924</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17280,10 +17280,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>428172</v>
+        <v>428445</v>
       </c>
       <c r="R159" t="n">
-        <v>6233315</v>
+        <v>6233151</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17310,12 +17310,12 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17342,10 +17342,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121471804</v>
+        <v>121471545</v>
       </c>
       <c r="B160" t="n">
-        <v>76948</v>
+        <v>80255</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17354,25 +17354,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17382,10 +17382,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>428335</v>
+        <v>428172</v>
       </c>
       <c r="R160" t="n">
-        <v>6233286</v>
+        <v>6233315</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17412,12 +17412,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17444,10 +17444,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121471543</v>
+        <v>121471804</v>
       </c>
       <c r="B161" t="n">
-        <v>80242</v>
+        <v>76948</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17456,25 +17456,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17484,10 +17484,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>428209</v>
+        <v>428335</v>
       </c>
       <c r="R161" t="n">
-        <v>6233279</v>
+        <v>6233286</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17546,10 +17546,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121471895</v>
+        <v>121471842</v>
       </c>
       <c r="B162" t="n">
-        <v>80242</v>
+        <v>94599</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17562,21 +17562,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17586,10 +17586,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>428355</v>
+        <v>428221</v>
       </c>
       <c r="R162" t="n">
-        <v>6233123</v>
+        <v>6233212</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17616,12 +17616,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17648,10 +17648,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121471881</v>
+        <v>121471543</v>
       </c>
       <c r="B163" t="n">
-        <v>78407</v>
+        <v>80242</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17660,25 +17660,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>924</v>
+        <v>230185</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17688,10 +17688,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>428445</v>
+        <v>428209</v>
       </c>
       <c r="R163" t="n">
-        <v>6233151</v>
+        <v>6233279</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17750,10 +17750,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121471842</v>
+        <v>121471895</v>
       </c>
       <c r="B164" t="n">
-        <v>94599</v>
+        <v>80242</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17766,21 +17766,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17790,10 +17790,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>428221</v>
+        <v>428355</v>
       </c>
       <c r="R164" t="n">
-        <v>6233212</v>
+        <v>6233123</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17820,12 +17820,12 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17954,10 +17954,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121471941</v>
+        <v>121471902</v>
       </c>
       <c r="B166" t="n">
-        <v>80242</v>
+        <v>94588</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17970,21 +17970,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>230185</v>
+        <v>2671</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17994,10 +17994,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>428046</v>
+        <v>428387</v>
       </c>
       <c r="R166" t="n">
-        <v>6233350</v>
+        <v>6233096</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18056,10 +18056,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121471938</v>
+        <v>121471858</v>
       </c>
       <c r="B167" t="n">
-        <v>80242</v>
+        <v>80255</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18068,25 +18068,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18096,10 +18096,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>428062</v>
+        <v>428372</v>
       </c>
       <c r="R167" t="n">
-        <v>6233301</v>
+        <v>6233270</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18126,12 +18126,12 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18158,10 +18158,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121471695</v>
+        <v>121471874</v>
       </c>
       <c r="B168" t="n">
-        <v>80242</v>
+        <v>80255</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18170,25 +18170,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18198,10 +18198,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>428053</v>
+        <v>428375</v>
       </c>
       <c r="R168" t="n">
-        <v>6233336</v>
+        <v>6233151</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18228,12 +18228,12 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18260,7 +18260,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121471858</v>
+        <v>121471694</v>
       </c>
       <c r="B169" t="n">
         <v>80255</v>
@@ -18300,10 +18300,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>428372</v>
+        <v>428125</v>
       </c>
       <c r="R169" t="n">
-        <v>6233270</v>
+        <v>6233379</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18330,12 +18330,12 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18362,10 +18362,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121471874</v>
+        <v>121471941</v>
       </c>
       <c r="B170" t="n">
-        <v>80255</v>
+        <v>80242</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18374,25 +18374,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18402,10 +18402,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>428375</v>
+        <v>428046</v>
       </c>
       <c r="R170" t="n">
-        <v>6233151</v>
+        <v>6233350</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18432,12 +18432,12 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18464,10 +18464,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121471694</v>
+        <v>121471938</v>
       </c>
       <c r="B171" t="n">
-        <v>80255</v>
+        <v>80242</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18476,25 +18476,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18504,10 +18504,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>428125</v>
+        <v>428062</v>
       </c>
       <c r="R171" t="n">
-        <v>6233379</v>
+        <v>6233301</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18534,12 +18534,12 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18566,10 +18566,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121471902</v>
+        <v>121471695</v>
       </c>
       <c r="B172" t="n">
-        <v>94588</v>
+        <v>80242</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18582,21 +18582,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>2671</v>
+        <v>230185</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18606,10 +18606,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>428387</v>
+        <v>428053</v>
       </c>
       <c r="R172" t="n">
-        <v>6233096</v>
+        <v>6233336</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18636,12 +18636,12 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD172" t="b">

--- a/artfynd/A 18989-2024 artfynd.xlsx
+++ b/artfynd/A 18989-2024 artfynd.xlsx
@@ -7740,10 +7740,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121471862</v>
+        <v>121471841</v>
       </c>
       <c r="B66" t="n">
-        <v>80242</v>
+        <v>96725</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7756,21 +7756,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>428411</v>
+        <v>428221</v>
       </c>
       <c r="R66" t="n">
-        <v>6233213</v>
+        <v>6233212</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7842,10 +7842,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121471846</v>
+        <v>121471835</v>
       </c>
       <c r="B67" t="n">
-        <v>80242</v>
+        <v>96725</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7858,21 +7858,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7882,10 +7882,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>428241</v>
+        <v>428145</v>
       </c>
       <c r="R67" t="n">
-        <v>6233222</v>
+        <v>6233244</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7944,10 +7944,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121471841</v>
+        <v>121471862</v>
       </c>
       <c r="B68" t="n">
-        <v>96725</v>
+        <v>80242</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7960,21 +7960,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7984,10 +7984,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>428221</v>
+        <v>428411</v>
       </c>
       <c r="R68" t="n">
-        <v>6233212</v>
+        <v>6233213</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8046,10 +8046,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121471835</v>
+        <v>121471846</v>
       </c>
       <c r="B69" t="n">
-        <v>96725</v>
+        <v>80242</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8062,21 +8062,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8086,10 +8086,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>428145</v>
+        <v>428241</v>
       </c>
       <c r="R69" t="n">
-        <v>6233244</v>
+        <v>6233222</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8250,10 +8250,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121471912</v>
+        <v>121471866</v>
       </c>
       <c r="B71" t="n">
-        <v>78407</v>
+        <v>80242</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8262,25 +8262,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>924</v>
+        <v>230185</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8290,10 +8290,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>428351</v>
+        <v>428442</v>
       </c>
       <c r="R71" t="n">
-        <v>6233082</v>
+        <v>6233170</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8320,12 +8320,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8352,10 +8352,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121471908</v>
+        <v>121471912</v>
       </c>
       <c r="B72" t="n">
-        <v>74609</v>
+        <v>78407</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8368,21 +8368,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1118</v>
+        <v>924</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8392,10 +8392,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>428377</v>
+        <v>428351</v>
       </c>
       <c r="R72" t="n">
-        <v>6233090</v>
+        <v>6233082</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8454,7 +8454,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121471930</v>
+        <v>121471908</v>
       </c>
       <c r="B73" t="n">
         <v>74609</v>
@@ -8494,10 +8494,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>428078</v>
+        <v>428377</v>
       </c>
       <c r="R73" t="n">
-        <v>6233294</v>
+        <v>6233090</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8556,10 +8556,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121471829</v>
+        <v>121471930</v>
       </c>
       <c r="B74" t="n">
-        <v>80255</v>
+        <v>74609</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8568,25 +8568,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1144</v>
+        <v>1118</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8596,10 +8596,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>428147</v>
+        <v>428078</v>
       </c>
       <c r="R74" t="n">
-        <v>6233304</v>
+        <v>6233294</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8626,12 +8626,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8658,7 +8658,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121471923</v>
+        <v>121471829</v>
       </c>
       <c r="B75" t="n">
         <v>80255</v>
@@ -8698,10 +8698,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>428091</v>
+        <v>428147</v>
       </c>
       <c r="R75" t="n">
-        <v>6233386</v>
+        <v>6233304</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8728,12 +8728,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8760,10 +8760,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121471927</v>
+        <v>121471923</v>
       </c>
       <c r="B76" t="n">
-        <v>76948</v>
+        <v>80255</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8772,25 +8772,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8800,10 +8800,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>428074</v>
+        <v>428091</v>
       </c>
       <c r="R76" t="n">
-        <v>6233297</v>
+        <v>6233386</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8862,10 +8862,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121471866</v>
+        <v>121471927</v>
       </c>
       <c r="B77" t="n">
-        <v>80242</v>
+        <v>76948</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8874,25 +8874,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8902,10 +8902,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>428442</v>
+        <v>428074</v>
       </c>
       <c r="R77" t="n">
-        <v>6233170</v>
+        <v>6233297</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8932,12 +8932,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -16219,10 +16219,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121471910</v>
+        <v>121471803</v>
       </c>
       <c r="B149" t="n">
-        <v>76948</v>
+        <v>80255</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16231,25 +16231,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16259,10 +16259,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>428377</v>
+        <v>428334</v>
       </c>
       <c r="R149" t="n">
-        <v>6233090</v>
+        <v>6233284</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16289,12 +16289,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16321,10 +16321,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121471861</v>
+        <v>121471849</v>
       </c>
       <c r="B150" t="n">
-        <v>94599</v>
+        <v>80255</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16333,25 +16333,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16361,10 +16361,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>428404</v>
+        <v>428299</v>
       </c>
       <c r="R150" t="n">
-        <v>6233275</v>
+        <v>6233126</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16423,10 +16423,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121471817</v>
+        <v>121471861</v>
       </c>
       <c r="B151" t="n">
-        <v>74697</v>
+        <v>94599</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16439,21 +16439,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6439</v>
+        <v>2667</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16463,10 +16463,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>428312</v>
+        <v>428404</v>
       </c>
       <c r="R151" t="n">
-        <v>6233323</v>
+        <v>6233275</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16525,10 +16525,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121471828</v>
+        <v>121471865</v>
       </c>
       <c r="B152" t="n">
-        <v>80242</v>
+        <v>74699</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16541,21 +16541,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>230185</v>
+        <v>306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16565,10 +16565,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>428185</v>
+        <v>428438</v>
       </c>
       <c r="R152" t="n">
-        <v>6233289</v>
+        <v>6233202</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16609,7 +16609,6 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -16628,10 +16627,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121471541</v>
+        <v>121471869</v>
       </c>
       <c r="B153" t="n">
-        <v>80242</v>
+        <v>96725</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16644,21 +16643,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16668,10 +16667,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>428209</v>
+        <v>428354</v>
       </c>
       <c r="R153" t="n">
-        <v>6233184</v>
+        <v>6233242</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16698,12 +16697,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16730,10 +16729,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121471690</v>
+        <v>121471817</v>
       </c>
       <c r="B154" t="n">
-        <v>80242</v>
+        <v>74697</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16746,21 +16745,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>230185</v>
+        <v>6439</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16770,10 +16769,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>428161</v>
+        <v>428312</v>
       </c>
       <c r="R154" t="n">
-        <v>6233396</v>
+        <v>6233323</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16800,12 +16799,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16832,10 +16831,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121471803</v>
+        <v>121471828</v>
       </c>
       <c r="B155" t="n">
-        <v>80255</v>
+        <v>80242</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16844,25 +16843,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16872,10 +16871,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>428334</v>
+        <v>428185</v>
       </c>
       <c r="R155" t="n">
-        <v>6233284</v>
+        <v>6233289</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16916,6 +16915,7 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
+      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
@@ -16934,10 +16934,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121471849</v>
+        <v>121471541</v>
       </c>
       <c r="B156" t="n">
-        <v>80255</v>
+        <v>80242</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16946,25 +16946,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16974,10 +16974,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>428299</v>
+        <v>428209</v>
       </c>
       <c r="R156" t="n">
-        <v>6233126</v>
+        <v>6233184</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17004,12 +17004,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17036,10 +17036,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121471865</v>
+        <v>121471690</v>
       </c>
       <c r="B157" t="n">
-        <v>74699</v>
+        <v>80242</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17052,21 +17052,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>306</v>
+        <v>230185</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17076,10 +17076,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>428438</v>
+        <v>428161</v>
       </c>
       <c r="R157" t="n">
-        <v>6233202</v>
+        <v>6233396</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17106,12 +17106,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17138,10 +17138,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121471869</v>
+        <v>121471910</v>
       </c>
       <c r="B158" t="n">
-        <v>96725</v>
+        <v>76948</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17150,25 +17150,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17178,10 +17178,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>428354</v>
+        <v>428377</v>
       </c>
       <c r="R158" t="n">
-        <v>6233242</v>
+        <v>6233090</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17208,12 +17208,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD158" t="b">

--- a/artfynd/A 18989-2024 artfynd.xlsx
+++ b/artfynd/A 18989-2024 artfynd.xlsx
@@ -3354,10 +3354,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121471805</v>
+        <v>121471940</v>
       </c>
       <c r="B23" t="n">
-        <v>80255</v>
+        <v>94615</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3366,25 +3366,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1144</v>
+        <v>1080</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>428333</v>
+        <v>428037</v>
       </c>
       <c r="R23" t="n">
-        <v>6233283</v>
+        <v>6233291</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3424,12 +3424,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3456,10 +3456,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121471684</v>
+        <v>121471828</v>
       </c>
       <c r="B24" t="n">
-        <v>80412</v>
+        <v>80243</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3468,25 +3468,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1557</v>
+        <v>230185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Röd pysslinglav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Thelopsis rubella</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>428227</v>
+        <v>428185</v>
       </c>
       <c r="R24" t="n">
-        <v>6233392</v>
+        <v>6233289</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3526,12 +3526,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3540,6 +3540,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3558,10 +3559,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121471532</v>
+        <v>121471690</v>
       </c>
       <c r="B25" t="n">
-        <v>94599</v>
+        <v>80243</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3574,21 +3575,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3598,10 +3599,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>428133</v>
+        <v>428161</v>
       </c>
       <c r="R25" t="n">
-        <v>6233219</v>
+        <v>6233396</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3660,10 +3661,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121471901</v>
+        <v>121471924</v>
       </c>
       <c r="B26" t="n">
-        <v>76948</v>
+        <v>80243</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3672,25 +3673,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3700,10 +3701,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>428390</v>
+        <v>428097</v>
       </c>
       <c r="R26" t="n">
-        <v>6233099</v>
+        <v>6233382</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3762,10 +3763,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121471539</v>
+        <v>121471917</v>
       </c>
       <c r="B27" t="n">
-        <v>94588</v>
+        <v>80243</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3778,21 +3779,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2671</v>
+        <v>230185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3802,10 +3803,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>428262</v>
+        <v>428284</v>
       </c>
       <c r="R27" t="n">
-        <v>6233134</v>
+        <v>6233109</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3832,12 +3833,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3864,10 +3865,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121471864</v>
+        <v>121471945</v>
       </c>
       <c r="B28" t="n">
-        <v>94588</v>
+        <v>96779</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3880,21 +3881,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2671</v>
+        <v>2604</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3904,10 +3905,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>428410</v>
+        <v>428035</v>
       </c>
       <c r="R28" t="n">
-        <v>6233214</v>
+        <v>6233349</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3934,12 +3935,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3966,10 +3967,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121471899</v>
+        <v>121471903</v>
       </c>
       <c r="B29" t="n">
-        <v>94393</v>
+        <v>76949</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3978,25 +3979,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2779</v>
+        <v>1342</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4006,10 +4007,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>428389</v>
+        <v>428385</v>
       </c>
       <c r="R29" t="n">
-        <v>6233099</v>
+        <v>6233097</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4068,10 +4069,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121471826</v>
+        <v>121471693</v>
       </c>
       <c r="B30" t="n">
-        <v>78863</v>
+        <v>94594</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4084,21 +4085,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6459</v>
+        <v>2671</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4108,10 +4109,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>428228</v>
+        <v>428125</v>
       </c>
       <c r="R30" t="n">
-        <v>6233340</v>
+        <v>6233379</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4138,12 +4139,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4170,10 +4171,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121471530</v>
+        <v>121471539</v>
       </c>
       <c r="B31" t="n">
-        <v>80242</v>
+        <v>94594</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4186,21 +4187,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>230185</v>
+        <v>2671</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4210,10 +4211,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>428111</v>
+        <v>428262</v>
       </c>
       <c r="R31" t="n">
-        <v>6233222</v>
+        <v>6233134</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4272,10 +4273,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121471873</v>
+        <v>121471836</v>
       </c>
       <c r="B32" t="n">
-        <v>74563</v>
+        <v>94594</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4284,25 +4285,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1116</v>
+        <v>2671</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4312,10 +4313,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>428301</v>
+        <v>428145</v>
       </c>
       <c r="R32" t="n">
-        <v>6233171</v>
+        <v>6233244</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4377,7 +4378,7 @@
         <v>121471814</v>
       </c>
       <c r="B33" t="n">
-        <v>80255</v>
+        <v>80256</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4476,10 +4477,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121471831</v>
+        <v>121471541</v>
       </c>
       <c r="B34" t="n">
-        <v>80255</v>
+        <v>80243</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4488,25 +4489,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4516,10 +4517,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>428145</v>
+        <v>428209</v>
       </c>
       <c r="R34" t="n">
-        <v>6233315</v>
+        <v>6233184</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4546,12 +4547,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4578,10 +4579,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121471922</v>
+        <v>121471535</v>
       </c>
       <c r="B35" t="n">
-        <v>76948</v>
+        <v>76949</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4618,10 +4619,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>428091</v>
+        <v>428160</v>
       </c>
       <c r="R35" t="n">
-        <v>6233385</v>
+        <v>6233209</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4648,12 +4649,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4680,10 +4681,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121471939</v>
+        <v>121471824</v>
       </c>
       <c r="B36" t="n">
-        <v>94599</v>
+        <v>76949</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4692,25 +4693,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4720,10 +4721,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>428046</v>
+        <v>428288</v>
       </c>
       <c r="R36" t="n">
-        <v>6233296</v>
+        <v>6233325</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4750,12 +4751,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4782,10 +4783,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121471934</v>
+        <v>121471835</v>
       </c>
       <c r="B37" t="n">
-        <v>94393</v>
+        <v>96731</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4798,21 +4799,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2779</v>
+        <v>2606</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4822,10 +4823,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>428090</v>
+        <v>428145</v>
       </c>
       <c r="R37" t="n">
-        <v>6233309</v>
+        <v>6233244</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4852,12 +4853,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4884,10 +4885,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121471689</v>
+        <v>121471827</v>
       </c>
       <c r="B38" t="n">
-        <v>94599</v>
+        <v>94605</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4924,10 +4925,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>428161</v>
+        <v>428185</v>
       </c>
       <c r="R38" t="n">
-        <v>6233396</v>
+        <v>6233287</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4954,12 +4955,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4986,10 +4987,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121471914</v>
+        <v>121471925</v>
       </c>
       <c r="B39" t="n">
-        <v>94599</v>
+        <v>94607</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5002,16 +5003,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5026,10 +5027,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>428318</v>
+        <v>428076</v>
       </c>
       <c r="R39" t="n">
-        <v>6233075</v>
+        <v>6233382</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5088,10 +5089,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121471825</v>
+        <v>121471686</v>
       </c>
       <c r="B40" t="n">
-        <v>80242</v>
+        <v>80256</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5100,25 +5101,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5128,10 +5129,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>428233</v>
+        <v>428187</v>
       </c>
       <c r="R40" t="n">
-        <v>6233332</v>
+        <v>6233403</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5158,12 +5159,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5190,10 +5191,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121471533</v>
+        <v>121471859</v>
       </c>
       <c r="B41" t="n">
-        <v>80242</v>
+        <v>80243</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5230,10 +5231,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>428144</v>
+        <v>428404</v>
       </c>
       <c r="R41" t="n">
-        <v>6233229</v>
+        <v>6233275</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5260,12 +5261,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5292,10 +5293,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121471535</v>
+        <v>121471534</v>
       </c>
       <c r="B42" t="n">
-        <v>76948</v>
+        <v>96731</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5304,25 +5305,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5332,10 +5333,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>428160</v>
+        <v>428147</v>
       </c>
       <c r="R42" t="n">
-        <v>6233209</v>
+        <v>6233224</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5394,10 +5395,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121471811</v>
+        <v>121471804</v>
       </c>
       <c r="B43" t="n">
-        <v>76948</v>
+        <v>76949</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5434,10 +5435,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>428349</v>
+        <v>428335</v>
       </c>
       <c r="R43" t="n">
-        <v>6233325</v>
+        <v>6233286</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5496,10 +5497,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121471801</v>
+        <v>121471937</v>
       </c>
       <c r="B44" t="n">
-        <v>80255</v>
+        <v>96731</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5508,25 +5509,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5536,10 +5537,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>428370</v>
+        <v>428062</v>
       </c>
       <c r="R44" t="n">
-        <v>6233336</v>
+        <v>6233301</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5566,12 +5567,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5598,10 +5599,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121471926</v>
+        <v>121471902</v>
       </c>
       <c r="B45" t="n">
-        <v>94393</v>
+        <v>94594</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5614,21 +5615,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5638,10 +5639,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>428073</v>
+        <v>428387</v>
       </c>
       <c r="R45" t="n">
-        <v>6233383</v>
+        <v>6233096</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5700,10 +5701,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121471540</v>
+        <v>121471532</v>
       </c>
       <c r="B46" t="n">
-        <v>96725</v>
+        <v>94605</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5716,21 +5717,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5740,10 +5741,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>428227</v>
+        <v>428133</v>
       </c>
       <c r="R46" t="n">
-        <v>6233132</v>
+        <v>6233219</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5802,10 +5803,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121471936</v>
+        <v>121471829</v>
       </c>
       <c r="B47" t="n">
-        <v>94609</v>
+        <v>80256</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5814,25 +5815,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1080</v>
+        <v>1144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5842,10 +5843,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>428079</v>
+        <v>428147</v>
       </c>
       <c r="R47" t="n">
-        <v>6233262</v>
+        <v>6233304</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5872,12 +5873,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5904,10 +5905,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121471806</v>
+        <v>121471810</v>
       </c>
       <c r="B48" t="n">
-        <v>80255</v>
+        <v>80256</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5944,10 +5945,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>428325</v>
+        <v>428347</v>
       </c>
       <c r="R48" t="n">
-        <v>6233291</v>
+        <v>6233326</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6006,10 +6007,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121471542</v>
+        <v>121471852</v>
       </c>
       <c r="B49" t="n">
-        <v>80255</v>
+        <v>80256</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6046,10 +6047,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>428198</v>
+        <v>428311</v>
       </c>
       <c r="R49" t="n">
-        <v>6233249</v>
+        <v>6233183</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6076,12 +6077,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6108,10 +6109,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121471940</v>
+        <v>121471536</v>
       </c>
       <c r="B50" t="n">
-        <v>94609</v>
+        <v>80579</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6120,25 +6121,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1080</v>
+        <v>1182</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6148,10 +6149,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>428037</v>
+        <v>428166</v>
       </c>
       <c r="R50" t="n">
-        <v>6233291</v>
+        <v>6233202</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6178,12 +6179,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6210,10 +6211,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121471867</v>
+        <v>121471844</v>
       </c>
       <c r="B51" t="n">
-        <v>76948</v>
+        <v>76949</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6250,10 +6251,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>428442</v>
+        <v>428248</v>
       </c>
       <c r="R51" t="n">
-        <v>6233170</v>
+        <v>6233241</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6312,10 +6313,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121471870</v>
+        <v>121471841</v>
       </c>
       <c r="B52" t="n">
-        <v>76948</v>
+        <v>96731</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6324,25 +6325,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6352,10 +6353,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>428356</v>
+        <v>428221</v>
       </c>
       <c r="R52" t="n">
-        <v>6233243</v>
+        <v>6233212</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6414,10 +6415,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121471815</v>
+        <v>121471540</v>
       </c>
       <c r="B53" t="n">
-        <v>80412</v>
+        <v>96731</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6426,25 +6427,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1557</v>
+        <v>2606</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Röd pysslinglav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Thelopsis rubella</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Nyl.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6454,10 +6455,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>428333</v>
+        <v>428227</v>
       </c>
       <c r="R53" t="n">
-        <v>6233339</v>
+        <v>6233132</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6484,12 +6485,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6516,10 +6517,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121471802</v>
+        <v>121471544</v>
       </c>
       <c r="B54" t="n">
-        <v>94588</v>
+        <v>94605</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6532,21 +6533,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6556,10 +6557,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>428332</v>
+        <v>428219</v>
       </c>
       <c r="R54" t="n">
-        <v>6233287</v>
+        <v>6233278</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6586,12 +6587,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6618,10 +6619,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121471683</v>
+        <v>121471855</v>
       </c>
       <c r="B55" t="n">
-        <v>94588</v>
+        <v>94399</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6634,21 +6635,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6658,10 +6659,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>428278</v>
+        <v>428365</v>
       </c>
       <c r="R55" t="n">
-        <v>6233417</v>
+        <v>6233269</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6688,12 +6689,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6720,10 +6721,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121471697</v>
+        <v>121471936</v>
       </c>
       <c r="B56" t="n">
-        <v>74699</v>
+        <v>94615</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6736,21 +6737,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>306</v>
+        <v>1080</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6760,10 +6761,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>428043</v>
+        <v>428079</v>
       </c>
       <c r="R56" t="n">
-        <v>6233298</v>
+        <v>6233262</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6790,12 +6791,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6822,10 +6823,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121471537</v>
+        <v>121471803</v>
       </c>
       <c r="B57" t="n">
-        <v>96725</v>
+        <v>80256</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6834,25 +6835,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6862,10 +6863,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>428163</v>
+        <v>428334</v>
       </c>
       <c r="R57" t="n">
-        <v>6233193</v>
+        <v>6233284</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6892,12 +6893,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6924,10 +6925,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121471859</v>
+        <v>121471897</v>
       </c>
       <c r="B58" t="n">
-        <v>80242</v>
+        <v>78408</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6936,25 +6937,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>230185</v>
+        <v>924</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6964,10 +6965,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>428404</v>
+        <v>428369</v>
       </c>
       <c r="R58" t="n">
-        <v>6233275</v>
+        <v>6233104</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6994,12 +6995,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7026,10 +7027,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121471876</v>
+        <v>121471865</v>
       </c>
       <c r="B59" t="n">
-        <v>80285</v>
+        <v>74700</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7042,21 +7043,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1223</v>
+        <v>306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rikfruktig blemlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phlyctis agelaea</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Flot.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7066,10 +7067,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>428446</v>
+        <v>428438</v>
       </c>
       <c r="R59" t="n">
-        <v>6233151</v>
+        <v>6233202</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7128,10 +7129,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121471685</v>
+        <v>121471871</v>
       </c>
       <c r="B60" t="n">
-        <v>80255</v>
+        <v>80243</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7140,25 +7141,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7168,10 +7169,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>428228</v>
+        <v>428302</v>
       </c>
       <c r="R60" t="n">
-        <v>6233391</v>
+        <v>6233176</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7198,12 +7199,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7230,10 +7231,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121471929</v>
+        <v>121471530</v>
       </c>
       <c r="B61" t="n">
-        <v>94393</v>
+        <v>80243</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7246,21 +7247,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2779</v>
+        <v>230185</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7270,10 +7271,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>428078</v>
+        <v>428111</v>
       </c>
       <c r="R61" t="n">
-        <v>6233294</v>
+        <v>6233222</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7300,12 +7301,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7332,10 +7333,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121471868</v>
+        <v>121471826</v>
       </c>
       <c r="B62" t="n">
-        <v>94599</v>
+        <v>78864</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7348,21 +7349,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2667</v>
+        <v>6459</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7372,10 +7373,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>428347</v>
+        <v>428228</v>
       </c>
       <c r="R62" t="n">
-        <v>6233241</v>
+        <v>6233340</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7434,10 +7435,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121471944</v>
+        <v>121471878</v>
       </c>
       <c r="B63" t="n">
-        <v>94599</v>
+        <v>96779</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7450,21 +7451,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2667</v>
+        <v>2604</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7474,10 +7475,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>428034</v>
+        <v>428445</v>
       </c>
       <c r="R63" t="n">
-        <v>6233348</v>
+        <v>6233151</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7504,12 +7505,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7536,10 +7537,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121471544</v>
+        <v>121471943</v>
       </c>
       <c r="B64" t="n">
-        <v>94599</v>
+        <v>96731</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7552,21 +7553,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7576,10 +7577,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>428219</v>
+        <v>428034</v>
       </c>
       <c r="R64" t="n">
-        <v>6233278</v>
+        <v>6233348</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7606,12 +7607,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7638,10 +7639,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121471855</v>
+        <v>121471862</v>
       </c>
       <c r="B65" t="n">
-        <v>94393</v>
+        <v>80243</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7654,21 +7655,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2779</v>
+        <v>230185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7678,10 +7679,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>428365</v>
+        <v>428411</v>
       </c>
       <c r="R65" t="n">
-        <v>6233269</v>
+        <v>6233213</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7740,10 +7741,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121471841</v>
+        <v>121471533</v>
       </c>
       <c r="B66" t="n">
-        <v>96725</v>
+        <v>80243</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7756,21 +7757,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7780,10 +7781,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>428221</v>
+        <v>428144</v>
       </c>
       <c r="R66" t="n">
-        <v>6233212</v>
+        <v>6233229</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7810,12 +7811,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7842,10 +7843,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121471835</v>
+        <v>121471696</v>
       </c>
       <c r="B67" t="n">
-        <v>96725</v>
+        <v>96731</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7882,10 +7883,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>428145</v>
+        <v>428054</v>
       </c>
       <c r="R67" t="n">
-        <v>6233244</v>
+        <v>6233337</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7912,12 +7913,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7944,10 +7945,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121471862</v>
+        <v>121471911</v>
       </c>
       <c r="B68" t="n">
-        <v>80242</v>
+        <v>76949</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7956,25 +7957,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7984,10 +7985,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>428411</v>
+        <v>428352</v>
       </c>
       <c r="R68" t="n">
-        <v>6233213</v>
+        <v>6233082</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8014,12 +8015,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8046,10 +8047,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121471846</v>
+        <v>121471867</v>
       </c>
       <c r="B69" t="n">
-        <v>80242</v>
+        <v>76949</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8058,25 +8059,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8086,10 +8087,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>428241</v>
+        <v>428442</v>
       </c>
       <c r="R69" t="n">
-        <v>6233222</v>
+        <v>6233170</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8148,10 +8149,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121471851</v>
+        <v>121471869</v>
       </c>
       <c r="B70" t="n">
-        <v>78863</v>
+        <v>96731</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8164,21 +8165,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6459</v>
+        <v>2606</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8188,10 +8189,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>428293</v>
+        <v>428354</v>
       </c>
       <c r="R70" t="n">
-        <v>6233170</v>
+        <v>6233242</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8250,10 +8251,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121471866</v>
+        <v>121471847</v>
       </c>
       <c r="B71" t="n">
-        <v>80242</v>
+        <v>76949</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8262,25 +8263,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8290,10 +8291,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>428442</v>
+        <v>428300</v>
       </c>
       <c r="R71" t="n">
-        <v>6233170</v>
+        <v>6233125</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8352,10 +8353,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121471912</v>
+        <v>121471815</v>
       </c>
       <c r="B72" t="n">
-        <v>78407</v>
+        <v>80413</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8364,25 +8365,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>924</v>
+        <v>1557</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Röd pysslinglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Thelopsis rubella</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>Nyl.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8392,10 +8393,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>428351</v>
+        <v>428333</v>
       </c>
       <c r="R72" t="n">
-        <v>6233082</v>
+        <v>6233339</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8422,12 +8423,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8454,10 +8455,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121471908</v>
+        <v>121471860</v>
       </c>
       <c r="B73" t="n">
-        <v>74609</v>
+        <v>96731</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8466,25 +8467,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1118</v>
+        <v>2606</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8494,10 +8495,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>428377</v>
+        <v>428404</v>
       </c>
       <c r="R73" t="n">
-        <v>6233090</v>
+        <v>6233275</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8524,12 +8525,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8556,10 +8557,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121471930</v>
+        <v>121471929</v>
       </c>
       <c r="B74" t="n">
-        <v>74609</v>
+        <v>94399</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8568,25 +8569,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1118</v>
+        <v>2779</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8658,10 +8659,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121471829</v>
+        <v>121471812</v>
       </c>
       <c r="B75" t="n">
-        <v>80255</v>
+        <v>94399</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8670,25 +8671,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1144</v>
+        <v>2779</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8698,10 +8699,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>428147</v>
+        <v>428331</v>
       </c>
       <c r="R75" t="n">
-        <v>6233304</v>
+        <v>6233335</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8760,10 +8761,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121471923</v>
+        <v>121471796</v>
       </c>
       <c r="B76" t="n">
-        <v>80255</v>
+        <v>80256</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8800,10 +8801,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>428091</v>
+        <v>428390</v>
       </c>
       <c r="R76" t="n">
-        <v>6233386</v>
+        <v>6233312</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8830,12 +8831,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8862,10 +8863,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121471927</v>
+        <v>121471866</v>
       </c>
       <c r="B77" t="n">
-        <v>76948</v>
+        <v>80243</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8874,25 +8875,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8902,10 +8903,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>428074</v>
+        <v>428442</v>
       </c>
       <c r="R77" t="n">
-        <v>6233297</v>
+        <v>6233170</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8932,12 +8933,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8964,10 +8965,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121471931</v>
+        <v>121471907</v>
       </c>
       <c r="B78" t="n">
-        <v>80255</v>
+        <v>76949</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8976,25 +8977,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9004,10 +9005,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>428075</v>
+        <v>428375</v>
       </c>
       <c r="R78" t="n">
-        <v>6233301</v>
+        <v>6233092</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9066,10 +9067,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121471919</v>
+        <v>121471817</v>
       </c>
       <c r="B79" t="n">
-        <v>80255</v>
+        <v>74698</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9078,25 +9079,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1144</v>
+        <v>6439</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9106,10 +9107,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>428106</v>
+        <v>428312</v>
       </c>
       <c r="R79" t="n">
-        <v>6233304</v>
+        <v>6233323</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9136,12 +9137,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9168,10 +9169,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121471800</v>
+        <v>121471837</v>
       </c>
       <c r="B80" t="n">
-        <v>80255</v>
+        <v>80243</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9180,25 +9181,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9208,10 +9209,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>428387</v>
+        <v>428145</v>
       </c>
       <c r="R80" t="n">
-        <v>6233322</v>
+        <v>6233244</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9270,10 +9271,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121471845</v>
+        <v>121471933</v>
       </c>
       <c r="B81" t="n">
-        <v>80255</v>
+        <v>94594</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9282,25 +9283,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1144</v>
+        <v>2671</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9310,10 +9311,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>428248</v>
+        <v>428090</v>
       </c>
       <c r="R81" t="n">
-        <v>6233242</v>
+        <v>6233309</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9340,12 +9341,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9372,10 +9373,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121471693</v>
+        <v>121471868</v>
       </c>
       <c r="B82" t="n">
-        <v>94588</v>
+        <v>94605</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9388,21 +9389,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9412,10 +9413,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>428125</v>
+        <v>428347</v>
       </c>
       <c r="R82" t="n">
-        <v>6233379</v>
+        <v>6233241</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9442,12 +9443,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9474,10 +9475,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121471813</v>
+        <v>121471873</v>
       </c>
       <c r="B83" t="n">
-        <v>94588</v>
+        <v>74564</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9486,25 +9487,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2671</v>
+        <v>1116</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9514,10 +9515,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>428332</v>
+        <v>428301</v>
       </c>
       <c r="R83" t="n">
-        <v>6233341</v>
+        <v>6233171</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9576,10 +9577,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121471863</v>
+        <v>121471808</v>
       </c>
       <c r="B84" t="n">
-        <v>96725</v>
+        <v>80256</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9588,25 +9589,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9616,10 +9617,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>428411</v>
+        <v>428350</v>
       </c>
       <c r="R84" t="n">
-        <v>6233213</v>
+        <v>6233316</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9678,10 +9679,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121471688</v>
+        <v>121471545</v>
       </c>
       <c r="B85" t="n">
-        <v>96725</v>
+        <v>80256</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9690,25 +9691,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9718,10 +9719,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>428159</v>
+        <v>428172</v>
       </c>
       <c r="R85" t="n">
-        <v>6233394</v>
+        <v>6233315</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9780,10 +9781,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121471534</v>
+        <v>121471809</v>
       </c>
       <c r="B86" t="n">
-        <v>96725</v>
+        <v>74564</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9792,25 +9793,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2606</v>
+        <v>1116</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9820,10 +9821,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>428147</v>
+        <v>428352</v>
       </c>
       <c r="R86" t="n">
-        <v>6233224</v>
+        <v>6233315</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9850,12 +9851,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9882,10 +9883,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121471816</v>
+        <v>121471818</v>
       </c>
       <c r="B87" t="n">
-        <v>96773</v>
+        <v>96731</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9898,21 +9899,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2604</v>
+        <v>2606</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9922,10 +9923,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>428317</v>
+        <v>428307</v>
       </c>
       <c r="R87" t="n">
-        <v>6233324</v>
+        <v>6233311</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9984,10 +9985,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121471799</v>
+        <v>121471919</v>
       </c>
       <c r="B88" t="n">
-        <v>94588</v>
+        <v>80256</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9996,25 +9997,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2671</v>
+        <v>1144</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10024,10 +10025,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>428389</v>
+        <v>428106</v>
       </c>
       <c r="R88" t="n">
-        <v>6233324</v>
+        <v>6233304</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10054,12 +10055,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10086,14 +10087,14 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121471852</v>
+        <v>121471875</v>
       </c>
       <c r="B89" t="n">
-        <v>80255</v>
+        <v>80256</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10120,16 +10121,19 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>428311</v>
+        <v>428340</v>
       </c>
       <c r="R89" t="n">
-        <v>6233183</v>
+        <v>6233229</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10164,11 +10168,21 @@
           <t>2024-11-21</t>
         </is>
       </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>kollekt</t>
+        </is>
+      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG89" t="b">
         <v>0</v>
@@ -10188,10 +10202,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121471840</v>
+        <v>121471805</v>
       </c>
       <c r="B90" t="n">
-        <v>78987</v>
+        <v>80256</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10200,25 +10214,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6431</v>
+        <v>1144</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10228,10 +10242,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>428183</v>
+        <v>428333</v>
       </c>
       <c r="R90" t="n">
-        <v>6233239</v>
+        <v>6233283</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10290,10 +10304,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121471916</v>
+        <v>121471684</v>
       </c>
       <c r="B91" t="n">
-        <v>94609</v>
+        <v>80413</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10302,25 +10316,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1080</v>
+        <v>1557</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Röd pysslinglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Thelopsis rubella</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Nyl.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10330,10 +10344,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>428283</v>
+        <v>428227</v>
       </c>
       <c r="R91" t="n">
-        <v>6233084</v>
+        <v>6233392</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10360,12 +10374,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10392,10 +10406,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121471909</v>
+        <v>121471849</v>
       </c>
       <c r="B92" t="n">
-        <v>76948</v>
+        <v>80256</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10404,25 +10418,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10432,10 +10446,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>428373</v>
+        <v>428299</v>
       </c>
       <c r="R92" t="n">
-        <v>6233088</v>
+        <v>6233126</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10462,12 +10476,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10494,10 +10508,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121471920</v>
+        <v>121471927</v>
       </c>
       <c r="B93" t="n">
-        <v>91112</v>
+        <v>76949</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10510,21 +10524,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2023</v>
+        <v>1342</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sydlig sotticka</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ischnoderma resinosum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Schrad.) P.Karst.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10534,10 +10548,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>428095</v>
+        <v>428074</v>
       </c>
       <c r="R93" t="n">
-        <v>6233349</v>
+        <v>6233297</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10596,10 +10610,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121471903</v>
+        <v>121471537</v>
       </c>
       <c r="B94" t="n">
-        <v>76948</v>
+        <v>96731</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10608,25 +10622,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10636,10 +10650,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>428385</v>
+        <v>428163</v>
       </c>
       <c r="R94" t="n">
-        <v>6233097</v>
+        <v>6233193</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10666,12 +10680,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10698,10 +10712,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121471812</v>
+        <v>121471926</v>
       </c>
       <c r="B95" t="n">
-        <v>94393</v>
+        <v>94399</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10738,10 +10752,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>428331</v>
+        <v>428073</v>
       </c>
       <c r="R95" t="n">
-        <v>6233335</v>
+        <v>6233383</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10768,12 +10782,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10800,10 +10814,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121471925</v>
+        <v>121471806</v>
       </c>
       <c r="B96" t="n">
-        <v>94601</v>
+        <v>80256</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10812,25 +10826,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2666</v>
+        <v>1144</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10840,10 +10854,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>428076</v>
+        <v>428325</v>
       </c>
       <c r="R96" t="n">
-        <v>6233382</v>
+        <v>6233291</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10870,12 +10884,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10902,10 +10916,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121471820</v>
+        <v>121471840</v>
       </c>
       <c r="B97" t="n">
-        <v>94393</v>
+        <v>78988</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10918,21 +10932,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2779</v>
+        <v>6431</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10942,10 +10956,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>428304</v>
+        <v>428183</v>
       </c>
       <c r="R97" t="n">
-        <v>6233306</v>
+        <v>6233239</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11004,10 +11018,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121471819</v>
+        <v>121471689</v>
       </c>
       <c r="B98" t="n">
-        <v>94599</v>
+        <v>94605</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11044,10 +11058,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>428304</v>
+        <v>428161</v>
       </c>
       <c r="R98" t="n">
-        <v>6233306</v>
+        <v>6233396</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11074,12 +11088,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11106,10 +11120,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121471943</v>
+        <v>121471799</v>
       </c>
       <c r="B99" t="n">
-        <v>96725</v>
+        <v>94594</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11122,21 +11136,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2606</v>
+        <v>2671</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11146,10 +11160,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>428034</v>
+        <v>428389</v>
       </c>
       <c r="R99" t="n">
-        <v>6233348</v>
+        <v>6233324</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11176,12 +11190,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11208,10 +11222,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121471897</v>
+        <v>121471820</v>
       </c>
       <c r="B100" t="n">
-        <v>78407</v>
+        <v>94399</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11220,25 +11234,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>924</v>
+        <v>2779</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11248,10 +11262,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>428369</v>
+        <v>428304</v>
       </c>
       <c r="R100" t="n">
-        <v>6233104</v>
+        <v>6233306</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11278,12 +11292,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11310,10 +11324,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121471882</v>
+        <v>121471538</v>
       </c>
       <c r="B101" t="n">
-        <v>74609</v>
+        <v>80243</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11322,25 +11336,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1118</v>
+        <v>230185</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11350,10 +11364,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>428445</v>
+        <v>428166</v>
       </c>
       <c r="R101" t="n">
-        <v>6233151</v>
+        <v>6233198</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11380,12 +11394,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11412,10 +11426,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121471928</v>
+        <v>121471688</v>
       </c>
       <c r="B102" t="n">
-        <v>80255</v>
+        <v>96731</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11424,25 +11438,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11452,10 +11466,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>428075</v>
+        <v>428159</v>
       </c>
       <c r="R102" t="n">
-        <v>6233294</v>
+        <v>6233394</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11482,12 +11496,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11514,10 +11528,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121471536</v>
+        <v>121471807</v>
       </c>
       <c r="B103" t="n">
-        <v>80578</v>
+        <v>76949</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11530,21 +11544,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1182</v>
+        <v>1342</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11554,10 +11568,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>428166</v>
+        <v>428327</v>
       </c>
       <c r="R103" t="n">
-        <v>6233202</v>
+        <v>6233292</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11584,12 +11598,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11616,53 +11630,50 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121471875</v>
+        <v>121471901</v>
       </c>
       <c r="B104" t="n">
-        <v>80255</v>
+        <v>76949</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>428340</v>
+        <v>428390</v>
       </c>
       <c r="R104" t="n">
-        <v>6233229</v>
+        <v>6233099</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11689,17 +11700,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>kollekt</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11707,11 +11713,6 @@
       </c>
       <c r="AE104" t="b">
         <v>0</v>
-      </c>
-      <c r="AF104" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG104" t="b">
         <v>0</v>
@@ -11731,10 +11732,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121471911</v>
+        <v>121471896</v>
       </c>
       <c r="B105" t="n">
-        <v>76948</v>
+        <v>80579</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11747,21 +11748,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1342</v>
+        <v>1182</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11771,10 +11772,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>428352</v>
+        <v>428370</v>
       </c>
       <c r="R105" t="n">
-        <v>6233082</v>
+        <v>6233102</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11833,10 +11834,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121471853</v>
+        <v>121471942</v>
       </c>
       <c r="B106" t="n">
-        <v>76948</v>
+        <v>76949</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11873,10 +11874,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>428311</v>
+        <v>428032</v>
       </c>
       <c r="R106" t="n">
-        <v>6233183</v>
+        <v>6233345</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11903,12 +11904,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11935,10 +11936,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121471807</v>
+        <v>121471694</v>
       </c>
       <c r="B107" t="n">
-        <v>76948</v>
+        <v>80256</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11947,25 +11948,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11975,10 +11976,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>428327</v>
+        <v>428125</v>
       </c>
       <c r="R107" t="n">
-        <v>6233292</v>
+        <v>6233379</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12005,12 +12006,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12037,10 +12038,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121471913</v>
+        <v>121471881</v>
       </c>
       <c r="B108" t="n">
-        <v>76948</v>
+        <v>78408</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12053,21 +12054,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1342</v>
+        <v>924</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12077,10 +12078,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>428342</v>
+        <v>428445</v>
       </c>
       <c r="R108" t="n">
-        <v>6233082</v>
+        <v>6233151</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12107,12 +12108,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12139,10 +12140,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121471854</v>
+        <v>121471531</v>
       </c>
       <c r="B109" t="n">
-        <v>96725</v>
+        <v>94615</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12155,21 +12156,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2606</v>
+        <v>1080</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12179,10 +12180,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>428302</v>
+        <v>428110</v>
       </c>
       <c r="R109" t="n">
-        <v>6233177</v>
+        <v>6233224</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12209,12 +12210,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12241,10 +12242,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121471935</v>
+        <v>121471834</v>
       </c>
       <c r="B110" t="n">
-        <v>80242</v>
+        <v>80256</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12253,25 +12254,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12281,10 +12282,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>428097</v>
+        <v>428137</v>
       </c>
       <c r="R110" t="n">
-        <v>6233286</v>
+        <v>6233320</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12311,12 +12312,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12343,10 +12344,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121471917</v>
+        <v>121471941</v>
       </c>
       <c r="B111" t="n">
-        <v>80242</v>
+        <v>80243</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12383,10 +12384,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>428284</v>
+        <v>428046</v>
       </c>
       <c r="R111" t="n">
-        <v>6233109</v>
+        <v>6233350</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12445,10 +12446,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121471808</v>
+        <v>121471879</v>
       </c>
       <c r="B112" t="n">
-        <v>80255</v>
+        <v>76949</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12457,25 +12458,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12485,10 +12486,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>428350</v>
+        <v>428445</v>
       </c>
       <c r="R112" t="n">
-        <v>6233316</v>
+        <v>6233151</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12547,10 +12548,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121471531</v>
+        <v>121471842</v>
       </c>
       <c r="B113" t="n">
-        <v>94609</v>
+        <v>94605</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12563,21 +12564,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1080</v>
+        <v>2667</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12587,10 +12588,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>428110</v>
+        <v>428221</v>
       </c>
       <c r="R113" t="n">
-        <v>6233224</v>
+        <v>6233212</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12617,12 +12618,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12649,10 +12650,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121471915</v>
+        <v>121471931</v>
       </c>
       <c r="B114" t="n">
-        <v>96773</v>
+        <v>80256</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12661,25 +12662,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2604</v>
+        <v>1144</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12689,10 +12690,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>428281</v>
+        <v>428075</v>
       </c>
       <c r="R114" t="n">
-        <v>6233082</v>
+        <v>6233301</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12751,10 +12752,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121471844</v>
+        <v>121471908</v>
       </c>
       <c r="B115" t="n">
-        <v>76948</v>
+        <v>74610</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12767,21 +12768,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1342</v>
+        <v>1118</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12791,10 +12792,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>428248</v>
+        <v>428377</v>
       </c>
       <c r="R115" t="n">
-        <v>6233241</v>
+        <v>6233090</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12821,12 +12822,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12853,10 +12854,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121471879</v>
+        <v>121471882</v>
       </c>
       <c r="B116" t="n">
-        <v>76948</v>
+        <v>74610</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12869,21 +12870,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1342</v>
+        <v>1118</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12955,10 +12956,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121471837</v>
+        <v>121471801</v>
       </c>
       <c r="B117" t="n">
-        <v>80242</v>
+        <v>80256</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12967,25 +12968,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12995,10 +12996,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>428145</v>
+        <v>428370</v>
       </c>
       <c r="R117" t="n">
-        <v>6233244</v>
+        <v>6233336</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13057,10 +13058,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121471822</v>
+        <v>121471935</v>
       </c>
       <c r="B118" t="n">
-        <v>94599</v>
+        <v>80243</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13073,21 +13074,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13097,10 +13098,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>428288</v>
+        <v>428097</v>
       </c>
       <c r="R118" t="n">
-        <v>6233325</v>
+        <v>6233286</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13127,12 +13128,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13159,10 +13160,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121471933</v>
+        <v>121471846</v>
       </c>
       <c r="B119" t="n">
-        <v>94588</v>
+        <v>80243</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13175,21 +13176,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2671</v>
+        <v>230185</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13199,10 +13200,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>428090</v>
+        <v>428241</v>
       </c>
       <c r="R119" t="n">
-        <v>6233309</v>
+        <v>6233222</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13229,12 +13230,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13261,10 +13262,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121471850</v>
+        <v>121471934</v>
       </c>
       <c r="B120" t="n">
-        <v>80242</v>
+        <v>94399</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13277,21 +13278,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>230185</v>
+        <v>2779</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13301,10 +13302,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>428293</v>
+        <v>428090</v>
       </c>
       <c r="R120" t="n">
-        <v>6233170</v>
+        <v>6233309</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13331,12 +13332,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13363,10 +13364,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121471538</v>
+        <v>121471802</v>
       </c>
       <c r="B121" t="n">
-        <v>80242</v>
+        <v>94594</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13379,21 +13380,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>230185</v>
+        <v>2671</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13403,10 +13404,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>428166</v>
+        <v>428332</v>
       </c>
       <c r="R121" t="n">
-        <v>6233198</v>
+        <v>6233287</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13433,12 +13434,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13465,10 +13466,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121471871</v>
+        <v>121471877</v>
       </c>
       <c r="B122" t="n">
-        <v>80242</v>
+        <v>94605</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13481,21 +13482,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13505,10 +13506,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>428302</v>
+        <v>428445</v>
       </c>
       <c r="R122" t="n">
-        <v>6233176</v>
+        <v>6233151</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13567,10 +13568,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121471905</v>
+        <v>121471912</v>
       </c>
       <c r="B123" t="n">
-        <v>74609</v>
+        <v>78408</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13583,21 +13584,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1118</v>
+        <v>924</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13607,10 +13608,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>428377</v>
+        <v>428351</v>
       </c>
       <c r="R123" t="n">
-        <v>6233095</v>
+        <v>6233082</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13669,10 +13670,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121471810</v>
+        <v>121471858</v>
       </c>
       <c r="B124" t="n">
-        <v>80255</v>
+        <v>80256</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13709,10 +13710,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>428347</v>
+        <v>428372</v>
       </c>
       <c r="R124" t="n">
-        <v>6233326</v>
+        <v>6233270</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13771,10 +13772,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121471945</v>
+        <v>121471923</v>
       </c>
       <c r="B125" t="n">
-        <v>96773</v>
+        <v>80256</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13783,25 +13784,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2604</v>
+        <v>1144</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13811,10 +13812,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>428035</v>
+        <v>428091</v>
       </c>
       <c r="R125" t="n">
-        <v>6233349</v>
+        <v>6233386</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13873,10 +13874,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121471818</v>
+        <v>121471915</v>
       </c>
       <c r="B126" t="n">
-        <v>96725</v>
+        <v>96779</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13889,21 +13890,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2606</v>
+        <v>2604</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13913,10 +13914,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>428307</v>
+        <v>428281</v>
       </c>
       <c r="R126" t="n">
-        <v>6233311</v>
+        <v>6233082</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13943,12 +13944,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13975,10 +13976,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121471691</v>
+        <v>121471870</v>
       </c>
       <c r="B127" t="n">
-        <v>96725</v>
+        <v>76949</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13987,25 +13988,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14015,10 +14016,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>428128</v>
+        <v>428356</v>
       </c>
       <c r="R127" t="n">
-        <v>6233385</v>
+        <v>6233243</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14045,12 +14046,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14077,10 +14078,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121471686</v>
+        <v>121471843</v>
       </c>
       <c r="B128" t="n">
-        <v>80255</v>
+        <v>57371</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14089,25 +14090,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1144</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14117,10 +14118,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>428187</v>
+        <v>428252</v>
       </c>
       <c r="R128" t="n">
-        <v>6233403</v>
+        <v>6233262</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14147,12 +14148,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14179,10 +14180,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121471809</v>
+        <v>121471938</v>
       </c>
       <c r="B129" t="n">
-        <v>74563</v>
+        <v>80243</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14191,25 +14192,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1116</v>
+        <v>230185</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14219,10 +14220,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>428352</v>
+        <v>428062</v>
       </c>
       <c r="R129" t="n">
-        <v>6233315</v>
+        <v>6233301</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14249,12 +14250,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14281,10 +14282,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121471856</v>
+        <v>121471920</v>
       </c>
       <c r="B130" t="n">
-        <v>76948</v>
+        <v>91118</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14297,21 +14298,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1342</v>
+        <v>2023</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Sydlig sotticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Ischnoderma resinosum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Schrad.) P.Karst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14321,10 +14322,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>428360</v>
+        <v>428095</v>
       </c>
       <c r="R130" t="n">
-        <v>6233266</v>
+        <v>6233349</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14351,12 +14352,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14383,10 +14384,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121471824</v>
+        <v>121471543</v>
       </c>
       <c r="B131" t="n">
-        <v>76948</v>
+        <v>80243</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14395,25 +14396,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14423,10 +14424,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>428288</v>
+        <v>428209</v>
       </c>
       <c r="R131" t="n">
-        <v>6233325</v>
+        <v>6233279</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14453,12 +14454,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14485,10 +14486,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121471907</v>
+        <v>121471895</v>
       </c>
       <c r="B132" t="n">
-        <v>76948</v>
+        <v>80243</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14497,25 +14498,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14525,10 +14526,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>428375</v>
+        <v>428355</v>
       </c>
       <c r="R132" t="n">
-        <v>6233092</v>
+        <v>6233123</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14587,10 +14588,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121471833</v>
+        <v>121471813</v>
       </c>
       <c r="B133" t="n">
-        <v>80242</v>
+        <v>94594</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14603,21 +14604,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>230185</v>
+        <v>2671</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14627,10 +14628,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>428139</v>
+        <v>428332</v>
       </c>
       <c r="R133" t="n">
-        <v>6233315</v>
+        <v>6233341</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14689,10 +14690,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121471847</v>
+        <v>121471939</v>
       </c>
       <c r="B134" t="n">
-        <v>76948</v>
+        <v>94605</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14701,25 +14702,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1342</v>
+        <v>2667</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14729,10 +14730,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>428300</v>
+        <v>428046</v>
       </c>
       <c r="R134" t="n">
-        <v>6233125</v>
+        <v>6233296</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14759,12 +14760,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14791,10 +14792,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121471692</v>
+        <v>121471683</v>
       </c>
       <c r="B135" t="n">
-        <v>94599</v>
+        <v>94594</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14807,21 +14808,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14831,10 +14832,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>428126</v>
+        <v>428278</v>
       </c>
       <c r="R135" t="n">
-        <v>6233380</v>
+        <v>6233417</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14893,10 +14894,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121471827</v>
+        <v>121471944</v>
       </c>
       <c r="B136" t="n">
-        <v>94599</v>
+        <v>94605</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14933,10 +14934,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>428185</v>
+        <v>428034</v>
       </c>
       <c r="R136" t="n">
-        <v>6233287</v>
+        <v>6233348</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14963,12 +14964,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14995,10 +14996,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121471937</v>
+        <v>121471800</v>
       </c>
       <c r="B137" t="n">
-        <v>96725</v>
+        <v>80256</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15007,25 +15008,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15035,10 +15036,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>428062</v>
+        <v>428387</v>
       </c>
       <c r="R137" t="n">
-        <v>6233301</v>
+        <v>6233322</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15065,12 +15066,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15097,10 +15098,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121471904</v>
+        <v>121471685</v>
       </c>
       <c r="B138" t="n">
-        <v>78407</v>
+        <v>80256</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15109,25 +15110,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>924</v>
+        <v>1144</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15137,10 +15138,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>428387</v>
+        <v>428228</v>
       </c>
       <c r="R138" t="n">
-        <v>6233098</v>
+        <v>6233391</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15167,12 +15168,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15199,10 +15200,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121471796</v>
+        <v>121471798</v>
       </c>
       <c r="B139" t="n">
-        <v>80255</v>
+        <v>96731</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15211,25 +15212,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15239,10 +15240,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>428390</v>
+        <v>428387</v>
       </c>
       <c r="R139" t="n">
-        <v>6233312</v>
+        <v>6233326</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15301,10 +15302,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121471857</v>
+        <v>121471856</v>
       </c>
       <c r="B140" t="n">
-        <v>80255</v>
+        <v>76949</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15313,25 +15314,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15341,10 +15342,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>428362</v>
+        <v>428360</v>
       </c>
       <c r="R140" t="n">
-        <v>6233272</v>
+        <v>6233266</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15403,10 +15404,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121471834</v>
+        <v>121471691</v>
       </c>
       <c r="B141" t="n">
-        <v>80255</v>
+        <v>96731</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15415,25 +15416,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15443,10 +15444,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>428137</v>
+        <v>428128</v>
       </c>
       <c r="R141" t="n">
-        <v>6233320</v>
+        <v>6233385</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15473,12 +15474,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15505,10 +15506,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121471896</v>
+        <v>121471909</v>
       </c>
       <c r="B142" t="n">
-        <v>80578</v>
+        <v>76949</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15521,21 +15522,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1182</v>
+        <v>1342</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15545,10 +15546,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>428370</v>
+        <v>428373</v>
       </c>
       <c r="R142" t="n">
-        <v>6233102</v>
+        <v>6233088</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15607,10 +15608,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121471836</v>
+        <v>121471811</v>
       </c>
       <c r="B143" t="n">
-        <v>94588</v>
+        <v>76949</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15619,25 +15620,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2671</v>
+        <v>1342</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15647,10 +15648,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>428145</v>
+        <v>428349</v>
       </c>
       <c r="R143" t="n">
-        <v>6233244</v>
+        <v>6233325</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15709,10 +15710,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121471877</v>
+        <v>121471819</v>
       </c>
       <c r="B144" t="n">
-        <v>94599</v>
+        <v>94605</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15749,10 +15750,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>428445</v>
+        <v>428304</v>
       </c>
       <c r="R144" t="n">
-        <v>6233151</v>
+        <v>6233306</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15811,10 +15812,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121471696</v>
+        <v>121471914</v>
       </c>
       <c r="B145" t="n">
-        <v>96725</v>
+        <v>94605</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15827,21 +15828,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15851,10 +15852,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>428054</v>
+        <v>428318</v>
       </c>
       <c r="R145" t="n">
-        <v>6233337</v>
+        <v>6233075</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15881,12 +15882,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15913,10 +15914,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121471860</v>
+        <v>121471928</v>
       </c>
       <c r="B146" t="n">
-        <v>96725</v>
+        <v>80256</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15925,25 +15926,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15953,10 +15954,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>428404</v>
+        <v>428075</v>
       </c>
       <c r="R146" t="n">
-        <v>6233275</v>
+        <v>6233294</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15983,12 +15984,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16015,10 +16016,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121471843</v>
+        <v>121471542</v>
       </c>
       <c r="B147" t="n">
-        <v>57370</v>
+        <v>80256</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16027,25 +16028,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100049</v>
+        <v>1144</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16055,10 +16056,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>428252</v>
+        <v>428198</v>
       </c>
       <c r="R147" t="n">
-        <v>6233262</v>
+        <v>6233249</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16085,12 +16086,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16117,10 +16118,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121471924</v>
+        <v>121471845</v>
       </c>
       <c r="B148" t="n">
-        <v>80242</v>
+        <v>80256</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16129,25 +16130,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16157,10 +16158,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>428097</v>
+        <v>428248</v>
       </c>
       <c r="R148" t="n">
-        <v>6233382</v>
+        <v>6233242</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16187,12 +16188,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16219,10 +16220,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121471803</v>
+        <v>121471863</v>
       </c>
       <c r="B149" t="n">
-        <v>80255</v>
+        <v>96731</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16231,25 +16232,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16259,10 +16260,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>428334</v>
+        <v>428411</v>
       </c>
       <c r="R149" t="n">
-        <v>6233284</v>
+        <v>6233213</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16321,10 +16322,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121471849</v>
+        <v>121471853</v>
       </c>
       <c r="B150" t="n">
-        <v>80255</v>
+        <v>76949</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16333,25 +16334,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16361,10 +16362,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>428299</v>
+        <v>428311</v>
       </c>
       <c r="R150" t="n">
-        <v>6233126</v>
+        <v>6233183</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16423,10 +16424,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121471861</v>
+        <v>121471822</v>
       </c>
       <c r="B151" t="n">
-        <v>94599</v>
+        <v>94605</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16463,10 +16464,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>428404</v>
+        <v>428288</v>
       </c>
       <c r="R151" t="n">
-        <v>6233275</v>
+        <v>6233325</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16525,10 +16526,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121471865</v>
+        <v>121471839</v>
       </c>
       <c r="B152" t="n">
-        <v>74699</v>
+        <v>94594</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16541,21 +16542,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>306</v>
+        <v>2671</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16565,10 +16566,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>428438</v>
+        <v>428184</v>
       </c>
       <c r="R152" t="n">
-        <v>6233202</v>
+        <v>6233240</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16627,10 +16628,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121471869</v>
+        <v>121471861</v>
       </c>
       <c r="B153" t="n">
-        <v>96725</v>
+        <v>94605</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16643,21 +16644,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16667,10 +16668,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>428354</v>
+        <v>428404</v>
       </c>
       <c r="R153" t="n">
-        <v>6233242</v>
+        <v>6233275</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16729,10 +16730,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121471817</v>
+        <v>121471857</v>
       </c>
       <c r="B154" t="n">
-        <v>74697</v>
+        <v>80256</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16741,25 +16742,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6439</v>
+        <v>1144</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16769,10 +16770,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>428312</v>
+        <v>428362</v>
       </c>
       <c r="R154" t="n">
-        <v>6233323</v>
+        <v>6233272</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16831,10 +16832,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121471828</v>
+        <v>121471850</v>
       </c>
       <c r="B155" t="n">
-        <v>80242</v>
+        <v>80243</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16871,10 +16872,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>428185</v>
+        <v>428293</v>
       </c>
       <c r="R155" t="n">
-        <v>6233289</v>
+        <v>6233170</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16915,7 +16916,6 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
-      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
@@ -16934,10 +16934,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121471541</v>
+        <v>121471695</v>
       </c>
       <c r="B156" t="n">
-        <v>80242</v>
+        <v>80243</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16974,10 +16974,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>428209</v>
+        <v>428053</v>
       </c>
       <c r="R156" t="n">
-        <v>6233184</v>
+        <v>6233336</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17036,10 +17036,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121471690</v>
+        <v>121471851</v>
       </c>
       <c r="B157" t="n">
-        <v>80242</v>
+        <v>78864</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17052,21 +17052,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>230185</v>
+        <v>6459</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17076,10 +17076,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>428161</v>
+        <v>428293</v>
       </c>
       <c r="R157" t="n">
-        <v>6233396</v>
+        <v>6233170</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17106,12 +17106,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17138,10 +17138,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121471910</v>
+        <v>121471833</v>
       </c>
       <c r="B158" t="n">
-        <v>76948</v>
+        <v>80243</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17150,25 +17150,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17178,10 +17178,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>428377</v>
+        <v>428139</v>
       </c>
       <c r="R158" t="n">
-        <v>6233090</v>
+        <v>6233315</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17208,12 +17208,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17240,10 +17240,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121471881</v>
+        <v>121471825</v>
       </c>
       <c r="B159" t="n">
-        <v>78407</v>
+        <v>80243</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17252,25 +17252,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>924</v>
+        <v>230185</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17280,10 +17280,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>428445</v>
+        <v>428233</v>
       </c>
       <c r="R159" t="n">
-        <v>6233151</v>
+        <v>6233332</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17342,10 +17342,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121471545</v>
+        <v>121471910</v>
       </c>
       <c r="B160" t="n">
-        <v>80255</v>
+        <v>76949</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17354,25 +17354,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17382,10 +17382,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>428172</v>
+        <v>428377</v>
       </c>
       <c r="R160" t="n">
-        <v>6233315</v>
+        <v>6233090</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17412,12 +17412,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17444,10 +17444,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121471804</v>
+        <v>121471913</v>
       </c>
       <c r="B161" t="n">
-        <v>76948</v>
+        <v>76949</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17484,10 +17484,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>428335</v>
+        <v>428342</v>
       </c>
       <c r="R161" t="n">
-        <v>6233286</v>
+        <v>6233082</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17546,10 +17546,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121471842</v>
+        <v>121471864</v>
       </c>
       <c r="B162" t="n">
-        <v>94599</v>
+        <v>94594</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17562,21 +17562,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17586,10 +17586,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>428221</v>
+        <v>428410</v>
       </c>
       <c r="R162" t="n">
-        <v>6233212</v>
+        <v>6233214</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17648,10 +17648,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121471543</v>
+        <v>121471905</v>
       </c>
       <c r="B163" t="n">
-        <v>80242</v>
+        <v>74610</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17660,25 +17660,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>230185</v>
+        <v>1118</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17688,10 +17688,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>428209</v>
+        <v>428377</v>
       </c>
       <c r="R163" t="n">
-        <v>6233279</v>
+        <v>6233095</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17750,10 +17750,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121471895</v>
+        <v>121471904</v>
       </c>
       <c r="B164" t="n">
-        <v>80242</v>
+        <v>78408</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17762,25 +17762,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>230185</v>
+        <v>924</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17790,10 +17790,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>428355</v>
+        <v>428387</v>
       </c>
       <c r="R164" t="n">
-        <v>6233123</v>
+        <v>6233098</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17852,10 +17852,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121471942</v>
+        <v>121471930</v>
       </c>
       <c r="B165" t="n">
-        <v>76948</v>
+        <v>74610</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17868,21 +17868,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1342</v>
+        <v>1118</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17892,10 +17892,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>428032</v>
+        <v>428078</v>
       </c>
       <c r="R165" t="n">
-        <v>6233345</v>
+        <v>6233294</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17954,10 +17954,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121471902</v>
+        <v>121471876</v>
       </c>
       <c r="B166" t="n">
-        <v>94588</v>
+        <v>80286</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17970,21 +17970,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>2671</v>
+        <v>1223</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Rikfruktig blemlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Phlyctis agelaea</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Flot.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17994,10 +17994,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>428387</v>
+        <v>428446</v>
       </c>
       <c r="R166" t="n">
-        <v>6233096</v>
+        <v>6233151</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18024,12 +18024,12 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18056,10 +18056,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121471858</v>
+        <v>121471922</v>
       </c>
       <c r="B167" t="n">
-        <v>80255</v>
+        <v>76949</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18068,25 +18068,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18096,10 +18096,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>428372</v>
+        <v>428091</v>
       </c>
       <c r="R167" t="n">
-        <v>6233270</v>
+        <v>6233385</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18126,12 +18126,12 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18158,10 +18158,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121471874</v>
+        <v>121471816</v>
       </c>
       <c r="B168" t="n">
-        <v>80255</v>
+        <v>96779</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18170,25 +18170,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1144</v>
+        <v>2604</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18198,10 +18198,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>428375</v>
+        <v>428317</v>
       </c>
       <c r="R168" t="n">
-        <v>6233151</v>
+        <v>6233324</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18260,10 +18260,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121471694</v>
+        <v>121471854</v>
       </c>
       <c r="B169" t="n">
-        <v>80255</v>
+        <v>96731</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -18272,25 +18272,25 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18300,10 +18300,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>428125</v>
+        <v>428302</v>
       </c>
       <c r="R169" t="n">
-        <v>6233379</v>
+        <v>6233177</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18330,12 +18330,12 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18362,10 +18362,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121471941</v>
+        <v>121471692</v>
       </c>
       <c r="B170" t="n">
-        <v>80242</v>
+        <v>94605</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18378,21 +18378,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18402,10 +18402,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>428046</v>
+        <v>428126</v>
       </c>
       <c r="R170" t="n">
-        <v>6233350</v>
+        <v>6233380</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18432,12 +18432,12 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18464,10 +18464,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121471938</v>
+        <v>121471899</v>
       </c>
       <c r="B171" t="n">
-        <v>80242</v>
+        <v>94399</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18480,21 +18480,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>230185</v>
+        <v>2779</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18504,10 +18504,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>428062</v>
+        <v>428389</v>
       </c>
       <c r="R171" t="n">
-        <v>6233301</v>
+        <v>6233099</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18566,10 +18566,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121471695</v>
+        <v>121471697</v>
       </c>
       <c r="B172" t="n">
-        <v>80242</v>
+        <v>74700</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18582,21 +18582,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>230185</v>
+        <v>306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18606,10 +18606,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>428053</v>
+        <v>428043</v>
       </c>
       <c r="R172" t="n">
-        <v>6233336</v>
+        <v>6233298</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18668,10 +18668,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121471798</v>
+        <v>121471916</v>
       </c>
       <c r="B173" t="n">
-        <v>96725</v>
+        <v>94615</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18684,21 +18684,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2606</v>
+        <v>1080</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18708,10 +18708,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>428387</v>
+        <v>428283</v>
       </c>
       <c r="R173" t="n">
-        <v>6233326</v>
+        <v>6233084</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18738,12 +18738,12 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18770,10 +18770,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121471839</v>
+        <v>121471874</v>
       </c>
       <c r="B174" t="n">
-        <v>94588</v>
+        <v>80256</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18782,25 +18782,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>2671</v>
+        <v>1144</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18810,10 +18810,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>428184</v>
+        <v>428375</v>
       </c>
       <c r="R174" t="n">
-        <v>6233240</v>
+        <v>6233151</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18872,10 +18872,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121471878</v>
+        <v>121471831</v>
       </c>
       <c r="B175" t="n">
-        <v>96773</v>
+        <v>80256</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18884,25 +18884,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>2604</v>
+        <v>1144</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18912,10 +18912,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>428445</v>
+        <v>428145</v>
       </c>
       <c r="R175" t="n">
-        <v>6233151</v>
+        <v>6233315</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>

--- a/artfynd/A 18989-2024 artfynd.xlsx
+++ b/artfynd/A 18989-2024 artfynd.xlsx
@@ -3354,10 +3354,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121471940</v>
+        <v>121471690</v>
       </c>
       <c r="B23" t="n">
-        <v>94615</v>
+        <v>80243</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3370,21 +3370,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1080</v>
+        <v>230185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>428037</v>
+        <v>428161</v>
       </c>
       <c r="R23" t="n">
-        <v>6233291</v>
+        <v>6233396</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3424,12 +3424,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3456,7 +3456,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121471828</v>
+        <v>121471924</v>
       </c>
       <c r="B24" t="n">
         <v>80243</v>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>428185</v>
+        <v>428097</v>
       </c>
       <c r="R24" t="n">
-        <v>6233289</v>
+        <v>6233382</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3526,12 +3526,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3540,7 +3540,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3559,10 +3558,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121471690</v>
+        <v>121471940</v>
       </c>
       <c r="B25" t="n">
-        <v>80243</v>
+        <v>94615</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3575,21 +3574,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>230185</v>
+        <v>1080</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3599,10 +3598,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>428161</v>
+        <v>428037</v>
       </c>
       <c r="R25" t="n">
-        <v>6233396</v>
+        <v>6233291</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3629,12 +3628,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3661,7 +3660,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121471924</v>
+        <v>121471828</v>
       </c>
       <c r="B26" t="n">
         <v>80243</v>
@@ -3701,10 +3700,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>428097</v>
+        <v>428185</v>
       </c>
       <c r="R26" t="n">
-        <v>6233382</v>
+        <v>6233289</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3731,12 +3730,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3745,6 +3744,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -5089,10 +5089,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121471686</v>
+        <v>121471859</v>
       </c>
       <c r="B40" t="n">
-        <v>80256</v>
+        <v>80243</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5101,25 +5101,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>428187</v>
+        <v>428404</v>
       </c>
       <c r="R40" t="n">
-        <v>6233403</v>
+        <v>6233275</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5159,12 +5159,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5191,10 +5191,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121471859</v>
+        <v>121471686</v>
       </c>
       <c r="B41" t="n">
-        <v>80243</v>
+        <v>80256</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5203,25 +5203,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5231,10 +5231,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>428404</v>
+        <v>428187</v>
       </c>
       <c r="R41" t="n">
-        <v>6233275</v>
+        <v>6233403</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5261,12 +5261,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -9883,10 +9883,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121471818</v>
+        <v>121471684</v>
       </c>
       <c r="B87" t="n">
-        <v>96731</v>
+        <v>80413</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9895,25 +9895,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2606</v>
+        <v>1557</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Röd pysslinglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelopsis rubella</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Nyl.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9923,10 +9923,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>428307</v>
+        <v>428227</v>
       </c>
       <c r="R87" t="n">
-        <v>6233311</v>
+        <v>6233392</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9953,12 +9953,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9985,10 +9985,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121471919</v>
+        <v>121471818</v>
       </c>
       <c r="B88" t="n">
-        <v>80256</v>
+        <v>96731</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9997,25 +9997,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10025,10 +10025,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>428106</v>
+        <v>428307</v>
       </c>
       <c r="R88" t="n">
-        <v>6233304</v>
+        <v>6233311</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10055,12 +10055,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10087,14 +10087,14 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121471875</v>
+        <v>121471919</v>
       </c>
       <c r="B89" t="n">
         <v>80256</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10121,19 +10121,16 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>428340</v>
+        <v>428106</v>
       </c>
       <c r="R89" t="n">
-        <v>6233229</v>
+        <v>6233304</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10160,17 +10157,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>kollekt</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10178,11 +10170,6 @@
       </c>
       <c r="AE89" t="b">
         <v>0</v>
-      </c>
-      <c r="AF89" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG89" t="b">
         <v>0</v>
@@ -10202,7 +10189,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121471805</v>
+        <v>121471849</v>
       </c>
       <c r="B90" t="n">
         <v>80256</v>
@@ -10242,10 +10229,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>428333</v>
+        <v>428299</v>
       </c>
       <c r="R90" t="n">
-        <v>6233283</v>
+        <v>6233126</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10304,14 +10291,14 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121471684</v>
+        <v>121471875</v>
       </c>
       <c r="B91" t="n">
-        <v>80413</v>
+        <v>80256</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -10320,34 +10307,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1557</v>
+        <v>1144</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Röd pysslinglav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Thelopsis rubella</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Nyl.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>428227</v>
+        <v>428340</v>
       </c>
       <c r="R91" t="n">
-        <v>6233392</v>
+        <v>6233229</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10374,12 +10364,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>kollekt</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10387,6 +10382,11 @@
       </c>
       <c r="AE91" t="b">
         <v>0</v>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG91" t="b">
         <v>0</v>
@@ -10406,7 +10406,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121471849</v>
+        <v>121471805</v>
       </c>
       <c r="B92" t="n">
         <v>80256</v>
@@ -10446,10 +10446,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>428299</v>
+        <v>428333</v>
       </c>
       <c r="R92" t="n">
-        <v>6233126</v>
+        <v>6233283</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10508,10 +10508,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121471927</v>
+        <v>121471926</v>
       </c>
       <c r="B93" t="n">
-        <v>76949</v>
+        <v>94399</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10520,25 +10520,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1342</v>
+        <v>2779</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10548,10 +10548,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>428074</v>
+        <v>428073</v>
       </c>
       <c r="R93" t="n">
-        <v>6233297</v>
+        <v>6233383</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10610,10 +10610,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121471537</v>
+        <v>121471806</v>
       </c>
       <c r="B94" t="n">
-        <v>96731</v>
+        <v>80256</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10622,25 +10622,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10650,10 +10650,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>428163</v>
+        <v>428325</v>
       </c>
       <c r="R94" t="n">
-        <v>6233193</v>
+        <v>6233291</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10680,12 +10680,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10712,10 +10712,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121471926</v>
+        <v>121471840</v>
       </c>
       <c r="B95" t="n">
-        <v>94399</v>
+        <v>78988</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10728,21 +10728,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2779</v>
+        <v>6431</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10752,10 +10752,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>428073</v>
+        <v>428183</v>
       </c>
       <c r="R95" t="n">
-        <v>6233383</v>
+        <v>6233239</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10782,12 +10782,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10814,10 +10814,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121471806</v>
+        <v>121471927</v>
       </c>
       <c r="B96" t="n">
-        <v>80256</v>
+        <v>76949</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10826,25 +10826,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10854,10 +10854,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>428325</v>
+        <v>428074</v>
       </c>
       <c r="R96" t="n">
-        <v>6233291</v>
+        <v>6233297</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10884,12 +10884,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10916,10 +10916,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121471840</v>
+        <v>121471537</v>
       </c>
       <c r="B97" t="n">
-        <v>78988</v>
+        <v>96731</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10932,21 +10932,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6431</v>
+        <v>2606</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10956,10 +10956,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>428183</v>
+        <v>428163</v>
       </c>
       <c r="R97" t="n">
-        <v>6233239</v>
+        <v>6233193</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10986,12 +10986,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12854,10 +12854,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121471882</v>
+        <v>121471935</v>
       </c>
       <c r="B116" t="n">
-        <v>74610</v>
+        <v>80243</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12866,25 +12866,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1118</v>
+        <v>230185</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12894,10 +12894,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>428445</v>
+        <v>428097</v>
       </c>
       <c r="R116" t="n">
-        <v>6233151</v>
+        <v>6233286</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12924,12 +12924,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12956,10 +12956,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121471801</v>
+        <v>121471846</v>
       </c>
       <c r="B117" t="n">
-        <v>80256</v>
+        <v>80243</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12968,25 +12968,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12996,10 +12996,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>428370</v>
+        <v>428241</v>
       </c>
       <c r="R117" t="n">
-        <v>6233336</v>
+        <v>6233222</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13058,10 +13058,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121471935</v>
+        <v>121471882</v>
       </c>
       <c r="B118" t="n">
-        <v>80243</v>
+        <v>74610</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13070,25 +13070,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>230185</v>
+        <v>1118</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13098,10 +13098,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>428097</v>
+        <v>428445</v>
       </c>
       <c r="R118" t="n">
-        <v>6233286</v>
+        <v>6233151</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13128,12 +13128,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13160,10 +13160,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121471846</v>
+        <v>121471801</v>
       </c>
       <c r="B119" t="n">
-        <v>80243</v>
+        <v>80256</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13172,25 +13172,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13200,10 +13200,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>428241</v>
+        <v>428370</v>
       </c>
       <c r="R119" t="n">
-        <v>6233222</v>
+        <v>6233336</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14078,10 +14078,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121471843</v>
+        <v>121471920</v>
       </c>
       <c r="B128" t="n">
-        <v>57371</v>
+        <v>91118</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14094,21 +14094,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100049</v>
+        <v>2023</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sydlig sotticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ischnoderma resinosum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schrad.) P.Karst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14118,10 +14118,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>428252</v>
+        <v>428095</v>
       </c>
       <c r="R128" t="n">
-        <v>6233262</v>
+        <v>6233349</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14148,12 +14148,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14180,10 +14180,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121471938</v>
+        <v>121471843</v>
       </c>
       <c r="B129" t="n">
-        <v>80243</v>
+        <v>57371</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14192,25 +14192,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>230185</v>
+        <v>100049</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14220,10 +14220,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>428062</v>
+        <v>428252</v>
       </c>
       <c r="R129" t="n">
-        <v>6233301</v>
+        <v>6233262</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14250,12 +14250,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14282,10 +14282,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121471920</v>
+        <v>121471543</v>
       </c>
       <c r="B130" t="n">
-        <v>91118</v>
+        <v>80243</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14294,25 +14294,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2023</v>
+        <v>230185</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Sydlig sotticka</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Ischnoderma resinosum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Schrad.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14322,10 +14322,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>428095</v>
+        <v>428209</v>
       </c>
       <c r="R130" t="n">
-        <v>6233349</v>
+        <v>6233279</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14352,12 +14352,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14384,7 +14384,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121471543</v>
+        <v>121471895</v>
       </c>
       <c r="B131" t="n">
         <v>80243</v>
@@ -14424,10 +14424,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>428209</v>
+        <v>428355</v>
       </c>
       <c r="R131" t="n">
-        <v>6233279</v>
+        <v>6233123</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14454,12 +14454,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14486,7 +14486,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121471895</v>
+        <v>121471938</v>
       </c>
       <c r="B132" t="n">
         <v>80243</v>
@@ -14526,10 +14526,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>428355</v>
+        <v>428062</v>
       </c>
       <c r="R132" t="n">
-        <v>6233123</v>
+        <v>6233301</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -16424,10 +16424,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121471822</v>
+        <v>121471850</v>
       </c>
       <c r="B151" t="n">
-        <v>94605</v>
+        <v>80243</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16440,21 +16440,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16464,10 +16464,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>428288</v>
+        <v>428293</v>
       </c>
       <c r="R151" t="n">
-        <v>6233325</v>
+        <v>6233170</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16526,10 +16526,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121471839</v>
+        <v>121471695</v>
       </c>
       <c r="B152" t="n">
-        <v>94594</v>
+        <v>80243</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16542,21 +16542,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>2671</v>
+        <v>230185</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16566,10 +16566,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>428184</v>
+        <v>428053</v>
       </c>
       <c r="R152" t="n">
-        <v>6233240</v>
+        <v>6233336</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16596,12 +16596,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16628,7 +16628,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121471861</v>
+        <v>121471822</v>
       </c>
       <c r="B153" t="n">
         <v>94605</v>
@@ -16668,10 +16668,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>428404</v>
+        <v>428288</v>
       </c>
       <c r="R153" t="n">
-        <v>6233275</v>
+        <v>6233325</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16730,10 +16730,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121471857</v>
+        <v>121471839</v>
       </c>
       <c r="B154" t="n">
-        <v>80256</v>
+        <v>94594</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16742,25 +16742,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1144</v>
+        <v>2671</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16770,10 +16770,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>428362</v>
+        <v>428184</v>
       </c>
       <c r="R154" t="n">
-        <v>6233272</v>
+        <v>6233240</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16832,10 +16832,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121471850</v>
+        <v>121471861</v>
       </c>
       <c r="B155" t="n">
-        <v>80243</v>
+        <v>94605</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16848,21 +16848,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16872,10 +16872,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>428293</v>
+        <v>428404</v>
       </c>
       <c r="R155" t="n">
-        <v>6233170</v>
+        <v>6233275</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16934,10 +16934,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121471695</v>
+        <v>121471857</v>
       </c>
       <c r="B156" t="n">
-        <v>80243</v>
+        <v>80256</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16946,25 +16946,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16974,10 +16974,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>428053</v>
+        <v>428362</v>
       </c>
       <c r="R156" t="n">
-        <v>6233336</v>
+        <v>6233272</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17004,12 +17004,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17036,10 +17036,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121471851</v>
+        <v>121471904</v>
       </c>
       <c r="B157" t="n">
-        <v>78864</v>
+        <v>78408</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17048,25 +17048,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6459</v>
+        <v>924</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17076,10 +17076,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>428293</v>
+        <v>428387</v>
       </c>
       <c r="R157" t="n">
-        <v>6233170</v>
+        <v>6233098</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17106,12 +17106,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17138,10 +17138,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121471833</v>
+        <v>121471851</v>
       </c>
       <c r="B158" t="n">
-        <v>80243</v>
+        <v>78864</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17154,21 +17154,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>230185</v>
+        <v>6459</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17178,10 +17178,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>428139</v>
+        <v>428293</v>
       </c>
       <c r="R158" t="n">
-        <v>6233315</v>
+        <v>6233170</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17240,10 +17240,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121471825</v>
+        <v>121471910</v>
       </c>
       <c r="B159" t="n">
-        <v>80243</v>
+        <v>76949</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17252,25 +17252,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17280,10 +17280,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>428233</v>
+        <v>428377</v>
       </c>
       <c r="R159" t="n">
-        <v>6233332</v>
+        <v>6233090</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17310,12 +17310,12 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17342,7 +17342,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121471910</v>
+        <v>121471913</v>
       </c>
       <c r="B160" t="n">
         <v>76949</v>
@@ -17382,10 +17382,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>428377</v>
+        <v>428342</v>
       </c>
       <c r="R160" t="n">
-        <v>6233090</v>
+        <v>6233082</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17444,10 +17444,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121471913</v>
+        <v>121471864</v>
       </c>
       <c r="B161" t="n">
-        <v>76949</v>
+        <v>94594</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17456,25 +17456,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1342</v>
+        <v>2671</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17484,10 +17484,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>428342</v>
+        <v>428410</v>
       </c>
       <c r="R161" t="n">
-        <v>6233082</v>
+        <v>6233214</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17546,10 +17546,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121471864</v>
+        <v>121471905</v>
       </c>
       <c r="B162" t="n">
-        <v>94594</v>
+        <v>74610</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17558,25 +17558,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>2671</v>
+        <v>1118</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17586,10 +17586,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>428410</v>
+        <v>428377</v>
       </c>
       <c r="R162" t="n">
-        <v>6233214</v>
+        <v>6233095</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17616,12 +17616,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17648,7 +17648,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121471905</v>
+        <v>121471930</v>
       </c>
       <c r="B163" t="n">
         <v>74610</v>
@@ -17688,10 +17688,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>428377</v>
+        <v>428078</v>
       </c>
       <c r="R163" t="n">
-        <v>6233095</v>
+        <v>6233294</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17750,10 +17750,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121471904</v>
+        <v>121471833</v>
       </c>
       <c r="B164" t="n">
-        <v>78408</v>
+        <v>80243</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17762,25 +17762,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>924</v>
+        <v>230185</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17790,10 +17790,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>428387</v>
+        <v>428139</v>
       </c>
       <c r="R164" t="n">
-        <v>6233098</v>
+        <v>6233315</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17820,12 +17820,12 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17852,10 +17852,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121471930</v>
+        <v>121471825</v>
       </c>
       <c r="B165" t="n">
-        <v>74610</v>
+        <v>80243</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17864,25 +17864,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1118</v>
+        <v>230185</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17892,10 +17892,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>428078</v>
+        <v>428233</v>
       </c>
       <c r="R165" t="n">
-        <v>6233294</v>
+        <v>6233332</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17922,12 +17922,12 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD165" t="b">

--- a/artfynd/A 18989-2024 artfynd.xlsx
+++ b/artfynd/A 18989-2024 artfynd.xlsx
@@ -3354,10 +3354,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121471690</v>
+        <v>121471869</v>
       </c>
       <c r="B23" t="n">
-        <v>80243</v>
+        <v>96732</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3370,21 +3370,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>428161</v>
+        <v>428354</v>
       </c>
       <c r="R23" t="n">
-        <v>6233396</v>
+        <v>6233242</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3424,12 +3424,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3456,10 +3456,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121471924</v>
+        <v>121471798</v>
       </c>
       <c r="B24" t="n">
-        <v>80243</v>
+        <v>96732</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3472,21 +3472,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>428097</v>
+        <v>428387</v>
       </c>
       <c r="R24" t="n">
-        <v>6233382</v>
+        <v>6233326</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3526,12 +3526,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3558,10 +3558,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121471940</v>
+        <v>121471876</v>
       </c>
       <c r="B25" t="n">
-        <v>94615</v>
+        <v>80287</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3574,21 +3574,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1080</v>
+        <v>1223</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Rikfruktig blemlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Phlyctis agelaea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Flot.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>428037</v>
+        <v>428446</v>
       </c>
       <c r="R25" t="n">
-        <v>6233291</v>
+        <v>6233151</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3628,12 +3628,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3660,10 +3660,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121471828</v>
+        <v>121471922</v>
       </c>
       <c r="B26" t="n">
-        <v>80243</v>
+        <v>76950</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3672,25 +3672,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>428185</v>
+        <v>428091</v>
       </c>
       <c r="R26" t="n">
-        <v>6233289</v>
+        <v>6233385</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3730,12 +3730,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3744,7 +3744,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3763,10 +3762,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121471917</v>
+        <v>121471928</v>
       </c>
       <c r="B27" t="n">
-        <v>80243</v>
+        <v>80257</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3775,25 +3774,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3803,10 +3802,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>428284</v>
+        <v>428075</v>
       </c>
       <c r="R27" t="n">
-        <v>6233109</v>
+        <v>6233294</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3865,10 +3864,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121471945</v>
+        <v>121471858</v>
       </c>
       <c r="B28" t="n">
-        <v>96779</v>
+        <v>80257</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3877,25 +3876,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2604</v>
+        <v>1144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3905,10 +3904,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>428035</v>
+        <v>428372</v>
       </c>
       <c r="R28" t="n">
-        <v>6233349</v>
+        <v>6233270</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3935,12 +3934,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3967,10 +3966,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121471903</v>
+        <v>121471808</v>
       </c>
       <c r="B29" t="n">
-        <v>76949</v>
+        <v>80257</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3979,25 +3978,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4007,10 +4006,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>428385</v>
+        <v>428350</v>
       </c>
       <c r="R29" t="n">
-        <v>6233097</v>
+        <v>6233316</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4037,12 +4036,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4069,10 +4068,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121471693</v>
+        <v>121471809</v>
       </c>
       <c r="B30" t="n">
-        <v>94594</v>
+        <v>74565</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4081,25 +4080,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2671</v>
+        <v>1116</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4109,10 +4108,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>428125</v>
+        <v>428352</v>
       </c>
       <c r="R30" t="n">
-        <v>6233379</v>
+        <v>6233315</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4139,12 +4138,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4171,10 +4170,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121471539</v>
+        <v>121471815</v>
       </c>
       <c r="B31" t="n">
-        <v>94594</v>
+        <v>80414</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4183,25 +4182,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2671</v>
+        <v>1557</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Röd pysslinglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Thelopsis rubella</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Nyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4211,10 +4210,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>428262</v>
+        <v>428333</v>
       </c>
       <c r="R31" t="n">
-        <v>6233134</v>
+        <v>6233339</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4241,12 +4240,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4273,10 +4272,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121471836</v>
+        <v>121471840</v>
       </c>
       <c r="B32" t="n">
-        <v>94594</v>
+        <v>78989</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4289,21 +4288,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2671</v>
+        <v>6431</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4313,10 +4312,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>428145</v>
+        <v>428183</v>
       </c>
       <c r="R32" t="n">
-        <v>6233244</v>
+        <v>6233239</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4375,10 +4374,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121471814</v>
+        <v>121471850</v>
       </c>
       <c r="B33" t="n">
-        <v>80256</v>
+        <v>80244</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4387,25 +4386,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4415,10 +4414,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>428331</v>
+        <v>428293</v>
       </c>
       <c r="R33" t="n">
-        <v>6233339</v>
+        <v>6233170</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4477,10 +4476,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121471541</v>
+        <v>121471696</v>
       </c>
       <c r="B34" t="n">
-        <v>80243</v>
+        <v>96732</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4493,21 +4492,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4517,10 +4516,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>428209</v>
+        <v>428054</v>
       </c>
       <c r="R34" t="n">
-        <v>6233184</v>
+        <v>6233337</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4579,10 +4578,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121471535</v>
+        <v>121471926</v>
       </c>
       <c r="B35" t="n">
-        <v>76949</v>
+        <v>94400</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4591,25 +4590,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1342</v>
+        <v>2779</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4619,10 +4618,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>428160</v>
+        <v>428073</v>
       </c>
       <c r="R35" t="n">
-        <v>6233209</v>
+        <v>6233383</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4649,12 +4648,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4681,10 +4680,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121471824</v>
+        <v>121471943</v>
       </c>
       <c r="B36" t="n">
-        <v>76949</v>
+        <v>96732</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4693,25 +4692,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4721,10 +4720,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>428288</v>
+        <v>428034</v>
       </c>
       <c r="R36" t="n">
-        <v>6233325</v>
+        <v>6233348</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4751,12 +4750,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4783,10 +4782,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121471835</v>
+        <v>121471820</v>
       </c>
       <c r="B37" t="n">
-        <v>96731</v>
+        <v>94400</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4799,21 +4798,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2606</v>
+        <v>2779</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4823,10 +4822,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>428145</v>
+        <v>428304</v>
       </c>
       <c r="R37" t="n">
-        <v>6233244</v>
+        <v>6233306</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4885,10 +4884,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121471827</v>
+        <v>121471916</v>
       </c>
       <c r="B38" t="n">
-        <v>94605</v>
+        <v>94616</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4901,21 +4900,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2667</v>
+        <v>1080</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4925,10 +4924,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>428185</v>
+        <v>428283</v>
       </c>
       <c r="R38" t="n">
-        <v>6233287</v>
+        <v>6233084</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4955,12 +4954,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4987,10 +4986,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121471925</v>
+        <v>121471909</v>
       </c>
       <c r="B39" t="n">
-        <v>94607</v>
+        <v>76950</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4999,25 +4998,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2666</v>
+        <v>1342</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5027,10 +5026,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>428076</v>
+        <v>428373</v>
       </c>
       <c r="R39" t="n">
-        <v>6233382</v>
+        <v>6233088</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5089,10 +5088,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121471859</v>
+        <v>121471849</v>
       </c>
       <c r="B40" t="n">
-        <v>80243</v>
+        <v>80257</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5101,25 +5100,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5129,10 +5128,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>428404</v>
+        <v>428299</v>
       </c>
       <c r="R40" t="n">
-        <v>6233275</v>
+        <v>6233126</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5191,10 +5190,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121471686</v>
+        <v>121471541</v>
       </c>
       <c r="B41" t="n">
-        <v>80256</v>
+        <v>80244</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5203,25 +5202,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5231,10 +5230,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>428187</v>
+        <v>428209</v>
       </c>
       <c r="R41" t="n">
-        <v>6233403</v>
+        <v>6233184</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5293,10 +5292,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121471534</v>
+        <v>121471538</v>
       </c>
       <c r="B42" t="n">
-        <v>96731</v>
+        <v>80244</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5309,21 +5308,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5333,10 +5332,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>428147</v>
+        <v>428166</v>
       </c>
       <c r="R42" t="n">
-        <v>6233224</v>
+        <v>6233198</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5395,10 +5394,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121471804</v>
+        <v>121471837</v>
       </c>
       <c r="B43" t="n">
-        <v>76949</v>
+        <v>80244</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5407,25 +5406,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5435,10 +5434,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>428335</v>
+        <v>428145</v>
       </c>
       <c r="R43" t="n">
-        <v>6233286</v>
+        <v>6233244</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5497,10 +5496,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121471937</v>
+        <v>121471860</v>
       </c>
       <c r="B44" t="n">
-        <v>96731</v>
+        <v>96732</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5537,10 +5536,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>428062</v>
+        <v>428404</v>
       </c>
       <c r="R44" t="n">
-        <v>6233301</v>
+        <v>6233275</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5567,12 +5566,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5599,10 +5598,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121471902</v>
+        <v>121471818</v>
       </c>
       <c r="B45" t="n">
-        <v>94594</v>
+        <v>96732</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5615,21 +5614,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5639,10 +5638,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>428387</v>
+        <v>428307</v>
       </c>
       <c r="R45" t="n">
-        <v>6233096</v>
+        <v>6233311</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5669,12 +5668,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5701,10 +5700,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121471532</v>
+        <v>121471812</v>
       </c>
       <c r="B46" t="n">
-        <v>94605</v>
+        <v>94400</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5717,21 +5716,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5741,10 +5740,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>428133</v>
+        <v>428331</v>
       </c>
       <c r="R46" t="n">
-        <v>6233219</v>
+        <v>6233335</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5771,12 +5770,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5803,10 +5802,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121471829</v>
+        <v>121471853</v>
       </c>
       <c r="B47" t="n">
-        <v>80256</v>
+        <v>76950</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5815,25 +5814,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5843,10 +5842,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>428147</v>
+        <v>428311</v>
       </c>
       <c r="R47" t="n">
-        <v>6233304</v>
+        <v>6233183</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5905,10 +5904,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121471810</v>
+        <v>121471857</v>
       </c>
       <c r="B48" t="n">
-        <v>80256</v>
+        <v>80257</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5945,10 +5944,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>428347</v>
+        <v>428362</v>
       </c>
       <c r="R48" t="n">
-        <v>6233326</v>
+        <v>6233272</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6007,10 +6006,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121471852</v>
+        <v>121471905</v>
       </c>
       <c r="B49" t="n">
-        <v>80256</v>
+        <v>74611</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6019,25 +6018,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1144</v>
+        <v>1118</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6047,10 +6046,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>428311</v>
+        <v>428377</v>
       </c>
       <c r="R49" t="n">
-        <v>6233183</v>
+        <v>6233095</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6077,12 +6076,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6109,10 +6108,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121471536</v>
+        <v>121471942</v>
       </c>
       <c r="B50" t="n">
-        <v>80579</v>
+        <v>76950</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6125,21 +6124,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1182</v>
+        <v>1342</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6149,10 +6148,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>428166</v>
+        <v>428032</v>
       </c>
       <c r="R50" t="n">
-        <v>6233202</v>
+        <v>6233345</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6179,12 +6178,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6211,10 +6210,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121471844</v>
+        <v>121471826</v>
       </c>
       <c r="B51" t="n">
-        <v>76949</v>
+        <v>78865</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6223,25 +6222,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1342</v>
+        <v>6459</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6251,10 +6250,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>428248</v>
+        <v>428228</v>
       </c>
       <c r="R51" t="n">
-        <v>6233241</v>
+        <v>6233340</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6313,10 +6312,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121471841</v>
+        <v>121471851</v>
       </c>
       <c r="B52" t="n">
-        <v>96731</v>
+        <v>78865</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6329,21 +6328,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2606</v>
+        <v>6459</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6353,10 +6352,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>428221</v>
+        <v>428293</v>
       </c>
       <c r="R52" t="n">
-        <v>6233212</v>
+        <v>6233170</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6415,10 +6414,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121471540</v>
+        <v>121471796</v>
       </c>
       <c r="B53" t="n">
-        <v>96731</v>
+        <v>80257</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6427,25 +6426,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6455,10 +6454,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>428227</v>
+        <v>428390</v>
       </c>
       <c r="R53" t="n">
-        <v>6233132</v>
+        <v>6233312</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6485,12 +6484,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6517,10 +6516,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121471544</v>
+        <v>121471945</v>
       </c>
       <c r="B54" t="n">
-        <v>94605</v>
+        <v>96780</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6533,21 +6532,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2667</v>
+        <v>2604</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6557,10 +6556,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>428219</v>
+        <v>428035</v>
       </c>
       <c r="R54" t="n">
-        <v>6233278</v>
+        <v>6233349</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6587,12 +6586,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6619,10 +6618,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121471855</v>
+        <v>121471929</v>
       </c>
       <c r="B55" t="n">
-        <v>94399</v>
+        <v>94400</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6659,10 +6658,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>428365</v>
+        <v>428078</v>
       </c>
       <c r="R55" t="n">
-        <v>6233269</v>
+        <v>6233294</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6689,12 +6688,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6721,10 +6720,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121471936</v>
+        <v>121471878</v>
       </c>
       <c r="B56" t="n">
-        <v>94615</v>
+        <v>96780</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6737,21 +6736,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1080</v>
+        <v>2604</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6761,10 +6760,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>428079</v>
+        <v>428445</v>
       </c>
       <c r="R56" t="n">
-        <v>6233262</v>
+        <v>6233151</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6791,12 +6790,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6823,10 +6822,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121471803</v>
+        <v>121471854</v>
       </c>
       <c r="B57" t="n">
-        <v>80256</v>
+        <v>96732</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6835,25 +6834,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6863,10 +6862,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>428334</v>
+        <v>428302</v>
       </c>
       <c r="R57" t="n">
-        <v>6233284</v>
+        <v>6233177</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6925,10 +6924,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121471897</v>
+        <v>121471839</v>
       </c>
       <c r="B58" t="n">
-        <v>78408</v>
+        <v>94595</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6937,25 +6936,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>924</v>
+        <v>2671</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6965,10 +6964,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>428369</v>
+        <v>428184</v>
       </c>
       <c r="R58" t="n">
-        <v>6233104</v>
+        <v>6233240</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6995,12 +6994,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7027,10 +7026,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121471865</v>
+        <v>121471543</v>
       </c>
       <c r="B59" t="n">
-        <v>74700</v>
+        <v>80244</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7043,21 +7042,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>306</v>
+        <v>230185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7067,10 +7066,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>428438</v>
+        <v>428209</v>
       </c>
       <c r="R59" t="n">
-        <v>6233202</v>
+        <v>6233279</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7097,12 +7096,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7129,10 +7128,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121471871</v>
+        <v>121471694</v>
       </c>
       <c r="B60" t="n">
-        <v>80243</v>
+        <v>80257</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7141,25 +7140,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7169,10 +7168,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>428302</v>
+        <v>428125</v>
       </c>
       <c r="R60" t="n">
-        <v>6233176</v>
+        <v>6233379</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7199,12 +7198,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7231,10 +7230,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121471530</v>
+        <v>121471801</v>
       </c>
       <c r="B61" t="n">
-        <v>80243</v>
+        <v>80257</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7243,25 +7242,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7271,10 +7270,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>428111</v>
+        <v>428370</v>
       </c>
       <c r="R61" t="n">
-        <v>6233222</v>
+        <v>6233336</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7301,12 +7300,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7333,10 +7332,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121471826</v>
+        <v>121471907</v>
       </c>
       <c r="B62" t="n">
-        <v>78864</v>
+        <v>76950</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7345,25 +7344,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6459</v>
+        <v>1342</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7373,10 +7372,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>428228</v>
+        <v>428375</v>
       </c>
       <c r="R62" t="n">
-        <v>6233340</v>
+        <v>6233092</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7403,12 +7402,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7435,10 +7434,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121471878</v>
+        <v>121471542</v>
       </c>
       <c r="B63" t="n">
-        <v>96779</v>
+        <v>80257</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7447,25 +7446,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2604</v>
+        <v>1144</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7475,10 +7474,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>428445</v>
+        <v>428198</v>
       </c>
       <c r="R63" t="n">
-        <v>6233151</v>
+        <v>6233249</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7505,12 +7504,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7537,10 +7536,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121471943</v>
+        <v>121471870</v>
       </c>
       <c r="B64" t="n">
-        <v>96731</v>
+        <v>76950</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7549,25 +7548,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7577,10 +7576,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>428034</v>
+        <v>428356</v>
       </c>
       <c r="R64" t="n">
-        <v>6233348</v>
+        <v>6233243</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7607,12 +7606,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7639,50 +7638,53 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121471862</v>
+        <v>121471875</v>
       </c>
       <c r="B65" t="n">
-        <v>80243</v>
+        <v>80257</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>428411</v>
+        <v>428340</v>
       </c>
       <c r="R65" t="n">
-        <v>6233213</v>
+        <v>6233229</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7717,11 +7719,21 @@
           <t>2024-11-21</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>kollekt</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG65" t="b">
         <v>0</v>
@@ -7741,10 +7753,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121471533</v>
+        <v>121471852</v>
       </c>
       <c r="B66" t="n">
-        <v>80243</v>
+        <v>80257</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7753,25 +7765,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7781,10 +7793,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>428144</v>
+        <v>428311</v>
       </c>
       <c r="R66" t="n">
-        <v>6233229</v>
+        <v>6233183</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7811,12 +7823,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7843,10 +7855,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121471696</v>
+        <v>121471846</v>
       </c>
       <c r="B67" t="n">
-        <v>96731</v>
+        <v>80244</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7859,21 +7871,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7883,10 +7895,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>428054</v>
+        <v>428241</v>
       </c>
       <c r="R67" t="n">
-        <v>6233337</v>
+        <v>6233222</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7913,12 +7925,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7945,10 +7957,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121471911</v>
+        <v>121471902</v>
       </c>
       <c r="B68" t="n">
-        <v>76949</v>
+        <v>94595</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7957,25 +7969,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1342</v>
+        <v>2671</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7985,10 +7997,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>428352</v>
+        <v>428387</v>
       </c>
       <c r="R68" t="n">
-        <v>6233082</v>
+        <v>6233096</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8047,10 +8059,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121471867</v>
+        <v>121471539</v>
       </c>
       <c r="B69" t="n">
-        <v>76949</v>
+        <v>94595</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8059,25 +8071,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1342</v>
+        <v>2671</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8087,10 +8099,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>428442</v>
+        <v>428262</v>
       </c>
       <c r="R69" t="n">
-        <v>6233170</v>
+        <v>6233134</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8117,12 +8129,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8149,10 +8161,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121471869</v>
+        <v>121471688</v>
       </c>
       <c r="B70" t="n">
-        <v>96731</v>
+        <v>96732</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8189,10 +8201,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>428354</v>
+        <v>428159</v>
       </c>
       <c r="R70" t="n">
-        <v>6233242</v>
+        <v>6233394</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8219,12 +8231,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8251,10 +8263,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121471847</v>
+        <v>121471939</v>
       </c>
       <c r="B71" t="n">
-        <v>76949</v>
+        <v>94606</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8263,25 +8275,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1342</v>
+        <v>2667</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8291,10 +8303,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>428300</v>
+        <v>428046</v>
       </c>
       <c r="R71" t="n">
-        <v>6233125</v>
+        <v>6233296</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8321,12 +8333,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8353,10 +8365,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121471815</v>
+        <v>121471816</v>
       </c>
       <c r="B72" t="n">
-        <v>80413</v>
+        <v>96780</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8365,25 +8377,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1557</v>
+        <v>2604</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Röd pysslinglav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Thelopsis rubella</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Nyl.</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8393,10 +8405,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>428333</v>
+        <v>428317</v>
       </c>
       <c r="R72" t="n">
-        <v>6233339</v>
+        <v>6233324</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8455,10 +8467,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121471860</v>
+        <v>121471899</v>
       </c>
       <c r="B73" t="n">
-        <v>96731</v>
+        <v>94400</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8471,21 +8483,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2606</v>
+        <v>2779</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8495,10 +8507,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>428404</v>
+        <v>428389</v>
       </c>
       <c r="R73" t="n">
-        <v>6233275</v>
+        <v>6233099</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8525,12 +8537,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8557,10 +8569,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121471929</v>
+        <v>121471536</v>
       </c>
       <c r="B74" t="n">
-        <v>94399</v>
+        <v>80580</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8569,25 +8581,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2779</v>
+        <v>1182</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8597,10 +8609,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>428078</v>
+        <v>428166</v>
       </c>
       <c r="R74" t="n">
-        <v>6233294</v>
+        <v>6233202</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8627,12 +8639,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8659,10 +8671,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121471812</v>
+        <v>121471874</v>
       </c>
       <c r="B75" t="n">
-        <v>94399</v>
+        <v>80257</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8671,25 +8683,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2779</v>
+        <v>1144</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8699,10 +8711,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>428331</v>
+        <v>428375</v>
       </c>
       <c r="R75" t="n">
-        <v>6233335</v>
+        <v>6233151</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8761,10 +8773,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121471796</v>
+        <v>121471805</v>
       </c>
       <c r="B76" t="n">
-        <v>80256</v>
+        <v>80257</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8801,10 +8813,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>428390</v>
+        <v>428333</v>
       </c>
       <c r="R76" t="n">
-        <v>6233312</v>
+        <v>6233283</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8863,10 +8875,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121471866</v>
+        <v>121471695</v>
       </c>
       <c r="B77" t="n">
-        <v>80243</v>
+        <v>80244</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8903,10 +8915,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>428442</v>
+        <v>428053</v>
       </c>
       <c r="R77" t="n">
-        <v>6233170</v>
+        <v>6233336</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8933,12 +8945,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8965,10 +8977,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121471907</v>
+        <v>121471895</v>
       </c>
       <c r="B78" t="n">
-        <v>76949</v>
+        <v>80244</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8977,25 +8989,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9005,10 +9017,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>428375</v>
+        <v>428355</v>
       </c>
       <c r="R78" t="n">
-        <v>6233092</v>
+        <v>6233123</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9067,10 +9079,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121471817</v>
+        <v>121471877</v>
       </c>
       <c r="B79" t="n">
-        <v>74698</v>
+        <v>94606</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9083,21 +9095,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6439</v>
+        <v>2667</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9107,10 +9119,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>428312</v>
+        <v>428445</v>
       </c>
       <c r="R79" t="n">
-        <v>6233323</v>
+        <v>6233151</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9169,10 +9181,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121471837</v>
+        <v>121471829</v>
       </c>
       <c r="B80" t="n">
-        <v>80243</v>
+        <v>80257</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9181,25 +9193,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9209,10 +9221,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>428145</v>
+        <v>428147</v>
       </c>
       <c r="R80" t="n">
-        <v>6233244</v>
+        <v>6233304</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9271,10 +9283,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121471933</v>
+        <v>121471685</v>
       </c>
       <c r="B81" t="n">
-        <v>94594</v>
+        <v>80257</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9283,25 +9295,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2671</v>
+        <v>1144</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9311,10 +9323,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>428090</v>
+        <v>428228</v>
       </c>
       <c r="R81" t="n">
-        <v>6233309</v>
+        <v>6233391</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9341,12 +9353,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9373,10 +9385,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121471868</v>
+        <v>121471831</v>
       </c>
       <c r="B82" t="n">
-        <v>94605</v>
+        <v>80257</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9385,25 +9397,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9413,10 +9425,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>428347</v>
+        <v>428145</v>
       </c>
       <c r="R82" t="n">
-        <v>6233241</v>
+        <v>6233315</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9475,10 +9487,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121471873</v>
+        <v>121471935</v>
       </c>
       <c r="B83" t="n">
-        <v>74564</v>
+        <v>80244</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9487,25 +9499,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1116</v>
+        <v>230185</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9515,10 +9527,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>428301</v>
+        <v>428097</v>
       </c>
       <c r="R83" t="n">
-        <v>6233171</v>
+        <v>6233286</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9545,12 +9557,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9577,10 +9589,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121471808</v>
+        <v>121471533</v>
       </c>
       <c r="B84" t="n">
-        <v>80256</v>
+        <v>80244</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9589,25 +9601,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9617,10 +9629,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>428350</v>
+        <v>428144</v>
       </c>
       <c r="R84" t="n">
-        <v>6233316</v>
+        <v>6233229</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9647,12 +9659,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9679,10 +9691,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121471545</v>
+        <v>121471827</v>
       </c>
       <c r="B85" t="n">
-        <v>80256</v>
+        <v>94606</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9691,25 +9703,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9719,10 +9731,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>428172</v>
+        <v>428185</v>
       </c>
       <c r="R85" t="n">
-        <v>6233315</v>
+        <v>6233287</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9749,12 +9761,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9781,10 +9793,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121471809</v>
+        <v>121471540</v>
       </c>
       <c r="B86" t="n">
-        <v>74564</v>
+        <v>96732</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9793,25 +9805,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1116</v>
+        <v>2606</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9821,10 +9833,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>428352</v>
+        <v>428227</v>
       </c>
       <c r="R86" t="n">
-        <v>6233315</v>
+        <v>6233132</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9851,12 +9863,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9883,10 +9895,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121471684</v>
+        <v>121471689</v>
       </c>
       <c r="B87" t="n">
-        <v>80413</v>
+        <v>94606</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9895,25 +9907,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1557</v>
+        <v>2667</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Röd pysslinglav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Thelopsis rubella</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Nyl.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9923,10 +9935,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>428227</v>
+        <v>428161</v>
       </c>
       <c r="R87" t="n">
-        <v>6233392</v>
+        <v>6233396</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9985,10 +9997,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121471818</v>
+        <v>121471537</v>
       </c>
       <c r="B88" t="n">
-        <v>96731</v>
+        <v>96732</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10025,10 +10037,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>428307</v>
+        <v>428163</v>
       </c>
       <c r="R88" t="n">
-        <v>6233311</v>
+        <v>6233193</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10055,12 +10067,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10087,10 +10099,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121471919</v>
+        <v>121471882</v>
       </c>
       <c r="B89" t="n">
-        <v>80256</v>
+        <v>74611</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10099,25 +10111,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1144</v>
+        <v>1118</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10127,10 +10139,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>428106</v>
+        <v>428445</v>
       </c>
       <c r="R89" t="n">
-        <v>6233304</v>
+        <v>6233151</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10157,12 +10169,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10189,10 +10201,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121471849</v>
+        <v>121471873</v>
       </c>
       <c r="B90" t="n">
-        <v>80256</v>
+        <v>74565</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10201,25 +10213,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1144</v>
+        <v>1116</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10229,10 +10241,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>428299</v>
+        <v>428301</v>
       </c>
       <c r="R90" t="n">
-        <v>6233126</v>
+        <v>6233171</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10291,53 +10303,50 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121471875</v>
+        <v>121471867</v>
       </c>
       <c r="B91" t="n">
-        <v>80256</v>
+        <v>76950</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>428340</v>
+        <v>428442</v>
       </c>
       <c r="R91" t="n">
-        <v>6233229</v>
+        <v>6233170</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10372,21 +10381,11 @@
           <t>2024-11-21</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>kollekt</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
-      </c>
-      <c r="AF91" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG91" t="b">
         <v>0</v>
@@ -10406,10 +10405,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121471805</v>
+        <v>121471800</v>
       </c>
       <c r="B92" t="n">
-        <v>80256</v>
+        <v>80257</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10446,10 +10445,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>428333</v>
+        <v>428387</v>
       </c>
       <c r="R92" t="n">
-        <v>6233283</v>
+        <v>6233322</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10508,10 +10507,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121471926</v>
+        <v>121471810</v>
       </c>
       <c r="B93" t="n">
-        <v>94399</v>
+        <v>80257</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10520,25 +10519,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2779</v>
+        <v>1144</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10548,10 +10547,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>428073</v>
+        <v>428347</v>
       </c>
       <c r="R93" t="n">
-        <v>6233383</v>
+        <v>6233326</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10578,12 +10577,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10610,10 +10609,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121471806</v>
+        <v>121471697</v>
       </c>
       <c r="B94" t="n">
-        <v>80256</v>
+        <v>74701</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10622,25 +10621,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1144</v>
+        <v>306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10650,10 +10649,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>428325</v>
+        <v>428043</v>
       </c>
       <c r="R94" t="n">
-        <v>6233291</v>
+        <v>6233298</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10680,12 +10679,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10712,10 +10711,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121471840</v>
+        <v>121471802</v>
       </c>
       <c r="B95" t="n">
-        <v>78988</v>
+        <v>94595</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10728,21 +10727,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6431</v>
+        <v>2671</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10752,10 +10751,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>428183</v>
+        <v>428332</v>
       </c>
       <c r="R95" t="n">
-        <v>6233239</v>
+        <v>6233287</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10814,10 +10813,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121471927</v>
+        <v>121471944</v>
       </c>
       <c r="B96" t="n">
-        <v>76949</v>
+        <v>94606</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10826,25 +10825,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1342</v>
+        <v>2667</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10854,10 +10853,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>428074</v>
+        <v>428034</v>
       </c>
       <c r="R96" t="n">
-        <v>6233297</v>
+        <v>6233348</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10916,10 +10915,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121471537</v>
+        <v>121471924</v>
       </c>
       <c r="B97" t="n">
-        <v>96731</v>
+        <v>80244</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10932,21 +10931,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10956,10 +10955,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>428163</v>
+        <v>428097</v>
       </c>
       <c r="R97" t="n">
-        <v>6233193</v>
+        <v>6233382</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10986,12 +10985,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11018,10 +11017,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121471689</v>
+        <v>121471911</v>
       </c>
       <c r="B98" t="n">
-        <v>94605</v>
+        <v>76950</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11030,25 +11029,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11058,10 +11057,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>428161</v>
+        <v>428352</v>
       </c>
       <c r="R98" t="n">
-        <v>6233396</v>
+        <v>6233082</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11088,12 +11087,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11120,10 +11119,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121471799</v>
+        <v>121471531</v>
       </c>
       <c r="B99" t="n">
-        <v>94594</v>
+        <v>94616</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11136,21 +11135,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2671</v>
+        <v>1080</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11160,10 +11159,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>428389</v>
+        <v>428110</v>
       </c>
       <c r="R99" t="n">
-        <v>6233324</v>
+        <v>6233224</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11190,12 +11189,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11222,10 +11221,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121471820</v>
+        <v>121471897</v>
       </c>
       <c r="B100" t="n">
-        <v>94399</v>
+        <v>78409</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11234,25 +11233,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2779</v>
+        <v>924</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11262,10 +11261,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>428304</v>
+        <v>428369</v>
       </c>
       <c r="R100" t="n">
-        <v>6233306</v>
+        <v>6233104</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11292,12 +11291,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11324,10 +11323,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121471538</v>
+        <v>121471930</v>
       </c>
       <c r="B101" t="n">
-        <v>80243</v>
+        <v>74611</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11336,25 +11335,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>230185</v>
+        <v>1118</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11364,10 +11363,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>428166</v>
+        <v>428078</v>
       </c>
       <c r="R101" t="n">
-        <v>6233198</v>
+        <v>6233294</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11394,12 +11393,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11426,10 +11425,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121471688</v>
+        <v>121471910</v>
       </c>
       <c r="B102" t="n">
-        <v>96731</v>
+        <v>76950</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11438,25 +11437,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11466,10 +11465,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>428159</v>
+        <v>428377</v>
       </c>
       <c r="R102" t="n">
-        <v>6233394</v>
+        <v>6233090</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11496,12 +11495,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11528,10 +11527,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121471807</v>
+        <v>121471903</v>
       </c>
       <c r="B103" t="n">
-        <v>76949</v>
+        <v>76950</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11568,10 +11567,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>428327</v>
+        <v>428385</v>
       </c>
       <c r="R103" t="n">
-        <v>6233292</v>
+        <v>6233097</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11598,12 +11597,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11630,10 +11629,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121471901</v>
+        <v>121471813</v>
       </c>
       <c r="B104" t="n">
-        <v>76949</v>
+        <v>94595</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11642,25 +11641,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1342</v>
+        <v>2671</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11670,10 +11669,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>428390</v>
+        <v>428332</v>
       </c>
       <c r="R104" t="n">
-        <v>6233099</v>
+        <v>6233341</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11700,12 +11699,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11732,10 +11731,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121471896</v>
+        <v>121471835</v>
       </c>
       <c r="B105" t="n">
-        <v>80579</v>
+        <v>96732</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11744,25 +11743,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1182</v>
+        <v>2606</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11772,10 +11771,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>428370</v>
+        <v>428145</v>
       </c>
       <c r="R105" t="n">
-        <v>6233102</v>
+        <v>6233244</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11802,12 +11801,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11834,10 +11833,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121471942</v>
+        <v>121471859</v>
       </c>
       <c r="B106" t="n">
-        <v>76949</v>
+        <v>80244</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11846,25 +11845,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11874,10 +11873,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>428032</v>
+        <v>428404</v>
       </c>
       <c r="R106" t="n">
-        <v>6233345</v>
+        <v>6233275</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11904,12 +11903,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11936,10 +11935,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121471694</v>
+        <v>121471806</v>
       </c>
       <c r="B107" t="n">
-        <v>80256</v>
+        <v>80257</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11976,10 +11975,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>428125</v>
+        <v>428325</v>
       </c>
       <c r="R107" t="n">
-        <v>6233379</v>
+        <v>6233291</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12006,12 +12005,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12038,10 +12037,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121471881</v>
+        <v>121471834</v>
       </c>
       <c r="B108" t="n">
-        <v>78408</v>
+        <v>80257</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12050,25 +12049,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>924</v>
+        <v>1144</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12078,10 +12077,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>428445</v>
+        <v>428137</v>
       </c>
       <c r="R108" t="n">
-        <v>6233151</v>
+        <v>6233320</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12140,10 +12139,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121471531</v>
+        <v>121471814</v>
       </c>
       <c r="B109" t="n">
-        <v>94615</v>
+        <v>80257</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12152,25 +12151,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1080</v>
+        <v>1144</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12180,10 +12179,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>428110</v>
+        <v>428331</v>
       </c>
       <c r="R109" t="n">
-        <v>6233224</v>
+        <v>6233339</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12210,12 +12209,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12242,10 +12241,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121471834</v>
+        <v>121471684</v>
       </c>
       <c r="B110" t="n">
-        <v>80256</v>
+        <v>80414</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12258,21 +12257,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1144</v>
+        <v>1557</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Röd pysslinglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelopsis rubella</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>Nyl.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12282,10 +12281,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>428137</v>
+        <v>428227</v>
       </c>
       <c r="R110" t="n">
-        <v>6233320</v>
+        <v>6233392</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12312,12 +12311,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12344,10 +12343,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121471941</v>
+        <v>121471545</v>
       </c>
       <c r="B111" t="n">
-        <v>80243</v>
+        <v>80257</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12356,25 +12355,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12384,10 +12383,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>428046</v>
+        <v>428172</v>
       </c>
       <c r="R111" t="n">
-        <v>6233350</v>
+        <v>6233315</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12414,12 +12413,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12446,10 +12445,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121471879</v>
+        <v>121471807</v>
       </c>
       <c r="B112" t="n">
-        <v>76949</v>
+        <v>76950</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12486,10 +12485,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>428445</v>
+        <v>428327</v>
       </c>
       <c r="R112" t="n">
-        <v>6233151</v>
+        <v>6233292</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12548,10 +12547,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121471842</v>
+        <v>121471530</v>
       </c>
       <c r="B113" t="n">
-        <v>94605</v>
+        <v>80244</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12564,21 +12563,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12588,10 +12587,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>428221</v>
+        <v>428111</v>
       </c>
       <c r="R113" t="n">
-        <v>6233212</v>
+        <v>6233222</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12618,12 +12617,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12650,10 +12649,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121471931</v>
+        <v>121471933</v>
       </c>
       <c r="B114" t="n">
-        <v>80256</v>
+        <v>94595</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12662,25 +12661,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1144</v>
+        <v>2671</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12690,10 +12689,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>428075</v>
+        <v>428090</v>
       </c>
       <c r="R114" t="n">
-        <v>6233301</v>
+        <v>6233309</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12752,10 +12751,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121471908</v>
+        <v>121471693</v>
       </c>
       <c r="B115" t="n">
-        <v>74610</v>
+        <v>94595</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12764,25 +12763,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1118</v>
+        <v>2671</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12792,10 +12791,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>428377</v>
+        <v>428125</v>
       </c>
       <c r="R115" t="n">
-        <v>6233090</v>
+        <v>6233379</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12822,12 +12821,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12854,10 +12853,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121471935</v>
+        <v>121471938</v>
       </c>
       <c r="B116" t="n">
-        <v>80243</v>
+        <v>80244</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12894,10 +12893,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>428097</v>
+        <v>428062</v>
       </c>
       <c r="R116" t="n">
-        <v>6233286</v>
+        <v>6233301</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12956,10 +12955,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121471846</v>
+        <v>121471917</v>
       </c>
       <c r="B117" t="n">
-        <v>80243</v>
+        <v>80244</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12996,10 +12995,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>428241</v>
+        <v>428284</v>
       </c>
       <c r="R117" t="n">
-        <v>6233222</v>
+        <v>6233109</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13026,12 +13025,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13058,10 +13057,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121471882</v>
+        <v>121471856</v>
       </c>
       <c r="B118" t="n">
-        <v>74610</v>
+        <v>76950</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13074,21 +13073,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1118</v>
+        <v>1342</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13098,10 +13097,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>428445</v>
+        <v>428360</v>
       </c>
       <c r="R118" t="n">
-        <v>6233151</v>
+        <v>6233266</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13160,10 +13159,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121471801</v>
+        <v>121471811</v>
       </c>
       <c r="B119" t="n">
-        <v>80256</v>
+        <v>76950</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13172,25 +13171,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13200,10 +13199,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>428370</v>
+        <v>428349</v>
       </c>
       <c r="R119" t="n">
-        <v>6233336</v>
+        <v>6233325</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13262,10 +13261,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121471934</v>
+        <v>121471819</v>
       </c>
       <c r="B120" t="n">
-        <v>94399</v>
+        <v>94606</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13278,21 +13277,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13302,10 +13301,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>428090</v>
+        <v>428304</v>
       </c>
       <c r="R120" t="n">
-        <v>6233309</v>
+        <v>6233306</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13332,12 +13331,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13364,10 +13363,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121471802</v>
+        <v>121471692</v>
       </c>
       <c r="B121" t="n">
-        <v>94594</v>
+        <v>94606</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13380,21 +13379,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13404,10 +13403,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>428332</v>
+        <v>428126</v>
       </c>
       <c r="R121" t="n">
-        <v>6233287</v>
+        <v>6233380</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13434,12 +13433,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13466,10 +13465,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121471877</v>
+        <v>121471532</v>
       </c>
       <c r="B122" t="n">
-        <v>94605</v>
+        <v>94606</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13506,10 +13505,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>428445</v>
+        <v>428133</v>
       </c>
       <c r="R122" t="n">
-        <v>6233151</v>
+        <v>6233219</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13536,12 +13535,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13568,10 +13567,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121471912</v>
+        <v>121471855</v>
       </c>
       <c r="B123" t="n">
-        <v>78408</v>
+        <v>94400</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13580,25 +13579,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>924</v>
+        <v>2779</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13608,10 +13607,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>428351</v>
+        <v>428365</v>
       </c>
       <c r="R123" t="n">
-        <v>6233082</v>
+        <v>6233269</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13638,12 +13637,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13670,10 +13669,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121471858</v>
+        <v>121471914</v>
       </c>
       <c r="B124" t="n">
-        <v>80256</v>
+        <v>94606</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13682,25 +13681,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13710,10 +13709,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>428372</v>
+        <v>428318</v>
       </c>
       <c r="R124" t="n">
-        <v>6233270</v>
+        <v>6233075</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13740,12 +13739,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13772,10 +13771,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121471923</v>
+        <v>121471915</v>
       </c>
       <c r="B125" t="n">
-        <v>80256</v>
+        <v>96780</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13784,25 +13783,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1144</v>
+        <v>2604</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13812,10 +13811,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>428091</v>
+        <v>428281</v>
       </c>
       <c r="R125" t="n">
-        <v>6233386</v>
+        <v>6233082</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13874,10 +13873,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121471915</v>
+        <v>121471937</v>
       </c>
       <c r="B126" t="n">
-        <v>96779</v>
+        <v>96732</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13890,21 +13889,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2604</v>
+        <v>2606</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13914,10 +13913,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>428281</v>
+        <v>428062</v>
       </c>
       <c r="R126" t="n">
-        <v>6233082</v>
+        <v>6233301</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13976,10 +13975,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121471870</v>
+        <v>121471822</v>
       </c>
       <c r="B127" t="n">
-        <v>76949</v>
+        <v>94606</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13988,25 +13987,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1342</v>
+        <v>2667</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14016,10 +14015,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>428356</v>
+        <v>428288</v>
       </c>
       <c r="R127" t="n">
-        <v>6233243</v>
+        <v>6233325</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14078,10 +14077,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121471920</v>
+        <v>121471841</v>
       </c>
       <c r="B128" t="n">
-        <v>91118</v>
+        <v>96732</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14090,25 +14089,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2023</v>
+        <v>2606</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sydlig sotticka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ischnoderma resinosum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Schrad.) P.Karst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14118,10 +14117,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>428095</v>
+        <v>428221</v>
       </c>
       <c r="R128" t="n">
-        <v>6233349</v>
+        <v>6233212</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14148,12 +14147,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14180,10 +14179,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121471843</v>
+        <v>121471863</v>
       </c>
       <c r="B129" t="n">
-        <v>57371</v>
+        <v>96732</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14192,25 +14191,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14220,10 +14219,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>428252</v>
+        <v>428411</v>
       </c>
       <c r="R129" t="n">
-        <v>6233262</v>
+        <v>6233213</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14282,10 +14281,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121471543</v>
+        <v>121471931</v>
       </c>
       <c r="B130" t="n">
-        <v>80243</v>
+        <v>80257</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14294,25 +14293,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14322,10 +14321,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>428209</v>
+        <v>428075</v>
       </c>
       <c r="R130" t="n">
-        <v>6233279</v>
+        <v>6233301</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14352,12 +14351,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14384,10 +14383,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121471895</v>
+        <v>121471535</v>
       </c>
       <c r="B131" t="n">
-        <v>80243</v>
+        <v>76950</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14396,25 +14395,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14424,10 +14423,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>428355</v>
+        <v>428160</v>
       </c>
       <c r="R131" t="n">
-        <v>6233123</v>
+        <v>6233209</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14454,12 +14453,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14486,10 +14485,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121471938</v>
+        <v>121471799</v>
       </c>
       <c r="B132" t="n">
-        <v>80243</v>
+        <v>94595</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14502,21 +14501,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>230185</v>
+        <v>2671</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14526,10 +14525,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>428062</v>
+        <v>428389</v>
       </c>
       <c r="R132" t="n">
-        <v>6233301</v>
+        <v>6233324</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14556,12 +14555,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14588,10 +14587,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121471813</v>
+        <v>121471683</v>
       </c>
       <c r="B133" t="n">
-        <v>94594</v>
+        <v>94595</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14628,10 +14627,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>428332</v>
+        <v>428278</v>
       </c>
       <c r="R133" t="n">
-        <v>6233341</v>
+        <v>6233417</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14658,12 +14657,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14690,10 +14689,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121471939</v>
+        <v>121471879</v>
       </c>
       <c r="B134" t="n">
-        <v>94605</v>
+        <v>76950</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14702,25 +14701,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14730,10 +14729,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>428046</v>
+        <v>428445</v>
       </c>
       <c r="R134" t="n">
-        <v>6233296</v>
+        <v>6233151</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14760,12 +14759,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14792,10 +14791,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121471683</v>
+        <v>121471824</v>
       </c>
       <c r="B135" t="n">
-        <v>94594</v>
+        <v>76950</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14804,25 +14803,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2671</v>
+        <v>1342</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14832,10 +14831,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>428278</v>
+        <v>428288</v>
       </c>
       <c r="R135" t="n">
-        <v>6233417</v>
+        <v>6233325</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14862,12 +14861,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14894,10 +14893,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121471944</v>
+        <v>121471845</v>
       </c>
       <c r="B136" t="n">
-        <v>94605</v>
+        <v>80257</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14906,25 +14905,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14934,10 +14933,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>428034</v>
+        <v>428248</v>
       </c>
       <c r="R136" t="n">
-        <v>6233348</v>
+        <v>6233242</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14964,12 +14963,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14996,10 +14995,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121471800</v>
+        <v>121471919</v>
       </c>
       <c r="B137" t="n">
-        <v>80256</v>
+        <v>80257</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15036,10 +15035,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>428387</v>
+        <v>428106</v>
       </c>
       <c r="R137" t="n">
-        <v>6233322</v>
+        <v>6233304</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15066,12 +15065,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15098,10 +15097,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121471685</v>
+        <v>121471923</v>
       </c>
       <c r="B138" t="n">
-        <v>80256</v>
+        <v>80257</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15138,10 +15137,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>428228</v>
+        <v>428091</v>
       </c>
       <c r="R138" t="n">
-        <v>6233391</v>
+        <v>6233386</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15168,12 +15167,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15200,10 +15199,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121471798</v>
+        <v>121471833</v>
       </c>
       <c r="B139" t="n">
-        <v>96731</v>
+        <v>80244</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15216,21 +15215,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15240,10 +15239,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>428387</v>
+        <v>428139</v>
       </c>
       <c r="R139" t="n">
-        <v>6233326</v>
+        <v>6233315</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15302,10 +15301,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121471856</v>
+        <v>121471690</v>
       </c>
       <c r="B140" t="n">
-        <v>76949</v>
+        <v>80244</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15314,25 +15313,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15342,10 +15341,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>428360</v>
+        <v>428161</v>
       </c>
       <c r="R140" t="n">
-        <v>6233266</v>
+        <v>6233396</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15372,12 +15371,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15404,10 +15403,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121471691</v>
+        <v>121471934</v>
       </c>
       <c r="B141" t="n">
-        <v>96731</v>
+        <v>94400</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15420,21 +15419,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2606</v>
+        <v>2779</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15444,10 +15443,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>428128</v>
+        <v>428090</v>
       </c>
       <c r="R141" t="n">
-        <v>6233385</v>
+        <v>6233309</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15474,12 +15473,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15506,10 +15505,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121471909</v>
+        <v>121471836</v>
       </c>
       <c r="B142" t="n">
-        <v>76949</v>
+        <v>94595</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15518,25 +15517,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1342</v>
+        <v>2671</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15546,10 +15545,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>428373</v>
+        <v>428145</v>
       </c>
       <c r="R142" t="n">
-        <v>6233088</v>
+        <v>6233244</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15576,12 +15575,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15608,10 +15607,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121471811</v>
+        <v>121471825</v>
       </c>
       <c r="B143" t="n">
-        <v>76949</v>
+        <v>80244</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15620,25 +15619,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15648,10 +15647,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>428349</v>
+        <v>428233</v>
       </c>
       <c r="R143" t="n">
-        <v>6233325</v>
+        <v>6233332</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15710,10 +15709,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121471819</v>
+        <v>121471936</v>
       </c>
       <c r="B144" t="n">
-        <v>94605</v>
+        <v>94616</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15726,21 +15725,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>2667</v>
+        <v>1080</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15750,10 +15749,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>428304</v>
+        <v>428079</v>
       </c>
       <c r="R144" t="n">
-        <v>6233306</v>
+        <v>6233262</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15780,12 +15779,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15812,10 +15811,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121471914</v>
+        <v>121471912</v>
       </c>
       <c r="B145" t="n">
-        <v>94605</v>
+        <v>78409</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15824,25 +15823,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>2667</v>
+        <v>924</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15852,10 +15851,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>428318</v>
+        <v>428351</v>
       </c>
       <c r="R145" t="n">
-        <v>6233075</v>
+        <v>6233082</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15914,10 +15913,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121471928</v>
+        <v>121471686</v>
       </c>
       <c r="B146" t="n">
-        <v>80256</v>
+        <v>80257</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15954,10 +15953,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>428075</v>
+        <v>428187</v>
       </c>
       <c r="R146" t="n">
-        <v>6233294</v>
+        <v>6233403</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15984,12 +15983,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16016,10 +16015,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121471542</v>
+        <v>121471940</v>
       </c>
       <c r="B147" t="n">
-        <v>80256</v>
+        <v>94616</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16028,25 +16027,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1144</v>
+        <v>1080</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16056,10 +16055,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>428198</v>
+        <v>428037</v>
       </c>
       <c r="R147" t="n">
-        <v>6233249</v>
+        <v>6233291</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16086,12 +16085,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16118,10 +16117,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121471845</v>
+        <v>121471828</v>
       </c>
       <c r="B148" t="n">
-        <v>80256</v>
+        <v>80244</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16130,25 +16129,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16158,10 +16157,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>428248</v>
+        <v>428185</v>
       </c>
       <c r="R148" t="n">
-        <v>6233242</v>
+        <v>6233289</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16202,6 +16201,7 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
@@ -16220,10 +16220,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121471863</v>
+        <v>121471871</v>
       </c>
       <c r="B149" t="n">
-        <v>96731</v>
+        <v>80244</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16236,21 +16236,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16260,10 +16260,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>428411</v>
+        <v>428302</v>
       </c>
       <c r="R149" t="n">
-        <v>6233213</v>
+        <v>6233176</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16322,10 +16322,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121471853</v>
+        <v>121471908</v>
       </c>
       <c r="B150" t="n">
-        <v>76949</v>
+        <v>74611</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16338,21 +16338,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1342</v>
+        <v>1118</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16362,10 +16362,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>428311</v>
+        <v>428377</v>
       </c>
       <c r="R150" t="n">
-        <v>6233183</v>
+        <v>6233090</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16392,12 +16392,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16424,10 +16424,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121471850</v>
+        <v>121471925</v>
       </c>
       <c r="B151" t="n">
-        <v>80243</v>
+        <v>94608</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16440,21 +16440,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>230185</v>
+        <v>2666</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16464,10 +16464,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>428293</v>
+        <v>428076</v>
       </c>
       <c r="R151" t="n">
-        <v>6233170</v>
+        <v>6233382</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16494,12 +16494,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16526,10 +16526,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121471695</v>
+        <v>121471847</v>
       </c>
       <c r="B152" t="n">
-        <v>80243</v>
+        <v>76950</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16538,25 +16538,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16566,10 +16566,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>428053</v>
+        <v>428300</v>
       </c>
       <c r="R152" t="n">
-        <v>6233336</v>
+        <v>6233125</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16596,12 +16596,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16628,10 +16628,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121471822</v>
+        <v>121471844</v>
       </c>
       <c r="B153" t="n">
-        <v>94605</v>
+        <v>76950</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16640,25 +16640,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16668,10 +16668,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>428288</v>
+        <v>428248</v>
       </c>
       <c r="R153" t="n">
-        <v>6233325</v>
+        <v>6233241</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16730,10 +16730,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121471839</v>
+        <v>121471896</v>
       </c>
       <c r="B154" t="n">
-        <v>94594</v>
+        <v>80580</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16742,25 +16742,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2671</v>
+        <v>1182</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16770,10 +16770,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>428184</v>
+        <v>428370</v>
       </c>
       <c r="R154" t="n">
-        <v>6233240</v>
+        <v>6233102</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16800,12 +16800,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16832,10 +16832,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121471861</v>
+        <v>121471817</v>
       </c>
       <c r="B155" t="n">
-        <v>94605</v>
+        <v>74699</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16848,21 +16848,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2667</v>
+        <v>6439</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16872,10 +16872,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>428404</v>
+        <v>428312</v>
       </c>
       <c r="R155" t="n">
-        <v>6233275</v>
+        <v>6233323</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16934,10 +16934,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121471857</v>
+        <v>121471904</v>
       </c>
       <c r="B156" t="n">
-        <v>80256</v>
+        <v>78409</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16946,25 +16946,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1144</v>
+        <v>924</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16974,10 +16974,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>428362</v>
+        <v>428387</v>
       </c>
       <c r="R156" t="n">
-        <v>6233272</v>
+        <v>6233098</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17004,12 +17004,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17036,10 +17036,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121471904</v>
+        <v>121471804</v>
       </c>
       <c r="B157" t="n">
-        <v>78408</v>
+        <v>76950</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17052,21 +17052,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>924</v>
+        <v>1342</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17076,10 +17076,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>428387</v>
+        <v>428335</v>
       </c>
       <c r="R157" t="n">
-        <v>6233098</v>
+        <v>6233286</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17106,12 +17106,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17138,10 +17138,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121471851</v>
+        <v>121471913</v>
       </c>
       <c r="B158" t="n">
-        <v>78864</v>
+        <v>76950</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17150,25 +17150,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6459</v>
+        <v>1342</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17178,10 +17178,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>428293</v>
+        <v>428342</v>
       </c>
       <c r="R158" t="n">
-        <v>6233170</v>
+        <v>6233082</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17208,12 +17208,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17240,10 +17240,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121471910</v>
+        <v>121471927</v>
       </c>
       <c r="B159" t="n">
-        <v>76949</v>
+        <v>76950</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17280,10 +17280,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>428377</v>
+        <v>428074</v>
       </c>
       <c r="R159" t="n">
-        <v>6233090</v>
+        <v>6233297</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17342,10 +17342,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121471913</v>
+        <v>121471843</v>
       </c>
       <c r="B160" t="n">
-        <v>76949</v>
+        <v>57372</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17358,21 +17358,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1342</v>
+        <v>100049</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17382,10 +17382,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>428342</v>
+        <v>428252</v>
       </c>
       <c r="R160" t="n">
-        <v>6233082</v>
+        <v>6233262</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17412,12 +17412,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17444,10 +17444,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121471864</v>
+        <v>121471920</v>
       </c>
       <c r="B161" t="n">
-        <v>94594</v>
+        <v>91119</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17456,25 +17456,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>2671</v>
+        <v>2023</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Sydlig sotticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Ischnoderma resinosum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Schrad.) P.Karst.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17484,10 +17484,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>428410</v>
+        <v>428095</v>
       </c>
       <c r="R161" t="n">
-        <v>6233214</v>
+        <v>6233349</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17546,10 +17546,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121471905</v>
+        <v>121471864</v>
       </c>
       <c r="B162" t="n">
-        <v>74610</v>
+        <v>94595</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17558,25 +17558,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1118</v>
+        <v>2671</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17586,10 +17586,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>428377</v>
+        <v>428410</v>
       </c>
       <c r="R162" t="n">
-        <v>6233095</v>
+        <v>6233214</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17616,12 +17616,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17648,10 +17648,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121471930</v>
+        <v>121471868</v>
       </c>
       <c r="B163" t="n">
-        <v>74610</v>
+        <v>94606</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17660,25 +17660,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1118</v>
+        <v>2667</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17688,10 +17688,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>428078</v>
+        <v>428347</v>
       </c>
       <c r="R163" t="n">
-        <v>6233294</v>
+        <v>6233241</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17750,10 +17750,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121471833</v>
+        <v>121471691</v>
       </c>
       <c r="B164" t="n">
-        <v>80243</v>
+        <v>96732</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17766,21 +17766,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17790,10 +17790,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>428139</v>
+        <v>428128</v>
       </c>
       <c r="R164" t="n">
-        <v>6233315</v>
+        <v>6233385</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17820,12 +17820,12 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17852,10 +17852,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121471825</v>
+        <v>121471861</v>
       </c>
       <c r="B165" t="n">
-        <v>80243</v>
+        <v>94606</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17868,21 +17868,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17892,10 +17892,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>428233</v>
+        <v>428404</v>
       </c>
       <c r="R165" t="n">
-        <v>6233332</v>
+        <v>6233275</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17954,10 +17954,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121471876</v>
+        <v>121471865</v>
       </c>
       <c r="B166" t="n">
-        <v>80286</v>
+        <v>74701</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17970,21 +17970,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1223</v>
+        <v>306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Rikfruktig blemlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Phlyctis agelaea</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Flot.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17994,10 +17994,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>428446</v>
+        <v>428438</v>
       </c>
       <c r="R166" t="n">
-        <v>6233151</v>
+        <v>6233202</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18056,10 +18056,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121471922</v>
+        <v>121471862</v>
       </c>
       <c r="B167" t="n">
-        <v>76949</v>
+        <v>80244</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18068,25 +18068,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18096,10 +18096,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>428091</v>
+        <v>428411</v>
       </c>
       <c r="R167" t="n">
-        <v>6233385</v>
+        <v>6233213</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18126,12 +18126,12 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18158,10 +18158,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121471816</v>
+        <v>121471544</v>
       </c>
       <c r="B168" t="n">
-        <v>96779</v>
+        <v>94606</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18174,21 +18174,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>2604</v>
+        <v>2667</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18198,10 +18198,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>428317</v>
+        <v>428219</v>
       </c>
       <c r="R168" t="n">
-        <v>6233324</v>
+        <v>6233278</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18228,12 +18228,12 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18260,10 +18260,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121471854</v>
+        <v>121471534</v>
       </c>
       <c r="B169" t="n">
-        <v>96731</v>
+        <v>96732</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -18300,10 +18300,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>428302</v>
+        <v>428147</v>
       </c>
       <c r="R169" t="n">
-        <v>6233177</v>
+        <v>6233224</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18330,12 +18330,12 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18362,10 +18362,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121471692</v>
+        <v>121471803</v>
       </c>
       <c r="B170" t="n">
-        <v>94605</v>
+        <v>80257</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18374,25 +18374,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18402,10 +18402,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>428126</v>
+        <v>428334</v>
       </c>
       <c r="R170" t="n">
-        <v>6233380</v>
+        <v>6233284</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18432,12 +18432,12 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18464,10 +18464,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121471899</v>
+        <v>121471901</v>
       </c>
       <c r="B171" t="n">
-        <v>94399</v>
+        <v>76950</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18476,25 +18476,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>2779</v>
+        <v>1342</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18504,7 +18504,7 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>428389</v>
+        <v>428390</v>
       </c>
       <c r="R171" t="n">
         <v>6233099</v>
@@ -18566,10 +18566,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121471697</v>
+        <v>121471881</v>
       </c>
       <c r="B172" t="n">
-        <v>74700</v>
+        <v>78409</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18578,25 +18578,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>306</v>
+        <v>924</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18606,10 +18606,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>428043</v>
+        <v>428445</v>
       </c>
       <c r="R172" t="n">
-        <v>6233298</v>
+        <v>6233151</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18636,12 +18636,12 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18668,10 +18668,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121471916</v>
+        <v>121471941</v>
       </c>
       <c r="B173" t="n">
-        <v>94615</v>
+        <v>80244</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18684,21 +18684,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1080</v>
+        <v>230185</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18708,10 +18708,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>428283</v>
+        <v>428046</v>
       </c>
       <c r="R173" t="n">
-        <v>6233084</v>
+        <v>6233350</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18770,10 +18770,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121471874</v>
+        <v>121471866</v>
       </c>
       <c r="B174" t="n">
-        <v>80256</v>
+        <v>80244</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18782,25 +18782,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18810,10 +18810,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>428375</v>
+        <v>428442</v>
       </c>
       <c r="R174" t="n">
-        <v>6233151</v>
+        <v>6233170</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18872,10 +18872,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121471831</v>
+        <v>121471842</v>
       </c>
       <c r="B175" t="n">
-        <v>80256</v>
+        <v>94606</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18884,25 +18884,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18912,10 +18912,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>428145</v>
+        <v>428221</v>
       </c>
       <c r="R175" t="n">
-        <v>6233315</v>
+        <v>6233212</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>

--- a/artfynd/A 18989-2024 artfynd.xlsx
+++ b/artfynd/A 18989-2024 artfynd.xlsx
@@ -3354,10 +3354,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121471869</v>
+        <v>121471908</v>
       </c>
       <c r="B23" t="n">
-        <v>96732</v>
+        <v>74611</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3366,25 +3366,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2606</v>
+        <v>1118</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>428354</v>
+        <v>428377</v>
       </c>
       <c r="R23" t="n">
-        <v>6233242</v>
+        <v>6233090</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3424,12 +3424,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3456,10 +3456,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121471798</v>
+        <v>121471938</v>
       </c>
       <c r="B24" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3472,21 +3472,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>428387</v>
+        <v>428062</v>
       </c>
       <c r="R24" t="n">
-        <v>6233326</v>
+        <v>6233301</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3526,12 +3526,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3558,10 +3558,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121471876</v>
+        <v>121471925</v>
       </c>
       <c r="B25" t="n">
-        <v>80287</v>
+        <v>94608</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3574,21 +3574,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1223</v>
+        <v>2666</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rikfruktig blemlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phlyctis agelaea</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Flot.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>428446</v>
+        <v>428076</v>
       </c>
       <c r="R25" t="n">
-        <v>6233151</v>
+        <v>6233382</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3628,12 +3628,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3660,10 +3660,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121471922</v>
+        <v>121471924</v>
       </c>
       <c r="B26" t="n">
-        <v>76950</v>
+        <v>80244</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3672,25 +3672,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>428091</v>
+        <v>428097</v>
       </c>
       <c r="R26" t="n">
-        <v>6233385</v>
+        <v>6233382</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3762,10 +3762,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121471928</v>
+        <v>121471905</v>
       </c>
       <c r="B27" t="n">
-        <v>80257</v>
+        <v>74611</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3774,25 +3774,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1144</v>
+        <v>1118</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>428075</v>
+        <v>428377</v>
       </c>
       <c r="R27" t="n">
-        <v>6233294</v>
+        <v>6233095</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121471808</v>
+        <v>121471881</v>
       </c>
       <c r="B29" t="n">
-        <v>80257</v>
+        <v>78409</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3978,25 +3978,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1144</v>
+        <v>924</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>428350</v>
+        <v>428445</v>
       </c>
       <c r="R29" t="n">
-        <v>6233316</v>
+        <v>6233151</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4068,10 +4068,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121471809</v>
+        <v>121471842</v>
       </c>
       <c r="B30" t="n">
-        <v>74565</v>
+        <v>94606</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4080,25 +4080,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1116</v>
+        <v>2667</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>428352</v>
+        <v>428221</v>
       </c>
       <c r="R30" t="n">
-        <v>6233315</v>
+        <v>6233212</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4170,10 +4170,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121471815</v>
+        <v>121471920</v>
       </c>
       <c r="B31" t="n">
-        <v>80414</v>
+        <v>91119</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4182,25 +4182,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1557</v>
+        <v>2023</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Röd pysslinglav</t>
+          <t>Sydlig sotticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Thelopsis rubella</t>
+          <t>Ischnoderma resinosum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Nyl.</t>
+          <t>(Schrad.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>428333</v>
+        <v>428095</v>
       </c>
       <c r="R31" t="n">
-        <v>6233339</v>
+        <v>6233349</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4240,12 +4240,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4272,10 +4272,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121471840</v>
+        <v>121471882</v>
       </c>
       <c r="B32" t="n">
-        <v>78989</v>
+        <v>74611</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4284,25 +4284,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6431</v>
+        <v>1118</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>428183</v>
+        <v>428445</v>
       </c>
       <c r="R32" t="n">
-        <v>6233239</v>
+        <v>6233151</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4374,10 +4374,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121471850</v>
+        <v>121471930</v>
       </c>
       <c r="B33" t="n">
-        <v>80244</v>
+        <v>74611</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4386,25 +4386,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>230185</v>
+        <v>1118</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4414,10 +4414,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>428293</v>
+        <v>428078</v>
       </c>
       <c r="R33" t="n">
-        <v>6233170</v>
+        <v>6233294</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4444,12 +4444,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4476,7 +4476,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121471696</v>
+        <v>121471688</v>
       </c>
       <c r="B34" t="n">
         <v>96732</v>
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>428054</v>
+        <v>428159</v>
       </c>
       <c r="R34" t="n">
-        <v>6233337</v>
+        <v>6233394</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4578,10 +4578,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121471926</v>
+        <v>121471897</v>
       </c>
       <c r="B35" t="n">
-        <v>94400</v>
+        <v>78409</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4590,25 +4590,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2779</v>
+        <v>924</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>428073</v>
+        <v>428369</v>
       </c>
       <c r="R35" t="n">
-        <v>6233383</v>
+        <v>6233104</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4680,10 +4680,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121471943</v>
+        <v>121471910</v>
       </c>
       <c r="B36" t="n">
-        <v>96732</v>
+        <v>76950</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4692,25 +4692,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4720,10 +4720,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>428034</v>
+        <v>428377</v>
       </c>
       <c r="R36" t="n">
-        <v>6233348</v>
+        <v>6233090</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4782,10 +4782,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121471820</v>
+        <v>121471693</v>
       </c>
       <c r="B37" t="n">
-        <v>94400</v>
+        <v>94595</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4798,21 +4798,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>428304</v>
+        <v>428125</v>
       </c>
       <c r="R37" t="n">
-        <v>6233306</v>
+        <v>6233379</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4884,10 +4884,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121471916</v>
+        <v>121471798</v>
       </c>
       <c r="B38" t="n">
-        <v>94616</v>
+        <v>96732</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4900,21 +4900,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1080</v>
+        <v>2606</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>428283</v>
+        <v>428387</v>
       </c>
       <c r="R38" t="n">
-        <v>6233084</v>
+        <v>6233326</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4954,12 +4954,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4986,10 +4986,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121471909</v>
+        <v>121471916</v>
       </c>
       <c r="B39" t="n">
-        <v>76950</v>
+        <v>94616</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4998,25 +4998,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1342</v>
+        <v>1080</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>428373</v>
+        <v>428283</v>
       </c>
       <c r="R39" t="n">
-        <v>6233088</v>
+        <v>6233084</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5088,10 +5088,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121471849</v>
+        <v>121471871</v>
       </c>
       <c r="B40" t="n">
-        <v>80257</v>
+        <v>80244</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5100,25 +5100,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5128,10 +5128,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>428299</v>
+        <v>428302</v>
       </c>
       <c r="R40" t="n">
-        <v>6233126</v>
+        <v>6233176</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5190,7 +5190,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121471541</v>
+        <v>121471846</v>
       </c>
       <c r="B41" t="n">
         <v>80244</v>
@@ -5230,10 +5230,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>428209</v>
+        <v>428241</v>
       </c>
       <c r="R41" t="n">
-        <v>6233184</v>
+        <v>6233222</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5260,12 +5260,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5292,10 +5292,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121471538</v>
+        <v>121471542</v>
       </c>
       <c r="B42" t="n">
-        <v>80244</v>
+        <v>80257</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5304,25 +5304,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5332,10 +5332,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>428166</v>
+        <v>428198</v>
       </c>
       <c r="R42" t="n">
-        <v>6233198</v>
+        <v>6233249</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5394,10 +5394,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121471837</v>
+        <v>121471855</v>
       </c>
       <c r="B43" t="n">
-        <v>80244</v>
+        <v>94400</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5410,21 +5410,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>230185</v>
+        <v>2779</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5434,10 +5434,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>428145</v>
+        <v>428365</v>
       </c>
       <c r="R43" t="n">
-        <v>6233244</v>
+        <v>6233269</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5496,50 +5496,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121471860</v>
+        <v>121471875</v>
       </c>
       <c r="B44" t="n">
-        <v>96732</v>
+        <v>80257</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>428404</v>
+        <v>428340</v>
       </c>
       <c r="R44" t="n">
-        <v>6233275</v>
+        <v>6233229</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5574,11 +5577,21 @@
           <t>2024-11-21</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>kollekt</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG44" t="b">
         <v>0</v>
@@ -5598,10 +5611,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121471818</v>
+        <v>121471911</v>
       </c>
       <c r="B45" t="n">
-        <v>96732</v>
+        <v>76950</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5610,25 +5623,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5638,10 +5651,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>428307</v>
+        <v>428352</v>
       </c>
       <c r="R45" t="n">
-        <v>6233311</v>
+        <v>6233082</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5668,12 +5681,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5700,10 +5713,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121471812</v>
+        <v>121471866</v>
       </c>
       <c r="B46" t="n">
-        <v>94400</v>
+        <v>80244</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5716,21 +5729,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2779</v>
+        <v>230185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5740,10 +5753,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>428331</v>
+        <v>428442</v>
       </c>
       <c r="R46" t="n">
-        <v>6233335</v>
+        <v>6233170</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5802,10 +5815,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121471853</v>
+        <v>121471531</v>
       </c>
       <c r="B47" t="n">
-        <v>76950</v>
+        <v>94616</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5814,25 +5827,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1342</v>
+        <v>1080</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5842,10 +5855,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>428311</v>
+        <v>428110</v>
       </c>
       <c r="R47" t="n">
-        <v>6233183</v>
+        <v>6233224</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5872,12 +5885,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5904,10 +5917,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121471857</v>
+        <v>121471937</v>
       </c>
       <c r="B48" t="n">
-        <v>80257</v>
+        <v>96732</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5916,25 +5929,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5944,10 +5957,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>428362</v>
+        <v>428062</v>
       </c>
       <c r="R48" t="n">
-        <v>6233272</v>
+        <v>6233301</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5974,12 +5987,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6006,10 +6019,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121471905</v>
+        <v>121471931</v>
       </c>
       <c r="B49" t="n">
-        <v>74611</v>
+        <v>80257</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6018,25 +6031,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1118</v>
+        <v>1144</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6046,10 +6059,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>428377</v>
+        <v>428075</v>
       </c>
       <c r="R49" t="n">
-        <v>6233095</v>
+        <v>6233301</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6108,10 +6121,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121471942</v>
+        <v>121471796</v>
       </c>
       <c r="B50" t="n">
-        <v>76950</v>
+        <v>80257</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6120,25 +6133,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6148,10 +6161,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>428032</v>
+        <v>428390</v>
       </c>
       <c r="R50" t="n">
-        <v>6233345</v>
+        <v>6233312</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6178,12 +6191,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6210,10 +6223,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121471826</v>
+        <v>121471817</v>
       </c>
       <c r="B51" t="n">
-        <v>78865</v>
+        <v>74699</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6226,21 +6239,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6459</v>
+        <v>6439</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6250,10 +6263,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>428228</v>
+        <v>428312</v>
       </c>
       <c r="R51" t="n">
-        <v>6233340</v>
+        <v>6233323</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6312,10 +6325,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121471851</v>
+        <v>121471534</v>
       </c>
       <c r="B52" t="n">
-        <v>78865</v>
+        <v>96732</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6328,21 +6341,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6459</v>
+        <v>2606</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6352,10 +6365,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>428293</v>
+        <v>428147</v>
       </c>
       <c r="R52" t="n">
-        <v>6233170</v>
+        <v>6233224</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6382,12 +6395,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6414,10 +6427,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121471796</v>
+        <v>121471909</v>
       </c>
       <c r="B53" t="n">
-        <v>80257</v>
+        <v>76950</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6426,25 +6439,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6454,10 +6467,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>428390</v>
+        <v>428373</v>
       </c>
       <c r="R53" t="n">
-        <v>6233312</v>
+        <v>6233088</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6484,12 +6497,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6516,10 +6529,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121471945</v>
+        <v>121471696</v>
       </c>
       <c r="B54" t="n">
-        <v>96780</v>
+        <v>96732</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6532,21 +6545,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2604</v>
+        <v>2606</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6556,10 +6569,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>428035</v>
+        <v>428054</v>
       </c>
       <c r="R54" t="n">
-        <v>6233349</v>
+        <v>6233337</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6586,12 +6599,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6618,10 +6631,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121471929</v>
+        <v>121471923</v>
       </c>
       <c r="B55" t="n">
-        <v>94400</v>
+        <v>80257</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6630,25 +6643,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2779</v>
+        <v>1144</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6658,10 +6671,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>428078</v>
+        <v>428091</v>
       </c>
       <c r="R55" t="n">
-        <v>6233294</v>
+        <v>6233386</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6720,7 +6733,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121471878</v>
+        <v>121471945</v>
       </c>
       <c r="B56" t="n">
         <v>96780</v>
@@ -6760,10 +6773,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>428445</v>
+        <v>428035</v>
       </c>
       <c r="R56" t="n">
-        <v>6233151</v>
+        <v>6233349</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6790,12 +6803,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6822,10 +6835,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121471854</v>
+        <v>121471825</v>
       </c>
       <c r="B57" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6838,21 +6851,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6862,10 +6875,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>428302</v>
+        <v>428233</v>
       </c>
       <c r="R57" t="n">
-        <v>6233177</v>
+        <v>6233332</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6924,10 +6937,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121471839</v>
+        <v>121471861</v>
       </c>
       <c r="B58" t="n">
-        <v>94595</v>
+        <v>94606</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6940,21 +6953,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6964,10 +6977,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>428184</v>
+        <v>428404</v>
       </c>
       <c r="R58" t="n">
-        <v>6233240</v>
+        <v>6233275</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7026,10 +7039,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121471543</v>
+        <v>121471839</v>
       </c>
       <c r="B59" t="n">
-        <v>80244</v>
+        <v>94595</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7042,21 +7055,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>230185</v>
+        <v>2671</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7066,10 +7079,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>428209</v>
+        <v>428184</v>
       </c>
       <c r="R59" t="n">
-        <v>6233279</v>
+        <v>6233240</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7096,12 +7109,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7128,10 +7141,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121471694</v>
+        <v>121471859</v>
       </c>
       <c r="B60" t="n">
-        <v>80257</v>
+        <v>80244</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7140,25 +7153,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7168,10 +7181,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>428125</v>
+        <v>428404</v>
       </c>
       <c r="R60" t="n">
-        <v>6233379</v>
+        <v>6233275</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7198,12 +7211,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7230,7 +7243,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121471801</v>
+        <v>121471694</v>
       </c>
       <c r="B61" t="n">
         <v>80257</v>
@@ -7270,10 +7283,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>428370</v>
+        <v>428125</v>
       </c>
       <c r="R61" t="n">
-        <v>6233336</v>
+        <v>6233379</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7300,12 +7313,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7332,10 +7345,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121471907</v>
+        <v>121471926</v>
       </c>
       <c r="B62" t="n">
-        <v>76950</v>
+        <v>94400</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7344,25 +7357,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1342</v>
+        <v>2779</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7372,10 +7385,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>428375</v>
+        <v>428073</v>
       </c>
       <c r="R62" t="n">
-        <v>6233092</v>
+        <v>6233383</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7434,10 +7447,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121471542</v>
+        <v>121471833</v>
       </c>
       <c r="B63" t="n">
-        <v>80257</v>
+        <v>80244</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7446,25 +7459,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7474,10 +7487,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>428198</v>
+        <v>428139</v>
       </c>
       <c r="R63" t="n">
-        <v>6233249</v>
+        <v>6233315</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7504,12 +7517,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7536,7 +7549,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121471870</v>
+        <v>121471807</v>
       </c>
       <c r="B64" t="n">
         <v>76950</v>
@@ -7576,10 +7589,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>428356</v>
+        <v>428327</v>
       </c>
       <c r="R64" t="n">
-        <v>6233243</v>
+        <v>6233292</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7638,53 +7651,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121471875</v>
+        <v>121471854</v>
       </c>
       <c r="B65" t="n">
-        <v>80257</v>
+        <v>96732</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>428340</v>
+        <v>428302</v>
       </c>
       <c r="R65" t="n">
-        <v>6233229</v>
+        <v>6233177</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7719,21 +7729,11 @@
           <t>2024-11-21</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>kollekt</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
-      </c>
-      <c r="AF65" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG65" t="b">
         <v>0</v>
@@ -7753,10 +7753,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121471852</v>
+        <v>121471537</v>
       </c>
       <c r="B66" t="n">
-        <v>80257</v>
+        <v>96732</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7765,25 +7765,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7793,10 +7793,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>428311</v>
+        <v>428163</v>
       </c>
       <c r="R66" t="n">
-        <v>6233183</v>
+        <v>6233193</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7823,12 +7823,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7855,10 +7855,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121471846</v>
+        <v>121471809</v>
       </c>
       <c r="B67" t="n">
-        <v>80244</v>
+        <v>74565</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7867,25 +7867,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>230185</v>
+        <v>1116</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7895,10 +7895,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>428241</v>
+        <v>428352</v>
       </c>
       <c r="R67" t="n">
-        <v>6233222</v>
+        <v>6233315</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7957,10 +7957,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121471902</v>
+        <v>121471801</v>
       </c>
       <c r="B68" t="n">
-        <v>94595</v>
+        <v>80257</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7969,25 +7969,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2671</v>
+        <v>1144</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7997,10 +7997,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>428387</v>
+        <v>428370</v>
       </c>
       <c r="R68" t="n">
-        <v>6233096</v>
+        <v>6233336</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8027,12 +8027,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8059,10 +8059,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121471539</v>
+        <v>121471690</v>
       </c>
       <c r="B69" t="n">
-        <v>94595</v>
+        <v>80244</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8075,21 +8075,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2671</v>
+        <v>230185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8099,10 +8099,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>428262</v>
+        <v>428161</v>
       </c>
       <c r="R69" t="n">
-        <v>6233134</v>
+        <v>6233396</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8161,10 +8161,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121471688</v>
+        <v>121471541</v>
       </c>
       <c r="B70" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8177,21 +8177,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>428159</v>
+        <v>428209</v>
       </c>
       <c r="R70" t="n">
-        <v>6233394</v>
+        <v>6233184</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8263,10 +8263,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121471939</v>
+        <v>121471844</v>
       </c>
       <c r="B71" t="n">
-        <v>94606</v>
+        <v>76950</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8275,25 +8275,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>428046</v>
+        <v>428248</v>
       </c>
       <c r="R71" t="n">
-        <v>6233296</v>
+        <v>6233241</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8333,12 +8333,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8365,10 +8365,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121471816</v>
+        <v>121471843</v>
       </c>
       <c r="B72" t="n">
-        <v>96780</v>
+        <v>57372</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8377,25 +8377,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2604</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>428317</v>
+        <v>428252</v>
       </c>
       <c r="R72" t="n">
-        <v>6233324</v>
+        <v>6233262</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8467,10 +8467,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121471899</v>
+        <v>121471862</v>
       </c>
       <c r="B73" t="n">
-        <v>94400</v>
+        <v>80244</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8483,21 +8483,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2779</v>
+        <v>230185</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8507,10 +8507,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>428389</v>
+        <v>428411</v>
       </c>
       <c r="R73" t="n">
-        <v>6233099</v>
+        <v>6233213</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8537,12 +8537,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8569,10 +8569,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121471536</v>
+        <v>121471942</v>
       </c>
       <c r="B74" t="n">
-        <v>80580</v>
+        <v>76950</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8585,21 +8585,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1182</v>
+        <v>1342</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8609,10 +8609,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>428166</v>
+        <v>428032</v>
       </c>
       <c r="R74" t="n">
-        <v>6233202</v>
+        <v>6233345</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8639,12 +8639,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8671,10 +8671,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121471874</v>
+        <v>121471901</v>
       </c>
       <c r="B75" t="n">
-        <v>80257</v>
+        <v>76950</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8683,25 +8683,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8711,10 +8711,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>428375</v>
+        <v>428390</v>
       </c>
       <c r="R75" t="n">
-        <v>6233151</v>
+        <v>6233099</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8741,12 +8741,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8773,10 +8773,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121471805</v>
+        <v>121471851</v>
       </c>
       <c r="B76" t="n">
-        <v>80257</v>
+        <v>78865</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8785,25 +8785,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1144</v>
+        <v>6459</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8813,10 +8813,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>428333</v>
+        <v>428293</v>
       </c>
       <c r="R76" t="n">
-        <v>6233283</v>
+        <v>6233170</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8875,10 +8875,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121471695</v>
+        <v>121471800</v>
       </c>
       <c r="B77" t="n">
-        <v>80244</v>
+        <v>80257</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8887,25 +8887,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8915,10 +8915,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>428053</v>
+        <v>428387</v>
       </c>
       <c r="R77" t="n">
-        <v>6233336</v>
+        <v>6233322</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8945,12 +8945,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8977,10 +8977,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121471895</v>
+        <v>121471903</v>
       </c>
       <c r="B78" t="n">
-        <v>80244</v>
+        <v>76950</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8989,25 +8989,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9017,10 +9017,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>428355</v>
+        <v>428385</v>
       </c>
       <c r="R78" t="n">
-        <v>6233123</v>
+        <v>6233097</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9079,10 +9079,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121471877</v>
+        <v>121471917</v>
       </c>
       <c r="B79" t="n">
-        <v>94606</v>
+        <v>80244</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9095,21 +9095,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9119,10 +9119,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>428445</v>
+        <v>428284</v>
       </c>
       <c r="R79" t="n">
-        <v>6233151</v>
+        <v>6233109</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9181,10 +9181,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121471829</v>
+        <v>121471811</v>
       </c>
       <c r="B80" t="n">
-        <v>80257</v>
+        <v>76950</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9193,25 +9193,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9221,10 +9221,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>428147</v>
+        <v>428349</v>
       </c>
       <c r="R80" t="n">
-        <v>6233304</v>
+        <v>6233325</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9283,7 +9283,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121471685</v>
+        <v>121471829</v>
       </c>
       <c r="B81" t="n">
         <v>80257</v>
@@ -9323,10 +9323,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>428228</v>
+        <v>428147</v>
       </c>
       <c r="R81" t="n">
-        <v>6233391</v>
+        <v>6233304</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9353,12 +9353,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9385,10 +9385,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121471831</v>
+        <v>121471902</v>
       </c>
       <c r="B82" t="n">
-        <v>80257</v>
+        <v>94595</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9397,25 +9397,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1144</v>
+        <v>2671</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9425,10 +9425,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>428145</v>
+        <v>428387</v>
       </c>
       <c r="R82" t="n">
-        <v>6233315</v>
+        <v>6233096</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9455,12 +9455,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9487,10 +9487,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121471935</v>
+        <v>121471915</v>
       </c>
       <c r="B83" t="n">
-        <v>80244</v>
+        <v>96780</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9503,21 +9503,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>230185</v>
+        <v>2604</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>428097</v>
+        <v>428281</v>
       </c>
       <c r="R83" t="n">
-        <v>6233286</v>
+        <v>6233082</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9589,10 +9589,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121471533</v>
+        <v>121471539</v>
       </c>
       <c r="B84" t="n">
-        <v>80244</v>
+        <v>94595</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9605,21 +9605,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>230185</v>
+        <v>2671</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9629,10 +9629,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>428144</v>
+        <v>428262</v>
       </c>
       <c r="R84" t="n">
-        <v>6233229</v>
+        <v>6233134</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9691,10 +9691,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121471827</v>
+        <v>121471841</v>
       </c>
       <c r="B85" t="n">
-        <v>94606</v>
+        <v>96732</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9707,21 +9707,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9731,10 +9731,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>428185</v>
+        <v>428221</v>
       </c>
       <c r="R85" t="n">
-        <v>6233287</v>
+        <v>6233212</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9793,10 +9793,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121471540</v>
+        <v>121471919</v>
       </c>
       <c r="B86" t="n">
-        <v>96732</v>
+        <v>80257</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9805,25 +9805,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>428227</v>
+        <v>428106</v>
       </c>
       <c r="R86" t="n">
-        <v>6233132</v>
+        <v>6233304</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9895,10 +9895,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121471689</v>
+        <v>121471803</v>
       </c>
       <c r="B87" t="n">
-        <v>94606</v>
+        <v>80257</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9907,25 +9907,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9935,10 +9935,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>428161</v>
+        <v>428334</v>
       </c>
       <c r="R87" t="n">
-        <v>6233396</v>
+        <v>6233284</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9965,12 +9965,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9997,10 +9997,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121471537</v>
+        <v>121471544</v>
       </c>
       <c r="B88" t="n">
-        <v>96732</v>
+        <v>94606</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10013,21 +10013,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10037,10 +10037,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>428163</v>
+        <v>428219</v>
       </c>
       <c r="R88" t="n">
-        <v>6233193</v>
+        <v>6233278</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10099,10 +10099,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121471882</v>
+        <v>121471836</v>
       </c>
       <c r="B89" t="n">
-        <v>74611</v>
+        <v>94595</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10111,25 +10111,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1118</v>
+        <v>2671</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10139,10 +10139,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>428445</v>
+        <v>428145</v>
       </c>
       <c r="R89" t="n">
-        <v>6233151</v>
+        <v>6233244</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10201,10 +10201,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121471873</v>
+        <v>121471899</v>
       </c>
       <c r="B90" t="n">
-        <v>74565</v>
+        <v>94400</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10213,25 +10213,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1116</v>
+        <v>2779</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10241,10 +10241,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>428301</v>
+        <v>428389</v>
       </c>
       <c r="R90" t="n">
-        <v>6233171</v>
+        <v>6233099</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10271,12 +10271,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10303,10 +10303,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121471867</v>
+        <v>121471863</v>
       </c>
       <c r="B91" t="n">
-        <v>76950</v>
+        <v>96732</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10315,25 +10315,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10343,10 +10343,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>428442</v>
+        <v>428411</v>
       </c>
       <c r="R91" t="n">
-        <v>6233170</v>
+        <v>6233213</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10405,10 +10405,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121471800</v>
+        <v>121471826</v>
       </c>
       <c r="B92" t="n">
-        <v>80257</v>
+        <v>78865</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10417,25 +10417,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1144</v>
+        <v>6459</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10445,10 +10445,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>428387</v>
+        <v>428228</v>
       </c>
       <c r="R92" t="n">
-        <v>6233322</v>
+        <v>6233340</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10507,10 +10507,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121471810</v>
+        <v>121471816</v>
       </c>
       <c r="B93" t="n">
-        <v>80257</v>
+        <v>96780</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10519,25 +10519,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1144</v>
+        <v>2604</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10547,10 +10547,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>428347</v>
+        <v>428317</v>
       </c>
       <c r="R93" t="n">
-        <v>6233326</v>
+        <v>6233324</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10609,10 +10609,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121471697</v>
+        <v>121471818</v>
       </c>
       <c r="B94" t="n">
-        <v>74701</v>
+        <v>96732</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10625,21 +10625,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>306</v>
+        <v>2606</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10649,10 +10649,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>428043</v>
+        <v>428307</v>
       </c>
       <c r="R94" t="n">
-        <v>6233298</v>
+        <v>6233311</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10679,12 +10679,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10711,10 +10711,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121471802</v>
+        <v>121471831</v>
       </c>
       <c r="B95" t="n">
-        <v>94595</v>
+        <v>80257</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10723,25 +10723,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2671</v>
+        <v>1144</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10751,10 +10751,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>428332</v>
+        <v>428145</v>
       </c>
       <c r="R95" t="n">
-        <v>6233287</v>
+        <v>6233315</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10813,10 +10813,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121471944</v>
+        <v>121471530</v>
       </c>
       <c r="B96" t="n">
-        <v>94606</v>
+        <v>80244</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10829,21 +10829,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10853,10 +10853,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>428034</v>
+        <v>428111</v>
       </c>
       <c r="R96" t="n">
-        <v>6233348</v>
+        <v>6233222</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10883,12 +10883,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10915,10 +10915,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121471924</v>
+        <v>121471867</v>
       </c>
       <c r="B97" t="n">
-        <v>80244</v>
+        <v>76950</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10927,25 +10927,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10955,10 +10955,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>428097</v>
+        <v>428442</v>
       </c>
       <c r="R97" t="n">
-        <v>6233382</v>
+        <v>6233170</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10985,12 +10985,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11017,10 +11017,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121471911</v>
+        <v>121471928</v>
       </c>
       <c r="B98" t="n">
-        <v>76950</v>
+        <v>80257</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11029,25 +11029,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11057,10 +11057,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>428352</v>
+        <v>428075</v>
       </c>
       <c r="R98" t="n">
-        <v>6233082</v>
+        <v>6233294</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11119,10 +11119,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121471531</v>
+        <v>121471837</v>
       </c>
       <c r="B99" t="n">
-        <v>94616</v>
+        <v>80244</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11135,21 +11135,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1080</v>
+        <v>230185</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11159,10 +11159,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>428110</v>
+        <v>428145</v>
       </c>
       <c r="R99" t="n">
-        <v>6233224</v>
+        <v>6233244</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11189,12 +11189,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11221,10 +11221,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121471897</v>
+        <v>121471939</v>
       </c>
       <c r="B100" t="n">
-        <v>78409</v>
+        <v>94606</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11233,25 +11233,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>924</v>
+        <v>2667</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11261,10 +11261,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>428369</v>
+        <v>428046</v>
       </c>
       <c r="R100" t="n">
-        <v>6233104</v>
+        <v>6233296</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11323,10 +11323,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121471930</v>
+        <v>121471876</v>
       </c>
       <c r="B101" t="n">
-        <v>74611</v>
+        <v>80287</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11335,25 +11335,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1118</v>
+        <v>1223</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Rikfruktig blemlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Phlyctis agelaea</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Ach.) Flot.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11363,10 +11363,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>428078</v>
+        <v>428446</v>
       </c>
       <c r="R101" t="n">
-        <v>6233294</v>
+        <v>6233151</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11393,12 +11393,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11425,10 +11425,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121471910</v>
+        <v>121471808</v>
       </c>
       <c r="B102" t="n">
-        <v>76950</v>
+        <v>80257</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11437,25 +11437,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11465,10 +11465,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>428377</v>
+        <v>428350</v>
       </c>
       <c r="R102" t="n">
-        <v>6233090</v>
+        <v>6233316</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11495,12 +11495,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11527,10 +11527,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121471903</v>
+        <v>121471806</v>
       </c>
       <c r="B103" t="n">
-        <v>76950</v>
+        <v>80257</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11539,25 +11539,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11567,10 +11567,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>428385</v>
+        <v>428325</v>
       </c>
       <c r="R103" t="n">
-        <v>6233097</v>
+        <v>6233291</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11597,12 +11597,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11629,10 +11629,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121471813</v>
+        <v>121471944</v>
       </c>
       <c r="B104" t="n">
-        <v>94595</v>
+        <v>94606</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11645,21 +11645,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11669,10 +11669,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>428332</v>
+        <v>428034</v>
       </c>
       <c r="R104" t="n">
-        <v>6233341</v>
+        <v>6233348</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11699,12 +11699,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11731,10 +11731,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121471835</v>
+        <v>121471692</v>
       </c>
       <c r="B105" t="n">
-        <v>96732</v>
+        <v>94606</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11747,21 +11747,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11771,10 +11771,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>428145</v>
+        <v>428126</v>
       </c>
       <c r="R105" t="n">
-        <v>6233244</v>
+        <v>6233380</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11801,12 +11801,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11833,10 +11833,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121471859</v>
+        <v>121471805</v>
       </c>
       <c r="B106" t="n">
-        <v>80244</v>
+        <v>80257</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11845,25 +11845,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11873,10 +11873,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>428404</v>
+        <v>428333</v>
       </c>
       <c r="R106" t="n">
-        <v>6233275</v>
+        <v>6233283</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11935,10 +11935,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121471806</v>
+        <v>121471877</v>
       </c>
       <c r="B107" t="n">
-        <v>80257</v>
+        <v>94606</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11947,25 +11947,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11975,10 +11975,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>428325</v>
+        <v>428445</v>
       </c>
       <c r="R107" t="n">
-        <v>6233291</v>
+        <v>6233151</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12037,10 +12037,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121471834</v>
+        <v>121471697</v>
       </c>
       <c r="B108" t="n">
-        <v>80257</v>
+        <v>74701</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12049,25 +12049,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1144</v>
+        <v>306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12077,10 +12077,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>428137</v>
+        <v>428043</v>
       </c>
       <c r="R108" t="n">
-        <v>6233320</v>
+        <v>6233298</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12107,12 +12107,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12139,10 +12139,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121471814</v>
+        <v>121471869</v>
       </c>
       <c r="B109" t="n">
-        <v>80257</v>
+        <v>96732</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12151,25 +12151,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12179,10 +12179,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>428331</v>
+        <v>428354</v>
       </c>
       <c r="R109" t="n">
-        <v>6233339</v>
+        <v>6233242</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12241,10 +12241,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121471684</v>
+        <v>121471538</v>
       </c>
       <c r="B110" t="n">
-        <v>80414</v>
+        <v>80244</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12253,25 +12253,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1557</v>
+        <v>230185</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Röd pysslinglav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Thelopsis rubella</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12281,10 +12281,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>428227</v>
+        <v>428166</v>
       </c>
       <c r="R110" t="n">
-        <v>6233392</v>
+        <v>6233198</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12343,10 +12343,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121471545</v>
+        <v>121471907</v>
       </c>
       <c r="B111" t="n">
-        <v>80257</v>
+        <v>76950</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12355,25 +12355,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12383,10 +12383,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>428172</v>
+        <v>428375</v>
       </c>
       <c r="R111" t="n">
-        <v>6233315</v>
+        <v>6233092</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12413,12 +12413,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12445,10 +12445,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121471807</v>
+        <v>121471935</v>
       </c>
       <c r="B112" t="n">
-        <v>76950</v>
+        <v>80244</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12457,25 +12457,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12485,10 +12485,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>428327</v>
+        <v>428097</v>
       </c>
       <c r="R112" t="n">
-        <v>6233292</v>
+        <v>6233286</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12515,12 +12515,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12547,10 +12547,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121471530</v>
+        <v>121471927</v>
       </c>
       <c r="B113" t="n">
-        <v>80244</v>
+        <v>76950</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12559,25 +12559,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12587,10 +12587,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>428111</v>
+        <v>428074</v>
       </c>
       <c r="R113" t="n">
-        <v>6233222</v>
+        <v>6233297</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12617,12 +12617,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12649,10 +12649,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121471933</v>
+        <v>121471853</v>
       </c>
       <c r="B114" t="n">
-        <v>94595</v>
+        <v>76950</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12661,25 +12661,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2671</v>
+        <v>1342</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12689,10 +12689,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>428090</v>
+        <v>428311</v>
       </c>
       <c r="R114" t="n">
-        <v>6233309</v>
+        <v>6233183</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12719,12 +12719,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12751,10 +12751,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121471693</v>
+        <v>121471936</v>
       </c>
       <c r="B115" t="n">
-        <v>94595</v>
+        <v>94616</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12767,21 +12767,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2671</v>
+        <v>1080</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12791,10 +12791,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>428125</v>
+        <v>428079</v>
       </c>
       <c r="R115" t="n">
-        <v>6233379</v>
+        <v>6233262</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12821,12 +12821,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12853,10 +12853,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121471938</v>
+        <v>121471864</v>
       </c>
       <c r="B116" t="n">
-        <v>80244</v>
+        <v>94595</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12869,21 +12869,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>230185</v>
+        <v>2671</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12893,10 +12893,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>428062</v>
+        <v>428410</v>
       </c>
       <c r="R116" t="n">
-        <v>6233301</v>
+        <v>6233214</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12923,12 +12923,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12955,10 +12955,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121471917</v>
+        <v>121471922</v>
       </c>
       <c r="B117" t="n">
-        <v>80244</v>
+        <v>76950</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12967,25 +12967,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12995,10 +12995,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>428284</v>
+        <v>428091</v>
       </c>
       <c r="R117" t="n">
-        <v>6233109</v>
+        <v>6233385</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13057,10 +13057,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121471856</v>
+        <v>121471685</v>
       </c>
       <c r="B118" t="n">
-        <v>76950</v>
+        <v>80257</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13069,25 +13069,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13097,10 +13097,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>428360</v>
+        <v>428228</v>
       </c>
       <c r="R118" t="n">
-        <v>6233266</v>
+        <v>6233391</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13127,12 +13127,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13159,10 +13159,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121471811</v>
+        <v>121471689</v>
       </c>
       <c r="B119" t="n">
-        <v>76950</v>
+        <v>94606</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13171,25 +13171,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1342</v>
+        <v>2667</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13199,10 +13199,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>428349</v>
+        <v>428161</v>
       </c>
       <c r="R119" t="n">
-        <v>6233325</v>
+        <v>6233396</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13229,12 +13229,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13261,10 +13261,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121471819</v>
+        <v>121471878</v>
       </c>
       <c r="B120" t="n">
-        <v>94606</v>
+        <v>96780</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13277,21 +13277,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2667</v>
+        <v>2604</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13301,10 +13301,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>428304</v>
+        <v>428445</v>
       </c>
       <c r="R120" t="n">
-        <v>6233306</v>
+        <v>6233151</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13363,10 +13363,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121471692</v>
+        <v>121471543</v>
       </c>
       <c r="B121" t="n">
-        <v>94606</v>
+        <v>80244</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13379,21 +13379,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13403,10 +13403,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>428126</v>
+        <v>428209</v>
       </c>
       <c r="R121" t="n">
-        <v>6233380</v>
+        <v>6233279</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13465,10 +13465,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121471532</v>
+        <v>121471870</v>
       </c>
       <c r="B122" t="n">
-        <v>94606</v>
+        <v>76950</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13477,25 +13477,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13505,10 +13505,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>428133</v>
+        <v>428356</v>
       </c>
       <c r="R122" t="n">
-        <v>6233219</v>
+        <v>6233243</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13535,12 +13535,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13567,10 +13567,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121471855</v>
+        <v>121471879</v>
       </c>
       <c r="B123" t="n">
-        <v>94400</v>
+        <v>76950</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13579,25 +13579,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>2779</v>
+        <v>1342</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13607,10 +13607,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>428365</v>
+        <v>428445</v>
       </c>
       <c r="R123" t="n">
-        <v>6233269</v>
+        <v>6233151</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13669,10 +13669,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121471914</v>
+        <v>121471940</v>
       </c>
       <c r="B124" t="n">
-        <v>94606</v>
+        <v>94616</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13685,21 +13685,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2667</v>
+        <v>1080</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13709,10 +13709,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>428318</v>
+        <v>428037</v>
       </c>
       <c r="R124" t="n">
-        <v>6233075</v>
+        <v>6233291</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13771,10 +13771,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121471915</v>
+        <v>121471873</v>
       </c>
       <c r="B125" t="n">
-        <v>96780</v>
+        <v>74565</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13783,25 +13783,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2604</v>
+        <v>1116</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13811,10 +13811,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>428281</v>
+        <v>428301</v>
       </c>
       <c r="R125" t="n">
-        <v>6233082</v>
+        <v>6233171</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13841,12 +13841,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13873,10 +13873,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121471937</v>
+        <v>121471686</v>
       </c>
       <c r="B126" t="n">
-        <v>96732</v>
+        <v>80257</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13885,25 +13885,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13913,10 +13913,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>428062</v>
+        <v>428187</v>
       </c>
       <c r="R126" t="n">
-        <v>6233301</v>
+        <v>6233403</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13943,12 +13943,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13975,10 +13975,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121471822</v>
+        <v>121471535</v>
       </c>
       <c r="B127" t="n">
-        <v>94606</v>
+        <v>76950</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13987,25 +13987,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14015,10 +14015,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>428288</v>
+        <v>428160</v>
       </c>
       <c r="R127" t="n">
-        <v>6233325</v>
+        <v>6233209</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14045,12 +14045,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14077,10 +14077,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121471841</v>
+        <v>121471914</v>
       </c>
       <c r="B128" t="n">
-        <v>96732</v>
+        <v>94606</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14093,21 +14093,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14117,10 +14117,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>428221</v>
+        <v>428318</v>
       </c>
       <c r="R128" t="n">
-        <v>6233212</v>
+        <v>6233075</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14147,12 +14147,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14179,7 +14179,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121471863</v>
+        <v>121471540</v>
       </c>
       <c r="B129" t="n">
         <v>96732</v>
@@ -14219,10 +14219,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>428411</v>
+        <v>428227</v>
       </c>
       <c r="R129" t="n">
-        <v>6233213</v>
+        <v>6233132</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14249,12 +14249,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14281,10 +14281,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121471931</v>
+        <v>121471896</v>
       </c>
       <c r="B130" t="n">
-        <v>80257</v>
+        <v>80580</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14293,25 +14293,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1144</v>
+        <v>1182</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14321,10 +14321,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>428075</v>
+        <v>428370</v>
       </c>
       <c r="R130" t="n">
-        <v>6233301</v>
+        <v>6233102</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14383,10 +14383,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121471535</v>
+        <v>121471865</v>
       </c>
       <c r="B131" t="n">
-        <v>76950</v>
+        <v>74701</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14395,25 +14395,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1342</v>
+        <v>306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14423,10 +14423,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>428160</v>
+        <v>428438</v>
       </c>
       <c r="R131" t="n">
-        <v>6233209</v>
+        <v>6233202</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14453,12 +14453,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14485,10 +14485,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121471799</v>
+        <v>121471532</v>
       </c>
       <c r="B132" t="n">
-        <v>94595</v>
+        <v>94606</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14501,21 +14501,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14525,10 +14525,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>428389</v>
+        <v>428133</v>
       </c>
       <c r="R132" t="n">
-        <v>6233324</v>
+        <v>6233219</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14555,12 +14555,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14587,10 +14587,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121471683</v>
+        <v>121471684</v>
       </c>
       <c r="B133" t="n">
-        <v>94595</v>
+        <v>80414</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14599,25 +14599,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2671</v>
+        <v>1557</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Röd pysslinglav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Thelopsis rubella</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Nyl.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14627,10 +14627,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>428278</v>
+        <v>428227</v>
       </c>
       <c r="R133" t="n">
-        <v>6233417</v>
+        <v>6233392</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14689,10 +14689,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121471879</v>
+        <v>121471874</v>
       </c>
       <c r="B134" t="n">
-        <v>76950</v>
+        <v>80257</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14701,25 +14701,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14729,7 +14729,7 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>428445</v>
+        <v>428375</v>
       </c>
       <c r="R134" t="n">
         <v>6233151</v>
@@ -14791,10 +14791,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121471824</v>
+        <v>121471683</v>
       </c>
       <c r="B135" t="n">
-        <v>76950</v>
+        <v>94595</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14803,25 +14803,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1342</v>
+        <v>2671</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14831,10 +14831,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>428288</v>
+        <v>428278</v>
       </c>
       <c r="R135" t="n">
-        <v>6233325</v>
+        <v>6233417</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14861,12 +14861,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14893,10 +14893,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121471845</v>
+        <v>121471933</v>
       </c>
       <c r="B136" t="n">
-        <v>80257</v>
+        <v>94595</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14905,25 +14905,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1144</v>
+        <v>2671</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14933,10 +14933,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>428248</v>
+        <v>428090</v>
       </c>
       <c r="R136" t="n">
-        <v>6233242</v>
+        <v>6233309</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14963,12 +14963,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14995,10 +14995,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121471919</v>
+        <v>121471868</v>
       </c>
       <c r="B137" t="n">
-        <v>80257</v>
+        <v>94606</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15007,25 +15007,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15035,10 +15035,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>428106</v>
+        <v>428347</v>
       </c>
       <c r="R137" t="n">
-        <v>6233304</v>
+        <v>6233241</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15065,12 +15065,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15097,10 +15097,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121471923</v>
+        <v>121471895</v>
       </c>
       <c r="B138" t="n">
-        <v>80257</v>
+        <v>80244</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15109,25 +15109,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15137,10 +15137,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>428091</v>
+        <v>428355</v>
       </c>
       <c r="R138" t="n">
-        <v>6233386</v>
+        <v>6233123</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15199,10 +15199,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121471833</v>
+        <v>121471847</v>
       </c>
       <c r="B139" t="n">
-        <v>80244</v>
+        <v>76950</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15211,25 +15211,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15239,10 +15239,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>428139</v>
+        <v>428300</v>
       </c>
       <c r="R139" t="n">
-        <v>6233315</v>
+        <v>6233125</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15301,10 +15301,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121471690</v>
+        <v>121471820</v>
       </c>
       <c r="B140" t="n">
-        <v>80244</v>
+        <v>94400</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15317,21 +15317,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>230185</v>
+        <v>2779</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15341,10 +15341,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>428161</v>
+        <v>428304</v>
       </c>
       <c r="R140" t="n">
-        <v>6233396</v>
+        <v>6233306</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15371,12 +15371,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15403,10 +15403,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121471934</v>
+        <v>121471695</v>
       </c>
       <c r="B141" t="n">
-        <v>94400</v>
+        <v>80244</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15419,21 +15419,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2779</v>
+        <v>230185</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15443,10 +15443,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>428090</v>
+        <v>428053</v>
       </c>
       <c r="R141" t="n">
-        <v>6233309</v>
+        <v>6233336</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15473,12 +15473,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15505,10 +15505,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121471836</v>
+        <v>121471533</v>
       </c>
       <c r="B142" t="n">
-        <v>94595</v>
+        <v>80244</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15521,21 +15521,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2671</v>
+        <v>230185</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15545,10 +15545,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>428145</v>
+        <v>428144</v>
       </c>
       <c r="R142" t="n">
-        <v>6233244</v>
+        <v>6233229</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15575,12 +15575,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15607,10 +15607,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121471825</v>
+        <v>121471929</v>
       </c>
       <c r="B143" t="n">
-        <v>80244</v>
+        <v>94400</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15623,21 +15623,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>230185</v>
+        <v>2779</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15647,10 +15647,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>428233</v>
+        <v>428078</v>
       </c>
       <c r="R143" t="n">
-        <v>6233332</v>
+        <v>6233294</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15677,12 +15677,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15709,10 +15709,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121471936</v>
+        <v>121471810</v>
       </c>
       <c r="B144" t="n">
-        <v>94616</v>
+        <v>80257</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15721,25 +15721,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1080</v>
+        <v>1144</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15749,10 +15749,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>428079</v>
+        <v>428347</v>
       </c>
       <c r="R144" t="n">
-        <v>6233262</v>
+        <v>6233326</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15779,12 +15779,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15811,10 +15811,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121471912</v>
+        <v>121471815</v>
       </c>
       <c r="B145" t="n">
-        <v>78409</v>
+        <v>80414</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15823,25 +15823,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>924</v>
+        <v>1557</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Röd pysslinglav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Thelopsis rubella</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>Nyl.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15851,10 +15851,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>428351</v>
+        <v>428333</v>
       </c>
       <c r="R145" t="n">
-        <v>6233082</v>
+        <v>6233339</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15881,12 +15881,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15913,7 +15913,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121471686</v>
+        <v>121471852</v>
       </c>
       <c r="B146" t="n">
         <v>80257</v>
@@ -15953,10 +15953,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>428187</v>
+        <v>428311</v>
       </c>
       <c r="R146" t="n">
-        <v>6233403</v>
+        <v>6233183</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15983,12 +15983,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16015,10 +16015,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121471940</v>
+        <v>121471799</v>
       </c>
       <c r="B147" t="n">
-        <v>94616</v>
+        <v>94595</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16031,21 +16031,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1080</v>
+        <v>2671</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16055,10 +16055,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>428037</v>
+        <v>428389</v>
       </c>
       <c r="R147" t="n">
-        <v>6233291</v>
+        <v>6233324</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16085,12 +16085,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16117,10 +16117,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121471828</v>
+        <v>121471860</v>
       </c>
       <c r="B148" t="n">
-        <v>80244</v>
+        <v>96732</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16133,21 +16133,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16157,10 +16157,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>428185</v>
+        <v>428404</v>
       </c>
       <c r="R148" t="n">
-        <v>6233289</v>
+        <v>6233275</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16201,7 +16201,6 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
-      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
@@ -16220,7 +16219,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121471871</v>
+        <v>121471850</v>
       </c>
       <c r="B149" t="n">
         <v>80244</v>
@@ -16260,10 +16259,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>428302</v>
+        <v>428293</v>
       </c>
       <c r="R149" t="n">
-        <v>6233176</v>
+        <v>6233170</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16322,10 +16321,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121471908</v>
+        <v>121471819</v>
       </c>
       <c r="B150" t="n">
-        <v>74611</v>
+        <v>94606</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16334,25 +16333,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1118</v>
+        <v>2667</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16362,10 +16361,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>428377</v>
+        <v>428304</v>
       </c>
       <c r="R150" t="n">
-        <v>6233090</v>
+        <v>6233306</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16392,12 +16391,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16424,10 +16423,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121471925</v>
+        <v>121471904</v>
       </c>
       <c r="B151" t="n">
-        <v>94608</v>
+        <v>78409</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16436,25 +16435,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2666</v>
+        <v>924</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16464,10 +16463,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>428076</v>
+        <v>428387</v>
       </c>
       <c r="R151" t="n">
-        <v>6233382</v>
+        <v>6233098</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16526,7 +16525,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121471847</v>
+        <v>121471804</v>
       </c>
       <c r="B152" t="n">
         <v>76950</v>
@@ -16566,10 +16565,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>428300</v>
+        <v>428335</v>
       </c>
       <c r="R152" t="n">
-        <v>6233125</v>
+        <v>6233286</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16628,10 +16627,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121471844</v>
+        <v>121471536</v>
       </c>
       <c r="B153" t="n">
-        <v>76950</v>
+        <v>80580</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16644,21 +16643,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1342</v>
+        <v>1182</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16668,10 +16667,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>428248</v>
+        <v>428166</v>
       </c>
       <c r="R153" t="n">
-        <v>6233241</v>
+        <v>6233202</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16698,12 +16697,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16730,10 +16729,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121471896</v>
+        <v>121471822</v>
       </c>
       <c r="B154" t="n">
-        <v>80580</v>
+        <v>94606</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16742,25 +16741,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1182</v>
+        <v>2667</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16770,10 +16769,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>428370</v>
+        <v>428288</v>
       </c>
       <c r="R154" t="n">
-        <v>6233102</v>
+        <v>6233325</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16800,12 +16799,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16832,10 +16831,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121471817</v>
+        <v>121471835</v>
       </c>
       <c r="B155" t="n">
-        <v>74699</v>
+        <v>96732</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16848,21 +16847,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6439</v>
+        <v>2606</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16872,10 +16871,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>428312</v>
+        <v>428145</v>
       </c>
       <c r="R155" t="n">
-        <v>6233323</v>
+        <v>6233244</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16934,10 +16933,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121471904</v>
+        <v>121471545</v>
       </c>
       <c r="B156" t="n">
-        <v>78409</v>
+        <v>80257</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16946,25 +16945,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>924</v>
+        <v>1144</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16974,10 +16973,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>428387</v>
+        <v>428172</v>
       </c>
       <c r="R156" t="n">
-        <v>6233098</v>
+        <v>6233315</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17004,12 +17003,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17036,10 +17035,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121471804</v>
+        <v>121471845</v>
       </c>
       <c r="B157" t="n">
-        <v>76950</v>
+        <v>80257</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17048,25 +17047,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17076,10 +17075,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>428335</v>
+        <v>428248</v>
       </c>
       <c r="R157" t="n">
-        <v>6233286</v>
+        <v>6233242</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17138,10 +17137,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121471913</v>
+        <v>121471812</v>
       </c>
       <c r="B158" t="n">
-        <v>76950</v>
+        <v>94400</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17150,25 +17149,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1342</v>
+        <v>2779</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17178,10 +17177,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>428342</v>
+        <v>428331</v>
       </c>
       <c r="R158" t="n">
-        <v>6233082</v>
+        <v>6233335</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17208,12 +17207,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17240,10 +17239,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121471927</v>
+        <v>121471828</v>
       </c>
       <c r="B159" t="n">
-        <v>76950</v>
+        <v>80244</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17252,25 +17251,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17280,10 +17279,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>428074</v>
+        <v>428185</v>
       </c>
       <c r="R159" t="n">
-        <v>6233297</v>
+        <v>6233289</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17310,12 +17309,12 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17324,6 +17323,7 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -17342,10 +17342,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121471843</v>
+        <v>121471913</v>
       </c>
       <c r="B160" t="n">
-        <v>57372</v>
+        <v>76950</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17358,21 +17358,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100049</v>
+        <v>1342</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17382,10 +17382,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>428252</v>
+        <v>428342</v>
       </c>
       <c r="R160" t="n">
-        <v>6233262</v>
+        <v>6233082</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17412,12 +17412,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17444,10 +17444,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121471920</v>
+        <v>121471827</v>
       </c>
       <c r="B161" t="n">
-        <v>91119</v>
+        <v>94606</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17456,25 +17456,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>2023</v>
+        <v>2667</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Sydlig sotticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Ischnoderma resinosum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Schrad.) P.Karst.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17484,10 +17484,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>428095</v>
+        <v>428185</v>
       </c>
       <c r="R161" t="n">
-        <v>6233349</v>
+        <v>6233287</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17546,10 +17546,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121471864</v>
+        <v>121471934</v>
       </c>
       <c r="B162" t="n">
-        <v>94595</v>
+        <v>94400</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17562,21 +17562,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17586,10 +17586,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>428410</v>
+        <v>428090</v>
       </c>
       <c r="R162" t="n">
-        <v>6233214</v>
+        <v>6233309</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17616,12 +17616,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17648,10 +17648,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121471868</v>
+        <v>121471802</v>
       </c>
       <c r="B163" t="n">
-        <v>94606</v>
+        <v>94595</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17664,21 +17664,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17688,10 +17688,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>428347</v>
+        <v>428332</v>
       </c>
       <c r="R163" t="n">
-        <v>6233241</v>
+        <v>6233287</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17750,10 +17750,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121471691</v>
+        <v>121471840</v>
       </c>
       <c r="B164" t="n">
-        <v>96732</v>
+        <v>78989</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17766,21 +17766,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>2606</v>
+        <v>6431</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17790,10 +17790,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>428128</v>
+        <v>428183</v>
       </c>
       <c r="R164" t="n">
-        <v>6233385</v>
+        <v>6233239</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17820,12 +17820,12 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17852,10 +17852,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121471861</v>
+        <v>121471814</v>
       </c>
       <c r="B165" t="n">
-        <v>94606</v>
+        <v>80257</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17864,25 +17864,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17892,10 +17892,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>428404</v>
+        <v>428331</v>
       </c>
       <c r="R165" t="n">
-        <v>6233275</v>
+        <v>6233339</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17954,10 +17954,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121471865</v>
+        <v>121471691</v>
       </c>
       <c r="B166" t="n">
-        <v>74701</v>
+        <v>96732</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17970,21 +17970,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>306</v>
+        <v>2606</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17994,10 +17994,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>428438</v>
+        <v>428128</v>
       </c>
       <c r="R166" t="n">
-        <v>6233202</v>
+        <v>6233385</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18024,12 +18024,12 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18056,10 +18056,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121471862</v>
+        <v>121471912</v>
       </c>
       <c r="B167" t="n">
-        <v>80244</v>
+        <v>78409</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18068,25 +18068,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>230185</v>
+        <v>924</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18096,10 +18096,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>428411</v>
+        <v>428351</v>
       </c>
       <c r="R167" t="n">
-        <v>6233213</v>
+        <v>6233082</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18126,12 +18126,12 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18158,10 +18158,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121471544</v>
+        <v>121471857</v>
       </c>
       <c r="B168" t="n">
-        <v>94606</v>
+        <v>80257</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18170,25 +18170,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18198,10 +18198,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>428219</v>
+        <v>428362</v>
       </c>
       <c r="R168" t="n">
-        <v>6233278</v>
+        <v>6233272</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18228,12 +18228,12 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18260,7 +18260,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121471534</v>
+        <v>121471943</v>
       </c>
       <c r="B169" t="n">
         <v>96732</v>
@@ -18300,10 +18300,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>428147</v>
+        <v>428034</v>
       </c>
       <c r="R169" t="n">
-        <v>6233224</v>
+        <v>6233348</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18330,12 +18330,12 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18362,10 +18362,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121471803</v>
+        <v>121471856</v>
       </c>
       <c r="B170" t="n">
-        <v>80257</v>
+        <v>76950</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18374,25 +18374,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18402,10 +18402,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>428334</v>
+        <v>428360</v>
       </c>
       <c r="R170" t="n">
-        <v>6233284</v>
+        <v>6233266</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18464,10 +18464,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121471901</v>
+        <v>121471813</v>
       </c>
       <c r="B171" t="n">
-        <v>76950</v>
+        <v>94595</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18476,25 +18476,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1342</v>
+        <v>2671</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18504,10 +18504,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>428390</v>
+        <v>428332</v>
       </c>
       <c r="R171" t="n">
-        <v>6233099</v>
+        <v>6233341</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18534,12 +18534,12 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18566,10 +18566,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121471881</v>
+        <v>121471941</v>
       </c>
       <c r="B172" t="n">
-        <v>78409</v>
+        <v>80244</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18578,25 +18578,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>924</v>
+        <v>230185</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18606,10 +18606,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>428445</v>
+        <v>428046</v>
       </c>
       <c r="R172" t="n">
-        <v>6233151</v>
+        <v>6233350</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18636,12 +18636,12 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18668,10 +18668,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121471941</v>
+        <v>121471834</v>
       </c>
       <c r="B173" t="n">
-        <v>80244</v>
+        <v>80257</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18680,25 +18680,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18708,10 +18708,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>428046</v>
+        <v>428137</v>
       </c>
       <c r="R173" t="n">
-        <v>6233350</v>
+        <v>6233320</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18738,12 +18738,12 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18770,10 +18770,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121471866</v>
+        <v>121471824</v>
       </c>
       <c r="B174" t="n">
-        <v>80244</v>
+        <v>76950</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18782,25 +18782,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18810,10 +18810,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>428442</v>
+        <v>428288</v>
       </c>
       <c r="R174" t="n">
-        <v>6233170</v>
+        <v>6233325</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18872,10 +18872,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121471842</v>
+        <v>121471849</v>
       </c>
       <c r="B175" t="n">
-        <v>94606</v>
+        <v>80257</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18884,25 +18884,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18912,10 +18912,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>428221</v>
+        <v>428299</v>
       </c>
       <c r="R175" t="n">
-        <v>6233212</v>
+        <v>6233126</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>

--- a/artfynd/A 18989-2024 artfynd.xlsx
+++ b/artfynd/A 18989-2024 artfynd.xlsx
@@ -3354,10 +3354,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121471908</v>
+        <v>121471693</v>
       </c>
       <c r="B23" t="n">
-        <v>74611</v>
+        <v>94595</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3366,25 +3366,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1118</v>
+        <v>2671</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>428377</v>
+        <v>428125</v>
       </c>
       <c r="R23" t="n">
-        <v>6233090</v>
+        <v>6233379</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3424,12 +3424,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3456,10 +3456,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121471938</v>
+        <v>121471877</v>
       </c>
       <c r="B24" t="n">
-        <v>80244</v>
+        <v>94606</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3472,21 +3472,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>428062</v>
+        <v>428445</v>
       </c>
       <c r="R24" t="n">
-        <v>6233301</v>
+        <v>6233151</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3526,12 +3526,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3558,10 +3558,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121471925</v>
+        <v>121471845</v>
       </c>
       <c r="B25" t="n">
-        <v>94608</v>
+        <v>80257</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3570,25 +3570,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2666</v>
+        <v>1144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>428076</v>
+        <v>428248</v>
       </c>
       <c r="R25" t="n">
-        <v>6233382</v>
+        <v>6233242</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3628,12 +3628,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3660,10 +3660,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121471924</v>
+        <v>121471826</v>
       </c>
       <c r="B26" t="n">
-        <v>80244</v>
+        <v>78865</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3676,21 +3676,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>230185</v>
+        <v>6459</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>428097</v>
+        <v>428228</v>
       </c>
       <c r="R26" t="n">
-        <v>6233382</v>
+        <v>6233340</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3730,12 +3730,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3762,10 +3762,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121471905</v>
+        <v>121471862</v>
       </c>
       <c r="B27" t="n">
-        <v>74611</v>
+        <v>80244</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3774,25 +3774,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1118</v>
+        <v>230185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>428377</v>
+        <v>428411</v>
       </c>
       <c r="R27" t="n">
-        <v>6233095</v>
+        <v>6233213</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3832,12 +3832,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3864,10 +3864,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121471858</v>
+        <v>121471873</v>
       </c>
       <c r="B28" t="n">
-        <v>80257</v>
+        <v>74565</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3876,25 +3876,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1144</v>
+        <v>1116</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>428372</v>
+        <v>428301</v>
       </c>
       <c r="R28" t="n">
-        <v>6233270</v>
+        <v>6233171</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121471881</v>
+        <v>121471853</v>
       </c>
       <c r="B29" t="n">
-        <v>78409</v>
+        <v>76950</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3982,21 +3982,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>924</v>
+        <v>1342</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>428445</v>
+        <v>428311</v>
       </c>
       <c r="R29" t="n">
-        <v>6233151</v>
+        <v>6233183</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4068,10 +4068,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121471842</v>
+        <v>121471896</v>
       </c>
       <c r="B30" t="n">
-        <v>94606</v>
+        <v>80580</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4080,25 +4080,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2667</v>
+        <v>1182</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>428221</v>
+        <v>428370</v>
       </c>
       <c r="R30" t="n">
-        <v>6233212</v>
+        <v>6233102</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4138,12 +4138,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4170,10 +4170,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121471920</v>
+        <v>121471815</v>
       </c>
       <c r="B31" t="n">
-        <v>91119</v>
+        <v>80414</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4182,25 +4182,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2023</v>
+        <v>1557</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sydlig sotticka</t>
+          <t>Röd pysslinglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ischnoderma resinosum</t>
+          <t>Thelopsis rubella</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schrad.) P.Karst.</t>
+          <t>Nyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>428095</v>
+        <v>428333</v>
       </c>
       <c r="R31" t="n">
-        <v>6233349</v>
+        <v>6233339</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4240,12 +4240,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4272,10 +4272,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121471882</v>
+        <v>121471798</v>
       </c>
       <c r="B32" t="n">
-        <v>74611</v>
+        <v>96732</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4284,25 +4284,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1118</v>
+        <v>2606</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>428445</v>
+        <v>428387</v>
       </c>
       <c r="R32" t="n">
-        <v>6233151</v>
+        <v>6233326</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4374,10 +4374,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121471930</v>
+        <v>121471688</v>
       </c>
       <c r="B33" t="n">
-        <v>74611</v>
+        <v>96732</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4386,25 +4386,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1118</v>
+        <v>2606</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4414,10 +4414,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>428078</v>
+        <v>428159</v>
       </c>
       <c r="R33" t="n">
-        <v>6233294</v>
+        <v>6233394</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4444,12 +4444,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4476,10 +4476,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121471688</v>
+        <v>121471934</v>
       </c>
       <c r="B34" t="n">
-        <v>96732</v>
+        <v>94400</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4492,21 +4492,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2606</v>
+        <v>2779</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>428159</v>
+        <v>428090</v>
       </c>
       <c r="R34" t="n">
-        <v>6233394</v>
+        <v>6233309</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4546,12 +4546,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4578,10 +4578,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121471897</v>
+        <v>121471819</v>
       </c>
       <c r="B35" t="n">
-        <v>78409</v>
+        <v>94606</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4590,25 +4590,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>924</v>
+        <v>2667</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>428369</v>
+        <v>428304</v>
       </c>
       <c r="R35" t="n">
-        <v>6233104</v>
+        <v>6233306</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4648,12 +4648,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4680,10 +4680,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121471910</v>
+        <v>121471691</v>
       </c>
       <c r="B36" t="n">
-        <v>76950</v>
+        <v>96732</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4692,25 +4692,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4720,10 +4720,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>428377</v>
+        <v>428128</v>
       </c>
       <c r="R36" t="n">
-        <v>6233090</v>
+        <v>6233385</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4750,12 +4750,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4782,10 +4782,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121471693</v>
+        <v>121471833</v>
       </c>
       <c r="B37" t="n">
-        <v>94595</v>
+        <v>80244</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4798,21 +4798,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2671</v>
+        <v>230185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>428125</v>
+        <v>428139</v>
       </c>
       <c r="R37" t="n">
-        <v>6233379</v>
+        <v>6233315</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4884,10 +4884,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121471798</v>
+        <v>121471686</v>
       </c>
       <c r="B38" t="n">
-        <v>96732</v>
+        <v>80257</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4896,25 +4896,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>428387</v>
+        <v>428187</v>
       </c>
       <c r="R38" t="n">
-        <v>6233326</v>
+        <v>6233403</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4954,12 +4954,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4986,10 +4986,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121471916</v>
+        <v>121471814</v>
       </c>
       <c r="B39" t="n">
-        <v>94616</v>
+        <v>80257</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4998,25 +4998,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1080</v>
+        <v>1144</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>428283</v>
+        <v>428331</v>
       </c>
       <c r="R39" t="n">
-        <v>6233084</v>
+        <v>6233339</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5088,10 +5088,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121471871</v>
+        <v>121471692</v>
       </c>
       <c r="B40" t="n">
-        <v>80244</v>
+        <v>94606</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5104,21 +5104,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5128,10 +5128,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>428302</v>
+        <v>428126</v>
       </c>
       <c r="R40" t="n">
-        <v>6233176</v>
+        <v>6233380</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5190,10 +5190,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121471846</v>
+        <v>121471878</v>
       </c>
       <c r="B41" t="n">
-        <v>80244</v>
+        <v>96780</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5206,21 +5206,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>230185</v>
+        <v>2604</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5230,10 +5230,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>428241</v>
+        <v>428445</v>
       </c>
       <c r="R41" t="n">
-        <v>6233222</v>
+        <v>6233151</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5292,10 +5292,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121471542</v>
+        <v>121471827</v>
       </c>
       <c r="B42" t="n">
-        <v>80257</v>
+        <v>94606</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5304,25 +5304,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5332,10 +5332,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>428198</v>
+        <v>428185</v>
       </c>
       <c r="R42" t="n">
-        <v>6233249</v>
+        <v>6233287</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5362,12 +5362,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5394,10 +5394,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121471855</v>
+        <v>121471539</v>
       </c>
       <c r="B43" t="n">
-        <v>94400</v>
+        <v>94595</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5410,21 +5410,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5434,10 +5434,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>428365</v>
+        <v>428262</v>
       </c>
       <c r="R43" t="n">
-        <v>6233269</v>
+        <v>6233134</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5464,12 +5464,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5496,53 +5496,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121471875</v>
+        <v>121471860</v>
       </c>
       <c r="B44" t="n">
-        <v>80257</v>
+        <v>96732</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>428340</v>
+        <v>428404</v>
       </c>
       <c r="R44" t="n">
-        <v>6233229</v>
+        <v>6233275</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5577,21 +5574,11 @@
           <t>2024-11-21</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>kollekt</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG44" t="b">
         <v>0</v>
@@ -5611,10 +5598,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121471911</v>
+        <v>121471945</v>
       </c>
       <c r="B45" t="n">
-        <v>76950</v>
+        <v>96780</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5623,25 +5610,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1342</v>
+        <v>2604</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5651,10 +5638,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>428352</v>
+        <v>428035</v>
       </c>
       <c r="R45" t="n">
-        <v>6233082</v>
+        <v>6233349</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5713,10 +5700,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121471866</v>
+        <v>121471534</v>
       </c>
       <c r="B46" t="n">
-        <v>80244</v>
+        <v>96732</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5729,21 +5716,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5753,10 +5740,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>428442</v>
+        <v>428147</v>
       </c>
       <c r="R46" t="n">
-        <v>6233170</v>
+        <v>6233224</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5783,12 +5770,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5815,10 +5802,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121471531</v>
+        <v>121471931</v>
       </c>
       <c r="B47" t="n">
-        <v>94616</v>
+        <v>80257</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5827,25 +5814,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1080</v>
+        <v>1144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5855,10 +5842,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>428110</v>
+        <v>428075</v>
       </c>
       <c r="R47" t="n">
-        <v>6233224</v>
+        <v>6233301</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5885,12 +5872,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5917,10 +5904,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121471937</v>
+        <v>121471849</v>
       </c>
       <c r="B48" t="n">
-        <v>96732</v>
+        <v>80257</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5929,25 +5916,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5957,10 +5944,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>428062</v>
+        <v>428299</v>
       </c>
       <c r="R48" t="n">
-        <v>6233301</v>
+        <v>6233126</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5987,12 +5974,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6019,10 +6006,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121471931</v>
+        <v>121471879</v>
       </c>
       <c r="B49" t="n">
-        <v>80257</v>
+        <v>76950</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6031,25 +6018,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6059,10 +6046,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>428075</v>
+        <v>428445</v>
       </c>
       <c r="R49" t="n">
-        <v>6233301</v>
+        <v>6233151</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6089,12 +6076,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6121,14 +6108,14 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121471796</v>
+        <v>121471875</v>
       </c>
       <c r="B50" t="n">
         <v>80257</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6155,16 +6142,19 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>428390</v>
+        <v>428340</v>
       </c>
       <c r="R50" t="n">
-        <v>6233312</v>
+        <v>6233229</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6199,11 +6189,21 @@
           <t>2024-11-21</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>kollekt</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG50" t="b">
         <v>0</v>
@@ -6223,10 +6223,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121471817</v>
+        <v>121471840</v>
       </c>
       <c r="B51" t="n">
-        <v>74699</v>
+        <v>78989</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6239,21 +6239,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6439</v>
+        <v>6431</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6263,10 +6263,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>428312</v>
+        <v>428183</v>
       </c>
       <c r="R51" t="n">
-        <v>6233323</v>
+        <v>6233239</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6325,10 +6325,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121471534</v>
+        <v>121471941</v>
       </c>
       <c r="B52" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6341,21 +6341,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6365,10 +6365,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>428147</v>
+        <v>428046</v>
       </c>
       <c r="R52" t="n">
-        <v>6233224</v>
+        <v>6233350</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6395,12 +6395,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6427,10 +6427,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121471909</v>
+        <v>121471538</v>
       </c>
       <c r="B53" t="n">
-        <v>76950</v>
+        <v>80244</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6439,25 +6439,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6467,10 +6467,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>428373</v>
+        <v>428166</v>
       </c>
       <c r="R53" t="n">
-        <v>6233088</v>
+        <v>6233198</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6497,12 +6497,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6529,10 +6529,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121471696</v>
+        <v>121471871</v>
       </c>
       <c r="B54" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6545,21 +6545,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6569,10 +6569,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>428054</v>
+        <v>428302</v>
       </c>
       <c r="R54" t="n">
-        <v>6233337</v>
+        <v>6233176</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6599,12 +6599,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6631,10 +6631,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121471923</v>
+        <v>121471924</v>
       </c>
       <c r="B55" t="n">
-        <v>80257</v>
+        <v>80244</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6643,25 +6643,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6671,10 +6671,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>428091</v>
+        <v>428097</v>
       </c>
       <c r="R55" t="n">
-        <v>6233386</v>
+        <v>6233382</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6733,10 +6733,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121471945</v>
+        <v>121471825</v>
       </c>
       <c r="B56" t="n">
-        <v>96780</v>
+        <v>80244</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6749,21 +6749,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2604</v>
+        <v>230185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6773,10 +6773,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>428035</v>
+        <v>428233</v>
       </c>
       <c r="R56" t="n">
-        <v>6233349</v>
+        <v>6233332</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6803,12 +6803,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6835,7 +6835,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121471825</v>
+        <v>121471543</v>
       </c>
       <c r="B57" t="n">
         <v>80244</v>
@@ -6875,10 +6875,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>428233</v>
+        <v>428209</v>
       </c>
       <c r="R57" t="n">
-        <v>6233332</v>
+        <v>6233279</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6905,12 +6905,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6937,10 +6937,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121471861</v>
+        <v>121471933</v>
       </c>
       <c r="B58" t="n">
-        <v>94606</v>
+        <v>94595</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6953,21 +6953,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6977,10 +6977,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>428404</v>
+        <v>428090</v>
       </c>
       <c r="R58" t="n">
-        <v>6233275</v>
+        <v>6233309</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7039,10 +7039,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121471839</v>
+        <v>121471542</v>
       </c>
       <c r="B59" t="n">
-        <v>94595</v>
+        <v>80257</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7051,25 +7051,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2671</v>
+        <v>1144</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7079,10 +7079,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>428184</v>
+        <v>428198</v>
       </c>
       <c r="R59" t="n">
-        <v>6233240</v>
+        <v>6233249</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7109,12 +7109,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7141,10 +7141,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121471859</v>
+        <v>121471910</v>
       </c>
       <c r="B60" t="n">
-        <v>80244</v>
+        <v>76950</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7153,25 +7153,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7181,10 +7181,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>428404</v>
+        <v>428377</v>
       </c>
       <c r="R60" t="n">
-        <v>6233275</v>
+        <v>6233090</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7211,12 +7211,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7243,7 +7243,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121471694</v>
+        <v>121471829</v>
       </c>
       <c r="B61" t="n">
         <v>80257</v>
@@ -7283,10 +7283,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>428125</v>
+        <v>428147</v>
       </c>
       <c r="R61" t="n">
-        <v>6233379</v>
+        <v>6233304</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7313,12 +7313,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7345,10 +7345,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121471926</v>
+        <v>121471697</v>
       </c>
       <c r="B62" t="n">
-        <v>94400</v>
+        <v>74701</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7361,21 +7361,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2779</v>
+        <v>306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>428073</v>
+        <v>428043</v>
       </c>
       <c r="R62" t="n">
-        <v>6233383</v>
+        <v>6233298</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7415,12 +7415,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7447,10 +7447,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121471833</v>
+        <v>121471855</v>
       </c>
       <c r="B63" t="n">
-        <v>80244</v>
+        <v>94400</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7463,21 +7463,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>230185</v>
+        <v>2779</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7487,10 +7487,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>428139</v>
+        <v>428365</v>
       </c>
       <c r="R63" t="n">
-        <v>6233315</v>
+        <v>6233269</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7549,10 +7549,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121471807</v>
+        <v>121471810</v>
       </c>
       <c r="B64" t="n">
-        <v>76950</v>
+        <v>80257</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7561,25 +7561,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7589,10 +7589,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>428327</v>
+        <v>428347</v>
       </c>
       <c r="R64" t="n">
-        <v>6233292</v>
+        <v>6233326</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7651,10 +7651,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121471854</v>
+        <v>121471694</v>
       </c>
       <c r="B65" t="n">
-        <v>96732</v>
+        <v>80257</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7663,25 +7663,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7691,10 +7691,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>428302</v>
+        <v>428125</v>
       </c>
       <c r="R65" t="n">
-        <v>6233177</v>
+        <v>6233379</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7721,12 +7721,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7753,10 +7753,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121471537</v>
+        <v>121471831</v>
       </c>
       <c r="B66" t="n">
-        <v>96732</v>
+        <v>80257</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7765,25 +7765,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7793,10 +7793,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>428163</v>
+        <v>428145</v>
       </c>
       <c r="R66" t="n">
-        <v>6233193</v>
+        <v>6233315</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7823,12 +7823,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7855,10 +7855,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121471809</v>
+        <v>121471907</v>
       </c>
       <c r="B67" t="n">
-        <v>74565</v>
+        <v>76950</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7871,21 +7871,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1116</v>
+        <v>1342</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7895,10 +7895,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>428352</v>
+        <v>428375</v>
       </c>
       <c r="R67" t="n">
-        <v>6233315</v>
+        <v>6233092</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7925,12 +7925,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7957,10 +7957,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121471801</v>
+        <v>121471807</v>
       </c>
       <c r="B68" t="n">
-        <v>80257</v>
+        <v>76950</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7969,25 +7969,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7997,10 +7997,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>428370</v>
+        <v>428327</v>
       </c>
       <c r="R68" t="n">
-        <v>6233336</v>
+        <v>6233292</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8059,10 +8059,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121471690</v>
+        <v>121471844</v>
       </c>
       <c r="B69" t="n">
-        <v>80244</v>
+        <v>76950</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8071,25 +8071,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8099,10 +8099,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>428161</v>
+        <v>428248</v>
       </c>
       <c r="R69" t="n">
-        <v>6233396</v>
+        <v>6233241</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8161,10 +8161,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121471541</v>
+        <v>121471801</v>
       </c>
       <c r="B70" t="n">
-        <v>80244</v>
+        <v>80257</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8173,25 +8173,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>428209</v>
+        <v>428370</v>
       </c>
       <c r="R70" t="n">
-        <v>6233184</v>
+        <v>6233336</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8231,12 +8231,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8263,10 +8263,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121471844</v>
+        <v>121471805</v>
       </c>
       <c r="B71" t="n">
-        <v>76950</v>
+        <v>80257</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8275,25 +8275,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>428248</v>
+        <v>428333</v>
       </c>
       <c r="R71" t="n">
-        <v>6233241</v>
+        <v>6233283</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8365,10 +8365,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121471843</v>
+        <v>121471922</v>
       </c>
       <c r="B72" t="n">
-        <v>57372</v>
+        <v>76950</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8381,21 +8381,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>1342</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>428252</v>
+        <v>428091</v>
       </c>
       <c r="R72" t="n">
-        <v>6233262</v>
+        <v>6233385</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8435,12 +8435,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8467,7 +8467,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121471862</v>
+        <v>121471846</v>
       </c>
       <c r="B73" t="n">
         <v>80244</v>
@@ -8507,10 +8507,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>428411</v>
+        <v>428241</v>
       </c>
       <c r="R73" t="n">
-        <v>6233213</v>
+        <v>6233222</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8569,10 +8569,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121471942</v>
+        <v>121471803</v>
       </c>
       <c r="B74" t="n">
-        <v>76950</v>
+        <v>80257</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8581,25 +8581,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8609,10 +8609,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>428032</v>
+        <v>428334</v>
       </c>
       <c r="R74" t="n">
-        <v>6233345</v>
+        <v>6233284</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8639,12 +8639,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8671,10 +8671,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121471901</v>
+        <v>121471545</v>
       </c>
       <c r="B75" t="n">
-        <v>76950</v>
+        <v>80257</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8683,25 +8683,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8711,10 +8711,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>428390</v>
+        <v>428172</v>
       </c>
       <c r="R75" t="n">
-        <v>6233099</v>
+        <v>6233315</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8741,12 +8741,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8773,10 +8773,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121471851</v>
+        <v>121471913</v>
       </c>
       <c r="B76" t="n">
-        <v>78865</v>
+        <v>76950</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8785,25 +8785,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6459</v>
+        <v>1342</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8813,10 +8813,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>428293</v>
+        <v>428342</v>
       </c>
       <c r="R76" t="n">
-        <v>6233170</v>
+        <v>6233082</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8843,12 +8843,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8875,10 +8875,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121471800</v>
+        <v>121471903</v>
       </c>
       <c r="B77" t="n">
-        <v>80257</v>
+        <v>76950</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8887,25 +8887,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8915,10 +8915,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>428387</v>
+        <v>428385</v>
       </c>
       <c r="R77" t="n">
-        <v>6233322</v>
+        <v>6233097</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8945,12 +8945,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8977,10 +8977,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121471903</v>
+        <v>121471850</v>
       </c>
       <c r="B78" t="n">
-        <v>76950</v>
+        <v>80244</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8989,25 +8989,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9017,10 +9017,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>428385</v>
+        <v>428293</v>
       </c>
       <c r="R78" t="n">
-        <v>6233097</v>
+        <v>6233170</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9047,12 +9047,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9079,10 +9079,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121471917</v>
+        <v>121471926</v>
       </c>
       <c r="B79" t="n">
-        <v>80244</v>
+        <v>94400</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9095,21 +9095,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>230185</v>
+        <v>2779</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9119,10 +9119,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>428284</v>
+        <v>428073</v>
       </c>
       <c r="R79" t="n">
-        <v>6233109</v>
+        <v>6233383</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9181,10 +9181,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121471811</v>
+        <v>121471820</v>
       </c>
       <c r="B80" t="n">
-        <v>76950</v>
+        <v>94400</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9193,25 +9193,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1342</v>
+        <v>2779</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9221,10 +9221,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>428349</v>
+        <v>428304</v>
       </c>
       <c r="R80" t="n">
-        <v>6233325</v>
+        <v>6233306</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9283,10 +9283,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121471829</v>
+        <v>121471914</v>
       </c>
       <c r="B81" t="n">
-        <v>80257</v>
+        <v>94606</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9295,25 +9295,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9323,10 +9323,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>428147</v>
+        <v>428318</v>
       </c>
       <c r="R81" t="n">
-        <v>6233304</v>
+        <v>6233075</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9353,12 +9353,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9385,10 +9385,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121471902</v>
+        <v>121471800</v>
       </c>
       <c r="B82" t="n">
-        <v>94595</v>
+        <v>80257</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9397,25 +9397,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2671</v>
+        <v>1144</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9428,7 +9428,7 @@
         <v>428387</v>
       </c>
       <c r="R82" t="n">
-        <v>6233096</v>
+        <v>6233322</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9455,12 +9455,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9487,10 +9487,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121471915</v>
+        <v>121471847</v>
       </c>
       <c r="B83" t="n">
-        <v>96780</v>
+        <v>76950</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9499,25 +9499,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2604</v>
+        <v>1342</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>428281</v>
+        <v>428300</v>
       </c>
       <c r="R83" t="n">
-        <v>6233082</v>
+        <v>6233125</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9557,12 +9557,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9589,10 +9589,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121471539</v>
+        <v>121471851</v>
       </c>
       <c r="B84" t="n">
-        <v>94595</v>
+        <v>78865</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9605,21 +9605,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2671</v>
+        <v>6459</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9629,10 +9629,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>428262</v>
+        <v>428293</v>
       </c>
       <c r="R84" t="n">
-        <v>6233134</v>
+        <v>6233170</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9659,12 +9659,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9691,10 +9691,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121471841</v>
+        <v>121471799</v>
       </c>
       <c r="B85" t="n">
-        <v>96732</v>
+        <v>94595</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9707,21 +9707,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2606</v>
+        <v>2671</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9731,10 +9731,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>428221</v>
+        <v>428389</v>
       </c>
       <c r="R85" t="n">
-        <v>6233212</v>
+        <v>6233324</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9793,7 +9793,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121471919</v>
+        <v>121471928</v>
       </c>
       <c r="B86" t="n">
         <v>80257</v>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>428106</v>
+        <v>428075</v>
       </c>
       <c r="R86" t="n">
-        <v>6233304</v>
+        <v>6233294</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9895,10 +9895,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121471803</v>
+        <v>121471536</v>
       </c>
       <c r="B87" t="n">
-        <v>80257</v>
+        <v>80580</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9907,25 +9907,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1144</v>
+        <v>1182</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9935,10 +9935,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>428334</v>
+        <v>428166</v>
       </c>
       <c r="R87" t="n">
-        <v>6233284</v>
+        <v>6233202</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9965,12 +9965,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9997,10 +9997,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121471544</v>
+        <v>121471899</v>
       </c>
       <c r="B88" t="n">
-        <v>94606</v>
+        <v>94400</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10013,21 +10013,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10037,10 +10037,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>428219</v>
+        <v>428389</v>
       </c>
       <c r="R88" t="n">
-        <v>6233278</v>
+        <v>6233099</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10067,12 +10067,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10099,10 +10099,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121471836</v>
+        <v>121471881</v>
       </c>
       <c r="B89" t="n">
-        <v>94595</v>
+        <v>78409</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10111,25 +10111,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2671</v>
+        <v>924</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10139,10 +10139,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>428145</v>
+        <v>428445</v>
       </c>
       <c r="R89" t="n">
-        <v>6233244</v>
+        <v>6233151</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10201,10 +10201,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121471899</v>
+        <v>121471837</v>
       </c>
       <c r="B90" t="n">
-        <v>94400</v>
+        <v>80244</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10217,21 +10217,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2779</v>
+        <v>230185</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10241,10 +10241,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>428389</v>
+        <v>428145</v>
       </c>
       <c r="R90" t="n">
-        <v>6233099</v>
+        <v>6233244</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10271,12 +10271,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10303,10 +10303,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121471863</v>
+        <v>121471895</v>
       </c>
       <c r="B91" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10319,21 +10319,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10343,10 +10343,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>428411</v>
+        <v>428355</v>
       </c>
       <c r="R91" t="n">
-        <v>6233213</v>
+        <v>6233123</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10373,12 +10373,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10405,10 +10405,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121471826</v>
+        <v>121471808</v>
       </c>
       <c r="B92" t="n">
-        <v>78865</v>
+        <v>80257</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10417,25 +10417,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6459</v>
+        <v>1144</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10445,10 +10445,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>428228</v>
+        <v>428350</v>
       </c>
       <c r="R92" t="n">
-        <v>6233340</v>
+        <v>6233316</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10507,10 +10507,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121471816</v>
+        <v>121471867</v>
       </c>
       <c r="B93" t="n">
-        <v>96780</v>
+        <v>76950</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10519,25 +10519,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2604</v>
+        <v>1342</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10547,10 +10547,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>428317</v>
+        <v>428442</v>
       </c>
       <c r="R93" t="n">
-        <v>6233324</v>
+        <v>6233170</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10609,10 +10609,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121471818</v>
+        <v>121471940</v>
       </c>
       <c r="B94" t="n">
-        <v>96732</v>
+        <v>94616</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10625,21 +10625,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2606</v>
+        <v>1080</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10649,10 +10649,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>428307</v>
+        <v>428037</v>
       </c>
       <c r="R94" t="n">
-        <v>6233311</v>
+        <v>6233291</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10679,12 +10679,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10711,10 +10711,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121471831</v>
+        <v>121471809</v>
       </c>
       <c r="B95" t="n">
-        <v>80257</v>
+        <v>74565</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10723,25 +10723,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1144</v>
+        <v>1116</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10751,7 +10751,7 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>428145</v>
+        <v>428352</v>
       </c>
       <c r="R95" t="n">
         <v>6233315</v>
@@ -10813,10 +10813,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121471530</v>
+        <v>121471804</v>
       </c>
       <c r="B96" t="n">
-        <v>80244</v>
+        <v>76950</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10825,25 +10825,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10853,10 +10853,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>428111</v>
+        <v>428335</v>
       </c>
       <c r="R96" t="n">
-        <v>6233222</v>
+        <v>6233286</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10883,12 +10883,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10915,10 +10915,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121471867</v>
+        <v>121471812</v>
       </c>
       <c r="B97" t="n">
-        <v>76950</v>
+        <v>94400</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10927,25 +10927,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1342</v>
+        <v>2779</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10955,10 +10955,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>428442</v>
+        <v>428331</v>
       </c>
       <c r="R97" t="n">
-        <v>6233170</v>
+        <v>6233335</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11017,10 +11017,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121471928</v>
+        <v>121471841</v>
       </c>
       <c r="B98" t="n">
-        <v>80257</v>
+        <v>96732</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11029,25 +11029,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11057,10 +11057,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>428075</v>
+        <v>428221</v>
       </c>
       <c r="R98" t="n">
-        <v>6233294</v>
+        <v>6233212</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11119,10 +11119,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121471837</v>
+        <v>121471817</v>
       </c>
       <c r="B99" t="n">
-        <v>80244</v>
+        <v>74699</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11135,21 +11135,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>230185</v>
+        <v>6439</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11159,10 +11159,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>428145</v>
+        <v>428312</v>
       </c>
       <c r="R99" t="n">
-        <v>6233244</v>
+        <v>6233323</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11221,10 +11221,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121471939</v>
+        <v>121471866</v>
       </c>
       <c r="B100" t="n">
-        <v>94606</v>
+        <v>80244</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11237,21 +11237,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11261,10 +11261,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>428046</v>
+        <v>428442</v>
       </c>
       <c r="R100" t="n">
-        <v>6233296</v>
+        <v>6233170</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11291,12 +11291,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11323,10 +11323,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121471876</v>
+        <v>121471927</v>
       </c>
       <c r="B101" t="n">
-        <v>80287</v>
+        <v>76950</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11335,25 +11335,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1223</v>
+        <v>1342</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rikfruktig blemlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phlyctis agelaea</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Flot.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11363,10 +11363,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>428446</v>
+        <v>428074</v>
       </c>
       <c r="R101" t="n">
-        <v>6233151</v>
+        <v>6233297</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11393,12 +11393,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11425,10 +11425,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121471808</v>
+        <v>121471696</v>
       </c>
       <c r="B102" t="n">
-        <v>80257</v>
+        <v>96732</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11437,25 +11437,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11465,10 +11465,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>428350</v>
+        <v>428054</v>
       </c>
       <c r="R102" t="n">
-        <v>6233316</v>
+        <v>6233337</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11495,12 +11495,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11527,10 +11527,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121471806</v>
+        <v>121471868</v>
       </c>
       <c r="B103" t="n">
-        <v>80257</v>
+        <v>94606</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11539,25 +11539,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11567,10 +11567,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>428325</v>
+        <v>428347</v>
       </c>
       <c r="R103" t="n">
-        <v>6233291</v>
+        <v>6233241</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11629,10 +11629,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121471944</v>
+        <v>121471856</v>
       </c>
       <c r="B104" t="n">
-        <v>94606</v>
+        <v>76950</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11641,25 +11641,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11669,10 +11669,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>428034</v>
+        <v>428360</v>
       </c>
       <c r="R104" t="n">
-        <v>6233348</v>
+        <v>6233266</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11699,12 +11699,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11731,10 +11731,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121471692</v>
+        <v>121471901</v>
       </c>
       <c r="B105" t="n">
-        <v>94606</v>
+        <v>76950</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11743,25 +11743,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11771,10 +11771,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>428126</v>
+        <v>428390</v>
       </c>
       <c r="R105" t="n">
-        <v>6233380</v>
+        <v>6233099</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11801,12 +11801,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11833,10 +11833,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121471805</v>
+        <v>121471813</v>
       </c>
       <c r="B106" t="n">
-        <v>80257</v>
+        <v>94595</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11845,25 +11845,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1144</v>
+        <v>2671</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11873,10 +11873,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>428333</v>
+        <v>428332</v>
       </c>
       <c r="R106" t="n">
-        <v>6233283</v>
+        <v>6233341</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11935,10 +11935,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121471877</v>
+        <v>121471683</v>
       </c>
       <c r="B107" t="n">
-        <v>94606</v>
+        <v>94595</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11951,21 +11951,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11975,10 +11975,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>428445</v>
+        <v>428278</v>
       </c>
       <c r="R107" t="n">
-        <v>6233151</v>
+        <v>6233417</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12005,12 +12005,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12037,10 +12037,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121471697</v>
+        <v>121471537</v>
       </c>
       <c r="B108" t="n">
-        <v>74701</v>
+        <v>96732</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12053,21 +12053,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>306</v>
+        <v>2606</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12077,10 +12077,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>428043</v>
+        <v>428163</v>
       </c>
       <c r="R108" t="n">
-        <v>6233298</v>
+        <v>6233193</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12139,10 +12139,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121471869</v>
+        <v>121471842</v>
       </c>
       <c r="B109" t="n">
-        <v>96732</v>
+        <v>94606</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12155,21 +12155,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12179,10 +12179,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>428354</v>
+        <v>428221</v>
       </c>
       <c r="R109" t="n">
-        <v>6233242</v>
+        <v>6233212</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12241,10 +12241,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121471538</v>
+        <v>121471882</v>
       </c>
       <c r="B110" t="n">
-        <v>80244</v>
+        <v>74611</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12253,25 +12253,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>230185</v>
+        <v>1118</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12281,10 +12281,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>428166</v>
+        <v>428445</v>
       </c>
       <c r="R110" t="n">
-        <v>6233198</v>
+        <v>6233151</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12311,12 +12311,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12343,10 +12343,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121471907</v>
+        <v>121471904</v>
       </c>
       <c r="B111" t="n">
-        <v>76950</v>
+        <v>78409</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12359,21 +12359,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1342</v>
+        <v>924</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12383,10 +12383,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>428375</v>
+        <v>428387</v>
       </c>
       <c r="R111" t="n">
-        <v>6233092</v>
+        <v>6233098</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12445,10 +12445,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121471935</v>
+        <v>121471920</v>
       </c>
       <c r="B112" t="n">
-        <v>80244</v>
+        <v>91119</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12457,25 +12457,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>230185</v>
+        <v>2023</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Sydlig sotticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Ischnoderma resinosum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schrad.) P.Karst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12485,10 +12485,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>428097</v>
+        <v>428095</v>
       </c>
       <c r="R112" t="n">
-        <v>6233286</v>
+        <v>6233349</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12547,10 +12547,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121471927</v>
+        <v>121471908</v>
       </c>
       <c r="B113" t="n">
-        <v>76950</v>
+        <v>74611</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12563,21 +12563,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1342</v>
+        <v>1118</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12587,10 +12587,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>428074</v>
+        <v>428377</v>
       </c>
       <c r="R113" t="n">
-        <v>6233297</v>
+        <v>6233090</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12649,10 +12649,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121471853</v>
+        <v>121471905</v>
       </c>
       <c r="B114" t="n">
-        <v>76950</v>
+        <v>74611</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12665,21 +12665,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1342</v>
+        <v>1118</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12689,10 +12689,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>428311</v>
+        <v>428377</v>
       </c>
       <c r="R114" t="n">
-        <v>6233183</v>
+        <v>6233095</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12719,12 +12719,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12751,10 +12751,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121471936</v>
+        <v>121471836</v>
       </c>
       <c r="B115" t="n">
-        <v>94616</v>
+        <v>94595</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12767,21 +12767,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1080</v>
+        <v>2671</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12791,10 +12791,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>428079</v>
+        <v>428145</v>
       </c>
       <c r="R115" t="n">
-        <v>6233262</v>
+        <v>6233244</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12821,12 +12821,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12955,10 +12955,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121471922</v>
+        <v>121471936</v>
       </c>
       <c r="B117" t="n">
-        <v>76950</v>
+        <v>94616</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12967,25 +12967,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1342</v>
+        <v>1080</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12995,10 +12995,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>428091</v>
+        <v>428079</v>
       </c>
       <c r="R117" t="n">
-        <v>6233385</v>
+        <v>6233262</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13057,10 +13057,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121471685</v>
+        <v>121471876</v>
       </c>
       <c r="B118" t="n">
-        <v>80257</v>
+        <v>80287</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13069,25 +13069,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1144</v>
+        <v>1223</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Rikfruktig blemlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Phlyctis agelaea</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Flot.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13097,10 +13097,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>428228</v>
+        <v>428446</v>
       </c>
       <c r="R118" t="n">
-        <v>6233391</v>
+        <v>6233151</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13127,12 +13127,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13159,10 +13159,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121471689</v>
+        <v>121471858</v>
       </c>
       <c r="B119" t="n">
-        <v>94606</v>
+        <v>80257</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13171,25 +13171,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13199,10 +13199,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>428161</v>
+        <v>428372</v>
       </c>
       <c r="R119" t="n">
-        <v>6233396</v>
+        <v>6233270</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13229,12 +13229,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13261,10 +13261,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121471878</v>
+        <v>121471935</v>
       </c>
       <c r="B120" t="n">
-        <v>96780</v>
+        <v>80244</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13277,21 +13277,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2604</v>
+        <v>230185</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13301,10 +13301,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>428445</v>
+        <v>428097</v>
       </c>
       <c r="R120" t="n">
-        <v>6233151</v>
+        <v>6233286</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13331,12 +13331,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13363,7 +13363,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121471543</v>
+        <v>121471828</v>
       </c>
       <c r="B121" t="n">
         <v>80244</v>
@@ -13403,10 +13403,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>428209</v>
+        <v>428185</v>
       </c>
       <c r="R121" t="n">
-        <v>6233279</v>
+        <v>6233289</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13433,12 +13433,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13447,6 +13447,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13465,10 +13466,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121471870</v>
+        <v>121471802</v>
       </c>
       <c r="B122" t="n">
-        <v>76950</v>
+        <v>94595</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13477,25 +13478,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1342</v>
+        <v>2671</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13505,10 +13506,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>428356</v>
+        <v>428332</v>
       </c>
       <c r="R122" t="n">
-        <v>6233243</v>
+        <v>6233287</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13567,10 +13568,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121471879</v>
+        <v>121471863</v>
       </c>
       <c r="B123" t="n">
-        <v>76950</v>
+        <v>96732</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13579,25 +13580,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13607,10 +13608,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>428445</v>
+        <v>428411</v>
       </c>
       <c r="R123" t="n">
-        <v>6233151</v>
+        <v>6233213</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13669,10 +13670,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121471940</v>
+        <v>121471915</v>
       </c>
       <c r="B124" t="n">
-        <v>94616</v>
+        <v>96780</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13685,21 +13686,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1080</v>
+        <v>2604</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13709,10 +13710,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>428037</v>
+        <v>428281</v>
       </c>
       <c r="R124" t="n">
-        <v>6233291</v>
+        <v>6233082</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13771,10 +13772,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121471873</v>
+        <v>121471943</v>
       </c>
       <c r="B125" t="n">
-        <v>74565</v>
+        <v>96732</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13783,25 +13784,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1116</v>
+        <v>2606</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13811,10 +13812,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>428301</v>
+        <v>428034</v>
       </c>
       <c r="R125" t="n">
-        <v>6233171</v>
+        <v>6233348</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13841,12 +13842,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13873,10 +13874,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121471686</v>
+        <v>121471909</v>
       </c>
       <c r="B126" t="n">
-        <v>80257</v>
+        <v>76950</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13885,25 +13886,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13913,10 +13914,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>428187</v>
+        <v>428373</v>
       </c>
       <c r="R126" t="n">
-        <v>6233403</v>
+        <v>6233088</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13943,12 +13944,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13975,10 +13976,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121471535</v>
+        <v>121471852</v>
       </c>
       <c r="B127" t="n">
-        <v>76950</v>
+        <v>80257</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13987,25 +13988,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14015,10 +14016,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>428160</v>
+        <v>428311</v>
       </c>
       <c r="R127" t="n">
-        <v>6233209</v>
+        <v>6233183</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14045,12 +14046,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14077,10 +14078,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121471914</v>
+        <v>121471541</v>
       </c>
       <c r="B128" t="n">
-        <v>94606</v>
+        <v>80244</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14093,21 +14094,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14117,10 +14118,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>428318</v>
+        <v>428209</v>
       </c>
       <c r="R128" t="n">
-        <v>6233075</v>
+        <v>6233184</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14147,12 +14148,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14179,10 +14180,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121471540</v>
+        <v>121471533</v>
       </c>
       <c r="B129" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14195,21 +14196,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14219,10 +14220,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>428227</v>
+        <v>428144</v>
       </c>
       <c r="R129" t="n">
-        <v>6233132</v>
+        <v>6233229</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14281,10 +14282,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121471896</v>
+        <v>121471843</v>
       </c>
       <c r="B130" t="n">
-        <v>80580</v>
+        <v>57372</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14297,21 +14298,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1182</v>
+        <v>100049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14321,10 +14322,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>428370</v>
+        <v>428252</v>
       </c>
       <c r="R130" t="n">
-        <v>6233102</v>
+        <v>6233262</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14351,12 +14352,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14383,10 +14384,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121471865</v>
+        <v>121471816</v>
       </c>
       <c r="B131" t="n">
-        <v>74701</v>
+        <v>96780</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14399,21 +14400,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>306</v>
+        <v>2604</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14423,10 +14424,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>428438</v>
+        <v>428317</v>
       </c>
       <c r="R131" t="n">
-        <v>6233202</v>
+        <v>6233324</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14485,10 +14486,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121471532</v>
+        <v>121471854</v>
       </c>
       <c r="B132" t="n">
-        <v>94606</v>
+        <v>96732</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14501,21 +14502,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14525,10 +14526,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>428133</v>
+        <v>428302</v>
       </c>
       <c r="R132" t="n">
-        <v>6233219</v>
+        <v>6233177</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14555,12 +14556,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14587,10 +14588,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121471684</v>
+        <v>121471835</v>
       </c>
       <c r="B133" t="n">
-        <v>80414</v>
+        <v>96732</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14599,25 +14600,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1557</v>
+        <v>2606</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Röd pysslinglav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Thelopsis rubella</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Nyl.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14627,10 +14628,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>428227</v>
+        <v>428145</v>
       </c>
       <c r="R133" t="n">
-        <v>6233392</v>
+        <v>6233244</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14657,12 +14658,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14689,10 +14690,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121471874</v>
+        <v>121471911</v>
       </c>
       <c r="B134" t="n">
-        <v>80257</v>
+        <v>76950</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14701,25 +14702,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14729,10 +14730,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>428375</v>
+        <v>428352</v>
       </c>
       <c r="R134" t="n">
-        <v>6233151</v>
+        <v>6233082</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14759,12 +14760,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14791,10 +14792,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121471683</v>
+        <v>121471531</v>
       </c>
       <c r="B135" t="n">
-        <v>94595</v>
+        <v>94616</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14807,21 +14808,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2671</v>
+        <v>1080</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14831,10 +14832,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>428278</v>
+        <v>428110</v>
       </c>
       <c r="R135" t="n">
-        <v>6233417</v>
+        <v>6233224</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14893,10 +14894,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121471933</v>
+        <v>121471870</v>
       </c>
       <c r="B136" t="n">
-        <v>94595</v>
+        <v>76950</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14905,25 +14906,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2671</v>
+        <v>1342</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14933,10 +14934,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>428090</v>
+        <v>428356</v>
       </c>
       <c r="R136" t="n">
-        <v>6233309</v>
+        <v>6233243</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14963,12 +14964,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14995,10 +14996,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121471868</v>
+        <v>121471690</v>
       </c>
       <c r="B137" t="n">
-        <v>94606</v>
+        <v>80244</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15011,21 +15012,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15035,10 +15036,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>428347</v>
+        <v>428161</v>
       </c>
       <c r="R137" t="n">
-        <v>6233241</v>
+        <v>6233396</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15065,12 +15066,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15097,7 +15098,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121471895</v>
+        <v>121471695</v>
       </c>
       <c r="B138" t="n">
         <v>80244</v>
@@ -15137,10 +15138,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>428355</v>
+        <v>428053</v>
       </c>
       <c r="R138" t="n">
-        <v>6233123</v>
+        <v>6233336</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15167,12 +15168,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15199,10 +15200,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121471847</v>
+        <v>121471684</v>
       </c>
       <c r="B139" t="n">
-        <v>76950</v>
+        <v>80414</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15211,25 +15212,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1342</v>
+        <v>1557</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Röd pysslinglav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelopsis rubella</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>Nyl.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15239,10 +15240,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>428300</v>
+        <v>428227</v>
       </c>
       <c r="R139" t="n">
-        <v>6233125</v>
+        <v>6233392</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15269,12 +15270,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15301,10 +15302,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121471820</v>
+        <v>121471939</v>
       </c>
       <c r="B140" t="n">
-        <v>94400</v>
+        <v>94606</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15317,21 +15318,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15341,10 +15342,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>428304</v>
+        <v>428046</v>
       </c>
       <c r="R140" t="n">
-        <v>6233306</v>
+        <v>6233296</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15371,12 +15372,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15403,10 +15404,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121471695</v>
+        <v>121471532</v>
       </c>
       <c r="B141" t="n">
-        <v>80244</v>
+        <v>94606</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15419,21 +15420,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15443,10 +15444,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>428053</v>
+        <v>428133</v>
       </c>
       <c r="R141" t="n">
-        <v>6233336</v>
+        <v>6233219</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15505,10 +15506,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121471533</v>
+        <v>121471869</v>
       </c>
       <c r="B142" t="n">
-        <v>80244</v>
+        <v>96732</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15521,21 +15522,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15545,10 +15546,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>428144</v>
+        <v>428354</v>
       </c>
       <c r="R142" t="n">
-        <v>6233229</v>
+        <v>6233242</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15575,12 +15576,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15607,10 +15608,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121471929</v>
+        <v>121471839</v>
       </c>
       <c r="B143" t="n">
-        <v>94400</v>
+        <v>94595</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15623,21 +15624,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15647,10 +15648,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>428078</v>
+        <v>428184</v>
       </c>
       <c r="R143" t="n">
-        <v>6233294</v>
+        <v>6233240</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15677,12 +15678,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15709,7 +15710,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121471810</v>
+        <v>121471923</v>
       </c>
       <c r="B144" t="n">
         <v>80257</v>
@@ -15749,10 +15750,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>428347</v>
+        <v>428091</v>
       </c>
       <c r="R144" t="n">
-        <v>6233326</v>
+        <v>6233386</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15779,12 +15780,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15811,10 +15812,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121471815</v>
+        <v>121471861</v>
       </c>
       <c r="B145" t="n">
-        <v>80414</v>
+        <v>94606</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15823,25 +15824,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1557</v>
+        <v>2667</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Röd pysslinglav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Thelopsis rubella</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Nyl.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15851,10 +15852,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>428333</v>
+        <v>428404</v>
       </c>
       <c r="R145" t="n">
-        <v>6233339</v>
+        <v>6233275</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15913,10 +15914,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121471852</v>
+        <v>121471916</v>
       </c>
       <c r="B146" t="n">
-        <v>80257</v>
+        <v>94616</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15925,25 +15926,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1144</v>
+        <v>1080</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15953,10 +15954,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>428311</v>
+        <v>428283</v>
       </c>
       <c r="R146" t="n">
-        <v>6233183</v>
+        <v>6233084</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15983,12 +15984,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16015,10 +16016,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121471799</v>
+        <v>121471806</v>
       </c>
       <c r="B147" t="n">
-        <v>94595</v>
+        <v>80257</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16027,25 +16028,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>2671</v>
+        <v>1144</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16055,10 +16056,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>428389</v>
+        <v>428325</v>
       </c>
       <c r="R147" t="n">
-        <v>6233324</v>
+        <v>6233291</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16117,10 +16118,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121471860</v>
+        <v>121471857</v>
       </c>
       <c r="B148" t="n">
-        <v>96732</v>
+        <v>80257</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16129,25 +16130,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16157,10 +16158,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>428404</v>
+        <v>428362</v>
       </c>
       <c r="R148" t="n">
-        <v>6233275</v>
+        <v>6233272</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16219,10 +16220,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121471850</v>
+        <v>121471824</v>
       </c>
       <c r="B149" t="n">
-        <v>80244</v>
+        <v>76950</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16231,25 +16232,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16259,10 +16260,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>428293</v>
+        <v>428288</v>
       </c>
       <c r="R149" t="n">
-        <v>6233170</v>
+        <v>6233325</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16321,10 +16322,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121471819</v>
+        <v>121471685</v>
       </c>
       <c r="B150" t="n">
-        <v>94606</v>
+        <v>80257</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16333,25 +16334,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16361,10 +16362,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>428304</v>
+        <v>428228</v>
       </c>
       <c r="R150" t="n">
-        <v>6233306</v>
+        <v>6233391</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16391,12 +16392,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16423,7 +16424,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121471904</v>
+        <v>121471897</v>
       </c>
       <c r="B151" t="n">
         <v>78409</v>
@@ -16463,10 +16464,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>428387</v>
+        <v>428369</v>
       </c>
       <c r="R151" t="n">
-        <v>6233098</v>
+        <v>6233104</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16525,10 +16526,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121471804</v>
+        <v>121471938</v>
       </c>
       <c r="B152" t="n">
-        <v>76950</v>
+        <v>80244</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16537,25 +16538,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16565,10 +16566,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>428335</v>
+        <v>428062</v>
       </c>
       <c r="R152" t="n">
-        <v>6233286</v>
+        <v>6233301</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16595,12 +16596,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16627,10 +16628,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121471536</v>
+        <v>121471530</v>
       </c>
       <c r="B153" t="n">
-        <v>80580</v>
+        <v>80244</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16639,25 +16640,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1182</v>
+        <v>230185</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16667,10 +16668,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>428166</v>
+        <v>428111</v>
       </c>
       <c r="R153" t="n">
-        <v>6233202</v>
+        <v>6233222</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16729,10 +16730,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121471822</v>
+        <v>121471865</v>
       </c>
       <c r="B154" t="n">
-        <v>94606</v>
+        <v>74701</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16745,21 +16746,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2667</v>
+        <v>306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16769,10 +16770,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>428288</v>
+        <v>428438</v>
       </c>
       <c r="R154" t="n">
-        <v>6233325</v>
+        <v>6233202</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16831,10 +16832,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121471835</v>
+        <v>121471929</v>
       </c>
       <c r="B155" t="n">
-        <v>96732</v>
+        <v>94400</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16847,21 +16848,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2606</v>
+        <v>2779</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16871,10 +16872,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>428145</v>
+        <v>428078</v>
       </c>
       <c r="R155" t="n">
-        <v>6233244</v>
+        <v>6233294</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16901,12 +16902,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16933,10 +16934,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121471545</v>
+        <v>121471925</v>
       </c>
       <c r="B156" t="n">
-        <v>80257</v>
+        <v>94608</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16945,25 +16946,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1144</v>
+        <v>2666</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16973,10 +16974,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>428172</v>
+        <v>428076</v>
       </c>
       <c r="R156" t="n">
-        <v>6233315</v>
+        <v>6233382</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17003,12 +17004,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17035,10 +17036,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121471845</v>
+        <v>121471944</v>
       </c>
       <c r="B157" t="n">
-        <v>80257</v>
+        <v>94606</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17047,25 +17048,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17075,10 +17076,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>428248</v>
+        <v>428034</v>
       </c>
       <c r="R157" t="n">
-        <v>6233242</v>
+        <v>6233348</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17105,12 +17106,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17137,10 +17138,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121471812</v>
+        <v>121471544</v>
       </c>
       <c r="B158" t="n">
-        <v>94400</v>
+        <v>94606</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17153,21 +17154,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17177,10 +17178,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>428331</v>
+        <v>428219</v>
       </c>
       <c r="R158" t="n">
-        <v>6233335</v>
+        <v>6233278</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17207,12 +17208,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17239,10 +17240,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121471828</v>
+        <v>121471902</v>
       </c>
       <c r="B159" t="n">
-        <v>80244</v>
+        <v>94595</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17255,21 +17256,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>230185</v>
+        <v>2671</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17279,10 +17280,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>428185</v>
+        <v>428387</v>
       </c>
       <c r="R159" t="n">
-        <v>6233289</v>
+        <v>6233096</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17309,12 +17310,12 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17323,7 +17324,6 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
-      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -17342,10 +17342,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121471913</v>
+        <v>121471796</v>
       </c>
       <c r="B160" t="n">
-        <v>76950</v>
+        <v>80257</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17354,25 +17354,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17382,10 +17382,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>428342</v>
+        <v>428390</v>
       </c>
       <c r="R160" t="n">
-        <v>6233082</v>
+        <v>6233312</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17412,12 +17412,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17444,10 +17444,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121471827</v>
+        <v>121471874</v>
       </c>
       <c r="B161" t="n">
-        <v>94606</v>
+        <v>80257</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17456,25 +17456,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17484,10 +17484,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>428185</v>
+        <v>428375</v>
       </c>
       <c r="R161" t="n">
-        <v>6233287</v>
+        <v>6233151</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17546,10 +17546,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121471934</v>
+        <v>121471811</v>
       </c>
       <c r="B162" t="n">
-        <v>94400</v>
+        <v>76950</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17558,25 +17558,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>2779</v>
+        <v>1342</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17586,10 +17586,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>428090</v>
+        <v>428349</v>
       </c>
       <c r="R162" t="n">
-        <v>6233309</v>
+        <v>6233325</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17616,12 +17616,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17648,10 +17648,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121471802</v>
+        <v>121471859</v>
       </c>
       <c r="B163" t="n">
-        <v>94595</v>
+        <v>80244</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17664,21 +17664,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>2671</v>
+        <v>230185</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17688,10 +17688,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>428332</v>
+        <v>428404</v>
       </c>
       <c r="R163" t="n">
-        <v>6233287</v>
+        <v>6233275</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17750,10 +17750,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121471840</v>
+        <v>121471818</v>
       </c>
       <c r="B164" t="n">
-        <v>78989</v>
+        <v>96732</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17766,21 +17766,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6431</v>
+        <v>2606</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17790,10 +17790,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>428183</v>
+        <v>428307</v>
       </c>
       <c r="R164" t="n">
-        <v>6233239</v>
+        <v>6233311</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17852,10 +17852,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121471814</v>
+        <v>121471689</v>
       </c>
       <c r="B165" t="n">
-        <v>80257</v>
+        <v>94606</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17864,25 +17864,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17892,10 +17892,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>428331</v>
+        <v>428161</v>
       </c>
       <c r="R165" t="n">
-        <v>6233339</v>
+        <v>6233396</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17922,12 +17922,12 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17954,7 +17954,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121471691</v>
+        <v>121471540</v>
       </c>
       <c r="B166" t="n">
         <v>96732</v>
@@ -17994,10 +17994,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>428128</v>
+        <v>428227</v>
       </c>
       <c r="R166" t="n">
-        <v>6233385</v>
+        <v>6233132</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18056,10 +18056,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121471912</v>
+        <v>121471937</v>
       </c>
       <c r="B167" t="n">
-        <v>78409</v>
+        <v>96732</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18068,25 +18068,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>924</v>
+        <v>2606</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18096,10 +18096,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>428351</v>
+        <v>428062</v>
       </c>
       <c r="R167" t="n">
-        <v>6233082</v>
+        <v>6233301</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18158,10 +18158,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121471857</v>
+        <v>121471942</v>
       </c>
       <c r="B168" t="n">
-        <v>80257</v>
+        <v>76950</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18170,25 +18170,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18198,10 +18198,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>428362</v>
+        <v>428032</v>
       </c>
       <c r="R168" t="n">
-        <v>6233272</v>
+        <v>6233345</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18228,12 +18228,12 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18260,10 +18260,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121471943</v>
+        <v>121471822</v>
       </c>
       <c r="B169" t="n">
-        <v>96732</v>
+        <v>94606</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -18276,21 +18276,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18300,10 +18300,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>428034</v>
+        <v>428288</v>
       </c>
       <c r="R169" t="n">
-        <v>6233348</v>
+        <v>6233325</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18330,12 +18330,12 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18362,10 +18362,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121471856</v>
+        <v>121471919</v>
       </c>
       <c r="B170" t="n">
-        <v>76950</v>
+        <v>80257</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18374,25 +18374,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18402,10 +18402,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>428360</v>
+        <v>428106</v>
       </c>
       <c r="R170" t="n">
-        <v>6233266</v>
+        <v>6233304</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18432,12 +18432,12 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18464,10 +18464,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121471813</v>
+        <v>121471535</v>
       </c>
       <c r="B171" t="n">
-        <v>94595</v>
+        <v>76950</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18476,25 +18476,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>2671</v>
+        <v>1342</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18504,10 +18504,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>428332</v>
+        <v>428160</v>
       </c>
       <c r="R171" t="n">
-        <v>6233341</v>
+        <v>6233209</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18534,12 +18534,12 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18566,10 +18566,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121471941</v>
+        <v>121471834</v>
       </c>
       <c r="B172" t="n">
-        <v>80244</v>
+        <v>80257</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18578,25 +18578,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18606,10 +18606,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>428046</v>
+        <v>428137</v>
       </c>
       <c r="R172" t="n">
-        <v>6233350</v>
+        <v>6233320</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18636,12 +18636,12 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18668,10 +18668,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121471834</v>
+        <v>121471930</v>
       </c>
       <c r="B173" t="n">
-        <v>80257</v>
+        <v>74611</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18680,25 +18680,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1144</v>
+        <v>1118</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18708,10 +18708,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>428137</v>
+        <v>428078</v>
       </c>
       <c r="R173" t="n">
-        <v>6233320</v>
+        <v>6233294</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18738,12 +18738,12 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18770,10 +18770,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121471824</v>
+        <v>121471912</v>
       </c>
       <c r="B174" t="n">
-        <v>76950</v>
+        <v>78409</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18786,21 +18786,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1342</v>
+        <v>924</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18810,10 +18810,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>428288</v>
+        <v>428351</v>
       </c>
       <c r="R174" t="n">
-        <v>6233325</v>
+        <v>6233082</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18840,12 +18840,12 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18872,10 +18872,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121471849</v>
+        <v>121471917</v>
       </c>
       <c r="B175" t="n">
-        <v>80257</v>
+        <v>80244</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18884,25 +18884,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18912,10 +18912,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>428299</v>
+        <v>428284</v>
       </c>
       <c r="R175" t="n">
-        <v>6233126</v>
+        <v>6233109</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18942,12 +18942,12 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD175" t="b">

--- a/artfynd/A 18989-2024 artfynd.xlsx
+++ b/artfynd/A 18989-2024 artfynd.xlsx
@@ -3354,10 +3354,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121471693</v>
+        <v>121471929</v>
       </c>
       <c r="B23" t="n">
-        <v>94595</v>
+        <v>94400</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3370,21 +3370,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>428125</v>
+        <v>428078</v>
       </c>
       <c r="R23" t="n">
-        <v>6233379</v>
+        <v>6233294</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3424,12 +3424,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3456,10 +3456,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121471877</v>
+        <v>121471816</v>
       </c>
       <c r="B24" t="n">
-        <v>94606</v>
+        <v>96780</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3472,21 +3472,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2667</v>
+        <v>2604</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>428445</v>
+        <v>428317</v>
       </c>
       <c r="R24" t="n">
-        <v>6233151</v>
+        <v>6233324</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121471845</v>
+        <v>121471863</v>
       </c>
       <c r="B25" t="n">
-        <v>80257</v>
+        <v>96732</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3570,25 +3570,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>428248</v>
+        <v>428411</v>
       </c>
       <c r="R25" t="n">
-        <v>6233242</v>
+        <v>6233213</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3660,10 +3660,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121471826</v>
+        <v>121471864</v>
       </c>
       <c r="B26" t="n">
-        <v>78865</v>
+        <v>94595</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3676,21 +3676,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6459</v>
+        <v>2671</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>428228</v>
+        <v>428410</v>
       </c>
       <c r="R26" t="n">
-        <v>6233340</v>
+        <v>6233214</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3762,10 +3762,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121471862</v>
+        <v>121471542</v>
       </c>
       <c r="B27" t="n">
-        <v>80244</v>
+        <v>80257</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3774,25 +3774,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>428411</v>
+        <v>428198</v>
       </c>
       <c r="R27" t="n">
-        <v>6233213</v>
+        <v>6233249</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3832,12 +3832,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3864,10 +3864,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121471873</v>
+        <v>121471867</v>
       </c>
       <c r="B28" t="n">
-        <v>74565</v>
+        <v>76950</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3880,21 +3880,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1116</v>
+        <v>1342</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>428301</v>
+        <v>428442</v>
       </c>
       <c r="R28" t="n">
-        <v>6233171</v>
+        <v>6233170</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121471853</v>
+        <v>121471814</v>
       </c>
       <c r="B29" t="n">
-        <v>76950</v>
+        <v>80257</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3978,25 +3978,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>428311</v>
+        <v>428331</v>
       </c>
       <c r="R29" t="n">
-        <v>6233183</v>
+        <v>6233339</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4068,50 +4068,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121471896</v>
+        <v>121471875</v>
       </c>
       <c r="B30" t="n">
-        <v>80580</v>
+        <v>80257</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1182</v>
+        <v>1144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>428370</v>
+        <v>428340</v>
       </c>
       <c r="R30" t="n">
-        <v>6233102</v>
+        <v>6233229</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4138,12 +4141,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>kollekt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4151,6 +4159,11 @@
       </c>
       <c r="AE30" t="b">
         <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG30" t="b">
         <v>0</v>
@@ -4170,10 +4183,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121471815</v>
+        <v>121471811</v>
       </c>
       <c r="B31" t="n">
-        <v>80414</v>
+        <v>76950</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4182,25 +4195,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1557</v>
+        <v>1342</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Röd pysslinglav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Thelopsis rubella</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Nyl.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4210,10 +4223,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>428333</v>
+        <v>428349</v>
       </c>
       <c r="R31" t="n">
-        <v>6233339</v>
+        <v>6233325</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4272,10 +4285,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121471798</v>
+        <v>121471684</v>
       </c>
       <c r="B32" t="n">
-        <v>96732</v>
+        <v>80414</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4284,25 +4297,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2606</v>
+        <v>1557</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Röd pysslinglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelopsis rubella</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Nyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4312,10 +4325,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>428387</v>
+        <v>428227</v>
       </c>
       <c r="R32" t="n">
-        <v>6233326</v>
+        <v>6233392</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4342,12 +4355,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4374,10 +4387,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121471688</v>
+        <v>121471804</v>
       </c>
       <c r="B33" t="n">
-        <v>96732</v>
+        <v>76950</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4386,25 +4399,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4414,10 +4427,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>428159</v>
+        <v>428335</v>
       </c>
       <c r="R33" t="n">
-        <v>6233394</v>
+        <v>6233286</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4444,12 +4457,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4476,10 +4489,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121471934</v>
+        <v>121471836</v>
       </c>
       <c r="B34" t="n">
-        <v>94400</v>
+        <v>94595</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4492,21 +4505,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4516,10 +4529,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>428090</v>
+        <v>428145</v>
       </c>
       <c r="R34" t="n">
-        <v>6233309</v>
+        <v>6233244</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4546,12 +4559,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4578,10 +4591,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121471819</v>
+        <v>121471935</v>
       </c>
       <c r="B35" t="n">
-        <v>94606</v>
+        <v>80244</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4594,21 +4607,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4618,10 +4631,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>428304</v>
+        <v>428097</v>
       </c>
       <c r="R35" t="n">
-        <v>6233306</v>
+        <v>6233286</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4648,12 +4661,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4680,10 +4693,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121471691</v>
+        <v>121471533</v>
       </c>
       <c r="B36" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4696,21 +4709,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4720,10 +4733,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>428128</v>
+        <v>428144</v>
       </c>
       <c r="R36" t="n">
-        <v>6233385</v>
+        <v>6233229</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4782,7 +4795,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121471833</v>
+        <v>121471837</v>
       </c>
       <c r="B37" t="n">
         <v>80244</v>
@@ -4822,10 +4835,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>428139</v>
+        <v>428145</v>
       </c>
       <c r="R37" t="n">
-        <v>6233315</v>
+        <v>6233244</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4884,10 +4897,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121471686</v>
+        <v>121471876</v>
       </c>
       <c r="B38" t="n">
-        <v>80257</v>
+        <v>80287</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4896,25 +4909,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1144</v>
+        <v>1223</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Rikfruktig blemlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Phlyctis agelaea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Flot.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4924,10 +4937,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>428187</v>
+        <v>428446</v>
       </c>
       <c r="R38" t="n">
-        <v>6233403</v>
+        <v>6233151</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4954,12 +4967,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4986,10 +4999,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121471814</v>
+        <v>121471916</v>
       </c>
       <c r="B39" t="n">
-        <v>80257</v>
+        <v>94616</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4998,25 +5011,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1144</v>
+        <v>1080</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5026,10 +5039,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>428331</v>
+        <v>428283</v>
       </c>
       <c r="R39" t="n">
-        <v>6233339</v>
+        <v>6233084</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5056,12 +5069,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5088,10 +5101,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121471692</v>
+        <v>121471531</v>
       </c>
       <c r="B40" t="n">
-        <v>94606</v>
+        <v>94616</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5104,21 +5117,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2667</v>
+        <v>1080</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5128,10 +5141,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>428126</v>
+        <v>428110</v>
       </c>
       <c r="R40" t="n">
-        <v>6233380</v>
+        <v>6233224</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5190,10 +5203,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121471878</v>
+        <v>121471930</v>
       </c>
       <c r="B41" t="n">
-        <v>96780</v>
+        <v>74611</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5202,25 +5215,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2604</v>
+        <v>1118</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5230,10 +5243,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>428445</v>
+        <v>428078</v>
       </c>
       <c r="R41" t="n">
-        <v>6233151</v>
+        <v>6233294</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5260,12 +5273,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5292,10 +5305,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121471827</v>
+        <v>121471879</v>
       </c>
       <c r="B42" t="n">
-        <v>94606</v>
+        <v>76950</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5304,25 +5317,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5332,10 +5345,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>428185</v>
+        <v>428445</v>
       </c>
       <c r="R42" t="n">
-        <v>6233287</v>
+        <v>6233151</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5394,10 +5407,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121471539</v>
+        <v>121471694</v>
       </c>
       <c r="B43" t="n">
-        <v>94595</v>
+        <v>80257</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5406,25 +5419,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2671</v>
+        <v>1144</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5434,10 +5447,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>428262</v>
+        <v>428125</v>
       </c>
       <c r="R43" t="n">
-        <v>6233134</v>
+        <v>6233379</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5496,10 +5509,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121471860</v>
+        <v>121471840</v>
       </c>
       <c r="B44" t="n">
-        <v>96732</v>
+        <v>78989</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5512,21 +5525,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2606</v>
+        <v>6431</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5536,10 +5549,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>428404</v>
+        <v>428183</v>
       </c>
       <c r="R44" t="n">
-        <v>6233275</v>
+        <v>6233239</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5598,10 +5611,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121471945</v>
+        <v>121471936</v>
       </c>
       <c r="B45" t="n">
-        <v>96780</v>
+        <v>94616</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5614,21 +5627,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2604</v>
+        <v>1080</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5638,10 +5651,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>428035</v>
+        <v>428079</v>
       </c>
       <c r="R45" t="n">
-        <v>6233349</v>
+        <v>6233262</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5700,10 +5713,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121471534</v>
+        <v>121471912</v>
       </c>
       <c r="B46" t="n">
-        <v>96732</v>
+        <v>78409</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5712,25 +5725,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2606</v>
+        <v>924</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5740,10 +5753,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>428147</v>
+        <v>428351</v>
       </c>
       <c r="R46" t="n">
-        <v>6233224</v>
+        <v>6233082</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5770,12 +5783,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5802,10 +5815,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121471931</v>
+        <v>121471807</v>
       </c>
       <c r="B47" t="n">
-        <v>80257</v>
+        <v>76950</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5814,25 +5827,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5842,10 +5855,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>428075</v>
+        <v>428327</v>
       </c>
       <c r="R47" t="n">
-        <v>6233301</v>
+        <v>6233292</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5872,12 +5885,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5904,10 +5917,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121471849</v>
+        <v>121471693</v>
       </c>
       <c r="B48" t="n">
-        <v>80257</v>
+        <v>94595</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5916,25 +5929,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1144</v>
+        <v>2671</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5944,10 +5957,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>428299</v>
+        <v>428125</v>
       </c>
       <c r="R48" t="n">
-        <v>6233126</v>
+        <v>6233379</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5974,12 +5987,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6006,10 +6019,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121471879</v>
+        <v>121471926</v>
       </c>
       <c r="B49" t="n">
-        <v>76950</v>
+        <v>94400</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6018,25 +6031,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1342</v>
+        <v>2779</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6046,10 +6059,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>428445</v>
+        <v>428073</v>
       </c>
       <c r="R49" t="n">
-        <v>6233151</v>
+        <v>6233383</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6076,12 +6089,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6108,53 +6121,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121471875</v>
+        <v>121471902</v>
       </c>
       <c r="B50" t="n">
-        <v>80257</v>
+        <v>94595</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1144</v>
+        <v>2671</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>428340</v>
+        <v>428387</v>
       </c>
       <c r="R50" t="n">
-        <v>6233229</v>
+        <v>6233096</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6181,17 +6191,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>kollekt</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6199,11 +6204,6 @@
       </c>
       <c r="AE50" t="b">
         <v>0</v>
-      </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG50" t="b">
         <v>0</v>
@@ -6223,10 +6223,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121471840</v>
+        <v>121471868</v>
       </c>
       <c r="B51" t="n">
-        <v>78989</v>
+        <v>94606</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6239,21 +6239,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6431</v>
+        <v>2667</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6263,10 +6263,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>428183</v>
+        <v>428347</v>
       </c>
       <c r="R51" t="n">
-        <v>6233239</v>
+        <v>6233241</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6325,10 +6325,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121471941</v>
+        <v>121471842</v>
       </c>
       <c r="B52" t="n">
-        <v>80244</v>
+        <v>94606</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6341,21 +6341,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6365,10 +6365,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>428046</v>
+        <v>428221</v>
       </c>
       <c r="R52" t="n">
-        <v>6233350</v>
+        <v>6233212</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6395,12 +6395,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6427,10 +6427,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121471538</v>
+        <v>121471873</v>
       </c>
       <c r="B53" t="n">
-        <v>80244</v>
+        <v>74565</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6439,25 +6439,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>230185</v>
+        <v>1116</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6467,10 +6467,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>428166</v>
+        <v>428301</v>
       </c>
       <c r="R53" t="n">
-        <v>6233198</v>
+        <v>6233171</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6497,12 +6497,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6529,10 +6529,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121471871</v>
+        <v>121471919</v>
       </c>
       <c r="B54" t="n">
-        <v>80244</v>
+        <v>80257</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6541,25 +6541,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6569,10 +6569,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>428302</v>
+        <v>428106</v>
       </c>
       <c r="R54" t="n">
-        <v>6233176</v>
+        <v>6233304</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6599,12 +6599,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6631,10 +6631,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121471924</v>
+        <v>121471907</v>
       </c>
       <c r="B55" t="n">
-        <v>80244</v>
+        <v>76950</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6643,25 +6643,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6671,10 +6671,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>428097</v>
+        <v>428375</v>
       </c>
       <c r="R55" t="n">
-        <v>6233382</v>
+        <v>6233092</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6733,7 +6733,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121471825</v>
+        <v>121471871</v>
       </c>
       <c r="B56" t="n">
         <v>80244</v>
@@ -6773,10 +6773,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>428233</v>
+        <v>428302</v>
       </c>
       <c r="R56" t="n">
-        <v>6233332</v>
+        <v>6233176</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6835,7 +6835,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121471543</v>
+        <v>121471924</v>
       </c>
       <c r="B57" t="n">
         <v>80244</v>
@@ -6875,10 +6875,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>428209</v>
+        <v>428097</v>
       </c>
       <c r="R57" t="n">
-        <v>6233279</v>
+        <v>6233382</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6905,12 +6905,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6937,10 +6937,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121471933</v>
+        <v>121471844</v>
       </c>
       <c r="B58" t="n">
-        <v>94595</v>
+        <v>76950</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6949,25 +6949,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2671</v>
+        <v>1342</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6977,10 +6977,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>428090</v>
+        <v>428248</v>
       </c>
       <c r="R58" t="n">
-        <v>6233309</v>
+        <v>6233241</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7039,10 +7039,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121471542</v>
+        <v>121471824</v>
       </c>
       <c r="B59" t="n">
-        <v>80257</v>
+        <v>76950</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7051,25 +7051,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7079,10 +7079,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>428198</v>
+        <v>428288</v>
       </c>
       <c r="R59" t="n">
-        <v>6233249</v>
+        <v>6233325</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7109,12 +7109,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7141,10 +7141,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121471910</v>
+        <v>121471826</v>
       </c>
       <c r="B60" t="n">
-        <v>76950</v>
+        <v>78865</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7153,25 +7153,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1342</v>
+        <v>6459</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7181,10 +7181,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>428377</v>
+        <v>428228</v>
       </c>
       <c r="R60" t="n">
-        <v>6233090</v>
+        <v>6233340</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7211,12 +7211,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7243,10 +7243,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121471829</v>
+        <v>121471911</v>
       </c>
       <c r="B61" t="n">
-        <v>80257</v>
+        <v>76950</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7255,25 +7255,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7283,10 +7283,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>428147</v>
+        <v>428352</v>
       </c>
       <c r="R61" t="n">
-        <v>6233304</v>
+        <v>6233082</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7313,12 +7313,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7345,10 +7345,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121471697</v>
+        <v>121471901</v>
       </c>
       <c r="B62" t="n">
-        <v>74701</v>
+        <v>76950</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7357,25 +7357,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>306</v>
+        <v>1342</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>428043</v>
+        <v>428390</v>
       </c>
       <c r="R62" t="n">
-        <v>6233298</v>
+        <v>6233099</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7415,12 +7415,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7447,10 +7447,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121471855</v>
+        <v>121471905</v>
       </c>
       <c r="B63" t="n">
-        <v>94400</v>
+        <v>74611</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7459,25 +7459,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2779</v>
+        <v>1118</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7487,10 +7487,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>428365</v>
+        <v>428377</v>
       </c>
       <c r="R63" t="n">
-        <v>6233269</v>
+        <v>6233095</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7517,12 +7517,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7549,10 +7549,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121471810</v>
+        <v>121471695</v>
       </c>
       <c r="B64" t="n">
-        <v>80257</v>
+        <v>80244</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7561,25 +7561,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7589,10 +7589,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>428347</v>
+        <v>428053</v>
       </c>
       <c r="R64" t="n">
-        <v>6233326</v>
+        <v>6233336</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7619,12 +7619,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7651,10 +7651,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121471694</v>
+        <v>121471530</v>
       </c>
       <c r="B65" t="n">
-        <v>80257</v>
+        <v>80244</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7663,25 +7663,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7691,10 +7691,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>428125</v>
+        <v>428111</v>
       </c>
       <c r="R65" t="n">
-        <v>6233379</v>
+        <v>6233222</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7753,10 +7753,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121471831</v>
+        <v>121471862</v>
       </c>
       <c r="B66" t="n">
-        <v>80257</v>
+        <v>80244</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7765,25 +7765,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7793,10 +7793,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>428145</v>
+        <v>428411</v>
       </c>
       <c r="R66" t="n">
-        <v>6233315</v>
+        <v>6233213</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7855,10 +7855,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121471907</v>
+        <v>121471697</v>
       </c>
       <c r="B67" t="n">
-        <v>76950</v>
+        <v>74701</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7867,25 +7867,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1342</v>
+        <v>306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7895,10 +7895,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>428375</v>
+        <v>428043</v>
       </c>
       <c r="R67" t="n">
-        <v>6233092</v>
+        <v>6233298</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7925,12 +7925,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7957,10 +7957,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121471807</v>
+        <v>121471882</v>
       </c>
       <c r="B68" t="n">
-        <v>76950</v>
+        <v>74611</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7973,21 +7973,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1342</v>
+        <v>1118</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7997,10 +7997,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>428327</v>
+        <v>428445</v>
       </c>
       <c r="R68" t="n">
-        <v>6233292</v>
+        <v>6233151</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8059,10 +8059,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121471844</v>
+        <v>121471796</v>
       </c>
       <c r="B69" t="n">
-        <v>76950</v>
+        <v>80257</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8071,25 +8071,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8099,10 +8099,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>428248</v>
+        <v>428390</v>
       </c>
       <c r="R69" t="n">
-        <v>6233241</v>
+        <v>6233312</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8161,10 +8161,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121471801</v>
+        <v>121471922</v>
       </c>
       <c r="B70" t="n">
-        <v>80257</v>
+        <v>76950</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8173,25 +8173,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>428370</v>
+        <v>428091</v>
       </c>
       <c r="R70" t="n">
-        <v>6233336</v>
+        <v>6233385</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8231,12 +8231,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8263,10 +8263,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121471805</v>
+        <v>121471536</v>
       </c>
       <c r="B71" t="n">
-        <v>80257</v>
+        <v>80580</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8275,25 +8275,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1144</v>
+        <v>1182</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>428333</v>
+        <v>428166</v>
       </c>
       <c r="R71" t="n">
-        <v>6233283</v>
+        <v>6233202</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8333,12 +8333,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8365,10 +8365,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121471922</v>
+        <v>121471896</v>
       </c>
       <c r="B72" t="n">
-        <v>76950</v>
+        <v>80580</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8381,21 +8381,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1342</v>
+        <v>1182</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>428091</v>
+        <v>428370</v>
       </c>
       <c r="R72" t="n">
-        <v>6233385</v>
+        <v>6233102</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8467,10 +8467,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121471846</v>
+        <v>121471692</v>
       </c>
       <c r="B73" t="n">
-        <v>80244</v>
+        <v>94606</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8483,21 +8483,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8507,10 +8507,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>428241</v>
+        <v>428126</v>
       </c>
       <c r="R73" t="n">
-        <v>6233222</v>
+        <v>6233380</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8537,12 +8537,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8569,10 +8569,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121471803</v>
+        <v>121471878</v>
       </c>
       <c r="B74" t="n">
-        <v>80257</v>
+        <v>96780</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8581,25 +8581,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1144</v>
+        <v>2604</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8609,10 +8609,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>428334</v>
+        <v>428445</v>
       </c>
       <c r="R74" t="n">
-        <v>6233284</v>
+        <v>6233151</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8671,10 +8671,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121471545</v>
+        <v>121471798</v>
       </c>
       <c r="B75" t="n">
-        <v>80257</v>
+        <v>96732</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8683,25 +8683,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8711,10 +8711,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>428172</v>
+        <v>428387</v>
       </c>
       <c r="R75" t="n">
-        <v>6233315</v>
+        <v>6233326</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8741,12 +8741,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8773,10 +8773,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121471913</v>
+        <v>121471540</v>
       </c>
       <c r="B76" t="n">
-        <v>76950</v>
+        <v>96732</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8785,25 +8785,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8813,10 +8813,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>428342</v>
+        <v>428227</v>
       </c>
       <c r="R76" t="n">
-        <v>6233082</v>
+        <v>6233132</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8843,12 +8843,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8875,10 +8875,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121471903</v>
+        <v>121471850</v>
       </c>
       <c r="B77" t="n">
-        <v>76950</v>
+        <v>80244</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8887,25 +8887,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8915,10 +8915,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>428385</v>
+        <v>428293</v>
       </c>
       <c r="R77" t="n">
-        <v>6233097</v>
+        <v>6233170</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8945,12 +8945,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8977,7 +8977,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121471850</v>
+        <v>121471690</v>
       </c>
       <c r="B78" t="n">
         <v>80244</v>
@@ -9017,10 +9017,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>428293</v>
+        <v>428161</v>
       </c>
       <c r="R78" t="n">
-        <v>6233170</v>
+        <v>6233396</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9047,12 +9047,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9079,10 +9079,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121471926</v>
+        <v>121471843</v>
       </c>
       <c r="B79" t="n">
-        <v>94400</v>
+        <v>57372</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9091,25 +9091,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2779</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9119,10 +9119,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>428073</v>
+        <v>428252</v>
       </c>
       <c r="R79" t="n">
-        <v>6233383</v>
+        <v>6233262</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9181,10 +9181,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121471820</v>
+        <v>121471903</v>
       </c>
       <c r="B80" t="n">
-        <v>94400</v>
+        <v>76950</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9193,25 +9193,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2779</v>
+        <v>1342</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9221,10 +9221,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>428304</v>
+        <v>428385</v>
       </c>
       <c r="R80" t="n">
-        <v>6233306</v>
+        <v>6233097</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9251,12 +9251,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9283,10 +9283,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121471914</v>
+        <v>121471937</v>
       </c>
       <c r="B81" t="n">
-        <v>94606</v>
+        <v>96732</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9299,21 +9299,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9323,10 +9323,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>428318</v>
+        <v>428062</v>
       </c>
       <c r="R81" t="n">
-        <v>6233075</v>
+        <v>6233301</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9385,10 +9385,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121471800</v>
+        <v>121471865</v>
       </c>
       <c r="B82" t="n">
-        <v>80257</v>
+        <v>74701</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9397,25 +9397,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1144</v>
+        <v>306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9425,10 +9425,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>428387</v>
+        <v>428438</v>
       </c>
       <c r="R82" t="n">
-        <v>6233322</v>
+        <v>6233202</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9487,10 +9487,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121471847</v>
+        <v>121471686</v>
       </c>
       <c r="B83" t="n">
-        <v>76950</v>
+        <v>80257</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9499,25 +9499,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>428300</v>
+        <v>428187</v>
       </c>
       <c r="R83" t="n">
-        <v>6233125</v>
+        <v>6233403</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9557,12 +9557,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9589,10 +9589,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121471851</v>
+        <v>121471909</v>
       </c>
       <c r="B84" t="n">
-        <v>78865</v>
+        <v>76950</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9601,25 +9601,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6459</v>
+        <v>1342</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9629,10 +9629,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>428293</v>
+        <v>428373</v>
       </c>
       <c r="R84" t="n">
-        <v>6233170</v>
+        <v>6233088</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9659,12 +9659,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9691,10 +9691,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121471799</v>
+        <v>121471853</v>
       </c>
       <c r="B85" t="n">
-        <v>94595</v>
+        <v>76950</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9703,25 +9703,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2671</v>
+        <v>1342</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9731,10 +9731,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>428389</v>
+        <v>428311</v>
       </c>
       <c r="R85" t="n">
-        <v>6233324</v>
+        <v>6233183</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9793,10 +9793,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121471928</v>
+        <v>121471940</v>
       </c>
       <c r="B86" t="n">
-        <v>80257</v>
+        <v>94616</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9805,25 +9805,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1144</v>
+        <v>1080</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>428075</v>
+        <v>428037</v>
       </c>
       <c r="R86" t="n">
-        <v>6233294</v>
+        <v>6233291</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9895,10 +9895,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121471536</v>
+        <v>121471923</v>
       </c>
       <c r="B87" t="n">
-        <v>80580</v>
+        <v>80257</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9907,25 +9907,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1182</v>
+        <v>1144</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9935,10 +9935,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>428166</v>
+        <v>428091</v>
       </c>
       <c r="R87" t="n">
-        <v>6233202</v>
+        <v>6233386</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9965,12 +9965,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9997,10 +9997,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121471899</v>
+        <v>121471799</v>
       </c>
       <c r="B88" t="n">
-        <v>94400</v>
+        <v>94595</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10013,21 +10013,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10040,7 +10040,7 @@
         <v>428389</v>
       </c>
       <c r="R88" t="n">
-        <v>6233099</v>
+        <v>6233324</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10067,12 +10067,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10099,10 +10099,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121471881</v>
+        <v>121471869</v>
       </c>
       <c r="B89" t="n">
-        <v>78409</v>
+        <v>96732</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10111,25 +10111,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>924</v>
+        <v>2606</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10139,10 +10139,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>428445</v>
+        <v>428354</v>
       </c>
       <c r="R89" t="n">
-        <v>6233151</v>
+        <v>6233242</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10201,10 +10201,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121471837</v>
+        <v>121471841</v>
       </c>
       <c r="B90" t="n">
-        <v>80244</v>
+        <v>96732</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10217,21 +10217,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10241,10 +10241,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>428145</v>
+        <v>428221</v>
       </c>
       <c r="R90" t="n">
-        <v>6233244</v>
+        <v>6233212</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10303,10 +10303,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121471895</v>
+        <v>121471943</v>
       </c>
       <c r="B91" t="n">
-        <v>80244</v>
+        <v>96732</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10319,21 +10319,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10343,10 +10343,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>428355</v>
+        <v>428034</v>
       </c>
       <c r="R91" t="n">
-        <v>6233123</v>
+        <v>6233348</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10405,10 +10405,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121471808</v>
+        <v>121471855</v>
       </c>
       <c r="B92" t="n">
-        <v>80257</v>
+        <v>94400</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10417,25 +10417,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1144</v>
+        <v>2779</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10445,10 +10445,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>428350</v>
+        <v>428365</v>
       </c>
       <c r="R92" t="n">
-        <v>6233316</v>
+        <v>6233269</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10507,10 +10507,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121471867</v>
+        <v>121471541</v>
       </c>
       <c r="B93" t="n">
-        <v>76950</v>
+        <v>80244</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10519,25 +10519,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10547,10 +10547,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>428442</v>
+        <v>428209</v>
       </c>
       <c r="R93" t="n">
-        <v>6233170</v>
+        <v>6233184</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10577,12 +10577,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10609,10 +10609,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121471940</v>
+        <v>121471938</v>
       </c>
       <c r="B94" t="n">
-        <v>94616</v>
+        <v>80244</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10625,21 +10625,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1080</v>
+        <v>230185</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10649,10 +10649,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>428037</v>
+        <v>428062</v>
       </c>
       <c r="R94" t="n">
-        <v>6233291</v>
+        <v>6233301</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10711,10 +10711,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121471809</v>
+        <v>121471858</v>
       </c>
       <c r="B95" t="n">
-        <v>74565</v>
+        <v>80257</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10723,25 +10723,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1116</v>
+        <v>1144</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10751,10 +10751,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>428352</v>
+        <v>428372</v>
       </c>
       <c r="R95" t="n">
-        <v>6233315</v>
+        <v>6233270</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10813,10 +10813,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121471804</v>
+        <v>121471685</v>
       </c>
       <c r="B96" t="n">
-        <v>76950</v>
+        <v>80257</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10825,25 +10825,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10853,10 +10853,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>428335</v>
+        <v>428228</v>
       </c>
       <c r="R96" t="n">
-        <v>6233286</v>
+        <v>6233391</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10883,12 +10883,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10915,10 +10915,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121471812</v>
+        <v>121471833</v>
       </c>
       <c r="B97" t="n">
-        <v>94400</v>
+        <v>80244</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10931,21 +10931,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2779</v>
+        <v>230185</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10955,10 +10955,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>428331</v>
+        <v>428139</v>
       </c>
       <c r="R97" t="n">
-        <v>6233335</v>
+        <v>6233315</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11017,10 +11017,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121471841</v>
+        <v>121471895</v>
       </c>
       <c r="B98" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11033,21 +11033,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11057,10 +11057,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>428221</v>
+        <v>428355</v>
       </c>
       <c r="R98" t="n">
-        <v>6233212</v>
+        <v>6233123</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11119,10 +11119,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121471817</v>
+        <v>121471857</v>
       </c>
       <c r="B99" t="n">
-        <v>74699</v>
+        <v>80257</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11131,25 +11131,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6439</v>
+        <v>1144</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11159,10 +11159,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>428312</v>
+        <v>428362</v>
       </c>
       <c r="R99" t="n">
-        <v>6233323</v>
+        <v>6233272</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11221,10 +11221,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121471866</v>
+        <v>121471535</v>
       </c>
       <c r="B100" t="n">
-        <v>80244</v>
+        <v>76950</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11233,25 +11233,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11261,10 +11261,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>428442</v>
+        <v>428160</v>
       </c>
       <c r="R100" t="n">
-        <v>6233170</v>
+        <v>6233209</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11291,12 +11291,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11323,10 +11323,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121471927</v>
+        <v>121471829</v>
       </c>
       <c r="B101" t="n">
-        <v>76950</v>
+        <v>80257</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11335,25 +11335,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11363,10 +11363,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>428074</v>
+        <v>428147</v>
       </c>
       <c r="R101" t="n">
-        <v>6233297</v>
+        <v>6233304</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11393,12 +11393,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11425,7 +11425,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121471696</v>
+        <v>121471818</v>
       </c>
       <c r="B102" t="n">
         <v>96732</v>
@@ -11465,10 +11465,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>428054</v>
+        <v>428307</v>
       </c>
       <c r="R102" t="n">
-        <v>6233337</v>
+        <v>6233311</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11495,12 +11495,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11527,7 +11527,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121471868</v>
+        <v>121471877</v>
       </c>
       <c r="B103" t="n">
         <v>94606</v>
@@ -11567,10 +11567,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>428347</v>
+        <v>428445</v>
       </c>
       <c r="R103" t="n">
-        <v>6233241</v>
+        <v>6233151</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11629,10 +11629,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121471856</v>
+        <v>121471689</v>
       </c>
       <c r="B104" t="n">
-        <v>76950</v>
+        <v>94606</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11641,25 +11641,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1342</v>
+        <v>2667</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11669,10 +11669,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>428360</v>
+        <v>428161</v>
       </c>
       <c r="R104" t="n">
-        <v>6233266</v>
+        <v>6233396</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11699,12 +11699,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11731,10 +11731,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121471901</v>
+        <v>121471537</v>
       </c>
       <c r="B105" t="n">
-        <v>76950</v>
+        <v>96732</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11743,25 +11743,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11771,10 +11771,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>428390</v>
+        <v>428163</v>
       </c>
       <c r="R105" t="n">
-        <v>6233099</v>
+        <v>6233193</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11801,12 +11801,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11833,10 +11833,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121471813</v>
+        <v>121471866</v>
       </c>
       <c r="B106" t="n">
-        <v>94595</v>
+        <v>80244</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11849,21 +11849,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2671</v>
+        <v>230185</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11873,10 +11873,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>428332</v>
+        <v>428442</v>
       </c>
       <c r="R106" t="n">
-        <v>6233341</v>
+        <v>6233170</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11935,10 +11935,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121471683</v>
+        <v>121471543</v>
       </c>
       <c r="B107" t="n">
-        <v>94595</v>
+        <v>80244</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11951,21 +11951,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2671</v>
+        <v>230185</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11975,10 +11975,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>428278</v>
+        <v>428209</v>
       </c>
       <c r="R107" t="n">
-        <v>6233417</v>
+        <v>6233279</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12037,10 +12037,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121471537</v>
+        <v>121471856</v>
       </c>
       <c r="B108" t="n">
-        <v>96732</v>
+        <v>76950</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12049,25 +12049,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12077,10 +12077,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>428163</v>
+        <v>428360</v>
       </c>
       <c r="R108" t="n">
-        <v>6233193</v>
+        <v>6233266</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12107,12 +12107,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12139,10 +12139,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121471842</v>
+        <v>121471800</v>
       </c>
       <c r="B109" t="n">
-        <v>94606</v>
+        <v>80257</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12151,25 +12151,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12179,10 +12179,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>428221</v>
+        <v>428387</v>
       </c>
       <c r="R109" t="n">
-        <v>6233212</v>
+        <v>6233322</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12241,10 +12241,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121471882</v>
+        <v>121471815</v>
       </c>
       <c r="B110" t="n">
-        <v>74611</v>
+        <v>80414</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12253,25 +12253,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1118</v>
+        <v>1557</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Röd pysslinglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Thelopsis rubella</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>Nyl.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12281,10 +12281,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>428445</v>
+        <v>428333</v>
       </c>
       <c r="R110" t="n">
-        <v>6233151</v>
+        <v>6233339</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12343,10 +12343,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121471904</v>
+        <v>121471927</v>
       </c>
       <c r="B111" t="n">
-        <v>78409</v>
+        <v>76950</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12359,21 +12359,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>924</v>
+        <v>1342</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12383,10 +12383,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>428387</v>
+        <v>428074</v>
       </c>
       <c r="R111" t="n">
-        <v>6233098</v>
+        <v>6233297</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12445,10 +12445,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121471920</v>
+        <v>121471852</v>
       </c>
       <c r="B112" t="n">
-        <v>91119</v>
+        <v>80257</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12457,25 +12457,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2023</v>
+        <v>1144</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sydlig sotticka</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ischnoderma resinosum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Schrad.) P.Karst.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12485,10 +12485,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>428095</v>
+        <v>428311</v>
       </c>
       <c r="R112" t="n">
-        <v>6233349</v>
+        <v>6233183</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12515,12 +12515,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12547,10 +12547,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121471908</v>
+        <v>121471845</v>
       </c>
       <c r="B113" t="n">
-        <v>74611</v>
+        <v>80257</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12559,25 +12559,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1118</v>
+        <v>1144</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12587,10 +12587,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>428377</v>
+        <v>428248</v>
       </c>
       <c r="R113" t="n">
-        <v>6233090</v>
+        <v>6233242</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12617,12 +12617,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12649,10 +12649,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121471905</v>
+        <v>121471939</v>
       </c>
       <c r="B114" t="n">
-        <v>74611</v>
+        <v>94606</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12661,25 +12661,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1118</v>
+        <v>2667</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Stiftklotterlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Opegrapha vermicellifera</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Kunze) J.R.Laundon</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12689,10 +12689,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>428377</v>
+        <v>428046</v>
       </c>
       <c r="R114" t="n">
-        <v>6233095</v>
+        <v>6233296</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12751,7 +12751,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121471836</v>
+        <v>121471539</v>
       </c>
       <c r="B115" t="n">
         <v>94595</v>
@@ -12791,10 +12791,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>428145</v>
+        <v>428262</v>
       </c>
       <c r="R115" t="n">
-        <v>6233244</v>
+        <v>6233134</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12821,12 +12821,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12853,10 +12853,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121471864</v>
+        <v>121471914</v>
       </c>
       <c r="B116" t="n">
-        <v>94595</v>
+        <v>94606</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12869,21 +12869,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12893,10 +12893,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>428410</v>
+        <v>428318</v>
       </c>
       <c r="R116" t="n">
-        <v>6233214</v>
+        <v>6233075</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12923,12 +12923,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12955,10 +12955,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121471936</v>
+        <v>121471854</v>
       </c>
       <c r="B117" t="n">
-        <v>94616</v>
+        <v>96732</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12971,21 +12971,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1080</v>
+        <v>2606</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12995,10 +12995,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>428079</v>
+        <v>428302</v>
       </c>
       <c r="R117" t="n">
-        <v>6233262</v>
+        <v>6233177</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13025,12 +13025,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13057,10 +13057,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121471876</v>
+        <v>121471941</v>
       </c>
       <c r="B118" t="n">
-        <v>80287</v>
+        <v>80244</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13073,21 +13073,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1223</v>
+        <v>230185</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rikfruktig blemlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phlyctis agelaea</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Flot.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13097,10 +13097,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>428446</v>
+        <v>428046</v>
       </c>
       <c r="R118" t="n">
-        <v>6233151</v>
+        <v>6233350</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13127,12 +13127,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13159,7 +13159,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121471858</v>
+        <v>121471803</v>
       </c>
       <c r="B119" t="n">
         <v>80257</v>
@@ -13199,10 +13199,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>428372</v>
+        <v>428334</v>
       </c>
       <c r="R119" t="n">
-        <v>6233270</v>
+        <v>6233284</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13261,10 +13261,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121471935</v>
+        <v>121471908</v>
       </c>
       <c r="B120" t="n">
-        <v>80244</v>
+        <v>74611</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13273,25 +13273,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>230185</v>
+        <v>1118</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13301,10 +13301,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>428097</v>
+        <v>428377</v>
       </c>
       <c r="R120" t="n">
-        <v>6233286</v>
+        <v>6233090</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13363,10 +13363,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121471828</v>
+        <v>121471897</v>
       </c>
       <c r="B121" t="n">
-        <v>80244</v>
+        <v>78409</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13375,25 +13375,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>230185</v>
+        <v>924</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13403,10 +13403,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>428185</v>
+        <v>428369</v>
       </c>
       <c r="R121" t="n">
-        <v>6233289</v>
+        <v>6233104</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13433,12 +13433,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13447,7 +13447,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13466,10 +13465,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121471802</v>
+        <v>121471913</v>
       </c>
       <c r="B122" t="n">
-        <v>94595</v>
+        <v>76950</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13478,25 +13477,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2671</v>
+        <v>1342</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13506,10 +13505,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>428332</v>
+        <v>428342</v>
       </c>
       <c r="R122" t="n">
-        <v>6233287</v>
+        <v>6233082</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13536,12 +13535,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13568,7 +13567,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121471863</v>
+        <v>121471688</v>
       </c>
       <c r="B123" t="n">
         <v>96732</v>
@@ -13608,10 +13607,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>428411</v>
+        <v>428159</v>
       </c>
       <c r="R123" t="n">
-        <v>6233213</v>
+        <v>6233394</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13638,12 +13637,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13772,10 +13771,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121471943</v>
+        <v>121471899</v>
       </c>
       <c r="B125" t="n">
-        <v>96732</v>
+        <v>94400</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13788,21 +13787,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2606</v>
+        <v>2779</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13812,10 +13811,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>428034</v>
+        <v>428389</v>
       </c>
       <c r="R125" t="n">
-        <v>6233348</v>
+        <v>6233099</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13874,10 +13873,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121471909</v>
+        <v>121471839</v>
       </c>
       <c r="B126" t="n">
-        <v>76950</v>
+        <v>94595</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13886,25 +13885,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1342</v>
+        <v>2671</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13914,10 +13913,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>428373</v>
+        <v>428184</v>
       </c>
       <c r="R126" t="n">
-        <v>6233088</v>
+        <v>6233240</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13944,12 +13943,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13976,10 +13975,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121471852</v>
+        <v>121471944</v>
       </c>
       <c r="B127" t="n">
-        <v>80257</v>
+        <v>94606</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13988,25 +13987,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14016,10 +14015,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>428311</v>
+        <v>428034</v>
       </c>
       <c r="R127" t="n">
-        <v>6233183</v>
+        <v>6233348</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14046,12 +14045,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14078,10 +14077,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121471541</v>
+        <v>121471819</v>
       </c>
       <c r="B128" t="n">
-        <v>80244</v>
+        <v>94606</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14094,21 +14093,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14118,10 +14117,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>428209</v>
+        <v>428304</v>
       </c>
       <c r="R128" t="n">
-        <v>6233184</v>
+        <v>6233306</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14148,12 +14147,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14180,10 +14179,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121471533</v>
+        <v>121471835</v>
       </c>
       <c r="B129" t="n">
-        <v>80244</v>
+        <v>96732</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14196,21 +14195,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14220,10 +14219,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>428144</v>
+        <v>428145</v>
       </c>
       <c r="R129" t="n">
-        <v>6233229</v>
+        <v>6233244</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14250,12 +14249,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14282,10 +14281,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121471843</v>
+        <v>121471881</v>
       </c>
       <c r="B130" t="n">
-        <v>57372</v>
+        <v>78409</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14298,21 +14297,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>924</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14322,10 +14321,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>428252</v>
+        <v>428445</v>
       </c>
       <c r="R130" t="n">
-        <v>6233262</v>
+        <v>6233151</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14384,10 +14383,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121471816</v>
+        <v>121471934</v>
       </c>
       <c r="B131" t="n">
-        <v>96780</v>
+        <v>94400</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14400,21 +14399,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2604</v>
+        <v>2779</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14424,10 +14423,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>428317</v>
+        <v>428090</v>
       </c>
       <c r="R131" t="n">
-        <v>6233324</v>
+        <v>6233309</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14454,12 +14453,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14486,10 +14485,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121471854</v>
+        <v>121471820</v>
       </c>
       <c r="B132" t="n">
-        <v>96732</v>
+        <v>94400</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14502,21 +14501,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2606</v>
+        <v>2779</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14526,10 +14525,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>428302</v>
+        <v>428304</v>
       </c>
       <c r="R132" t="n">
-        <v>6233177</v>
+        <v>6233306</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14588,7 +14587,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121471835</v>
+        <v>121471691</v>
       </c>
       <c r="B133" t="n">
         <v>96732</v>
@@ -14628,10 +14627,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>428145</v>
+        <v>428128</v>
       </c>
       <c r="R133" t="n">
-        <v>6233244</v>
+        <v>6233385</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14658,12 +14657,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14690,10 +14689,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121471911</v>
+        <v>121471544</v>
       </c>
       <c r="B134" t="n">
-        <v>76950</v>
+        <v>94606</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14702,25 +14701,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1342</v>
+        <v>2667</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14730,10 +14729,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>428352</v>
+        <v>428219</v>
       </c>
       <c r="R134" t="n">
-        <v>6233082</v>
+        <v>6233278</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14760,12 +14759,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14792,10 +14791,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121471531</v>
+        <v>121471846</v>
       </c>
       <c r="B135" t="n">
-        <v>94616</v>
+        <v>80244</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14808,21 +14807,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1080</v>
+        <v>230185</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14832,10 +14831,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>428110</v>
+        <v>428241</v>
       </c>
       <c r="R135" t="n">
-        <v>6233224</v>
+        <v>6233222</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14862,12 +14861,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14894,10 +14893,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121471870</v>
+        <v>121471931</v>
       </c>
       <c r="B136" t="n">
-        <v>76950</v>
+        <v>80257</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14906,25 +14905,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14934,10 +14933,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>428356</v>
+        <v>428075</v>
       </c>
       <c r="R136" t="n">
-        <v>6233243</v>
+        <v>6233301</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14964,12 +14963,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14996,10 +14995,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121471690</v>
+        <v>121471849</v>
       </c>
       <c r="B137" t="n">
-        <v>80244</v>
+        <v>80257</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15008,25 +15007,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15036,10 +15035,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>428161</v>
+        <v>428299</v>
       </c>
       <c r="R137" t="n">
-        <v>6233396</v>
+        <v>6233126</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15066,12 +15065,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15098,10 +15097,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121471695</v>
+        <v>121471942</v>
       </c>
       <c r="B138" t="n">
-        <v>80244</v>
+        <v>76950</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15110,25 +15109,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15138,10 +15137,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>428053</v>
+        <v>428032</v>
       </c>
       <c r="R138" t="n">
-        <v>6233336</v>
+        <v>6233345</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15168,12 +15167,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15200,10 +15199,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121471684</v>
+        <v>121471827</v>
       </c>
       <c r="B139" t="n">
-        <v>80414</v>
+        <v>94606</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15212,25 +15211,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1557</v>
+        <v>2667</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Röd pysslinglav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Thelopsis rubella</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Nyl.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15240,10 +15239,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>428227</v>
+        <v>428185</v>
       </c>
       <c r="R139" t="n">
-        <v>6233392</v>
+        <v>6233287</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15270,12 +15269,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15302,10 +15301,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121471939</v>
+        <v>121471925</v>
       </c>
       <c r="B140" t="n">
-        <v>94606</v>
+        <v>94608</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15318,16 +15317,16 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -15342,10 +15341,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>428046</v>
+        <v>428076</v>
       </c>
       <c r="R140" t="n">
-        <v>6233296</v>
+        <v>6233382</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15506,7 +15505,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121471869</v>
+        <v>121471860</v>
       </c>
       <c r="B142" t="n">
         <v>96732</v>
@@ -15546,10 +15545,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>428354</v>
+        <v>428404</v>
       </c>
       <c r="R142" t="n">
-        <v>6233242</v>
+        <v>6233275</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15608,10 +15607,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121471839</v>
+        <v>121471538</v>
       </c>
       <c r="B143" t="n">
-        <v>94595</v>
+        <v>80244</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15624,21 +15623,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2671</v>
+        <v>230185</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15648,10 +15647,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>428184</v>
+        <v>428166</v>
       </c>
       <c r="R143" t="n">
-        <v>6233240</v>
+        <v>6233198</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15678,12 +15677,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15710,10 +15709,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121471923</v>
+        <v>121471828</v>
       </c>
       <c r="B144" t="n">
-        <v>80257</v>
+        <v>80244</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15722,25 +15721,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15750,10 +15749,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>428091</v>
+        <v>428185</v>
       </c>
       <c r="R144" t="n">
-        <v>6233386</v>
+        <v>6233289</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15780,12 +15779,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15794,6 +15793,7 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -15812,10 +15812,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121471861</v>
+        <v>121471928</v>
       </c>
       <c r="B145" t="n">
-        <v>94606</v>
+        <v>80257</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15824,25 +15824,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15852,10 +15852,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>428404</v>
+        <v>428075</v>
       </c>
       <c r="R145" t="n">
-        <v>6233275</v>
+        <v>6233294</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15882,12 +15882,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15914,10 +15914,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121471916</v>
+        <v>121471806</v>
       </c>
       <c r="B146" t="n">
-        <v>94616</v>
+        <v>80257</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15926,25 +15926,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1080</v>
+        <v>1144</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15954,10 +15954,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>428283</v>
+        <v>428325</v>
       </c>
       <c r="R146" t="n">
-        <v>6233084</v>
+        <v>6233291</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15984,12 +15984,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16016,7 +16016,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121471806</v>
+        <v>121471831</v>
       </c>
       <c r="B147" t="n">
         <v>80257</v>
@@ -16056,10 +16056,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>428325</v>
+        <v>428145</v>
       </c>
       <c r="R147" t="n">
-        <v>6233291</v>
+        <v>6233315</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16118,10 +16118,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121471857</v>
+        <v>121471822</v>
       </c>
       <c r="B148" t="n">
-        <v>80257</v>
+        <v>94606</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16130,25 +16130,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16158,10 +16158,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>428362</v>
+        <v>428288</v>
       </c>
       <c r="R148" t="n">
-        <v>6233272</v>
+        <v>6233325</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16220,10 +16220,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121471824</v>
+        <v>121471812</v>
       </c>
       <c r="B149" t="n">
-        <v>76950</v>
+        <v>94400</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16232,25 +16232,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1342</v>
+        <v>2779</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16260,10 +16260,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>428288</v>
+        <v>428331</v>
       </c>
       <c r="R149" t="n">
-        <v>6233325</v>
+        <v>6233335</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16322,10 +16322,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121471685</v>
+        <v>121471813</v>
       </c>
       <c r="B150" t="n">
-        <v>80257</v>
+        <v>94595</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16334,25 +16334,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1144</v>
+        <v>2671</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16362,10 +16362,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>428228</v>
+        <v>428332</v>
       </c>
       <c r="R150" t="n">
-        <v>6233391</v>
+        <v>6233341</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16392,12 +16392,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16424,10 +16424,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121471897</v>
+        <v>121471683</v>
       </c>
       <c r="B151" t="n">
-        <v>78409</v>
+        <v>94595</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16436,25 +16436,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>924</v>
+        <v>2671</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16464,10 +16464,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>428369</v>
+        <v>428278</v>
       </c>
       <c r="R151" t="n">
-        <v>6233104</v>
+        <v>6233417</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16494,12 +16494,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16526,10 +16526,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121471938</v>
+        <v>121471534</v>
       </c>
       <c r="B152" t="n">
-        <v>80244</v>
+        <v>96732</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16542,21 +16542,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16566,10 +16566,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>428062</v>
+        <v>428147</v>
       </c>
       <c r="R152" t="n">
-        <v>6233301</v>
+        <v>6233224</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16596,12 +16596,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16628,10 +16628,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121471530</v>
+        <v>121471933</v>
       </c>
       <c r="B153" t="n">
-        <v>80244</v>
+        <v>94595</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16644,21 +16644,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>230185</v>
+        <v>2671</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16668,10 +16668,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>428111</v>
+        <v>428090</v>
       </c>
       <c r="R153" t="n">
-        <v>6233222</v>
+        <v>6233309</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16698,12 +16698,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16730,10 +16730,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121471865</v>
+        <v>121471917</v>
       </c>
       <c r="B154" t="n">
-        <v>74701</v>
+        <v>80244</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16746,21 +16746,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>306</v>
+        <v>230185</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16770,10 +16770,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>428438</v>
+        <v>428284</v>
       </c>
       <c r="R154" t="n">
-        <v>6233202</v>
+        <v>6233109</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16800,12 +16800,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16832,10 +16832,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121471929</v>
+        <v>121471696</v>
       </c>
       <c r="B155" t="n">
-        <v>94400</v>
+        <v>96732</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16848,21 +16848,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2779</v>
+        <v>2606</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16872,10 +16872,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>428078</v>
+        <v>428054</v>
       </c>
       <c r="R155" t="n">
-        <v>6233294</v>
+        <v>6233337</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16902,12 +16902,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16934,10 +16934,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121471925</v>
+        <v>121471834</v>
       </c>
       <c r="B156" t="n">
-        <v>94608</v>
+        <v>80257</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16946,25 +16946,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>2666</v>
+        <v>1144</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16974,10 +16974,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>428076</v>
+        <v>428137</v>
       </c>
       <c r="R156" t="n">
-        <v>6233382</v>
+        <v>6233320</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17004,12 +17004,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17036,10 +17036,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121471944</v>
+        <v>121471870</v>
       </c>
       <c r="B157" t="n">
-        <v>94606</v>
+        <v>76950</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17048,25 +17048,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17076,10 +17076,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>428034</v>
+        <v>428356</v>
       </c>
       <c r="R157" t="n">
-        <v>6233348</v>
+        <v>6233243</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17106,12 +17106,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17138,10 +17138,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121471544</v>
+        <v>121471817</v>
       </c>
       <c r="B158" t="n">
-        <v>94606</v>
+        <v>74699</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17154,21 +17154,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>2667</v>
+        <v>6439</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17178,10 +17178,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>428219</v>
+        <v>428312</v>
       </c>
       <c r="R158" t="n">
-        <v>6233278</v>
+        <v>6233323</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17208,12 +17208,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17240,10 +17240,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121471902</v>
+        <v>121471904</v>
       </c>
       <c r="B159" t="n">
-        <v>94595</v>
+        <v>78409</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17252,25 +17252,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>2671</v>
+        <v>924</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17283,7 +17283,7 @@
         <v>428387</v>
       </c>
       <c r="R159" t="n">
-        <v>6233096</v>
+        <v>6233098</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17342,10 +17342,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121471796</v>
+        <v>121471910</v>
       </c>
       <c r="B160" t="n">
-        <v>80257</v>
+        <v>76950</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17354,25 +17354,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17382,10 +17382,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>428390</v>
+        <v>428377</v>
       </c>
       <c r="R160" t="n">
-        <v>6233312</v>
+        <v>6233090</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17412,12 +17412,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17444,10 +17444,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121471874</v>
+        <v>121471809</v>
       </c>
       <c r="B161" t="n">
-        <v>80257</v>
+        <v>74565</v>
       </c>
       